--- a/STS_holy_grail.xlsx
+++ b/STS_holy_grail.xlsx
@@ -1734,10 +1734,10 @@
         </is>
       </c>
       <c r="T12" t="n">
-        <v>3.82</v>
+        <v>3.83</v>
       </c>
       <c r="U12" t="n">
-        <v>3.82</v>
+        <v>3.83</v>
       </c>
       <c r="X12" t="n">
         <v>131.16</v>
@@ -1761,7 +1761,7 @@
         <v>-0.97</v>
       </c>
       <c r="AE12" t="n">
-        <v>3.82</v>
+        <v>3.83</v>
       </c>
       <c r="AF12" t="n">
         <v>2</v>
@@ -1770,10 +1770,10 @@
         <v>1</v>
       </c>
       <c r="AJ12" t="n">
-        <v>-0.19</v>
+        <v>0.06</v>
       </c>
       <c r="AL12" t="n">
-        <v>3.8</v>
+        <v>3.55</v>
       </c>
     </row>
     <row r="13">
@@ -1876,10 +1876,10 @@
         <v>1</v>
       </c>
       <c r="AJ13" t="n">
-        <v>-0.19</v>
+        <v>0.06</v>
       </c>
       <c r="AL13" t="n">
-        <v>-0.08</v>
+        <v>-0.33</v>
       </c>
     </row>
     <row r="14">
@@ -1982,10 +1982,10 @@
         <v>1</v>
       </c>
       <c r="AJ14" t="n">
-        <v>-0.19</v>
+        <v>0.06</v>
       </c>
       <c r="AL14" t="n">
-        <v>-0.64</v>
+        <v>-0.88</v>
       </c>
     </row>
     <row r="15">
@@ -2088,10 +2088,10 @@
         <v>0</v>
       </c>
       <c r="AJ15" t="n">
-        <v>-0.19</v>
+        <v>0.06</v>
       </c>
       <c r="AL15" t="n">
-        <v>-4.24</v>
+        <v>-4.49</v>
       </c>
     </row>
     <row r="16">
@@ -2199,10 +2199,10 @@
         <v>0</v>
       </c>
       <c r="AJ16" t="n">
-        <v>-0.19</v>
+        <v>0.06</v>
       </c>
       <c r="AL16" t="n">
-        <v>-0.38</v>
+        <v>-0.63</v>
       </c>
     </row>
     <row r="17">
@@ -2308,10 +2308,10 @@
         <v>2</v>
       </c>
       <c r="AJ17" t="n">
-        <v>0.29</v>
+        <v>0.54</v>
       </c>
       <c r="AL17" t="n">
-        <v>4.44</v>
+        <v>4.19</v>
       </c>
     </row>
     <row r="18">
@@ -2414,10 +2414,10 @@
         <v>0</v>
       </c>
       <c r="AJ18" t="n">
-        <v>0.29</v>
+        <v>0.54</v>
       </c>
       <c r="AL18" t="n">
-        <v>-4.19</v>
+        <v>-4.44</v>
       </c>
     </row>
     <row r="19">
@@ -2520,10 +2520,10 @@
         <v>1</v>
       </c>
       <c r="AJ19" t="n">
-        <v>0.29</v>
+        <v>0.54</v>
       </c>
       <c r="AL19" t="n">
-        <v>1.67</v>
+        <v>1.42</v>
       </c>
     </row>
     <row r="20">
@@ -2626,10 +2626,10 @@
         <v>2</v>
       </c>
       <c r="AJ20" t="n">
-        <v>0.29</v>
+        <v>0.54</v>
       </c>
       <c r="AL20" t="n">
-        <v>-1.31</v>
+        <v>-1.56</v>
       </c>
     </row>
     <row r="21">
@@ -2740,10 +2740,10 @@
         <v>3</v>
       </c>
       <c r="AJ21" t="n">
-        <v>0.21</v>
+        <v>0.46</v>
       </c>
       <c r="AL21" t="n">
-        <v>5.58</v>
+        <v>5.33</v>
       </c>
     </row>
     <row r="22">
@@ -2810,10 +2810,10 @@
         </is>
       </c>
       <c r="T22" t="n">
-        <v>3.46</v>
+        <v>3.47</v>
       </c>
       <c r="U22" t="n">
-        <v>3.46</v>
+        <v>3.47</v>
       </c>
       <c r="X22" t="n">
         <v>278.61</v>
@@ -2837,7 +2837,7 @@
         <v>-4.75</v>
       </c>
       <c r="AE22" t="n">
-        <v>3.46</v>
+        <v>3.47</v>
       </c>
       <c r="AF22" t="n">
         <v>4</v>
@@ -2846,10 +2846,10 @@
         <v>3</v>
       </c>
       <c r="AJ22" t="n">
-        <v>0.21</v>
+        <v>0.46</v>
       </c>
       <c r="AL22" t="n">
-        <v>3.2</v>
+        <v>2.95</v>
       </c>
     </row>
     <row r="23">
@@ -2958,10 +2958,10 @@
         <v>2</v>
       </c>
       <c r="AJ23" t="n">
-        <v>0.21</v>
+        <v>0.46</v>
       </c>
       <c r="AL23" t="n">
-        <v>7.09</v>
+        <v>6.84</v>
       </c>
     </row>
     <row r="24">
@@ -3003,7 +3003,7 @@
         <v>32.2</v>
       </c>
       <c r="L24" t="n">
-        <v>-7.45</v>
+        <v>-7.49</v>
       </c>
       <c r="M24" t="n">
         <v>-10.3</v>
@@ -3052,7 +3052,7 @@
         <v>-6.84</v>
       </c>
       <c r="AD24" t="n">
-        <v>-7.45</v>
+        <v>-7.49</v>
       </c>
       <c r="AE24" t="n">
         <v>3.38</v>
@@ -3064,10 +3064,10 @@
         <v>0</v>
       </c>
       <c r="AJ24" t="n">
-        <v>0.21</v>
+        <v>0.46</v>
       </c>
       <c r="AL24" t="n">
-        <v>-7.05</v>
+        <v>-7.3</v>
       </c>
     </row>
     <row r="25">
@@ -3175,10 +3175,10 @@
         <v>0</v>
       </c>
       <c r="AJ25" t="n">
-        <v>0.21</v>
+        <v>0.46</v>
       </c>
       <c r="AL25" t="n">
-        <v>-5.06</v>
+        <v>-5.31</v>
       </c>
     </row>
     <row r="26">
@@ -3284,10 +3284,10 @@
         <v>0</v>
       </c>
       <c r="AJ26" t="n">
-        <v>0.35</v>
+        <v>0.6</v>
       </c>
       <c r="AL26" t="n">
-        <v>-5.99</v>
+        <v>-6.24</v>
       </c>
     </row>
     <row r="27">
@@ -3329,7 +3329,7 @@
         <v>13.5</v>
       </c>
       <c r="L27" t="n">
-        <v>-3.99</v>
+        <v>-4</v>
       </c>
       <c r="M27" t="n">
         <v>6.2</v>
@@ -3378,7 +3378,7 @@
         <v>-3.71</v>
       </c>
       <c r="AD27" t="n">
-        <v>-3.99</v>
+        <v>-4</v>
       </c>
       <c r="AE27" t="n">
         <v>1.86</v>
@@ -3390,10 +3390,10 @@
         <v>0</v>
       </c>
       <c r="AJ27" t="n">
-        <v>0.35</v>
+        <v>0.6</v>
       </c>
       <c r="AL27" t="n">
-        <v>-4.06</v>
+        <v>-4.31</v>
       </c>
     </row>
     <row r="28">
@@ -3496,10 +3496,10 @@
         <v>0</v>
       </c>
       <c r="AJ28" t="n">
-        <v>0.35</v>
+        <v>0.6</v>
       </c>
       <c r="AL28" t="n">
-        <v>-3.62</v>
+        <v>-3.87</v>
       </c>
     </row>
     <row r="29">
@@ -3607,10 +3607,10 @@
         <v>0</v>
       </c>
       <c r="AJ29" t="n">
-        <v>-0.4</v>
+        <v>-0.15</v>
       </c>
       <c r="AL29" t="n">
-        <v>-6.6</v>
+        <v>-6.85</v>
       </c>
     </row>
     <row r="30">
@@ -3713,10 +3713,10 @@
         <v>0</v>
       </c>
       <c r="AJ30" t="n">
-        <v>-0.4</v>
+        <v>-0.15</v>
       </c>
       <c r="AL30" t="n">
-        <v>-20.22</v>
+        <v>-20.47</v>
       </c>
       <c r="AM30" t="inlineStr">
         <is>
@@ -3824,10 +3824,10 @@
         <v>1</v>
       </c>
       <c r="AJ31" t="n">
-        <v>0.48</v>
+        <v>0.73</v>
       </c>
       <c r="AL31" t="n">
-        <v>-6.54</v>
+        <v>-6.79</v>
       </c>
     </row>
     <row r="32">
@@ -3936,10 +3936,10 @@
         <v>3</v>
       </c>
       <c r="AJ32" t="n">
-        <v>0.48</v>
+        <v>0.73</v>
       </c>
       <c r="AL32" t="n">
-        <v>6.02</v>
+        <v>5.77</v>
       </c>
     </row>
     <row r="33">
@@ -4042,10 +4042,10 @@
         <v>0</v>
       </c>
       <c r="AJ33" t="n">
-        <v>-0.31</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="AL33" t="n">
-        <v>-6.12</v>
+        <v>-6.37</v>
       </c>
     </row>
     <row r="34">
@@ -4148,10 +4148,10 @@
         <v>2</v>
       </c>
       <c r="AJ34" t="n">
-        <v>-0.31</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="AL34" t="n">
-        <v>0.61</v>
+        <v>0.37</v>
       </c>
     </row>
     <row r="35">
@@ -4254,10 +4254,10 @@
         <v>3</v>
       </c>
       <c r="AJ35" t="n">
-        <v>-0.31</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="AL35" t="n">
-        <v>3.05</v>
+        <v>2.8</v>
       </c>
     </row>
     <row r="36">
@@ -4360,10 +4360,10 @@
         <v>0</v>
       </c>
       <c r="AJ36" t="n">
-        <v>-0.31</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="AL36" t="n">
-        <v>-6.26</v>
+        <v>-6.51</v>
       </c>
     </row>
     <row r="37">
@@ -4477,10 +4477,10 @@
         <v>8</v>
       </c>
       <c r="AJ37" t="n">
-        <v>-0.96</v>
+        <v>-0.71</v>
       </c>
       <c r="AL37" t="n">
-        <v>20.1</v>
+        <v>19.85</v>
       </c>
     </row>
     <row r="38">
@@ -4522,7 +4522,7 @@
         <v>-40.3</v>
       </c>
       <c r="L38" t="n">
-        <v>-11.77</v>
+        <v>-11.81</v>
       </c>
       <c r="M38" t="n">
         <v>-32.6</v>
@@ -4571,7 +4571,7 @@
         <v>-11.74</v>
       </c>
       <c r="AD38" t="n">
-        <v>-11.77</v>
+        <v>-11.81</v>
       </c>
       <c r="AE38" t="n">
         <v>0.42</v>
@@ -4583,10 +4583,10 @@
         <v>0</v>
       </c>
       <c r="AJ38" t="n">
-        <v>-0.96</v>
+        <v>-0.71</v>
       </c>
       <c r="AL38" t="n">
-        <v>-10.78</v>
+        <v>-11.03</v>
       </c>
     </row>
     <row r="39">
@@ -4697,10 +4697,10 @@
         <v>1</v>
       </c>
       <c r="AJ39" t="n">
-        <v>-1.34</v>
+        <v>-1.09</v>
       </c>
       <c r="AL39" t="n">
-        <v>-6.09</v>
+        <v>-6.34</v>
       </c>
     </row>
     <row r="40">
@@ -4814,10 +4814,10 @@
         <v>1</v>
       </c>
       <c r="AJ40" t="n">
-        <v>-1.34</v>
+        <v>-1.09</v>
       </c>
       <c r="AL40" t="n">
-        <v>7.2</v>
+        <v>6.95</v>
       </c>
       <c r="AM40" t="inlineStr">
         <is>
@@ -4925,10 +4925,10 @@
         <v>0</v>
       </c>
       <c r="AJ41" t="n">
-        <v>-1.34</v>
+        <v>-1.09</v>
       </c>
       <c r="AL41" t="n">
-        <v>-6.29</v>
+        <v>-6.54</v>
       </c>
     </row>
     <row r="42">
@@ -5039,10 +5039,10 @@
         <v>0</v>
       </c>
       <c r="AJ42" t="n">
-        <v>-0.8100000000000001</v>
+        <v>-0.5600000000000001</v>
       </c>
       <c r="AL42" t="n">
-        <v>-23.33</v>
+        <v>-23.57</v>
       </c>
       <c r="AM42" t="inlineStr">
         <is>
@@ -5156,10 +5156,10 @@
         <v>9</v>
       </c>
       <c r="AJ43" t="n">
-        <v>-0.8100000000000001</v>
+        <v>-0.5600000000000001</v>
       </c>
       <c r="AL43" t="n">
-        <v>2.08</v>
+        <v>1.83</v>
       </c>
     </row>
     <row r="44">
@@ -5268,10 +5268,10 @@
         <v>4</v>
       </c>
       <c r="AJ44" t="n">
-        <v>-0.1</v>
+        <v>0.15</v>
       </c>
       <c r="AL44" t="n">
-        <v>0.34</v>
+        <v>0.09</v>
       </c>
     </row>
     <row r="45">
@@ -5380,10 +5380,10 @@
         <v>1</v>
       </c>
       <c r="AJ45" t="n">
-        <v>-0.1</v>
+        <v>0.15</v>
       </c>
       <c r="AL45" t="n">
-        <v>0.04</v>
+        <v>-0.21</v>
       </c>
     </row>
     <row r="46">
@@ -5495,10 +5495,10 @@
         <v>12</v>
       </c>
       <c r="AJ46" t="n">
-        <v>-0.04</v>
+        <v>0.21</v>
       </c>
       <c r="AL46" t="n">
-        <v>8.029999999999999</v>
+        <v>7.78</v>
       </c>
     </row>
     <row r="47">
@@ -5604,10 +5604,10 @@
         <v>0</v>
       </c>
       <c r="AJ47" t="n">
-        <v>-0.74</v>
+        <v>-0.49</v>
       </c>
       <c r="AL47" t="n">
-        <v>-10.53</v>
+        <v>-10.78</v>
       </c>
       <c r="AM47" t="inlineStr">
         <is>
@@ -5718,10 +5718,10 @@
         <v>4</v>
       </c>
       <c r="AJ48" t="n">
-        <v>-0.74</v>
+        <v>-0.49</v>
       </c>
       <c r="AL48" t="n">
-        <v>-7.42</v>
+        <v>-7.66</v>
       </c>
     </row>
     <row r="49">
@@ -5833,10 +5833,10 @@
         <v>5</v>
       </c>
       <c r="AJ49" t="n">
-        <v>-0.74</v>
+        <v>-0.49</v>
       </c>
       <c r="AL49" t="n">
-        <v>-2.67</v>
+        <v>-2.91</v>
       </c>
     </row>
     <row r="50">
@@ -5953,10 +5953,10 @@
         <v>14</v>
       </c>
       <c r="AJ50" t="n">
-        <v>-1.3</v>
+        <v>-1.06</v>
       </c>
       <c r="AL50" t="n">
-        <v>16.17</v>
+        <v>15.93</v>
       </c>
     </row>
     <row r="51">
@@ -6073,10 +6073,10 @@
         <v>10</v>
       </c>
       <c r="AJ51" t="n">
-        <v>-1.3</v>
+        <v>-1.06</v>
       </c>
       <c r="AL51" t="n">
-        <v>3.25</v>
+        <v>3.01</v>
       </c>
     </row>
     <row r="52">
@@ -6182,10 +6182,10 @@
         <v>0</v>
       </c>
       <c r="AJ52" t="n">
-        <v>-1.3</v>
+        <v>-1.06</v>
       </c>
       <c r="AL52" t="n">
-        <v>-2.98</v>
+        <v>-3.22</v>
       </c>
     </row>
     <row r="53">
@@ -6291,10 +6291,10 @@
         <v>0</v>
       </c>
       <c r="AJ53" t="n">
-        <v>-1.3</v>
+        <v>-1.06</v>
       </c>
       <c r="AL53" t="n">
-        <v>-8.720000000000001</v>
+        <v>-8.970000000000001</v>
       </c>
       <c r="AM53" t="inlineStr">
         <is>
@@ -6411,10 +6411,10 @@
         <v>10</v>
       </c>
       <c r="AJ54" t="n">
-        <v>-0.89</v>
+        <v>-0.64</v>
       </c>
       <c r="AL54" t="n">
-        <v>25.56</v>
+        <v>25.31</v>
       </c>
     </row>
     <row r="55">
@@ -6526,10 +6526,10 @@
         <v>16</v>
       </c>
       <c r="AJ55" t="n">
-        <v>-0.4</v>
+        <v>-0.15</v>
       </c>
       <c r="AL55" t="n">
-        <v>16.9</v>
+        <v>16.66</v>
       </c>
       <c r="AM55" t="inlineStr">
         <is>
@@ -6645,10 +6645,10 @@
         <v>0</v>
       </c>
       <c r="AJ56" t="n">
-        <v>-0.4</v>
+        <v>-0.15</v>
       </c>
       <c r="AL56" t="n">
-        <v>-9.76</v>
+        <v>-10</v>
       </c>
       <c r="AM56" t="inlineStr">
         <is>
@@ -6765,10 +6765,10 @@
         <v>10</v>
       </c>
       <c r="AJ57" t="n">
-        <v>-0.58</v>
+        <v>-0.34</v>
       </c>
       <c r="AL57" t="n">
-        <v>23.82</v>
+        <v>23.58</v>
       </c>
     </row>
     <row r="58">
@@ -6885,10 +6885,10 @@
         <v>16</v>
       </c>
       <c r="AJ58" t="n">
-        <v>-0.58</v>
+        <v>-0.34</v>
       </c>
       <c r="AL58" t="n">
-        <v>11.01</v>
+        <v>10.76</v>
       </c>
     </row>
     <row r="59">
@@ -6994,10 +6994,10 @@
         <v>10</v>
       </c>
       <c r="AJ59" t="n">
-        <v>-0.58</v>
+        <v>-0.34</v>
       </c>
       <c r="AL59" t="n">
-        <v>-4.09</v>
+        <v>-4.33</v>
       </c>
     </row>
     <row r="60">
@@ -7103,10 +7103,10 @@
         <v>0</v>
       </c>
       <c r="AJ60" t="n">
-        <v>-0.58</v>
+        <v>-0.34</v>
       </c>
       <c r="AL60" t="n">
-        <v>-9.029999999999999</v>
+        <v>-9.279999999999999</v>
       </c>
       <c r="AM60" t="inlineStr">
         <is>
@@ -7222,10 +7222,10 @@
         <v>18</v>
       </c>
       <c r="AJ61" t="n">
-        <v>-0.4</v>
+        <v>-0.16</v>
       </c>
       <c r="AL61" t="n">
-        <v>3.32</v>
+        <v>3.07</v>
       </c>
       <c r="AM61" t="inlineStr">
         <is>
@@ -7339,10 +7339,10 @@
         <v>10</v>
       </c>
       <c r="AJ62" t="n">
-        <v>-0.4</v>
+        <v>-0.16</v>
       </c>
       <c r="AL62" t="n">
-        <v>-1.28</v>
+        <v>-1.53</v>
       </c>
     </row>
     <row r="63">
@@ -7453,10 +7453,10 @@
         <v>4</v>
       </c>
       <c r="AJ63" t="n">
-        <v>-0.4</v>
+        <v>-0.16</v>
       </c>
       <c r="AL63" t="n">
-        <v>-9.050000000000001</v>
+        <v>-9.289999999999999</v>
       </c>
     </row>
     <row r="64">
@@ -7562,10 +7562,10 @@
         <v>0</v>
       </c>
       <c r="AJ64" t="n">
-        <v>-0.4</v>
+        <v>-0.16</v>
       </c>
       <c r="AL64" t="n">
-        <v>-5.43</v>
+        <v>-5.67</v>
       </c>
     </row>
     <row r="65">
@@ -7679,10 +7679,10 @@
         <v>15</v>
       </c>
       <c r="AJ65" t="n">
-        <v>-0.4</v>
+        <v>-0.16</v>
       </c>
       <c r="AL65" t="n">
-        <v>-1.41</v>
+        <v>-1.66</v>
       </c>
     </row>
     <row r="66">
@@ -7788,10 +7788,10 @@
         <v>0</v>
       </c>
       <c r="AJ66" t="n">
-        <v>-0.4</v>
+        <v>-0.16</v>
       </c>
       <c r="AL66" t="n">
-        <v>-11.37</v>
+        <v>-11.61</v>
       </c>
     </row>
     <row r="67">
@@ -7903,10 +7903,10 @@
         <v>17</v>
       </c>
       <c r="AJ67" t="n">
-        <v>-0.4</v>
+        <v>-0.16</v>
       </c>
       <c r="AL67" t="n">
-        <v>7.29</v>
+        <v>7.04</v>
       </c>
     </row>
     <row r="68">
@@ -8015,10 +8015,10 @@
         <v>6</v>
       </c>
       <c r="AJ68" t="n">
-        <v>-0.4</v>
+        <v>-0.16</v>
       </c>
       <c r="AL68" t="n">
-        <v>-9.08</v>
+        <v>-9.33</v>
       </c>
     </row>
     <row r="69">
@@ -8063,7 +8063,7 @@
         <v>-12.32</v>
       </c>
       <c r="L69" t="n">
-        <v>-25.32</v>
+        <v>-25.33</v>
       </c>
       <c r="M69" t="n">
         <v>9</v>
@@ -8115,7 +8115,7 @@
         <v>-24.47</v>
       </c>
       <c r="AD69" t="n">
-        <v>-25.32</v>
+        <v>-25.33</v>
       </c>
       <c r="AE69" t="n">
         <v>6.36</v>
@@ -8127,10 +8127,10 @@
         <v>0</v>
       </c>
       <c r="AJ69" t="n">
-        <v>-0.4</v>
+        <v>-0.16</v>
       </c>
       <c r="AL69" t="n">
-        <v>-24.06</v>
+        <v>-24.31</v>
       </c>
       <c r="AM69" t="inlineStr">
         <is>
@@ -8164,7 +8164,7 @@
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>G</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -8208,7 +8208,7 @@
         <v>6.58</v>
       </c>
       <c r="U70" t="n">
-        <v>13.84</v>
+        <v>13.85</v>
       </c>
       <c r="V70" t="n">
         <v>-5.81</v>
@@ -8238,7 +8238,7 @@
         <v>-14.62</v>
       </c>
       <c r="AE70" t="n">
-        <v>13.84</v>
+        <v>13.85</v>
       </c>
       <c r="AF70" t="n">
         <v>20</v>
@@ -8247,10 +8247,10 @@
         <v>19</v>
       </c>
       <c r="AJ70" t="n">
-        <v>-0.57</v>
+        <v>-0.32</v>
       </c>
       <c r="AL70" t="n">
-        <v>13.73</v>
+        <v>13.48</v>
       </c>
       <c r="AM70" t="inlineStr">
         <is>
@@ -8284,7 +8284,7 @@
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>G</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -8367,10 +8367,10 @@
         <v>18</v>
       </c>
       <c r="AJ71" t="n">
-        <v>-0.57</v>
+        <v>-0.32</v>
       </c>
       <c r="AL71" t="n">
-        <v>5.48</v>
+        <v>5.24</v>
       </c>
     </row>
     <row r="72">
@@ -8399,7 +8399,7 @@
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>G</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -8479,10 +8479,10 @@
         <v>6</v>
       </c>
       <c r="AJ72" t="n">
-        <v>-0.57</v>
+        <v>-0.32</v>
       </c>
       <c r="AL72" t="n">
-        <v>-14.31</v>
+        <v>-14.56</v>
       </c>
       <c r="AM72" t="inlineStr">
         <is>
@@ -8602,10 +8602,10 @@
         <v>13</v>
       </c>
       <c r="AJ73" t="n">
-        <v>-0.5600000000000001</v>
+        <v>-0.31</v>
       </c>
       <c r="AL73" t="n">
-        <v>-0.66</v>
+        <v>-0.9</v>
       </c>
     </row>
     <row r="74">
@@ -8720,10 +8720,10 @@
         <v>20</v>
       </c>
       <c r="AJ74" t="n">
-        <v>-0.5600000000000001</v>
+        <v>-0.31</v>
       </c>
       <c r="AL74" t="n">
-        <v>5.52</v>
+        <v>5.27</v>
       </c>
     </row>
     <row r="75">
@@ -8832,10 +8832,10 @@
         <v>5</v>
       </c>
       <c r="AJ75" t="n">
-        <v>-0.5600000000000001</v>
+        <v>-0.31</v>
       </c>
       <c r="AL75" t="n">
-        <v>-12.32</v>
+        <v>-12.57</v>
       </c>
       <c r="AM75" t="inlineStr">
         <is>
@@ -8949,10 +8949,10 @@
         <v>1</v>
       </c>
       <c r="AJ76" t="n">
-        <v>-0.5600000000000001</v>
+        <v>-0.31</v>
       </c>
       <c r="AL76" t="n">
-        <v>-20.13</v>
+        <v>-20.38</v>
       </c>
       <c r="AM76" t="inlineStr">
         <is>
@@ -9005,7 +9005,7 @@
         <v>-17.17</v>
       </c>
       <c r="L77" t="n">
-        <v>-17.36</v>
+        <v>-17.38</v>
       </c>
       <c r="M77" t="n">
         <v>-9.5</v>
@@ -9054,7 +9054,7 @@
         <v>-17.17</v>
       </c>
       <c r="AD77" t="n">
-        <v>-17.36</v>
+        <v>-17.38</v>
       </c>
       <c r="AE77" t="n">
         <v>1.98</v>
@@ -9066,10 +9066,10 @@
         <v>0</v>
       </c>
       <c r="AJ77" t="n">
-        <v>-0.5600000000000001</v>
+        <v>-0.31</v>
       </c>
       <c r="AL77" t="n">
-        <v>-16.62</v>
+        <v>-16.86</v>
       </c>
       <c r="AM77" t="inlineStr">
         <is>
@@ -9186,10 +9186,10 @@
         <v>3</v>
       </c>
       <c r="AJ78" t="n">
-        <v>-0.5600000000000001</v>
+        <v>-0.31</v>
       </c>
       <c r="AL78" t="n">
-        <v>-10.57</v>
+        <v>-10.82</v>
       </c>
       <c r="AM78" t="inlineStr">
         <is>
@@ -9303,10 +9303,10 @@
         <v>13</v>
       </c>
       <c r="AJ79" t="n">
-        <v>-0.5600000000000001</v>
+        <v>-0.31</v>
       </c>
       <c r="AL79" t="n">
-        <v>-6.28</v>
+        <v>-6.53</v>
       </c>
     </row>
     <row r="80">
@@ -9415,10 +9415,10 @@
         <v>3</v>
       </c>
       <c r="AJ80" t="n">
-        <v>-0.5600000000000001</v>
+        <v>-0.31</v>
       </c>
       <c r="AL80" t="n">
-        <v>-19.7</v>
+        <v>-19.95</v>
       </c>
       <c r="AM80" t="inlineStr">
         <is>
@@ -9532,10 +9532,10 @@
         <v>2</v>
       </c>
       <c r="AJ81" t="n">
-        <v>-0.5600000000000001</v>
+        <v>-0.31</v>
       </c>
       <c r="AL81" t="n">
-        <v>-7.47</v>
+        <v>-7.72</v>
       </c>
     </row>
     <row r="82">
@@ -9644,10 +9644,10 @@
         <v>1</v>
       </c>
       <c r="AJ82" t="n">
-        <v>-0.5600000000000001</v>
+        <v>-0.31</v>
       </c>
       <c r="AL82" t="n">
-        <v>-8.59</v>
+        <v>-8.84</v>
       </c>
     </row>
     <row r="83">
@@ -9762,10 +9762,10 @@
         <v>20</v>
       </c>
       <c r="AJ83" t="n">
-        <v>-0.5600000000000001</v>
+        <v>-0.31</v>
       </c>
       <c r="AL83" t="n">
-        <v>12.84</v>
+        <v>12.59</v>
       </c>
     </row>
     <row r="84">
@@ -9877,10 +9877,10 @@
         <v>6</v>
       </c>
       <c r="AJ84" t="n">
-        <v>-0.5600000000000001</v>
+        <v>-0.31</v>
       </c>
       <c r="AL84" t="n">
-        <v>-3.73</v>
+        <v>-3.98</v>
       </c>
     </row>
     <row r="85">
@@ -9994,10 +9994,10 @@
         <v>10</v>
       </c>
       <c r="AJ85" t="n">
-        <v>-0.5600000000000001</v>
+        <v>-0.31</v>
       </c>
       <c r="AL85" t="n">
-        <v>-9.859999999999999</v>
+        <v>-10.11</v>
       </c>
     </row>
     <row r="86">
@@ -10109,10 +10109,10 @@
         <v>11</v>
       </c>
       <c r="AJ86" t="n">
-        <v>-1.13</v>
+        <v>-0.88</v>
       </c>
       <c r="AL86" t="n">
-        <v>-9.42</v>
+        <v>-9.67</v>
       </c>
       <c r="AM86" t="inlineStr">
         <is>
@@ -10223,7 +10223,7 @@
         <v>-1.82</v>
       </c>
       <c r="AE87" t="n">
-        <v>30.46</v>
+        <v>30.91</v>
       </c>
       <c r="AF87" t="n">
         <v>24</v>
@@ -10232,10 +10232,10 @@
         <v>23</v>
       </c>
       <c r="AJ87" t="n">
-        <v>-1.87</v>
+        <v>-1.62</v>
       </c>
       <c r="AL87" t="n">
-        <v>27.32</v>
+        <v>27.07</v>
       </c>
     </row>
     <row r="88">
@@ -10350,10 +10350,10 @@
         <v>14</v>
       </c>
       <c r="AJ88" t="n">
-        <v>-2.16</v>
+        <v>-1.92</v>
       </c>
       <c r="AL88" t="n">
-        <v>1.12</v>
+        <v>0.88</v>
       </c>
     </row>
     <row r="89">
@@ -10470,10 +10470,10 @@
         <v>1</v>
       </c>
       <c r="AJ89" t="n">
-        <v>-2.16</v>
+        <v>-1.92</v>
       </c>
       <c r="AL89" t="n">
-        <v>-25.22</v>
+        <v>-25.47</v>
       </c>
       <c r="AM89" t="inlineStr">
         <is>
@@ -10592,10 +10592,10 @@
         <v>0</v>
       </c>
       <c r="AJ90" t="n">
-        <v>-2.16</v>
+        <v>-1.92</v>
       </c>
       <c r="AL90" t="n">
-        <v>-31.79</v>
+        <v>-32.03</v>
       </c>
       <c r="AM90" t="inlineStr">
         <is>
@@ -10712,10 +10712,10 @@
         <v>24</v>
       </c>
       <c r="AJ91" t="n">
-        <v>-2.16</v>
+        <v>-1.92</v>
       </c>
       <c r="AL91" t="n">
-        <v>6.01</v>
+        <v>5.77</v>
       </c>
       <c r="AM91" t="inlineStr">
         <is>
@@ -10822,7 +10822,7 @@
         <v>-15.34</v>
       </c>
       <c r="AD92" t="n">
-        <v>-15.43</v>
+        <v>-15.45</v>
       </c>
       <c r="AE92" t="n">
         <v>3.67</v>
@@ -10834,10 +10834,10 @@
         <v>1</v>
       </c>
       <c r="AJ92" t="n">
-        <v>-2.16</v>
+        <v>-1.92</v>
       </c>
       <c r="AL92" t="n">
-        <v>-13.17</v>
+        <v>-13.42</v>
       </c>
       <c r="AM92" t="inlineStr">
         <is>
@@ -10957,10 +10957,10 @@
         <v>16</v>
       </c>
       <c r="AJ93" t="n">
-        <v>-2.16</v>
+        <v>-1.92</v>
       </c>
       <c r="AL93" t="n">
-        <v>24.43</v>
+        <v>24.19</v>
       </c>
     </row>
     <row r="94">
@@ -11069,10 +11069,10 @@
         <v>0</v>
       </c>
       <c r="AJ94" t="n">
-        <v>-2.16</v>
+        <v>-1.92</v>
       </c>
       <c r="AL94" t="n">
-        <v>-17.87</v>
+        <v>-18.11</v>
       </c>
       <c r="AM94" t="inlineStr">
         <is>
@@ -11186,10 +11186,10 @@
         <v>14</v>
       </c>
       <c r="AJ95" t="n">
-        <v>-2.16</v>
+        <v>-1.92</v>
       </c>
       <c r="AL95" t="n">
-        <v>-1.87</v>
+        <v>-2.12</v>
       </c>
     </row>
     <row r="96">
@@ -11301,10 +11301,10 @@
         <v>1</v>
       </c>
       <c r="AJ96" t="n">
-        <v>-2.16</v>
+        <v>-1.92</v>
       </c>
       <c r="AL96" t="n">
-        <v>-16.71</v>
+        <v>-16.95</v>
       </c>
       <c r="AM96" t="inlineStr">
         <is>
@@ -11418,10 +11418,10 @@
         <v>1</v>
       </c>
       <c r="AJ97" t="n">
-        <v>-2.16</v>
+        <v>-1.92</v>
       </c>
       <c r="AL97" t="n">
-        <v>-12.33</v>
+        <v>-12.57</v>
       </c>
       <c r="AM97" t="inlineStr">
         <is>
@@ -11546,10 +11546,10 @@
         <v>8</v>
       </c>
       <c r="AJ98" t="n">
-        <v>-2.16</v>
+        <v>-1.92</v>
       </c>
       <c r="AL98" t="n">
-        <v>-13.89</v>
+        <v>-14.14</v>
       </c>
       <c r="AM98" t="inlineStr">
         <is>
@@ -11660,7 +11660,7 @@
         <v>-7.59</v>
       </c>
       <c r="AE99" t="n">
-        <v>27.98</v>
+        <v>28</v>
       </c>
       <c r="AF99" t="n">
         <v>25</v>
@@ -11669,10 +11669,10 @@
         <v>24</v>
       </c>
       <c r="AJ99" t="n">
-        <v>-2.16</v>
+        <v>-1.92</v>
       </c>
       <c r="AL99" t="n">
-        <v>28.36</v>
+        <v>28.12</v>
       </c>
     </row>
     <row r="100">
@@ -11787,10 +11787,10 @@
         <v>11</v>
       </c>
       <c r="AJ100" t="n">
-        <v>-2.16</v>
+        <v>-1.92</v>
       </c>
       <c r="AL100" t="n">
-        <v>8.25</v>
+        <v>8.01</v>
       </c>
     </row>
     <row r="101">
@@ -11899,10 +11899,10 @@
         <v>0</v>
       </c>
       <c r="AJ101" t="n">
-        <v>-2.16</v>
+        <v>-1.92</v>
       </c>
       <c r="AL101" t="n">
-        <v>-13.18</v>
+        <v>-13.43</v>
       </c>
       <c r="AM101" t="inlineStr">
         <is>
@@ -12022,10 +12022,10 @@
         <v>24</v>
       </c>
       <c r="AJ102" t="n">
-        <v>-2.16</v>
+        <v>-1.92</v>
       </c>
       <c r="AL102" t="n">
-        <v>22.68</v>
+        <v>22.44</v>
       </c>
     </row>
     <row r="103">
@@ -12140,10 +12140,10 @@
         <v>5</v>
       </c>
       <c r="AJ103" t="n">
-        <v>-2.16</v>
+        <v>-1.92</v>
       </c>
       <c r="AL103" t="n">
-        <v>6.92</v>
+        <v>6.68</v>
       </c>
     </row>
     <row r="104">
@@ -12258,10 +12258,10 @@
         <v>25</v>
       </c>
       <c r="AJ104" t="n">
-        <v>-1.7</v>
+        <v>-1.46</v>
       </c>
       <c r="AL104" t="n">
-        <v>25.05</v>
+        <v>24.81</v>
       </c>
     </row>
     <row r="105">
@@ -12376,10 +12376,10 @@
         <v>17</v>
       </c>
       <c r="AJ105" t="n">
-        <v>-1.66</v>
+        <v>-1.41</v>
       </c>
       <c r="AL105" t="n">
-        <v>1.48</v>
+        <v>1.24</v>
       </c>
     </row>
     <row r="106">
@@ -12494,10 +12494,10 @@
         <v>28</v>
       </c>
       <c r="AJ106" t="n">
-        <v>-1.41</v>
+        <v>-1.17</v>
       </c>
       <c r="AL106" t="n">
-        <v>10.92</v>
+        <v>10.68</v>
       </c>
     </row>
     <row r="107">
@@ -12609,10 +12609,10 @@
         <v>4</v>
       </c>
       <c r="AJ107" t="n">
-        <v>-1.41</v>
+        <v>-1.17</v>
       </c>
       <c r="AL107" t="n">
-        <v>-13.17</v>
+        <v>-13.42</v>
       </c>
       <c r="AM107" t="inlineStr">
         <is>
@@ -12720,7 +12720,7 @@
         <v>-5.62</v>
       </c>
       <c r="AD108" t="n">
-        <v>-5.67</v>
+        <v>-5.68</v>
       </c>
       <c r="AE108" t="n">
         <v>13.31</v>
@@ -12732,10 +12732,10 @@
         <v>20</v>
       </c>
       <c r="AJ108" t="n">
-        <v>-1.41</v>
+        <v>-1.17</v>
       </c>
       <c r="AL108" t="n">
-        <v>-4.21</v>
+        <v>-4.46</v>
       </c>
     </row>
     <row r="109">
@@ -12847,10 +12847,10 @@
         <v>5</v>
       </c>
       <c r="AJ109" t="n">
-        <v>-1.41</v>
+        <v>-1.17</v>
       </c>
       <c r="AL109" t="n">
-        <v>-4.76</v>
+        <v>-5</v>
       </c>
     </row>
     <row r="110">
@@ -12965,10 +12965,10 @@
         <v>9</v>
       </c>
       <c r="AJ110" t="n">
-        <v>-1.41</v>
+        <v>-1.17</v>
       </c>
       <c r="AL110" t="n">
-        <v>-6.35</v>
+        <v>-6.59</v>
       </c>
       <c r="AM110" t="inlineStr">
         <is>
@@ -13088,10 +13088,10 @@
         <v>15</v>
       </c>
       <c r="AJ111" t="n">
-        <v>-1.21</v>
+        <v>-0.96</v>
       </c>
       <c r="AL111" t="n">
-        <v>12.19</v>
+        <v>11.94</v>
       </c>
     </row>
     <row r="112">
@@ -13206,10 +13206,10 @@
         <v>21</v>
       </c>
       <c r="AJ112" t="n">
-        <v>-1.21</v>
+        <v>-0.96</v>
       </c>
       <c r="AL112" t="n">
-        <v>2.69</v>
+        <v>2.45</v>
       </c>
     </row>
     <row r="113">
@@ -13318,10 +13318,10 @@
         <v>1</v>
       </c>
       <c r="AJ113" t="n">
-        <v>-1.11</v>
+        <v>-0.86</v>
       </c>
       <c r="AL113" t="n">
-        <v>-0.59</v>
+        <v>-0.83</v>
       </c>
     </row>
     <row r="114">
@@ -13436,10 +13436,10 @@
         <v>27</v>
       </c>
       <c r="AJ114" t="n">
-        <v>-1.83</v>
+        <v>-1.58</v>
       </c>
       <c r="AL114" t="n">
-        <v>6.36</v>
+        <v>6.12</v>
       </c>
     </row>
     <row r="115">
@@ -13554,10 +13554,10 @@
         <v>7</v>
       </c>
       <c r="AJ115" t="n">
-        <v>-1.83</v>
+        <v>-1.58</v>
       </c>
       <c r="AL115" t="n">
-        <v>7.25</v>
+        <v>7.01</v>
       </c>
     </row>
     <row r="116">
@@ -13669,10 +13669,10 @@
         <v>16</v>
       </c>
       <c r="AJ116" t="n">
-        <v>1.63</v>
+        <v>1.89</v>
       </c>
       <c r="AL116" t="n">
-        <v>3.71</v>
+        <v>3.45</v>
       </c>
     </row>
     <row r="117">
@@ -13787,10 +13787,10 @@
         <v>22</v>
       </c>
       <c r="AJ117" t="n">
-        <v>1.63</v>
+        <v>1.89</v>
       </c>
       <c r="AL117" t="n">
-        <v>31.63</v>
+        <v>31.38</v>
       </c>
     </row>
     <row r="118">
@@ -13905,10 +13905,10 @@
         <v>29</v>
       </c>
       <c r="AJ118" t="n">
-        <v>1.63</v>
+        <v>1.89</v>
       </c>
       <c r="AL118" t="n">
-        <v>3.64</v>
+        <v>3.39</v>
       </c>
       <c r="AM118" t="inlineStr">
         <is>
@@ -14025,10 +14025,10 @@
         <v>2</v>
       </c>
       <c r="AJ119" t="n">
-        <v>1.63</v>
+        <v>1.89</v>
       </c>
       <c r="AL119" t="n">
-        <v>-19.45</v>
+        <v>-19.71</v>
       </c>
       <c r="AM119" t="inlineStr">
         <is>
@@ -14148,10 +14148,10 @@
         <v>8</v>
       </c>
       <c r="AJ120" t="n">
-        <v>1.63</v>
+        <v>1.89</v>
       </c>
       <c r="AL120" t="n">
-        <v>15.27</v>
+        <v>15.01</v>
       </c>
     </row>
     <row r="121">
@@ -14266,10 +14266,10 @@
         <v>9</v>
       </c>
       <c r="AJ121" t="n">
-        <v>2.28</v>
+        <v>2.54</v>
       </c>
       <c r="AL121" t="n">
-        <v>-4.41</v>
+        <v>-4.67</v>
       </c>
     </row>
     <row r="122">
@@ -14389,10 +14389,10 @@
         <v>24</v>
       </c>
       <c r="AJ122" t="n">
-        <v>2.28</v>
+        <v>2.54</v>
       </c>
       <c r="AL122" t="n">
-        <v>6.84</v>
+        <v>6.59</v>
       </c>
     </row>
     <row r="123">
@@ -14512,10 +14512,10 @@
         <v>31</v>
       </c>
       <c r="AJ123" t="n">
-        <v>2.28</v>
+        <v>2.54</v>
       </c>
       <c r="AL123" t="n">
-        <v>27.89</v>
+        <v>27.64</v>
       </c>
     </row>
     <row r="124">
@@ -14624,10 +14624,10 @@
         <v>1</v>
       </c>
       <c r="AJ124" t="n">
-        <v>2.28</v>
+        <v>2.54</v>
       </c>
       <c r="AL124" t="n">
-        <v>-16.85</v>
+        <v>-17.1</v>
       </c>
       <c r="AM124" t="inlineStr">
         <is>
@@ -14741,10 +14741,10 @@
         <v>2</v>
       </c>
       <c r="AJ125" t="n">
-        <v>3.48</v>
+        <v>3.74</v>
       </c>
       <c r="AL125" t="n">
-        <v>-25.17</v>
+        <v>-25.43</v>
       </c>
       <c r="AM125" t="inlineStr">
         <is>
@@ -14861,10 +14861,10 @@
         <v>9</v>
       </c>
       <c r="AJ126" t="n">
-        <v>3.48</v>
+        <v>3.74</v>
       </c>
       <c r="AL126" t="n">
-        <v>-6.67</v>
+        <v>-6.92</v>
       </c>
     </row>
     <row r="127">
@@ -14976,10 +14976,10 @@
         <v>25</v>
       </c>
       <c r="AJ127" t="n">
-        <v>3.48</v>
+        <v>3.74</v>
       </c>
       <c r="AL127" t="n">
-        <v>-9.75</v>
+        <v>-10.01</v>
       </c>
     </row>
     <row r="128">
@@ -15094,10 +15094,10 @@
         <v>21</v>
       </c>
       <c r="AJ128" t="n">
-        <v>3.48</v>
+        <v>3.74</v>
       </c>
       <c r="AL128" t="n">
-        <v>-3.07</v>
+        <v>-3.33</v>
       </c>
     </row>
     <row r="129">
@@ -15209,10 +15209,10 @@
         <v>4</v>
       </c>
       <c r="AJ129" t="n">
-        <v>3.48</v>
+        <v>3.74</v>
       </c>
       <c r="AL129" t="n">
-        <v>-10.01</v>
+        <v>-10.27</v>
       </c>
       <c r="AM129" t="inlineStr">
         <is>
@@ -15329,10 +15329,10 @@
         <v>7</v>
       </c>
       <c r="AJ130" t="n">
-        <v>2.94</v>
+        <v>3.19</v>
       </c>
       <c r="AL130" t="n">
-        <v>-14.36</v>
+        <v>-14.61</v>
       </c>
     </row>
     <row r="131">
@@ -15444,10 +15444,10 @@
         <v>29</v>
       </c>
       <c r="AJ131" t="n">
-        <v>2.94</v>
+        <v>3.19</v>
       </c>
       <c r="AL131" t="n">
-        <v>-3.45</v>
+        <v>-3.7</v>
       </c>
     </row>
     <row r="132">
@@ -15562,10 +15562,10 @@
         <v>1</v>
       </c>
       <c r="AJ132" t="n">
-        <v>2.94</v>
+        <v>3.19</v>
       </c>
       <c r="AL132" t="n">
-        <v>-9.460000000000001</v>
+        <v>-9.710000000000001</v>
       </c>
     </row>
     <row r="133">
@@ -15680,10 +15680,10 @@
         <v>26</v>
       </c>
       <c r="AJ133" t="n">
-        <v>2.94</v>
+        <v>3.19</v>
       </c>
       <c r="AL133" t="n">
-        <v>-3.49</v>
+        <v>-3.74</v>
       </c>
     </row>
     <row r="134">
@@ -15798,10 +15798,10 @@
         <v>22</v>
       </c>
       <c r="AJ134" t="n">
-        <v>3.04</v>
+        <v>3.3</v>
       </c>
       <c r="AL134" t="n">
-        <v>-4.98</v>
+        <v>-5.24</v>
       </c>
     </row>
     <row r="135">
@@ -15921,10 +15921,10 @@
         <v>27</v>
       </c>
       <c r="AJ135" t="n">
-        <v>3.04</v>
+        <v>3.3</v>
       </c>
       <c r="AL135" t="n">
-        <v>-3.21</v>
+        <v>-3.47</v>
       </c>
     </row>
     <row r="136">
@@ -16044,10 +16044,10 @@
         <v>23</v>
       </c>
       <c r="AJ136" t="n">
-        <v>3.04</v>
+        <v>3.3</v>
       </c>
       <c r="AL136" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.68</v>
       </c>
     </row>
     <row r="137">
@@ -16159,10 +16159,10 @@
         <v>3</v>
       </c>
       <c r="AJ137" t="n">
-        <v>3.14</v>
+        <v>3.39</v>
       </c>
       <c r="AL137" t="n">
-        <v>-14</v>
+        <v>-14.25</v>
       </c>
       <c r="AM137" t="inlineStr">
         <is>
@@ -16282,10 +16282,10 @@
         <v>24</v>
       </c>
       <c r="AJ138" t="n">
-        <v>3.02</v>
+        <v>3.27</v>
       </c>
       <c r="AL138" t="n">
-        <v>4.95</v>
+        <v>4.69</v>
       </c>
     </row>
     <row r="139">
@@ -16400,10 +16400,10 @@
         <v>12</v>
       </c>
       <c r="AJ139" t="n">
-        <v>3.02</v>
+        <v>3.27</v>
       </c>
       <c r="AL139" t="n">
-        <v>-5.24</v>
+        <v>-5.5</v>
       </c>
     </row>
     <row r="140">
@@ -16518,10 +16518,10 @@
         <v>40</v>
       </c>
       <c r="AJ140" t="n">
-        <v>2.02</v>
+        <v>2.27</v>
       </c>
       <c r="AL140" t="n">
-        <v>27.08</v>
+        <v>26.83</v>
       </c>
     </row>
     <row r="141">
@@ -16636,10 +16636,10 @@
         <v>23</v>
       </c>
       <c r="AJ141" t="n">
-        <v>2.02</v>
+        <v>2.27</v>
       </c>
       <c r="AL141" t="n">
-        <v>0.91</v>
+        <v>0.66</v>
       </c>
     </row>
     <row r="142">
@@ -16754,10 +16754,10 @@
         <v>23</v>
       </c>
       <c r="AJ142" t="n">
-        <v>2.06</v>
+        <v>2.32</v>
       </c>
       <c r="AL142" t="n">
-        <v>18.3</v>
+        <v>18.05</v>
       </c>
     </row>
     <row r="143">
@@ -16866,10 +16866,10 @@
         <v>1</v>
       </c>
       <c r="AJ143" t="n">
-        <v>2.06</v>
+        <v>2.32</v>
       </c>
       <c r="AL143" t="n">
-        <v>-15.81</v>
+        <v>-16.07</v>
       </c>
       <c r="AM143" t="inlineStr">
         <is>
@@ -16989,10 +16989,10 @@
         <v>14</v>
       </c>
       <c r="AJ144" t="n">
-        <v>1.96</v>
+        <v>2.21</v>
       </c>
       <c r="AL144" t="n">
-        <v>-0.63</v>
+        <v>-0.88</v>
       </c>
       <c r="AM144" t="inlineStr">
         <is>
@@ -17107,10 +17107,10 @@
         <v>28</v>
       </c>
       <c r="AJ145" t="n">
-        <v>1.96</v>
+        <v>2.21</v>
       </c>
       <c r="AL145" t="n">
-        <v>24.59</v>
+        <v>24.34</v>
       </c>
       <c r="AM145" t="inlineStr">
         <is>
@@ -17225,10 +17225,10 @@
         <v>9</v>
       </c>
       <c r="AJ146" t="n">
-        <v>1.96</v>
+        <v>2.21</v>
       </c>
       <c r="AL146" t="n">
-        <v>-12.11</v>
+        <v>-12.36</v>
       </c>
       <c r="AM146" t="inlineStr">
         <is>
@@ -17348,10 +17348,10 @@
         <v>20</v>
       </c>
       <c r="AJ147" t="n">
-        <v>1.96</v>
+        <v>2.21</v>
       </c>
       <c r="AL147" t="n">
-        <v>25.23</v>
+        <v>24.98</v>
       </c>
       <c r="AM147" t="inlineStr">
         <is>
@@ -17471,10 +17471,10 @@
         <v>11</v>
       </c>
       <c r="AJ148" t="n">
-        <v>1.96</v>
+        <v>2.21</v>
       </c>
       <c r="AL148" t="n">
-        <v>-3.94</v>
+        <v>-4.2</v>
       </c>
       <c r="AM148" t="inlineStr">
         <is>
@@ -17589,10 +17589,10 @@
         <v>36</v>
       </c>
       <c r="AJ149" t="n">
-        <v>1.96</v>
+        <v>2.21</v>
       </c>
       <c r="AL149" t="n">
-        <v>12.75</v>
+        <v>12.49</v>
       </c>
       <c r="AM149" t="inlineStr">
         <is>
@@ -17707,10 +17707,10 @@
         <v>18</v>
       </c>
       <c r="AJ150" t="n">
-        <v>1.96</v>
+        <v>2.21</v>
       </c>
       <c r="AL150" t="n">
-        <v>30.12</v>
+        <v>29.86</v>
       </c>
     </row>
     <row r="151">
@@ -17825,10 +17825,10 @@
         <v>20</v>
       </c>
       <c r="AJ151" t="n">
-        <v>1.96</v>
+        <v>2.21</v>
       </c>
       <c r="AL151" t="n">
-        <v>17.6</v>
+        <v>17.35</v>
       </c>
       <c r="AM151" t="inlineStr">
         <is>
@@ -17943,10 +17943,10 @@
         <v>20</v>
       </c>
       <c r="AJ152" t="n">
-        <v>1.96</v>
+        <v>2.21</v>
       </c>
       <c r="AL152" t="n">
-        <v>4.06</v>
+        <v>3.81</v>
       </c>
       <c r="AM152" t="inlineStr">
         <is>
@@ -18061,10 +18061,10 @@
         <v>20</v>
       </c>
       <c r="AJ153" t="n">
-        <v>1.96</v>
+        <v>2.21</v>
       </c>
       <c r="AL153" t="n">
-        <v>-6.68</v>
+        <v>-6.93</v>
       </c>
       <c r="AM153" t="inlineStr">
         <is>
@@ -18176,10 +18176,10 @@
         <v>3</v>
       </c>
       <c r="AJ154" t="n">
-        <v>1.96</v>
+        <v>2.21</v>
       </c>
       <c r="AL154" t="n">
-        <v>-20.39</v>
+        <v>-20.65</v>
       </c>
       <c r="AM154" t="inlineStr">
         <is>
@@ -18294,10 +18294,10 @@
         <v>42</v>
       </c>
       <c r="AJ155" t="n">
-        <v>1.96</v>
+        <v>2.21</v>
       </c>
       <c r="AL155" t="n">
-        <v>9.33</v>
+        <v>9.08</v>
       </c>
       <c r="AM155" t="inlineStr">
         <is>
@@ -18412,10 +18412,10 @@
         <v>36</v>
       </c>
       <c r="AJ156" t="n">
-        <v>1.96</v>
+        <v>2.21</v>
       </c>
       <c r="AL156" t="n">
-        <v>19.87</v>
+        <v>19.61</v>
       </c>
       <c r="AM156" t="inlineStr">
         <is>
@@ -18530,10 +18530,10 @@
         <v>43</v>
       </c>
       <c r="AJ157" t="n">
-        <v>1.96</v>
+        <v>2.21</v>
       </c>
       <c r="AL157" t="n">
-        <v>40.19</v>
+        <v>39.94</v>
       </c>
     </row>
     <row r="158">
@@ -18640,10 +18640,10 @@
         <v>3</v>
       </c>
       <c r="AJ158" t="n">
-        <v>1.96</v>
+        <v>2.21</v>
       </c>
       <c r="AL158" t="n">
-        <v>-11.84</v>
+        <v>-12.09</v>
       </c>
       <c r="AM158" t="inlineStr">
         <is>
@@ -18763,10 +18763,10 @@
         <v>3</v>
       </c>
       <c r="AJ159" t="n">
-        <v>1.96</v>
+        <v>2.21</v>
       </c>
       <c r="AL159" t="n">
-        <v>-4.69</v>
+        <v>-4.94</v>
       </c>
       <c r="AM159" t="inlineStr">
         <is>
@@ -18875,10 +18875,10 @@
         <v>1</v>
       </c>
       <c r="AJ160" t="n">
-        <v>1.96</v>
+        <v>2.21</v>
       </c>
       <c r="AL160" t="n">
-        <v>-20.47</v>
+        <v>-20.73</v>
       </c>
       <c r="AM160" t="inlineStr">
         <is>
@@ -18998,10 +18998,10 @@
         <v>33</v>
       </c>
       <c r="AJ161" t="n">
-        <v>1.96</v>
+        <v>2.21</v>
       </c>
       <c r="AL161" t="n">
-        <v>4.99</v>
+        <v>4.74</v>
       </c>
       <c r="AM161" t="inlineStr">
         <is>
@@ -19116,10 +19116,10 @@
         <v>14</v>
       </c>
       <c r="AJ162" t="n">
-        <v>1.96</v>
+        <v>2.21</v>
       </c>
       <c r="AL162" t="n">
-        <v>7.99</v>
+        <v>7.73</v>
       </c>
       <c r="AM162" t="inlineStr">
         <is>
@@ -19230,7 +19230,7 @@
         <v>-21.66</v>
       </c>
       <c r="AE163" t="n">
-        <v>20.21</v>
+        <v>20.22</v>
       </c>
       <c r="AF163" t="n">
         <v>44</v>
@@ -19239,10 +19239,10 @@
         <v>43</v>
       </c>
       <c r="AJ163" t="n">
-        <v>1.96</v>
+        <v>2.21</v>
       </c>
       <c r="AL163" t="n">
-        <v>17.54</v>
+        <v>17.28</v>
       </c>
       <c r="AM163" t="inlineStr">
         <is>
@@ -19357,10 +19357,10 @@
         <v>22</v>
       </c>
       <c r="AJ164" t="n">
-        <v>1.96</v>
+        <v>2.21</v>
       </c>
       <c r="AL164" t="n">
-        <v>148.68</v>
+        <v>148.42</v>
       </c>
       <c r="AM164" t="inlineStr">
         <is>
@@ -19475,10 +19475,10 @@
         <v>18</v>
       </c>
       <c r="AJ165" t="n">
-        <v>1.96</v>
+        <v>2.21</v>
       </c>
       <c r="AL165" t="n">
-        <v>-8.949999999999999</v>
+        <v>-9.199999999999999</v>
       </c>
       <c r="AM165" t="inlineStr">
         <is>
@@ -19598,10 +19598,10 @@
         <v>20</v>
       </c>
       <c r="AJ166" t="n">
-        <v>1.96</v>
+        <v>2.21</v>
       </c>
       <c r="AL166" t="n">
-        <v>-0.87</v>
+        <v>-1.12</v>
       </c>
       <c r="AM166" t="inlineStr">
         <is>
@@ -19716,10 +19716,10 @@
         <v>18</v>
       </c>
       <c r="AJ167" t="n">
-        <v>1.96</v>
+        <v>2.21</v>
       </c>
       <c r="AL167" t="n">
-        <v>58.58</v>
+        <v>58.32</v>
       </c>
     </row>
     <row r="168">
@@ -19829,10 +19829,10 @@
         <v>20</v>
       </c>
       <c r="AJ168" t="n">
-        <v>1.96</v>
+        <v>2.21</v>
       </c>
       <c r="AL168" t="n">
-        <v>8.9</v>
+        <v>8.640000000000001</v>
       </c>
     </row>
     <row r="169">
@@ -19939,10 +19939,10 @@
         <v>20</v>
       </c>
       <c r="AJ169" t="n">
-        <v>1.96</v>
+        <v>2.21</v>
       </c>
       <c r="AL169" t="n">
-        <v>-12.25</v>
+        <v>-12.5</v>
       </c>
       <c r="AM169" t="inlineStr">
         <is>
@@ -20054,10 +20054,10 @@
         <v>2</v>
       </c>
       <c r="AJ170" t="n">
-        <v>1.96</v>
+        <v>2.21</v>
       </c>
       <c r="AL170" t="n">
-        <v>6.32</v>
+        <v>6.07</v>
       </c>
       <c r="AM170" t="inlineStr">
         <is>
@@ -20174,10 +20174,10 @@
         <v>3</v>
       </c>
       <c r="AJ171" t="n">
-        <v>1.96</v>
+        <v>2.21</v>
       </c>
       <c r="AL171" t="n">
-        <v>-11.43</v>
+        <v>-11.68</v>
       </c>
       <c r="AM171" t="inlineStr">
         <is>
@@ -20297,10 +20297,10 @@
         <v>12</v>
       </c>
       <c r="AJ172" t="n">
-        <v>1.96</v>
+        <v>2.21</v>
       </c>
       <c r="AL172" t="n">
-        <v>-17.23</v>
+        <v>-17.48</v>
       </c>
       <c r="AM172" t="inlineStr">
         <is>
@@ -20420,10 +20420,10 @@
         <v>19</v>
       </c>
       <c r="AJ173" t="n">
-        <v>1.96</v>
+        <v>2.21</v>
       </c>
       <c r="AL173" t="n">
-        <v>-26.36</v>
+        <v>-26.61</v>
       </c>
       <c r="AM173" t="inlineStr">
         <is>
@@ -20532,10 +20532,10 @@
         <v>2</v>
       </c>
       <c r="AJ174" t="n">
-        <v>1.96</v>
+        <v>2.21</v>
       </c>
       <c r="AL174" t="n">
-        <v>-24.1</v>
+        <v>-24.35</v>
       </c>
       <c r="AM174" t="inlineStr">
         <is>
@@ -20649,10 +20649,10 @@
         <v>0</v>
       </c>
       <c r="AJ175" t="n">
-        <v>1.96</v>
+        <v>2.21</v>
       </c>
       <c r="AL175" t="n">
-        <v>-37.21</v>
+        <v>-37.46</v>
       </c>
       <c r="AM175" t="inlineStr">
         <is>
@@ -20772,10 +20772,10 @@
         <v>32</v>
       </c>
       <c r="AJ176" t="n">
-        <v>1.96</v>
+        <v>2.21</v>
       </c>
       <c r="AL176" t="n">
-        <v>-10.73</v>
+        <v>-10.98</v>
       </c>
     </row>
     <row r="177">
@@ -20872,7 +20872,7 @@
         <v>-16.43</v>
       </c>
       <c r="AD177" t="n">
-        <v>-17.51</v>
+        <v>-17.52</v>
       </c>
       <c r="AE177" t="n">
         <v>4.41</v>
@@ -20884,10 +20884,10 @@
         <v>17</v>
       </c>
       <c r="AJ177" t="n">
-        <v>1.96</v>
+        <v>2.21</v>
       </c>
       <c r="AL177" t="n">
-        <v>-18.39</v>
+        <v>-18.64</v>
       </c>
       <c r="AM177" t="inlineStr">
         <is>
@@ -21004,10 +21004,10 @@
         <v>20</v>
       </c>
       <c r="AJ178" t="n">
-        <v>1.96</v>
+        <v>2.21</v>
       </c>
       <c r="AL178" t="n">
-        <v>-1.2</v>
+        <v>-1.45</v>
       </c>
     </row>
     <row r="179">
@@ -21127,10 +21127,10 @@
         <v>35</v>
       </c>
       <c r="AJ179" t="n">
-        <v>1.96</v>
+        <v>2.21</v>
       </c>
       <c r="AL179" t="n">
-        <v>29.31</v>
+        <v>29.05</v>
       </c>
     </row>
     <row r="180">
@@ -21245,10 +21245,10 @@
         <v>3</v>
       </c>
       <c r="AJ180" t="n">
-        <v>1.96</v>
+        <v>2.21</v>
       </c>
       <c r="AL180" t="n">
-        <v>24.64</v>
+        <v>24.39</v>
       </c>
     </row>
     <row r="181">
@@ -21363,10 +21363,10 @@
         <v>3</v>
       </c>
       <c r="AJ181" t="n">
-        <v>1.96</v>
+        <v>2.21</v>
       </c>
       <c r="AL181" t="n">
-        <v>5.23</v>
+        <v>4.97</v>
       </c>
       <c r="AM181" t="inlineStr">
         <is>
@@ -21481,10 +21481,10 @@
         <v>35</v>
       </c>
       <c r="AJ182" t="n">
-        <v>1.96</v>
+        <v>2.21</v>
       </c>
       <c r="AL182" t="n">
-        <v>16.82</v>
+        <v>16.57</v>
       </c>
     </row>
     <row r="183">
@@ -21599,10 +21599,10 @@
         <v>15</v>
       </c>
       <c r="AJ183" t="n">
-        <v>1.96</v>
+        <v>2.21</v>
       </c>
       <c r="AL183" t="n">
-        <v>-7.54</v>
+        <v>-7.8</v>
       </c>
       <c r="AM183" t="inlineStr">
         <is>
@@ -21716,10 +21716,10 @@
         <v>0</v>
       </c>
       <c r="AJ184" t="n">
-        <v>1.96</v>
+        <v>2.21</v>
       </c>
       <c r="AL184" t="n">
-        <v>-30.83</v>
+        <v>-31.08</v>
       </c>
       <c r="AM184" t="inlineStr">
         <is>
@@ -21839,10 +21839,10 @@
         <v>3</v>
       </c>
       <c r="AJ185" t="n">
-        <v>1.96</v>
+        <v>2.21</v>
       </c>
       <c r="AL185" t="n">
-        <v>-4.3</v>
+        <v>-4.55</v>
       </c>
       <c r="AM185" t="inlineStr">
         <is>
@@ -21945,7 +21945,7 @@
         <v>-6.54</v>
       </c>
       <c r="AD186" t="n">
-        <v>-6.64</v>
+        <v>-6.63</v>
       </c>
       <c r="AE186" t="n">
         <v>12.16</v>
@@ -21957,10 +21957,10 @@
         <v>12</v>
       </c>
       <c r="AJ186" t="n">
-        <v>1.96</v>
+        <v>2.21</v>
       </c>
       <c r="AL186" t="n">
-        <v>-8.49</v>
+        <v>-8.75</v>
       </c>
     </row>
     <row r="187">
@@ -22070,10 +22070,10 @@
         <v>43</v>
       </c>
       <c r="AJ187" t="n">
-        <v>1.96</v>
+        <v>2.21</v>
       </c>
       <c r="AL187" t="n">
-        <v>4.17</v>
+        <v>3.92</v>
       </c>
     </row>
     <row r="188">
@@ -22188,10 +22188,10 @@
         <v>33</v>
       </c>
       <c r="AJ188" t="n">
-        <v>1.96</v>
+        <v>2.21</v>
       </c>
       <c r="AL188" t="n">
-        <v>109.05</v>
+        <v>108.8</v>
       </c>
     </row>
     <row r="189">
@@ -22306,10 +22306,10 @@
         <v>7</v>
       </c>
       <c r="AJ189" t="n">
-        <v>1.96</v>
+        <v>2.21</v>
       </c>
       <c r="AL189" t="n">
-        <v>-5.3</v>
+        <v>-5.56</v>
       </c>
     </row>
     <row r="190">
@@ -22419,10 +22419,10 @@
         <v>25</v>
       </c>
       <c r="AJ190" t="n">
-        <v>1.96</v>
+        <v>2.21</v>
       </c>
       <c r="AL190" t="n">
-        <v>32.66</v>
+        <v>32.41</v>
       </c>
     </row>
     <row r="191">
@@ -22537,10 +22537,10 @@
         <v>33</v>
       </c>
       <c r="AJ191" t="n">
-        <v>1.96</v>
+        <v>2.21</v>
       </c>
       <c r="AL191" t="n">
-        <v>-2.21</v>
+        <v>-2.47</v>
       </c>
     </row>
     <row r="192">
@@ -22655,10 +22655,10 @@
         <v>18</v>
       </c>
       <c r="AJ192" t="n">
-        <v>1.96</v>
+        <v>2.21</v>
       </c>
       <c r="AL192" t="n">
-        <v>5.43</v>
+        <v>5.17</v>
       </c>
       <c r="AM192" t="inlineStr">
         <is>
@@ -22772,10 +22772,10 @@
         <v>12</v>
       </c>
       <c r="AJ193" t="n">
-        <v>1.96</v>
+        <v>2.21</v>
       </c>
       <c r="AL193" t="n">
-        <v>-17.53</v>
+        <v>-17.78</v>
       </c>
       <c r="AM193" t="inlineStr">
         <is>
@@ -23010,10 +23010,10 @@
         <v>33</v>
       </c>
       <c r="AJ195" t="n">
-        <v>1.96</v>
+        <v>2.21</v>
       </c>
       <c r="AL195" t="n">
-        <v>-3.6</v>
+        <v>-3.85</v>
       </c>
       <c r="AM195" t="inlineStr">
         <is>
@@ -23128,10 +23128,10 @@
         <v>18</v>
       </c>
       <c r="AJ196" t="n">
-        <v>1.96</v>
+        <v>2.21</v>
       </c>
       <c r="AL196" t="n">
-        <v>-3.39</v>
+        <v>-3.65</v>
       </c>
     </row>
     <row r="197">
@@ -23366,10 +23366,10 @@
         <v>27</v>
       </c>
       <c r="AJ198" t="n">
-        <v>1.96</v>
+        <v>2.21</v>
       </c>
       <c r="AL198" t="n">
-        <v>2.23</v>
+        <v>1.98</v>
       </c>
       <c r="AM198" t="inlineStr">
         <is>
@@ -23486,10 +23486,10 @@
         <v>0</v>
       </c>
       <c r="AJ199" t="n">
-        <v>1.96</v>
+        <v>2.21</v>
       </c>
       <c r="AL199" t="n">
-        <v>-10</v>
+        <v>-10.25</v>
       </c>
       <c r="AM199" t="inlineStr">
         <is>
@@ -23601,10 +23601,10 @@
         <v>3</v>
       </c>
       <c r="AJ200" t="n">
-        <v>1.96</v>
+        <v>2.21</v>
       </c>
       <c r="AL200" t="n">
-        <v>-17.4</v>
+        <v>-17.65</v>
       </c>
       <c r="AM200" t="inlineStr">
         <is>
@@ -23716,10 +23716,10 @@
         <v>42</v>
       </c>
       <c r="AJ201" t="n">
-        <v>1.96</v>
+        <v>2.21</v>
       </c>
       <c r="AL201" t="n">
-        <v>-6.81</v>
+        <v>-7.06</v>
       </c>
       <c r="AM201" t="inlineStr">
         <is>
@@ -23834,10 +23834,10 @@
         <v>41</v>
       </c>
       <c r="AJ202" t="n">
-        <v>1.96</v>
+        <v>2.21</v>
       </c>
       <c r="AL202" t="n">
-        <v>14.6</v>
+        <v>14.35</v>
       </c>
       <c r="AM202" t="inlineStr">
         <is>
@@ -23949,10 +23949,10 @@
         <v>42</v>
       </c>
       <c r="AJ203" t="n">
-        <v>1.96</v>
+        <v>2.21</v>
       </c>
       <c r="AL203" t="n">
-        <v>3.77</v>
+        <v>3.52</v>
       </c>
     </row>
     <row r="204">
@@ -24062,10 +24062,10 @@
         <v>12</v>
       </c>
       <c r="AJ204" t="n">
-        <v>1.96</v>
+        <v>2.21</v>
       </c>
       <c r="AL204" t="n">
-        <v>-2.23</v>
+        <v>-2.48</v>
       </c>
     </row>
     <row r="205">
@@ -24175,10 +24175,10 @@
         <v>43</v>
       </c>
       <c r="AJ205" t="n">
-        <v>1.96</v>
+        <v>2.21</v>
       </c>
       <c r="AL205" t="n">
-        <v>20.84</v>
+        <v>20.58</v>
       </c>
     </row>
     <row r="206">
@@ -24288,10 +24288,10 @@
         <v>33</v>
       </c>
       <c r="AJ206" t="n">
-        <v>1.96</v>
+        <v>2.21</v>
       </c>
       <c r="AL206" t="n">
-        <v>9.77</v>
+        <v>9.52</v>
       </c>
     </row>
     <row r="207">
@@ -24406,10 +24406,10 @@
         <v>17</v>
       </c>
       <c r="AJ207" t="n">
-        <v>1.96</v>
+        <v>2.21</v>
       </c>
       <c r="AL207" t="n">
-        <v>-1.25</v>
+        <v>-1.51</v>
       </c>
     </row>
     <row r="208">
@@ -24513,10 +24513,10 @@
         <v>14</v>
       </c>
       <c r="AJ208" t="n">
-        <v>1.96</v>
+        <v>2.21</v>
       </c>
       <c r="AL208" t="n">
-        <v>-23.94</v>
+        <v>-24.2</v>
       </c>
       <c r="AM208" t="inlineStr">
         <is>
@@ -24630,10 +24630,10 @@
         <v>7</v>
       </c>
       <c r="AJ209" t="n">
-        <v>1.96</v>
+        <v>2.21</v>
       </c>
       <c r="AL209" t="n">
-        <v>-41.41</v>
+        <v>-41.66</v>
       </c>
       <c r="AM209" t="inlineStr">
         <is>
@@ -24742,10 +24742,10 @@
         <v>10</v>
       </c>
       <c r="AJ210" t="n">
-        <v>1.96</v>
+        <v>2.21</v>
       </c>
       <c r="AL210" t="n">
-        <v>-24.19</v>
+        <v>-24.45</v>
       </c>
       <c r="AM210" t="inlineStr">
         <is>
@@ -24865,10 +24865,10 @@
         <v>17</v>
       </c>
       <c r="AJ211" t="n">
-        <v>1.96</v>
+        <v>2.21</v>
       </c>
       <c r="AL211" t="n">
-        <v>-1.63</v>
+        <v>-1.88</v>
       </c>
     </row>
     <row r="212">
@@ -24988,10 +24988,10 @@
         <v>11</v>
       </c>
       <c r="AJ212" t="n">
-        <v>1.96</v>
+        <v>2.21</v>
       </c>
       <c r="AL212" t="n">
-        <v>-21.72</v>
+        <v>-21.97</v>
       </c>
       <c r="AM212" t="inlineStr">
         <is>
@@ -25106,10 +25106,10 @@
         <v>12</v>
       </c>
       <c r="AJ213" t="n">
-        <v>1.96</v>
+        <v>2.21</v>
       </c>
       <c r="AL213" t="n">
-        <v>-13.05</v>
+        <v>-13.3</v>
       </c>
       <c r="AM213" t="inlineStr">
         <is>
@@ -25224,10 +25224,10 @@
         <v>12</v>
       </c>
       <c r="AJ214" t="n">
-        <v>1.96</v>
+        <v>2.21</v>
       </c>
       <c r="AL214" t="n">
-        <v>2.48</v>
+        <v>2.23</v>
       </c>
     </row>
     <row r="215">
@@ -25337,10 +25337,10 @@
         <v>18</v>
       </c>
       <c r="AJ215" t="n">
-        <v>1.96</v>
+        <v>2.21</v>
       </c>
       <c r="AL215" t="n">
-        <v>0.54</v>
+        <v>0.29</v>
       </c>
       <c r="AM215" t="inlineStr">
         <is>
@@ -25455,10 +25455,10 @@
         <v>20</v>
       </c>
       <c r="AJ216" t="n">
-        <v>1.96</v>
+        <v>2.21</v>
       </c>
       <c r="AL216" t="n">
-        <v>-4.77</v>
+        <v>-5.02</v>
       </c>
     </row>
     <row r="217">
@@ -25566,7 +25566,7 @@
         <v>-13.68</v>
       </c>
       <c r="AD217" t="n">
-        <v>-14.65</v>
+        <v>-14.67</v>
       </c>
       <c r="AE217" t="n">
         <v>52.35</v>
@@ -25578,10 +25578,10 @@
         <v>18</v>
       </c>
       <c r="AJ217" t="n">
-        <v>1.96</v>
+        <v>2.21</v>
       </c>
       <c r="AL217" t="n">
-        <v>-15.64</v>
+        <v>-15.89</v>
       </c>
       <c r="AM217" t="inlineStr">
         <is>
@@ -25698,10 +25698,10 @@
         <v>3</v>
       </c>
       <c r="AJ218" t="n">
-        <v>1.96</v>
+        <v>2.21</v>
       </c>
       <c r="AL218" t="n">
-        <v>-38.42</v>
+        <v>-38.67</v>
       </c>
       <c r="AM218" t="inlineStr">
         <is>
@@ -25821,10 +25821,10 @@
         <v>25</v>
       </c>
       <c r="AJ219" t="n">
-        <v>1.96</v>
+        <v>2.21</v>
       </c>
       <c r="AL219" t="n">
-        <v>-8</v>
+        <v>-8.26</v>
       </c>
     </row>
     <row r="220">
@@ -25934,10 +25934,10 @@
         <v>18</v>
       </c>
       <c r="AJ220" t="n">
-        <v>1.96</v>
+        <v>2.21</v>
       </c>
       <c r="AL220" t="n">
-        <v>18.8</v>
+        <v>18.55</v>
       </c>
     </row>
     <row r="221">
@@ -26052,10 +26052,10 @@
         <v>22</v>
       </c>
       <c r="AJ221" t="n">
-        <v>1.96</v>
+        <v>2.21</v>
       </c>
       <c r="AL221" t="n">
-        <v>-12.7</v>
+        <v>-12.95</v>
       </c>
       <c r="AM221" t="inlineStr">
         <is>
@@ -26167,10 +26167,10 @@
         <v>24</v>
       </c>
       <c r="AJ222" t="n">
-        <v>1.96</v>
+        <v>2.21</v>
       </c>
       <c r="AL222" t="n">
-        <v>4.27</v>
+        <v>4.02</v>
       </c>
     </row>
     <row r="223">
@@ -26280,10 +26280,10 @@
         <v>30</v>
       </c>
       <c r="AJ223" t="n">
-        <v>1.96</v>
+        <v>2.21</v>
       </c>
       <c r="AL223" t="n">
-        <v>32.81</v>
+        <v>32.56</v>
       </c>
     </row>
     <row r="224">
@@ -26398,10 +26398,10 @@
         <v>18</v>
       </c>
       <c r="AJ224" t="n">
-        <v>1.96</v>
+        <v>2.21</v>
       </c>
       <c r="AL224" t="n">
-        <v>10.28</v>
+        <v>10.02</v>
       </c>
     </row>
     <row r="225">
@@ -26516,10 +26516,10 @@
         <v>12</v>
       </c>
       <c r="AJ225" t="n">
-        <v>1.96</v>
+        <v>2.21</v>
       </c>
       <c r="AL225" t="n">
-        <v>-13.25</v>
+        <v>-13.5</v>
       </c>
       <c r="AM225" t="inlineStr">
         <is>
@@ -26636,10 +26636,10 @@
         <v>20</v>
       </c>
       <c r="AJ226" t="n">
-        <v>1.96</v>
+        <v>2.21</v>
       </c>
       <c r="AL226" t="n">
-        <v>-14.01</v>
+        <v>-14.26</v>
       </c>
       <c r="AM226" t="inlineStr">
         <is>
@@ -26751,10 +26751,10 @@
         <v>25</v>
       </c>
       <c r="AJ227" t="n">
-        <v>1.96</v>
+        <v>2.21</v>
       </c>
       <c r="AL227" t="n">
-        <v>-9.99</v>
+        <v>-10.24</v>
       </c>
     </row>
     <row r="228">
@@ -26861,10 +26861,10 @@
         <v>38</v>
       </c>
       <c r="AJ228" t="n">
-        <v>1.96</v>
+        <v>2.21</v>
       </c>
       <c r="AL228" t="n">
-        <v>45.93</v>
+        <v>45.67</v>
       </c>
     </row>
     <row r="229">
@@ -26974,10 +26974,10 @@
         <v>43</v>
       </c>
       <c r="AJ229" t="n">
-        <v>1.96</v>
+        <v>2.21</v>
       </c>
       <c r="AL229" t="n">
-        <v>-0.17</v>
+        <v>-0.42</v>
       </c>
       <c r="AM229" t="inlineStr">
         <is>
@@ -27102,10 +27102,10 @@
         <v>33</v>
       </c>
       <c r="AJ230" t="n">
-        <v>1.96</v>
+        <v>2.21</v>
       </c>
       <c r="AL230" t="n">
-        <v>52.93</v>
+        <v>52.68</v>
       </c>
     </row>
     <row r="231">
@@ -27215,10 +27215,10 @@
         <v>35</v>
       </c>
       <c r="AJ231" t="n">
-        <v>1.96</v>
+        <v>2.21</v>
       </c>
       <c r="AL231" t="n">
-        <v>14.95</v>
+        <v>14.7</v>
       </c>
       <c r="AM231" t="inlineStr">
         <is>
@@ -27327,10 +27327,10 @@
         <v>1</v>
       </c>
       <c r="AJ232" t="n">
-        <v>1.96</v>
+        <v>2.21</v>
       </c>
       <c r="AL232" t="n">
-        <v>-15.17</v>
+        <v>-15.42</v>
       </c>
       <c r="AM232" t="inlineStr">
         <is>
@@ -27450,10 +27450,10 @@
         <v>7</v>
       </c>
       <c r="AJ233" t="n">
-        <v>1.96</v>
+        <v>2.21</v>
       </c>
       <c r="AL233" t="n">
-        <v>3.39</v>
+        <v>3.14</v>
       </c>
       <c r="AM233" t="inlineStr">
         <is>
@@ -27568,10 +27568,10 @@
         <v>36</v>
       </c>
       <c r="AJ234" t="n">
-        <v>1.96</v>
+        <v>2.21</v>
       </c>
       <c r="AL234" t="n">
-        <v>8.6</v>
+        <v>8.34</v>
       </c>
     </row>
     <row r="235">
@@ -27678,10 +27678,10 @@
         <v>20</v>
       </c>
       <c r="AJ235" t="n">
-        <v>1.96</v>
+        <v>2.21</v>
       </c>
       <c r="AL235" t="n">
-        <v>-1.56</v>
+        <v>-1.81</v>
       </c>
     </row>
     <row r="236">
@@ -27793,10 +27793,10 @@
         <v>6</v>
       </c>
       <c r="AJ236" t="n">
-        <v>1.96</v>
+        <v>2.21</v>
       </c>
       <c r="AL236" t="n">
-        <v>-15.97</v>
+        <v>-16.22</v>
       </c>
       <c r="AM236" t="inlineStr">
         <is>
@@ -27916,10 +27916,10 @@
         <v>19</v>
       </c>
       <c r="AJ237" t="n">
-        <v>1.96</v>
+        <v>2.21</v>
       </c>
       <c r="AL237" t="n">
-        <v>0.68</v>
+        <v>0.43</v>
       </c>
     </row>
     <row r="238">
@@ -28034,10 +28034,10 @@
         <v>14</v>
       </c>
       <c r="AJ238" t="n">
-        <v>1.96</v>
+        <v>2.21</v>
       </c>
       <c r="AL238" t="n">
-        <v>-9.84</v>
+        <v>-10.09</v>
       </c>
       <c r="AM238" t="inlineStr">
         <is>
@@ -28151,10 +28151,10 @@
         <v>0</v>
       </c>
       <c r="AJ239" t="n">
-        <v>1.96</v>
+        <v>2.21</v>
       </c>
       <c r="AL239" t="n">
-        <v>-23.17</v>
+        <v>-23.43</v>
       </c>
       <c r="AM239" t="inlineStr">
         <is>
@@ -28279,10 +28279,10 @@
         <v>32</v>
       </c>
       <c r="AJ240" t="n">
-        <v>1.96</v>
+        <v>2.21</v>
       </c>
       <c r="AL240" t="n">
-        <v>49.1</v>
+        <v>48.85</v>
       </c>
     </row>
     <row r="241">
@@ -28397,10 +28397,10 @@
         <v>36</v>
       </c>
       <c r="AJ241" t="n">
-        <v>1.96</v>
+        <v>2.21</v>
       </c>
       <c r="AL241" t="n">
-        <v>38.96</v>
+        <v>38.71</v>
       </c>
     </row>
     <row r="242">
@@ -28510,10 +28510,10 @@
         <v>23</v>
       </c>
       <c r="AJ242" t="n">
-        <v>1.96</v>
+        <v>2.21</v>
       </c>
       <c r="AL242" t="n">
-        <v>-8.949999999999999</v>
+        <v>-9.199999999999999</v>
       </c>
     </row>
     <row r="243">
@@ -28633,10 +28633,10 @@
         <v>26</v>
       </c>
       <c r="AJ243" t="n">
-        <v>1.96</v>
+        <v>2.21</v>
       </c>
       <c r="AL243" t="n">
-        <v>-2.83</v>
+        <v>-3.08</v>
       </c>
     </row>
     <row r="244">
@@ -28748,10 +28748,10 @@
         <v>15</v>
       </c>
       <c r="AJ244" t="n">
-        <v>1.96</v>
+        <v>2.21</v>
       </c>
       <c r="AL244" t="n">
-        <v>-15.85</v>
+        <v>-16.11</v>
       </c>
       <c r="AM244" t="inlineStr">
         <is>
@@ -28871,10 +28871,10 @@
         <v>19</v>
       </c>
       <c r="AJ245" t="n">
-        <v>1.96</v>
+        <v>2.21</v>
       </c>
       <c r="AL245" t="n">
-        <v>10.21</v>
+        <v>9.960000000000001</v>
       </c>
     </row>
     <row r="246">
@@ -28989,10 +28989,10 @@
         <v>19</v>
       </c>
       <c r="AJ246" t="n">
-        <v>1.96</v>
+        <v>2.21</v>
       </c>
       <c r="AL246" t="n">
-        <v>-26.34</v>
+        <v>-26.59</v>
       </c>
       <c r="AM246" t="inlineStr">
         <is>
@@ -29112,10 +29112,10 @@
         <v>12</v>
       </c>
       <c r="AJ247" t="n">
-        <v>1.96</v>
+        <v>2.21</v>
       </c>
       <c r="AL247" t="n">
-        <v>-22.01</v>
+        <v>-22.26</v>
       </c>
       <c r="AM247" t="inlineStr">
         <is>
@@ -29232,10 +29232,10 @@
         <v>3</v>
       </c>
       <c r="AJ248" t="n">
-        <v>1.96</v>
+        <v>2.21</v>
       </c>
       <c r="AL248" t="n">
-        <v>-2.13</v>
+        <v>-2.39</v>
       </c>
     </row>
     <row r="249">
@@ -29342,10 +29342,10 @@
         <v>23</v>
       </c>
       <c r="AJ249" t="n">
-        <v>1.96</v>
+        <v>2.21</v>
       </c>
       <c r="AL249" t="n">
-        <v>-4.27</v>
+        <v>-4.52</v>
       </c>
     </row>
     <row r="250">
@@ -29455,10 +29455,10 @@
         <v>20</v>
       </c>
       <c r="AJ250" t="n">
-        <v>1.96</v>
+        <v>2.21</v>
       </c>
       <c r="AL250" t="n">
-        <v>3.25</v>
+        <v>2.99</v>
       </c>
     </row>
     <row r="251">
@@ -29565,10 +29565,10 @@
         <v>40</v>
       </c>
       <c r="AJ251" t="n">
-        <v>1.96</v>
+        <v>2.21</v>
       </c>
       <c r="AL251" t="n">
-        <v>28.15</v>
+        <v>27.89</v>
       </c>
     </row>
     <row r="252">
@@ -29678,10 +29678,10 @@
         <v>14</v>
       </c>
       <c r="AJ252" t="n">
-        <v>1.96</v>
+        <v>2.21</v>
       </c>
       <c r="AL252" t="n">
-        <v>-10.87</v>
+        <v>-11.13</v>
       </c>
     </row>
     <row r="253">
@@ -29788,10 +29788,10 @@
         <v>11</v>
       </c>
       <c r="AJ253" t="n">
-        <v>1.96</v>
+        <v>2.21</v>
       </c>
       <c r="AL253" t="n">
-        <v>-11.06</v>
+        <v>-11.31</v>
       </c>
       <c r="AM253" t="inlineStr">
         <is>
@@ -29911,10 +29911,10 @@
         <v>43</v>
       </c>
       <c r="AJ254" t="n">
-        <v>1.96</v>
+        <v>2.21</v>
       </c>
       <c r="AL254" t="n">
-        <v>59.01</v>
+        <v>58.76</v>
       </c>
     </row>
     <row r="255">
@@ -30023,10 +30023,10 @@
         <v>1</v>
       </c>
       <c r="AJ255" t="n">
-        <v>1.96</v>
+        <v>2.21</v>
       </c>
       <c r="AL255" t="n">
-        <v>-23.17</v>
+        <v>-23.43</v>
       </c>
       <c r="AM255" t="inlineStr">
         <is>
@@ -30146,10 +30146,10 @@
         <v>6</v>
       </c>
       <c r="AJ256" t="n">
-        <v>1.96</v>
+        <v>2.21</v>
       </c>
       <c r="AL256" t="n">
-        <v>-9.539999999999999</v>
+        <v>-9.800000000000001</v>
       </c>
     </row>
     <row r="257">
@@ -30253,10 +30253,10 @@
         <v>0</v>
       </c>
       <c r="AJ257" t="n">
-        <v>1.96</v>
+        <v>2.21</v>
       </c>
       <c r="AL257" t="n">
-        <v>-20.33</v>
+        <v>-20.58</v>
       </c>
       <c r="AM257" t="inlineStr">
         <is>
@@ -30371,10 +30371,10 @@
         <v>9</v>
       </c>
       <c r="AJ258" t="n">
-        <v>1.96</v>
+        <v>2.21</v>
       </c>
       <c r="AL258" t="n">
-        <v>-10.6</v>
+        <v>-10.85</v>
       </c>
       <c r="AM258" t="inlineStr">
         <is>
@@ -30488,10 +30488,10 @@
         <v>11</v>
       </c>
       <c r="AJ259" t="n">
-        <v>1.96</v>
+        <v>2.21</v>
       </c>
       <c r="AL259" t="n">
-        <v>-13.75</v>
+        <v>-14</v>
       </c>
       <c r="AM259" t="inlineStr">
         <is>
@@ -30611,10 +30611,10 @@
         <v>29</v>
       </c>
       <c r="AJ260" t="n">
-        <v>1.96</v>
+        <v>2.21</v>
       </c>
       <c r="AL260" t="n">
-        <v>-4.6</v>
+        <v>-4.85</v>
       </c>
       <c r="AM260" t="inlineStr">
         <is>
@@ -30734,10 +30734,10 @@
         <v>42</v>
       </c>
       <c r="AJ261" t="n">
-        <v>1.96</v>
+        <v>2.21</v>
       </c>
       <c r="AL261" t="n">
-        <v>15.06</v>
+        <v>14.81</v>
       </c>
       <c r="AM261" t="inlineStr">
         <is>
@@ -30862,10 +30862,10 @@
         <v>23</v>
       </c>
       <c r="AJ262" t="n">
-        <v>1.96</v>
+        <v>2.21</v>
       </c>
       <c r="AL262" t="n">
-        <v>41.44</v>
+        <v>41.19</v>
       </c>
     </row>
     <row r="263">
@@ -30980,10 +30980,10 @@
         <v>43</v>
       </c>
       <c r="AJ263" t="n">
-        <v>1.96</v>
+        <v>2.21</v>
       </c>
       <c r="AL263" t="n">
-        <v>31.97</v>
+        <v>31.71</v>
       </c>
     </row>
     <row r="264">
@@ -31100,10 +31100,10 @@
         <v>6</v>
       </c>
       <c r="AJ264" t="n">
-        <v>1.96</v>
+        <v>2.21</v>
       </c>
       <c r="AL264" t="n">
-        <v>-30.03</v>
+        <v>-30.28</v>
       </c>
       <c r="AM264" t="inlineStr">
         <is>
@@ -31179,7 +31179,7 @@
       </c>
       <c r="B271" t="inlineStr">
         <is>
-          <t>+0.50%</t>
+          <t>+0.26%</t>
         </is>
       </c>
     </row>
@@ -31270,7 +31270,7 @@
         <v>-0.55</v>
       </c>
       <c r="D277" t="n">
-        <v>-1.43</v>
+        <v>-1.68</v>
       </c>
       <c r="F277" t="n">
         <v>36.42</v>
@@ -31292,7 +31292,7 @@
         <v>4.34</v>
       </c>
       <c r="D278" t="n">
-        <v>3.53</v>
+        <v>3.29</v>
       </c>
       <c r="F278" t="n">
         <v>52.11</v>
@@ -31314,7 +31314,7 @@
         <v>5.6</v>
       </c>
       <c r="D279" t="n">
-        <v>4.59</v>
+        <v>4.35</v>
       </c>
       <c r="F279" t="n">
         <v>58.33</v>
@@ -31377,7 +31377,7 @@
         <v>42.17</v>
       </c>
       <c r="E282" t="n">
-        <v>0.72</v>
+        <v>0.48</v>
       </c>
       <c r="G282" t="n">
         <v>-13.79</v>
@@ -31399,7 +31399,7 @@
         <v>44.44</v>
       </c>
       <c r="E283" t="n">
-        <v>-1.68</v>
+        <v>-1.93</v>
       </c>
       <c r="G283" t="n">
         <v>-11.05</v>
@@ -31421,7 +31421,7 @@
         <v>50</v>
       </c>
       <c r="E284" t="n">
-        <v>1.05</v>
+        <v>0.8</v>
       </c>
       <c r="G284" t="n">
         <v>-10.73</v>
@@ -31443,7 +31443,7 @@
         <v>41.67</v>
       </c>
       <c r="E285" t="n">
-        <v>0.92</v>
+        <v>0.68</v>
       </c>
       <c r="G285" t="n">
         <v>-11.58</v>
@@ -31668,7 +31668,7 @@
         <v>50</v>
       </c>
       <c r="E296" t="n">
-        <v>4.71</v>
+        <v>4.46</v>
       </c>
       <c r="F296" t="n">
         <v>-11.1</v>
@@ -31690,7 +31690,7 @@
         <v>33.33</v>
       </c>
       <c r="E297" t="n">
-        <v>-6.15</v>
+        <v>-6.39</v>
       </c>
       <c r="F297" t="n">
         <v>-13.2</v>
@@ -31712,7 +31712,7 @@
         <v>47.37</v>
       </c>
       <c r="E298" t="n">
-        <v>4.32</v>
+        <v>4.07</v>
       </c>
       <c r="F298" t="n">
         <v>-10.05</v>
@@ -32213,7 +32213,7 @@
         <v>40</v>
       </c>
       <c r="G4" t="n">
-        <v>1.6</v>
+        <v>1.35</v>
       </c>
       <c r="H4" t="n">
         <v>-11.33</v>
@@ -32225,7 +32225,7 @@
         <v>16.8</v>
       </c>
       <c r="K4" t="n">
-        <v>16.59</v>
+        <v>16.6</v>
       </c>
       <c r="L4" t="n">
         <v>0</v>
@@ -32253,7 +32253,7 @@
         <v>52</v>
       </c>
       <c r="G5" t="n">
-        <v>1.89</v>
+        <v>1.64</v>
       </c>
       <c r="H5" t="n">
         <v>-11.68</v>
@@ -32293,7 +32293,7 @@
         <v>41.1</v>
       </c>
       <c r="G6" t="n">
-        <v>-1.05</v>
+        <v>-1.29</v>
       </c>
       <c r="H6" t="n">
         <v>-13.08</v>
@@ -32333,7 +32333,7 @@
         <v>42.8</v>
       </c>
       <c r="G7" t="n">
-        <v>0.5</v>
+        <v>0.26</v>
       </c>
       <c r="H7" t="n">
         <v>-12.16</v>
@@ -32671,7 +32671,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>YELP</t>
+          <t>ADBE</t>
         </is>
       </c>
       <c r="B4" s="15" t="inlineStr">
@@ -32691,12 +32691,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>92.7</t>
+          <t>91.6</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>1.38</t>
+          <t>0.719</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -32706,32 +32706,32 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>3.78</t>
+          <t>7.64</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>25.5</t>
+          <t>9.0</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>13.4</t>
+          <t>34.2</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>0.57</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>12.6</t>
+          <t>36.6</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>Communication Services</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
@@ -32744,7 +32744,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>ADBE</t>
+          <t>YELP</t>
         </is>
       </c>
       <c r="B5" s="15" t="inlineStr">
@@ -32762,49 +32762,33 @@
           <t>CORE</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>91.6</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>0.719</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>7.64</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>9.0</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>34.2</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>0.57</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>36.6</t>
-        </is>
+      <c r="E5" t="n">
+        <v>91.40000000000001</v>
+      </c>
+      <c r="F5" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="G5" t="n">
+        <v>7</v>
+      </c>
+      <c r="H5" t="n">
+        <v>3.29</v>
+      </c>
+      <c r="I5" t="n">
+        <v>30.4</v>
+      </c>
+      <c r="J5" t="n">
+        <v>13.4</v>
+      </c>
+      <c r="K5" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="L5" t="n">
+        <v>12.6</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Communication Services</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
@@ -34802,29 +34786,45 @@
           <t>CORE</t>
         </is>
       </c>
-      <c r="E33" t="n">
-        <v>77.8</v>
-      </c>
-      <c r="F33" t="n">
-        <v>0.451</v>
-      </c>
-      <c r="G33" t="n">
-        <v>7</v>
-      </c>
-      <c r="H33" t="n">
-        <v>12.38</v>
-      </c>
-      <c r="I33" t="n">
-        <v>2</v>
-      </c>
-      <c r="J33" t="n">
-        <v>14.1</v>
-      </c>
-      <c r="K33" t="n">
-        <v>0.48</v>
-      </c>
-      <c r="L33" t="n">
-        <v>31.1</v>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>77.8</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>0.451</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>12.38</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>14.1</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>0.48</t>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>31.1</t>
+        </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
@@ -35881,29 +35881,45 @@
           <t>CORE</t>
         </is>
       </c>
-      <c r="E48" t="n">
-        <v>74.59999999999999</v>
-      </c>
-      <c r="F48" t="n">
-        <v>0.457</v>
-      </c>
-      <c r="G48" t="n">
-        <v>5</v>
-      </c>
-      <c r="H48" t="n">
-        <v>5.06</v>
-      </c>
-      <c r="I48" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="J48" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="K48" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="L48" t="n">
-        <v>20.8</v>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>74.6</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>0.457</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>5.06</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>4.7</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>3.6</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>0.25</t>
+        </is>
+      </c>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>20.8</t>
+        </is>
       </c>
       <c r="M48" t="inlineStr">
         <is>
@@ -36084,26 +36100,41 @@
           <t>GROWTH</t>
         </is>
       </c>
-      <c r="E51" t="n">
-        <v>73.90000000000001</v>
-      </c>
-      <c r="F51" t="n">
-        <v>0.386</v>
-      </c>
-      <c r="G51" t="n">
-        <v>5</v>
-      </c>
-      <c r="H51" t="n">
-        <v>2.83</v>
-      </c>
-      <c r="I51" t="n">
-        <v>94.2</v>
-      </c>
-      <c r="K51" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="L51" t="n">
-        <v>21.6</v>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>73.9</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>0.386</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>2.83</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>94.2</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr"/>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>21.6</t>
+        </is>
       </c>
       <c r="M51" t="inlineStr">
         <is>
@@ -38168,80 +38199,68 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>DELL</t>
-        </is>
-      </c>
-      <c r="B80" s="15" t="inlineStr">
-        <is>
-          <t>PASS</t>
+          <t>ETSY</t>
+        </is>
+      </c>
+      <c r="B80" s="14" t="inlineStr">
+        <is>
+          <t>FAIL</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>FAIL/LEV</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>CORE</t>
-        </is>
-      </c>
-      <c r="E80" t="inlineStr">
-        <is>
-          <t>66.0</t>
-        </is>
-      </c>
-      <c r="F80" t="inlineStr">
-        <is>
-          <t>0.224</t>
-        </is>
-      </c>
-      <c r="G80" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="H80" t="inlineStr">
-        <is>
-          <t>3.04</t>
-        </is>
-      </c>
-      <c r="I80" t="inlineStr">
-        <is>
-          <t>3.0</t>
-        </is>
-      </c>
-      <c r="J80" t="inlineStr">
-        <is>
-          <t>5.7</t>
-        </is>
-      </c>
-      <c r="K80" t="inlineStr">
-        <is>
-          <t>-12.75</t>
-        </is>
-      </c>
-      <c r="L80" t="inlineStr">
-        <is>
-          <t>7.4</t>
-        </is>
+          <t>LEVERAGED</t>
+        </is>
+      </c>
+      <c r="E80" t="n">
+        <v>66.09999999999999</v>
+      </c>
+      <c r="F80" t="n">
+        <v>0.731</v>
+      </c>
+      <c r="G80" t="n">
+        <v>5</v>
+      </c>
+      <c r="H80" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="I80" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="J80" t="n">
+        <v>14.3</v>
+      </c>
+      <c r="K80" t="n">
+        <v>-2.8</v>
+      </c>
+      <c r="L80" t="n">
+        <v>12.8</v>
       </c>
       <c r="M80" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Consumer Cyclical</t>
         </is>
       </c>
       <c r="N80" t="inlineStr">
         <is>
-          <t>mature / stable</t>
-        </is>
-      </c>
-      <c r="O80" t="inlineStr"/>
+          <t>distress/leverage flag</t>
+        </is>
+      </c>
+      <c r="O80" t="inlineStr">
+        <is>
+          <t>Altman-Z 1.41 in distress zone (&lt;1.81)</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>PSX</t>
+          <t>DELL</t>
         </is>
       </c>
       <c r="B81" s="15" t="inlineStr">
@@ -38251,12 +38270,12 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>PASS/DECL</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>DECLINING</t>
+          <t>CORE</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
@@ -38266,7 +38285,7 @@
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>0.177</t>
+          <t>0.224</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
@@ -38276,37 +38295,37 @@
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>4.12</t>
+          <t>3.04</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>2.8</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>5.7</t>
         </is>
       </c>
       <c r="K81" t="inlineStr">
         <is>
-          <t>0.68</t>
+          <t>-12.75</t>
         </is>
       </c>
       <c r="L81" t="inlineStr">
         <is>
-          <t>2.6</t>
+          <t>7.4</t>
         </is>
       </c>
       <c r="M81" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="N81" t="inlineStr">
         <is>
-          <t>revenue -8% YoY</t>
+          <t>mature / stable</t>
         </is>
       </c>
       <c r="O81" t="inlineStr"/>
@@ -38314,63 +38333,47 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>DASH</t>
-        </is>
-      </c>
-      <c r="B82" s="15" t="inlineStr">
-        <is>
-          <t>PASS</t>
+          <t>PLNT</t>
+        </is>
+      </c>
+      <c r="B82" s="14" t="inlineStr">
+        <is>
+          <t>FAIL</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>PASS/GS</t>
+          <t>FAIL/LEV</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>GROWTH</t>
-        </is>
-      </c>
-      <c r="E82" t="inlineStr">
-        <is>
-          <t>65.5</t>
-        </is>
-      </c>
-      <c r="F82" t="inlineStr">
-        <is>
-          <t>0.355</t>
-        </is>
-      </c>
-      <c r="G82" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="H82" t="inlineStr">
-        <is>
-          <t>6.97</t>
-        </is>
-      </c>
-      <c r="I82" t="inlineStr">
-        <is>
-          <t>1.8</t>
-        </is>
-      </c>
-      <c r="J82" t="inlineStr">
-        <is>
-          <t>3.4</t>
-        </is>
-      </c>
-      <c r="K82" t="inlineStr">
-        <is>
-          <t>0.33</t>
-        </is>
-      </c>
-      <c r="L82" t="inlineStr">
-        <is>
-          <t>5.3</t>
-        </is>
+          <t>LEVERAGED</t>
+        </is>
+      </c>
+      <c r="E82" t="n">
+        <v>65.8</v>
+      </c>
+      <c r="F82" t="n">
+        <v>0.222</v>
+      </c>
+      <c r="G82" t="n">
+        <v>7</v>
+      </c>
+      <c r="H82" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="I82" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="J82" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="K82" t="n">
+        <v>-6.01</v>
+      </c>
+      <c r="L82" t="n">
+        <v>29.8</v>
       </c>
       <c r="M82" t="inlineStr">
         <is>
@@ -38379,15 +38382,19 @@
       </c>
       <c r="N82" t="inlineStr">
         <is>
-          <t>rev +28%/yr, profitable</t>
-        </is>
-      </c>
-      <c r="O82" t="inlineStr"/>
+          <t>distress/leverage flag</t>
+        </is>
+      </c>
+      <c r="O82" t="inlineStr">
+        <is>
+          <t>Altman-Z 1.13 in distress zone (&lt;1.81)</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>GLW</t>
+          <t>PSX</t>
         </is>
       </c>
       <c r="B83" s="15" t="inlineStr">
@@ -38397,62 +38404,46 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>PASS/DECL</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>CORE</t>
-        </is>
-      </c>
-      <c r="E83" t="inlineStr">
-        <is>
-          <t>65.5</t>
-        </is>
-      </c>
-      <c r="F83" t="inlineStr">
-        <is>
-          <t>0.181</t>
-        </is>
-      </c>
-      <c r="G83" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="H83" t="inlineStr">
-        <is>
-          <t>5.78</t>
-        </is>
-      </c>
-      <c r="I83" t="inlineStr">
-        <is>
-          <t>1.1</t>
-        </is>
-      </c>
-      <c r="J83" t="inlineStr">
-        <is>
-          <t>7.1</t>
-        </is>
-      </c>
-      <c r="K83" t="inlineStr">
-        <is>
-          <t>0.79</t>
-        </is>
-      </c>
-      <c r="L83" t="inlineStr">
-        <is>
-          <t>14.6</t>
-        </is>
+          <t>DECLINING</t>
+        </is>
+      </c>
+      <c r="E83" t="n">
+        <v>65.7</v>
+      </c>
+      <c r="F83" t="n">
+        <v>0.177</v>
+      </c>
+      <c r="G83" t="n">
+        <v>7</v>
+      </c>
+      <c r="H83" t="n">
+        <v>4.29</v>
+      </c>
+      <c r="I83" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="J83" t="n">
+        <v>6</v>
+      </c>
+      <c r="K83" t="n">
+        <v>0.68</v>
+      </c>
+      <c r="L83" t="n">
+        <v>2.6</v>
       </c>
       <c r="M83" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="N83" t="inlineStr">
         <is>
-          <t>mature / stable</t>
+          <t>revenue -8% YoY</t>
         </is>
       </c>
       <c r="O83" t="inlineStr"/>
@@ -38460,7 +38451,7 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>VRT</t>
+          <t>DASH</t>
         </is>
       </c>
       <c r="B84" s="15" t="inlineStr">
@@ -38485,7 +38476,7 @@
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>0.304</t>
+          <t>0.355</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
@@ -38495,32 +38486,32 @@
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>9.0</t>
+          <t>6.97</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>1.9</t>
+          <t>1.8</t>
         </is>
       </c>
       <c r="J84" t="inlineStr">
         <is>
-          <t>21.2</t>
+          <t>3.4</t>
         </is>
       </c>
       <c r="K84" t="inlineStr">
         <is>
-          <t>0.82</t>
+          <t>0.33</t>
         </is>
       </c>
       <c r="L84" t="inlineStr">
         <is>
-          <t>18.5</t>
+          <t>5.3</t>
         </is>
       </c>
       <c r="M84" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Consumer Cyclical</t>
         </is>
       </c>
       <c r="N84" t="inlineStr">
@@ -38533,156 +38524,148 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>ETSY</t>
-        </is>
-      </c>
-      <c r="B85" s="14" t="inlineStr">
-        <is>
-          <t>FAIL</t>
+          <t>GLW</t>
+        </is>
+      </c>
+      <c r="B85" s="15" t="inlineStr">
+        <is>
+          <t>PASS</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>FAIL/LEV</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>LEVERAGED</t>
+          <t>CORE</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>65.4</t>
+          <t>65.5</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>0.731</t>
+          <t>0.181</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>1.52</t>
+          <t>5.78</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>8.6</t>
+          <t>1.1</t>
         </is>
       </c>
       <c r="J85" t="inlineStr">
         <is>
-          <t>14.3</t>
+          <t>7.1</t>
         </is>
       </c>
       <c r="K85" t="inlineStr">
         <is>
-          <t>-2.8</t>
+          <t>0.79</t>
         </is>
       </c>
       <c r="L85" t="inlineStr">
         <is>
-          <t>12.8</t>
+          <t>14.6</t>
         </is>
       </c>
       <c r="M85" t="inlineStr">
         <is>
-          <t>Consumer Cyclical</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="N85" t="inlineStr">
         <is>
-          <t>distress/leverage flag</t>
-        </is>
-      </c>
-      <c r="O85" t="inlineStr">
-        <is>
-          <t>Altman-Z 1.52 in distress zone (&lt;1.81)</t>
-        </is>
-      </c>
+          <t>mature / stable</t>
+        </is>
+      </c>
+      <c r="O85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>PLNT</t>
-        </is>
-      </c>
-      <c r="B86" s="14" t="inlineStr">
-        <is>
-          <t>FAIL</t>
+          <t>VRT</t>
+        </is>
+      </c>
+      <c r="B86" s="15" t="inlineStr">
+        <is>
+          <t>PASS</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>FAIL/LEV</t>
+          <t>PASS/GS</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>LEVERAGED</t>
+          <t>GROWTH</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>65.4</t>
+          <t>65.5</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>0.222</t>
+          <t>0.304</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>5</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>1.19</t>
+          <t>9.0</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>6.3</t>
+          <t>1.9</t>
         </is>
       </c>
       <c r="J86" t="inlineStr">
         <is>
-          <t>3.9</t>
+          <t>21.2</t>
         </is>
       </c>
       <c r="K86" t="inlineStr">
         <is>
-          <t>-6.01</t>
+          <t>0.82</t>
         </is>
       </c>
       <c r="L86" t="inlineStr">
         <is>
-          <t>29.8</t>
+          <t>18.5</t>
         </is>
       </c>
       <c r="M86" t="inlineStr">
         <is>
-          <t>Consumer Cyclical</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="N86" t="inlineStr">
         <is>
-          <t>distress/leverage flag</t>
-        </is>
-      </c>
-      <c r="O86" t="inlineStr">
-        <is>
-          <t>Altman-Z 1.19 in distress zone (&lt;1.81)</t>
-        </is>
-      </c>
+          <t>rev +28%/yr, profitable</t>
+        </is>
+      </c>
+      <c r="O86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -38705,29 +38688,45 @@
           <t>LEVERAGED</t>
         </is>
       </c>
-      <c r="E87" t="n">
-        <v>65.3</v>
-      </c>
-      <c r="F87" t="n">
-        <v>0.543</v>
-      </c>
-      <c r="G87" t="n">
-        <v>7</v>
-      </c>
-      <c r="H87" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="I87" t="n">
-        <v>9.300000000000001</v>
-      </c>
-      <c r="J87" t="n">
-        <v>6.3</v>
-      </c>
-      <c r="K87" t="n">
-        <v>5</v>
-      </c>
-      <c r="L87" t="n">
-        <v>14.7</v>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>65.3</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>0.543</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>1.65</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr">
+        <is>
+          <t>9.3</t>
+        </is>
+      </c>
+      <c r="J87" t="inlineStr">
+        <is>
+          <t>6.3</t>
+        </is>
+      </c>
+      <c r="K87" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="L87" t="inlineStr">
+        <is>
+          <t>14.7</t>
+        </is>
       </c>
       <c r="M87" t="inlineStr">
         <is>
@@ -41771,45 +41770,29 @@
           <t>CORE</t>
         </is>
       </c>
-      <c r="E129" t="inlineStr">
-        <is>
-          <t>53.1</t>
-        </is>
-      </c>
-      <c r="F129" t="inlineStr">
-        <is>
-          <t>0.1</t>
-        </is>
-      </c>
-      <c r="G129" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="H129" t="inlineStr">
-        <is>
-          <t>2.09</t>
-        </is>
-      </c>
-      <c r="I129" t="inlineStr">
-        <is>
-          <t>8.2</t>
-        </is>
-      </c>
-      <c r="J129" t="inlineStr">
-        <is>
-          <t>6.0</t>
-        </is>
-      </c>
-      <c r="K129" t="inlineStr">
-        <is>
-          <t>1.3</t>
-        </is>
-      </c>
-      <c r="L129" t="inlineStr">
-        <is>
-          <t>6.6</t>
-        </is>
+      <c r="E129" t="n">
+        <v>53.1</v>
+      </c>
+      <c r="F129" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="G129" t="n">
+        <v>7</v>
+      </c>
+      <c r="H129" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="I129" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="J129" t="n">
+        <v>6</v>
+      </c>
+      <c r="K129" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="L129" t="n">
+        <v>6.6</v>
       </c>
       <c r="M129" t="inlineStr">
         <is>
@@ -42840,7 +42823,7 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>BROS</t>
+          <t>OWL</t>
         </is>
       </c>
       <c r="B144" s="14" t="inlineStr">
@@ -42860,52 +42843,52 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>49.7</t>
+          <t>49.2</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>0.141</t>
+          <t>0.125</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>3.31</t>
+          <t>0.95</t>
         </is>
       </c>
       <c r="I144" t="inlineStr">
         <is>
-          <t>0.6</t>
+          <t>14.6</t>
         </is>
       </c>
       <c r="J144" t="inlineStr">
         <is>
-          <t>5.8</t>
+          <t>3.1</t>
         </is>
       </c>
       <c r="K144" t="inlineStr">
         <is>
-          <t>1.6</t>
+          <t>1.75</t>
         </is>
       </c>
       <c r="L144" t="inlineStr">
         <is>
-          <t>9.8</t>
+          <t>15.9</t>
         </is>
       </c>
       <c r="M144" t="inlineStr">
         <is>
-          <t>Consumer Cyclical</t>
+          <t>Financial Services</t>
         </is>
       </c>
       <c r="N144" t="inlineStr">
         <is>
-          <t>rev +28%/yr, profitable</t>
+          <t>rev +25%/yr, profitable</t>
         </is>
       </c>
       <c r="O144" t="inlineStr"/>
@@ -42913,7 +42896,7 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>OWL</t>
+          <t>TTE</t>
         </is>
       </c>
       <c r="B145" s="14" t="inlineStr">
@@ -42923,22 +42906,22 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>FAIL/GS</t>
+          <t>FAIL/DECL</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>GROWTH</t>
+          <t>DECLINING</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>49.2</t>
+          <t>49.1</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>0.125</t>
+          <t>0.178</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
@@ -42946,39 +42929,35 @@
           <t>5</t>
         </is>
       </c>
-      <c r="H145" t="inlineStr">
-        <is>
-          <t>0.95</t>
-        </is>
-      </c>
+      <c r="H145" t="inlineStr"/>
       <c r="I145" t="inlineStr">
         <is>
-          <t>14.6</t>
+          <t>5.3</t>
         </is>
       </c>
       <c r="J145" t="inlineStr">
         <is>
-          <t>3.1</t>
+          <t>9.8</t>
         </is>
       </c>
       <c r="K145" t="inlineStr">
         <is>
-          <t>1.75</t>
+          <t>0.52</t>
         </is>
       </c>
       <c r="L145" t="inlineStr">
         <is>
-          <t>15.9</t>
+          <t>10.9</t>
         </is>
       </c>
       <c r="M145" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="N145" t="inlineStr">
         <is>
-          <t>rev +25%/yr, profitable</t>
+          <t>revenue -7% YoY</t>
         </is>
       </c>
       <c r="O145" t="inlineStr"/>
@@ -42986,7 +42965,7 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>TTE</t>
+          <t>OKLO</t>
         </is>
       </c>
       <c r="B146" s="14" t="inlineStr">
@@ -42996,66 +42975,66 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>FAIL/DECL</t>
+          <t>FAIL</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>DECLINING</t>
+          <t>CORE</t>
         </is>
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>49.1</t>
-        </is>
-      </c>
-      <c r="F146" t="inlineStr">
-        <is>
-          <t>0.178</t>
-        </is>
-      </c>
+          <t>49.0</t>
+        </is>
+      </c>
+      <c r="F146" t="inlineStr"/>
       <c r="G146" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="H146" t="inlineStr"/>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="H146" t="inlineStr">
+        <is>
+          <t>90.36</t>
+        </is>
+      </c>
       <c r="I146" t="inlineStr">
         <is>
-          <t>5.3</t>
+          <t>-1.5</t>
         </is>
       </c>
       <c r="J146" t="inlineStr">
         <is>
-          <t>9.8</t>
+          <t>-4.8</t>
         </is>
       </c>
       <c r="K146" t="inlineStr">
         <is>
-          <t>0.52</t>
-        </is>
-      </c>
-      <c r="L146" t="inlineStr">
-        <is>
-          <t>10.9</t>
-        </is>
-      </c>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="L146" t="inlineStr"/>
       <c r="M146" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Utilities</t>
         </is>
       </c>
       <c r="N146" t="inlineStr">
         <is>
-          <t>revenue -7% YoY</t>
-        </is>
-      </c>
-      <c r="O146" t="inlineStr"/>
+          <t>mature / stable</t>
+        </is>
+      </c>
+      <c r="O146" t="inlineStr">
+        <is>
+          <t>Interest coverage -4.8x &lt; 1.0x and FCF not positive | Burning cash and unprofitable (FCF&lt;0 and NI&lt;0)</t>
+        </is>
+      </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>OKLO</t>
+          <t>MGM</t>
         </is>
       </c>
       <c r="B147" s="14" t="inlineStr">
@@ -43065,66 +43044,74 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>FAIL/LEV</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>CORE</t>
+          <t>LEVERAGED</t>
         </is>
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>49.0</t>
-        </is>
-      </c>
-      <c r="F147" t="inlineStr"/>
+          <t>48.6</t>
+        </is>
+      </c>
+      <c r="F147" t="inlineStr">
+        <is>
+          <t>0.188</t>
+        </is>
+      </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>90.36</t>
+          <t>0.75</t>
         </is>
       </c>
       <c r="I147" t="inlineStr">
         <is>
-          <t>-1.5</t>
+          <t>13.1</t>
         </is>
       </c>
       <c r="J147" t="inlineStr">
         <is>
-          <t>-4.8</t>
+          <t>1.7</t>
         </is>
       </c>
       <c r="K147" t="inlineStr">
         <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="L147" t="inlineStr"/>
+          <t>12.91</t>
+        </is>
+      </c>
+      <c r="L147" t="inlineStr">
+        <is>
+          <t>7.6</t>
+        </is>
+      </c>
       <c r="M147" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>Consumer Cyclical</t>
         </is>
       </c>
       <c r="N147" t="inlineStr">
         <is>
-          <t>mature / stable</t>
+          <t>distress/leverage flag</t>
         </is>
       </c>
       <c r="O147" t="inlineStr">
         <is>
-          <t>Interest coverage -4.8x &lt; 1.0x and FCF not positive | Burning cash and unprofitable (FCF&lt;0 and NI&lt;0)</t>
+          <t>Altman-Z 0.75 in distress zone (&lt;1.81)</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>MGM</t>
+          <t>NET</t>
         </is>
       </c>
       <c r="B148" s="14" t="inlineStr">
@@ -43134,74 +43121,70 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>FAIL/LEV</t>
+          <t>FAIL/SPEC</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>LEVERAGED</t>
+          <t>SPECULATIVE</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>48.6</t>
+          <t>48.1</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>0.188</t>
+          <t>0.268</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>4</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>0.75</t>
+          <t>13.51</t>
         </is>
       </c>
       <c r="I148" t="inlineStr">
         <is>
-          <t>13.1</t>
+          <t>0.3</t>
         </is>
       </c>
       <c r="J148" t="inlineStr">
         <is>
-          <t>1.7</t>
+          <t>-9.6</t>
         </is>
       </c>
       <c r="K148" t="inlineStr">
         <is>
-          <t>12.91</t>
+          <t>2.41</t>
         </is>
       </c>
       <c r="L148" t="inlineStr">
         <is>
-          <t>7.6</t>
+          <t>-9.6</t>
         </is>
       </c>
       <c r="M148" t="inlineStr">
         <is>
-          <t>Consumer Cyclical</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="N148" t="inlineStr">
         <is>
-          <t>distress/leverage flag</t>
-        </is>
-      </c>
-      <c r="O148" t="inlineStr">
-        <is>
-          <t>Altman-Z 0.75 in distress zone (&lt;1.81)</t>
-        </is>
-      </c>
+          <t>pre-commercial (P/S 46)</t>
+        </is>
+      </c>
+      <c r="O148" t="inlineStr"/>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>NET</t>
+          <t>AA</t>
         </is>
       </c>
       <c r="B149" s="14" t="inlineStr">
@@ -43211,62 +43194,62 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>FAIL/SPEC</t>
+          <t>FAIL</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>SPECULATIVE</t>
+          <t>CORE</t>
         </is>
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>48.1</t>
+          <t>47.9</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>0.268</t>
+          <t>0.135</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>13.51</t>
+          <t>1.97</t>
         </is>
       </c>
       <c r="I149" t="inlineStr">
         <is>
-          <t>0.3</t>
+          <t>4.1</t>
         </is>
       </c>
       <c r="J149" t="inlineStr">
         <is>
-          <t>-9.6</t>
+          <t>7.7</t>
         </is>
       </c>
       <c r="K149" t="inlineStr">
         <is>
-          <t>2.41</t>
+          <t>0.44</t>
         </is>
       </c>
       <c r="L149" t="inlineStr">
         <is>
-          <t>-9.6</t>
+          <t>5.9</t>
         </is>
       </c>
       <c r="M149" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Basic Materials</t>
         </is>
       </c>
       <c r="N149" t="inlineStr">
         <is>
-          <t>pre-commercial (P/S 46)</t>
+          <t>mature / stable</t>
         </is>
       </c>
       <c r="O149" t="inlineStr"/>
@@ -43274,7 +43257,7 @@
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>AA</t>
+          <t>XPEV</t>
         </is>
       </c>
       <c r="B150" s="14" t="inlineStr">
@@ -43284,22 +43267,22 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>FAIL/GS</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>CORE</t>
+          <t>GROWTH</t>
         </is>
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>47.9</t>
+          <t>47.6</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>0.135</t>
+          <t>0.14</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
@@ -43309,45 +43292,49 @@
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>1.97</t>
+          <t>0.29</t>
         </is>
       </c>
       <c r="I150" t="inlineStr">
         <is>
-          <t>4.1</t>
+          <t>42.1</t>
         </is>
       </c>
       <c r="J150" t="inlineStr">
         <is>
-          <t>7.7</t>
+          <t>-2.0</t>
         </is>
       </c>
       <c r="K150" t="inlineStr">
         <is>
-          <t>0.44</t>
+          <t>0.64</t>
         </is>
       </c>
       <c r="L150" t="inlineStr">
         <is>
-          <t>5.9</t>
+          <t>-3.5</t>
         </is>
       </c>
       <c r="M150" t="inlineStr">
         <is>
-          <t>Basic Materials</t>
+          <t>Consumer Cyclical</t>
         </is>
       </c>
       <c r="N150" t="inlineStr">
         <is>
-          <t>mature / stable</t>
-        </is>
-      </c>
-      <c r="O150" t="inlineStr"/>
+          <t>rev +88%/yr, not yet FCF-safe</t>
+        </is>
+      </c>
+      <c r="O150" t="inlineStr">
+        <is>
+          <t>Altman-Z 0.29 in distress zone (&lt;1.81)</t>
+        </is>
+      </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>XPEV</t>
+          <t>URI</t>
         </is>
       </c>
       <c r="B151" s="14" t="inlineStr">
@@ -43357,74 +43344,70 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>FAIL/GS</t>
+          <t>FAIL</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>GROWTH</t>
+          <t>CORE</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>47.6</t>
+          <t>47.1</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>0.14</t>
+          <t>0.206</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>0.29</t>
+          <t>3.49</t>
         </is>
       </c>
       <c r="I151" t="inlineStr">
         <is>
-          <t>42.1</t>
+          <t>1.1</t>
         </is>
       </c>
       <c r="J151" t="inlineStr">
         <is>
-          <t>-2.0</t>
+          <t>5.7</t>
         </is>
       </c>
       <c r="K151" t="inlineStr">
         <is>
-          <t>0.64</t>
+          <t>1.75</t>
         </is>
       </c>
       <c r="L151" t="inlineStr">
         <is>
-          <t>-3.5</t>
+          <t>24.7</t>
         </is>
       </c>
       <c r="M151" t="inlineStr">
         <is>
-          <t>Consumer Cyclical</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="N151" t="inlineStr">
         <is>
-          <t>rev +88%/yr, not yet FCF-safe</t>
-        </is>
-      </c>
-      <c r="O151" t="inlineStr">
-        <is>
-          <t>Altman-Z 0.29 in distress zone (&lt;1.81)</t>
-        </is>
-      </c>
+          <t>mature / stable</t>
+        </is>
+      </c>
+      <c r="O151" t="inlineStr"/>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>URI</t>
+          <t>ARES</t>
         </is>
       </c>
       <c r="B152" s="14" t="inlineStr">
@@ -43434,22 +43417,22 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>FAIL/GS</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>CORE</t>
+          <t>GROWTH</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>47.1</t>
+          <t>46.2</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>0.206</t>
+          <t>0.106</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
@@ -43459,37 +43442,37 @@
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>3.49</t>
+          <t>1.39</t>
         </is>
       </c>
       <c r="I152" t="inlineStr">
         <is>
-          <t>1.1</t>
+          <t>9.9</t>
         </is>
       </c>
       <c r="J152" t="inlineStr">
         <is>
-          <t>5.7</t>
+          <t>2.7</t>
         </is>
       </c>
       <c r="K152" t="inlineStr">
         <is>
-          <t>1.75</t>
+          <t>3.33</t>
         </is>
       </c>
       <c r="L152" t="inlineStr">
         <is>
-          <t>24.7</t>
+          <t>15.9</t>
         </is>
       </c>
       <c r="M152" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Financial Services</t>
         </is>
       </c>
       <c r="N152" t="inlineStr">
         <is>
-          <t>mature / stable</t>
+          <t>rev +44%/yr, profitable</t>
         </is>
       </c>
       <c r="O152" t="inlineStr"/>
@@ -43497,7 +43480,7 @@
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>ARES</t>
+          <t>KTOS</t>
         </is>
       </c>
       <c r="B153" s="14" t="inlineStr">
@@ -43507,12 +43490,12 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>FAIL/GS</t>
+          <t>FAIL</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>GROWTH</t>
+          <t>CORE</t>
         </is>
       </c>
       <c r="E153" t="inlineStr">
@@ -43522,47 +43505,47 @@
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>0.106</t>
+          <t>0.125</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>1.39</t>
+          <t>14.38</t>
         </is>
       </c>
       <c r="I153" t="inlineStr">
         <is>
-          <t>9.9</t>
+          <t>-1.3</t>
         </is>
       </c>
       <c r="J153" t="inlineStr">
         <is>
-          <t>2.7</t>
+          <t>4.5</t>
         </is>
       </c>
       <c r="K153" t="inlineStr">
         <is>
-          <t>3.33</t>
+          <t>0.07</t>
         </is>
       </c>
       <c r="L153" t="inlineStr">
         <is>
-          <t>15.9</t>
+          <t>2.1</t>
         </is>
       </c>
       <c r="M153" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="N153" t="inlineStr">
         <is>
-          <t>rev +44%/yr, profitable</t>
+          <t>mature / stable</t>
         </is>
       </c>
       <c r="O153" t="inlineStr"/>
@@ -43570,7 +43553,7 @@
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>KTOS</t>
+          <t>LYFT</t>
         </is>
       </c>
       <c r="B154" s="14" t="inlineStr">
@@ -43580,22 +43563,22 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>FAIL/LEV</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>CORE</t>
+          <t>LEVERAGED</t>
         </is>
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>46.2</t>
+          <t>45.4</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>0.125</t>
+          <t>0.29</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
@@ -43605,45 +43588,49 @@
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>14.38</t>
+          <t>0.01</t>
         </is>
       </c>
       <c r="I154" t="inlineStr">
         <is>
-          <t>-1.3</t>
+          <t>16.9</t>
         </is>
       </c>
       <c r="J154" t="inlineStr">
         <is>
-          <t>4.5</t>
+          <t>-1.6</t>
         </is>
       </c>
       <c r="K154" t="inlineStr">
         <is>
-          <t>0.07</t>
+          <t>0.39</t>
         </is>
       </c>
       <c r="L154" t="inlineStr">
         <is>
-          <t>2.1</t>
+          <t>-3.0</t>
         </is>
       </c>
       <c r="M154" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="N154" t="inlineStr">
         <is>
-          <t>mature / stable</t>
-        </is>
-      </c>
-      <c r="O154" t="inlineStr"/>
+          <t>distress/leverage flag</t>
+        </is>
+      </c>
+      <c r="O154" t="inlineStr">
+        <is>
+          <t>Altman-Z 0.01 in distress zone (&lt;1.81)</t>
+        </is>
+      </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>LYFT</t>
+          <t>RKLB</t>
         </is>
       </c>
       <c r="B155" s="14" t="inlineStr">
@@ -43653,74 +43640,74 @@
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>FAIL/LEV</t>
+          <t>FAIL/SPEC</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>LEVERAGED</t>
+          <t>SPECULATIVE</t>
         </is>
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>45.4</t>
+          <t>44.4</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>0.29</t>
+          <t>0.089</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>46.09</t>
         </is>
       </c>
       <c r="I155" t="inlineStr">
         <is>
-          <t>16.9</t>
+          <t>-0.7</t>
         </is>
       </c>
       <c r="J155" t="inlineStr">
         <is>
-          <t>-1.6</t>
+          <t>-7.5</t>
         </is>
       </c>
       <c r="K155" t="inlineStr">
         <is>
-          <t>0.39</t>
+          <t>0.15</t>
         </is>
       </c>
       <c r="L155" t="inlineStr">
         <is>
-          <t>-3.0</t>
+          <t>-38.0</t>
         </is>
       </c>
       <c r="M155" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="N155" t="inlineStr">
         <is>
-          <t>distress/leverage flag</t>
+          <t>pre-commercial (P/S 77)</t>
         </is>
       </c>
       <c r="O155" t="inlineStr">
         <is>
-          <t>Altman-Z 0.01 in distress zone (&lt;1.81)</t>
+          <t>Operating margin negative (-38.0%) and FCF not positive | Interest coverage -7.5x &lt; 1.0x and FCF not positive | Burning cash and unprofitable (FCF&lt;0 and NI&lt;0)</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>RKLB</t>
+          <t>NBIS</t>
         </is>
       </c>
       <c r="B156" s="14" t="inlineStr">
@@ -43740,64 +43727,64 @@
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>44.4</t>
+          <t>44.1</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>0.089</t>
+          <t>0.029</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>46.09</t>
+          <t>5.3</t>
         </is>
       </c>
       <c r="I156" t="inlineStr">
         <is>
-          <t>-0.7</t>
+          <t>-6.2</t>
         </is>
       </c>
       <c r="J156" t="inlineStr">
         <is>
-          <t>-7.5</t>
+          <t>1.2</t>
         </is>
       </c>
       <c r="K156" t="inlineStr">
         <is>
-          <t>0.15</t>
+          <t>1.08</t>
         </is>
       </c>
       <c r="L156" t="inlineStr">
         <is>
-          <t>-38.0</t>
+          <t>-115.5</t>
         </is>
       </c>
       <c r="M156" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Communication Services</t>
         </is>
       </c>
       <c r="N156" t="inlineStr">
         <is>
-          <t>pre-commercial (P/S 77)</t>
+          <t>pre-commercial (P/S 112)</t>
         </is>
       </c>
       <c r="O156" t="inlineStr">
         <is>
-          <t>Operating margin negative (-38.0%) and FCF not positive | Interest coverage -7.5x &lt; 1.0x and FCF not positive | Burning cash and unprofitable (FCF&lt;0 and NI&lt;0)</t>
+          <t>Operating margin negative (-115.5%) and FCF not positive</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>NBIS</t>
+          <t>FIS</t>
         </is>
       </c>
       <c r="B157" s="14" t="inlineStr">
@@ -43807,22 +43794,22 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>FAIL/SPEC</t>
+          <t>FAIL/LEV</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>SPECULATIVE</t>
+          <t>LEVERAGED</t>
         </is>
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>44.1</t>
+          <t>43.9</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>0.029</t>
+          <t>0.118</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
@@ -43832,49 +43819,49 @@
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>5.3</t>
+          <t>0.07</t>
         </is>
       </c>
       <c r="I157" t="inlineStr">
         <is>
-          <t>-6.2</t>
+          <t>8.5</t>
         </is>
       </c>
       <c r="J157" t="inlineStr">
         <is>
-          <t>1.2</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="K157" t="inlineStr">
         <is>
-          <t>1.08</t>
+          <t>0.96</t>
         </is>
       </c>
       <c r="L157" t="inlineStr">
         <is>
-          <t>-115.5</t>
+          <t>16.5</t>
         </is>
       </c>
       <c r="M157" t="inlineStr">
         <is>
-          <t>Communication Services</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="N157" t="inlineStr">
         <is>
-          <t>pre-commercial (P/S 112)</t>
+          <t>distress/leverage flag</t>
         </is>
       </c>
       <c r="O157" t="inlineStr">
         <is>
-          <t>Operating margin negative (-115.5%) and FCF not positive</t>
+          <t>Altman-Z 0.07 in distress zone (&lt;1.81)</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>FIS</t>
+          <t>KMX</t>
         </is>
       </c>
       <c r="B158" s="14" t="inlineStr">
@@ -43894,12 +43881,12 @@
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>43.9</t>
+          <t>43.7</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>0.118</t>
+          <t>0.106</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
@@ -43909,32 +43896,32 @@
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>0.07</t>
+          <t>1.75</t>
         </is>
       </c>
       <c r="I158" t="inlineStr">
         <is>
-          <t>8.5</t>
+          <t>13.7</t>
         </is>
       </c>
       <c r="J158" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>1.4</t>
         </is>
       </c>
       <c r="K158" t="inlineStr">
         <is>
-          <t>0.96</t>
+          <t>3.15</t>
         </is>
       </c>
       <c r="L158" t="inlineStr">
         <is>
-          <t>16.5</t>
+          <t>-1.6</t>
         </is>
       </c>
       <c r="M158" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Consumer Cyclical</t>
         </is>
       </c>
       <c r="N158" t="inlineStr">
@@ -43944,14 +43931,14 @@
       </c>
       <c r="O158" t="inlineStr">
         <is>
-          <t>Altman-Z 0.07 in distress zone (&lt;1.81)</t>
+          <t>Altman-Z 1.75 in distress zone (&lt;1.81)</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>KMX</t>
+          <t>BROS</t>
         </is>
       </c>
       <c r="B159" s="14" t="inlineStr">
@@ -43961,53 +43948,37 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>FAIL/LEV</t>
+          <t>FAIL/GS</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>LEVERAGED</t>
-        </is>
-      </c>
-      <c r="E159" t="inlineStr">
-        <is>
-          <t>43.7</t>
-        </is>
-      </c>
-      <c r="F159" t="inlineStr">
-        <is>
-          <t>0.106</t>
-        </is>
-      </c>
-      <c r="G159" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="H159" t="inlineStr">
-        <is>
-          <t>1.75</t>
-        </is>
-      </c>
-      <c r="I159" t="inlineStr">
-        <is>
-          <t>13.7</t>
-        </is>
-      </c>
-      <c r="J159" t="inlineStr">
-        <is>
-          <t>1.4</t>
-        </is>
-      </c>
-      <c r="K159" t="inlineStr">
-        <is>
-          <t>3.15</t>
-        </is>
-      </c>
-      <c r="L159" t="inlineStr">
-        <is>
-          <t>-1.6</t>
-        </is>
+          <t>GROWTH</t>
+        </is>
+      </c>
+      <c r="E159" t="n">
+        <v>43.3</v>
+      </c>
+      <c r="F159" t="n">
+        <v>0.141</v>
+      </c>
+      <c r="G159" t="n">
+        <v>6</v>
+      </c>
+      <c r="H159" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="I159" t="n">
+        <v>1</v>
+      </c>
+      <c r="J159" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="K159" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="L159" t="n">
+        <v>9.800000000000001</v>
       </c>
       <c r="M159" t="inlineStr">
         <is>
@@ -44016,14 +43987,10 @@
       </c>
       <c r="N159" t="inlineStr">
         <is>
-          <t>distress/leverage flag</t>
-        </is>
-      </c>
-      <c r="O159" t="inlineStr">
-        <is>
-          <t>Altman-Z 1.75 in distress zone (&lt;1.81)</t>
-        </is>
-      </c>
+          <t>rev +28%/yr, profitable</t>
+        </is>
+      </c>
+      <c r="O159" t="inlineStr"/>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
@@ -45988,45 +45955,29 @@
           <t>NEW-IPO</t>
         </is>
       </c>
-      <c r="E186" t="inlineStr">
-        <is>
-          <t>30.7</t>
-        </is>
-      </c>
-      <c r="F186" t="inlineStr">
-        <is>
-          <t>0.068</t>
-        </is>
-      </c>
-      <c r="G186" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="H186" t="inlineStr">
-        <is>
-          <t>1.63</t>
-        </is>
-      </c>
-      <c r="I186" t="inlineStr">
-        <is>
-          <t>11.8</t>
-        </is>
-      </c>
-      <c r="J186" t="inlineStr">
-        <is>
-          <t>0.1</t>
-        </is>
-      </c>
-      <c r="K186" t="inlineStr">
-        <is>
-          <t>1.71</t>
-        </is>
-      </c>
-      <c r="L186" t="inlineStr">
-        <is>
-          <t>0.6</t>
-        </is>
+      <c r="E186" t="n">
+        <v>30.7</v>
+      </c>
+      <c r="F186" t="n">
+        <v>0.068</v>
+      </c>
+      <c r="G186" t="n">
+        <v>4</v>
+      </c>
+      <c r="H186" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="I186" t="n">
+        <v>12.9</v>
+      </c>
+      <c r="J186" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="K186" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="L186" t="n">
+        <v>0.6</v>
       </c>
       <c r="M186" t="inlineStr">
         <is>
@@ -46040,7 +45991,7 @@
       </c>
       <c r="O186" t="inlineStr">
         <is>
-          <t>Altman-Z 1.63 in distress zone (&lt;1.81)</t>
+          <t>Altman-Z 1.61 in distress zone (&lt;1.81)</t>
         </is>
       </c>
     </row>
@@ -48599,18 +48550,30 @@
           <t>DECLINING</t>
         </is>
       </c>
-      <c r="E221" t="n">
-        <v>1</v>
-      </c>
-      <c r="G221" t="n">
-        <v>2</v>
-      </c>
-      <c r="I221" t="n">
-        <v>-23.6</v>
-      </c>
-      <c r="K221" t="n">
-        <v>2.41</v>
-      </c>
+      <c r="E221" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="F221" t="inlineStr"/>
+      <c r="G221" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H221" t="inlineStr"/>
+      <c r="I221" t="inlineStr">
+        <is>
+          <t>-23.6</t>
+        </is>
+      </c>
+      <c r="J221" t="inlineStr"/>
+      <c r="K221" t="inlineStr">
+        <is>
+          <t>2.41</t>
+        </is>
+      </c>
+      <c r="L221" t="inlineStr"/>
       <c r="M221" t="inlineStr">
         <is>
           <t>Financial Services</t>
@@ -48804,8 +48767,10 @@
           <t>LEVERAGED</t>
         </is>
       </c>
-      <c r="L2" t="n">
-        <v>65.3</v>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>65.3</t>
+        </is>
       </c>
     </row>
     <row r="3">
@@ -48856,8 +48821,10 @@
           <t>GROWTH</t>
         </is>
       </c>
-      <c r="L3" t="n">
-        <v>73.90000000000001</v>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>73.9</t>
+        </is>
       </c>
     </row>
     <row r="4">
@@ -48908,8 +48875,10 @@
           <t>DECLINING</t>
         </is>
       </c>
-      <c r="L4" t="n">
-        <v>1</v>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
       </c>
     </row>
     <row r="5">
@@ -48960,8 +48929,10 @@
           <t>CORE</t>
         </is>
       </c>
-      <c r="L5" t="n">
-        <v>77.8</v>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>77.8</t>
+        </is>
       </c>
     </row>
     <row r="6">
@@ -49012,8 +48983,10 @@
           <t>CORE</t>
         </is>
       </c>
-      <c r="L6" t="n">
-        <v>74.59999999999999</v>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>74.6</t>
+        </is>
       </c>
     </row>
     <row r="7">
@@ -52844,10 +52817,8 @@
           <t>CORE</t>
         </is>
       </c>
-      <c r="L77" t="inlineStr">
-        <is>
-          <t>53.1</t>
-        </is>
+      <c r="L77" t="n">
+        <v>53.1</v>
       </c>
     </row>
     <row r="78">
@@ -52898,10 +52869,8 @@
           <t>DECLINING</t>
         </is>
       </c>
-      <c r="L78" t="inlineStr">
-        <is>
-          <t>66.0</t>
-        </is>
+      <c r="L78" t="n">
+        <v>65.7</v>
       </c>
     </row>
     <row r="79">
@@ -52952,10 +52921,8 @@
           <t>LEVERAGED</t>
         </is>
       </c>
-      <c r="L79" t="inlineStr">
-        <is>
-          <t>65.4</t>
-        </is>
+      <c r="L79" t="n">
+        <v>65.8</v>
       </c>
     </row>
     <row r="80">
@@ -53006,10 +52973,8 @@
           <t>GROWTH</t>
         </is>
       </c>
-      <c r="L80" t="inlineStr">
-        <is>
-          <t>49.7</t>
-        </is>
+      <c r="L80" t="n">
+        <v>43.3</v>
       </c>
     </row>
     <row r="81">
@@ -53060,10 +53025,8 @@
           <t>LEVERAGED</t>
         </is>
       </c>
-      <c r="L81" t="inlineStr">
-        <is>
-          <t>65.4</t>
-        </is>
+      <c r="L81" t="n">
+        <v>66.09999999999999</v>
       </c>
     </row>
     <row r="82">
@@ -53222,10 +53185,8 @@
           <t>NEW-IPO</t>
         </is>
       </c>
-      <c r="L84" t="inlineStr">
-        <is>
-          <t>30.7</t>
-        </is>
+      <c r="L84" t="n">
+        <v>30.7</v>
       </c>
     </row>
     <row r="85">
@@ -53276,10 +53237,8 @@
           <t>CORE</t>
         </is>
       </c>
-      <c r="L85" t="inlineStr">
-        <is>
-          <t>92.7</t>
-        </is>
+      <c r="L85" t="n">
+        <v>91.40000000000001</v>
       </c>
     </row>
     <row r="86">

--- a/STS_holy_grail.xlsx
+++ b/STS_holy_grail.xlsx
@@ -32762,29 +32762,45 @@
           <t>CORE</t>
         </is>
       </c>
-      <c r="E5" t="n">
-        <v>91.40000000000001</v>
-      </c>
-      <c r="F5" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="G5" t="n">
-        <v>7</v>
-      </c>
-      <c r="H5" t="n">
-        <v>3.29</v>
-      </c>
-      <c r="I5" t="n">
-        <v>30.4</v>
-      </c>
-      <c r="J5" t="n">
-        <v>13.4</v>
-      </c>
-      <c r="K5" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="L5" t="n">
-        <v>12.6</v>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>91.4</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>1.38</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>3.29</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>30.4</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>13.4</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>0.03</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>12.6</t>
+        </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
@@ -38217,29 +38233,45 @@
           <t>LEVERAGED</t>
         </is>
       </c>
-      <c r="E80" t="n">
-        <v>66.09999999999999</v>
-      </c>
-      <c r="F80" t="n">
-        <v>0.731</v>
-      </c>
-      <c r="G80" t="n">
-        <v>5</v>
-      </c>
-      <c r="H80" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="I80" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="J80" t="n">
-        <v>14.3</v>
-      </c>
-      <c r="K80" t="n">
-        <v>-2.8</v>
-      </c>
-      <c r="L80" t="n">
-        <v>12.8</v>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>66.1</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>0.731</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>1.41</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>9.6</t>
+        </is>
+      </c>
+      <c r="J80" t="inlineStr">
+        <is>
+          <t>14.3</t>
+        </is>
+      </c>
+      <c r="K80" t="inlineStr">
+        <is>
+          <t>-2.8</t>
+        </is>
+      </c>
+      <c r="L80" t="inlineStr">
+        <is>
+          <t>12.8</t>
+        </is>
       </c>
       <c r="M80" t="inlineStr">
         <is>
@@ -38351,29 +38383,45 @@
           <t>LEVERAGED</t>
         </is>
       </c>
-      <c r="E82" t="n">
-        <v>65.8</v>
-      </c>
-      <c r="F82" t="n">
-        <v>0.222</v>
-      </c>
-      <c r="G82" t="n">
-        <v>7</v>
-      </c>
-      <c r="H82" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="I82" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="J82" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="K82" t="n">
-        <v>-6.01</v>
-      </c>
-      <c r="L82" t="n">
-        <v>29.8</v>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>65.8</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>0.222</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>1.13</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>6.8</t>
+        </is>
+      </c>
+      <c r="J82" t="inlineStr">
+        <is>
+          <t>3.9</t>
+        </is>
+      </c>
+      <c r="K82" t="inlineStr">
+        <is>
+          <t>-6.01</t>
+        </is>
+      </c>
+      <c r="L82" t="inlineStr">
+        <is>
+          <t>29.8</t>
+        </is>
       </c>
       <c r="M82" t="inlineStr">
         <is>
@@ -38412,29 +38460,45 @@
           <t>DECLINING</t>
         </is>
       </c>
-      <c r="E83" t="n">
-        <v>65.7</v>
-      </c>
-      <c r="F83" t="n">
-        <v>0.177</v>
-      </c>
-      <c r="G83" t="n">
-        <v>7</v>
-      </c>
-      <c r="H83" t="n">
-        <v>4.29</v>
-      </c>
-      <c r="I83" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="J83" t="n">
-        <v>6</v>
-      </c>
-      <c r="K83" t="n">
-        <v>0.68</v>
-      </c>
-      <c r="L83" t="n">
-        <v>2.6</v>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>65.7</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>0.177</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>4.29</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>2.5</t>
+        </is>
+      </c>
+      <c r="J83" t="inlineStr">
+        <is>
+          <t>6.0</t>
+        </is>
+      </c>
+      <c r="K83" t="inlineStr">
+        <is>
+          <t>0.68</t>
+        </is>
+      </c>
+      <c r="L83" t="inlineStr">
+        <is>
+          <t>2.6</t>
+        </is>
       </c>
       <c r="M83" t="inlineStr">
         <is>
@@ -41770,29 +41834,45 @@
           <t>CORE</t>
         </is>
       </c>
-      <c r="E129" t="n">
-        <v>53.1</v>
-      </c>
-      <c r="F129" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="G129" t="n">
-        <v>7</v>
-      </c>
-      <c r="H129" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="I129" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="J129" t="n">
-        <v>6</v>
-      </c>
-      <c r="K129" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="L129" t="n">
-        <v>6.6</v>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>53.1</t>
+        </is>
+      </c>
+      <c r="F129" t="inlineStr">
+        <is>
+          <t>0.1</t>
+        </is>
+      </c>
+      <c r="G129" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="H129" t="inlineStr">
+        <is>
+          <t>2.06</t>
+        </is>
+      </c>
+      <c r="I129" t="inlineStr">
+        <is>
+          <t>8.6</t>
+        </is>
+      </c>
+      <c r="J129" t="inlineStr">
+        <is>
+          <t>6.0</t>
+        </is>
+      </c>
+      <c r="K129" t="inlineStr">
+        <is>
+          <t>1.3</t>
+        </is>
+      </c>
+      <c r="L129" t="inlineStr">
+        <is>
+          <t>6.6</t>
+        </is>
       </c>
       <c r="M129" t="inlineStr">
         <is>
@@ -43956,29 +44036,45 @@
           <t>GROWTH</t>
         </is>
       </c>
-      <c r="E159" t="n">
-        <v>43.3</v>
-      </c>
-      <c r="F159" t="n">
-        <v>0.141</v>
-      </c>
-      <c r="G159" t="n">
-        <v>6</v>
-      </c>
-      <c r="H159" t="n">
-        <v>2.39</v>
-      </c>
-      <c r="I159" t="n">
-        <v>1</v>
-      </c>
-      <c r="J159" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="K159" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="L159" t="n">
-        <v>9.800000000000001</v>
+      <c r="E159" t="inlineStr">
+        <is>
+          <t>43.3</t>
+        </is>
+      </c>
+      <c r="F159" t="inlineStr">
+        <is>
+          <t>0.141</t>
+        </is>
+      </c>
+      <c r="G159" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H159" t="inlineStr">
+        <is>
+          <t>2.39</t>
+        </is>
+      </c>
+      <c r="I159" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="J159" t="inlineStr">
+        <is>
+          <t>5.8</t>
+        </is>
+      </c>
+      <c r="K159" t="inlineStr">
+        <is>
+          <t>1.6</t>
+        </is>
+      </c>
+      <c r="L159" t="inlineStr">
+        <is>
+          <t>9.8</t>
+        </is>
       </c>
       <c r="M159" t="inlineStr">
         <is>
@@ -45955,29 +46051,45 @@
           <t>NEW-IPO</t>
         </is>
       </c>
-      <c r="E186" t="n">
-        <v>30.7</v>
-      </c>
-      <c r="F186" t="n">
-        <v>0.068</v>
-      </c>
-      <c r="G186" t="n">
-        <v>4</v>
-      </c>
-      <c r="H186" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="I186" t="n">
-        <v>12.9</v>
-      </c>
-      <c r="J186" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="K186" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="L186" t="n">
-        <v>0.6</v>
+      <c r="E186" t="inlineStr">
+        <is>
+          <t>30.7</t>
+        </is>
+      </c>
+      <c r="F186" t="inlineStr">
+        <is>
+          <t>0.068</t>
+        </is>
+      </c>
+      <c r="G186" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="H186" t="inlineStr">
+        <is>
+          <t>1.61</t>
+        </is>
+      </c>
+      <c r="I186" t="inlineStr">
+        <is>
+          <t>12.9</t>
+        </is>
+      </c>
+      <c r="J186" t="inlineStr">
+        <is>
+          <t>0.1</t>
+        </is>
+      </c>
+      <c r="K186" t="inlineStr">
+        <is>
+          <t>1.71</t>
+        </is>
+      </c>
+      <c r="L186" t="inlineStr">
+        <is>
+          <t>0.6</t>
+        </is>
       </c>
       <c r="M186" t="inlineStr">
         <is>
@@ -52817,8 +52929,10 @@
           <t>CORE</t>
         </is>
       </c>
-      <c r="L77" t="n">
-        <v>53.1</v>
+      <c r="L77" t="inlineStr">
+        <is>
+          <t>53.1</t>
+        </is>
       </c>
     </row>
     <row r="78">
@@ -52869,8 +52983,10 @@
           <t>DECLINING</t>
         </is>
       </c>
-      <c r="L78" t="n">
-        <v>65.7</v>
+      <c r="L78" t="inlineStr">
+        <is>
+          <t>65.7</t>
+        </is>
       </c>
     </row>
     <row r="79">
@@ -52921,8 +53037,10 @@
           <t>LEVERAGED</t>
         </is>
       </c>
-      <c r="L79" t="n">
-        <v>65.8</v>
+      <c r="L79" t="inlineStr">
+        <is>
+          <t>65.8</t>
+        </is>
       </c>
     </row>
     <row r="80">
@@ -52973,8 +53091,10 @@
           <t>GROWTH</t>
         </is>
       </c>
-      <c r="L80" t="n">
-        <v>43.3</v>
+      <c r="L80" t="inlineStr">
+        <is>
+          <t>43.3</t>
+        </is>
       </c>
     </row>
     <row r="81">
@@ -53025,8 +53145,10 @@
           <t>LEVERAGED</t>
         </is>
       </c>
-      <c r="L81" t="n">
-        <v>66.09999999999999</v>
+      <c r="L81" t="inlineStr">
+        <is>
+          <t>66.1</t>
+        </is>
       </c>
     </row>
     <row r="82">
@@ -53185,8 +53307,10 @@
           <t>NEW-IPO</t>
         </is>
       </c>
-      <c r="L84" t="n">
-        <v>30.7</v>
+      <c r="L84" t="inlineStr">
+        <is>
+          <t>30.7</t>
+        </is>
       </c>
     </row>
     <row r="85">
@@ -53237,8 +53361,10 @@
           <t>CORE</t>
         </is>
       </c>
-      <c r="L85" t="n">
-        <v>91.40000000000001</v>
+      <c r="L85" t="inlineStr">
+        <is>
+          <t>91.4</t>
+        </is>
       </c>
     </row>
     <row r="86">

--- a/STS_holy_grail.xlsx
+++ b/STS_holy_grail.xlsx
@@ -1262,7 +1262,7 @@
         <v>21.6</v>
       </c>
       <c r="L4" t="n">
-        <v>-2.57</v>
+        <v>-2.54</v>
       </c>
       <c r="M4" t="n">
         <v>-3.7</v>
@@ -1316,7 +1316,7 @@
         <v>0.97</v>
       </c>
       <c r="AD4" t="n">
-        <v>-2.57</v>
+        <v>-2.54</v>
       </c>
       <c r="AE4" t="n">
         <v>1.51</v>
@@ -1694,7 +1694,7 @@
         <v>-4</v>
       </c>
       <c r="L8" t="n">
-        <v>-4.82</v>
+        <v>-4.83</v>
       </c>
       <c r="M8" t="n">
         <v>-12.9</v>
@@ -1743,7 +1743,7 @@
         <v>-4.67</v>
       </c>
       <c r="AD8" t="n">
-        <v>-4.82</v>
+        <v>-4.83</v>
       </c>
       <c r="AE8" t="n">
         <v>4.59</v>
@@ -2467,10 +2467,10 @@
         </is>
       </c>
       <c r="T15" t="n">
-        <v>0.57</v>
+        <v>0.59</v>
       </c>
       <c r="U15" t="n">
-        <v>0.57</v>
+        <v>0.59</v>
       </c>
       <c r="X15" t="n">
         <v>30.76</v>
@@ -2494,7 +2494,7 @@
         <v>-6.45</v>
       </c>
       <c r="AE15" t="n">
-        <v>0.57</v>
+        <v>0.59</v>
       </c>
       <c r="AF15" t="n">
         <v>6</v>
@@ -2872,7 +2872,7 @@
         <v>-13.6</v>
       </c>
       <c r="L19" t="n">
-        <v>-3.74</v>
+        <v>-3.73</v>
       </c>
       <c r="M19" t="n">
         <v>-23</v>
@@ -2921,7 +2921,7 @@
         <v>-3.33</v>
       </c>
       <c r="AD19" t="n">
-        <v>-3.74</v>
+        <v>-3.73</v>
       </c>
       <c r="AE19" t="n">
         <v>1.72</v>
@@ -5218,7 +5218,7 @@
         <v>4.79</v>
       </c>
       <c r="U40" t="n">
-        <v>8.050000000000001</v>
+        <v>8.09</v>
       </c>
       <c r="V40" t="n">
         <v>-5.89</v>
@@ -5245,7 +5245,7 @@
         <v>-5.89</v>
       </c>
       <c r="AE40" t="n">
-        <v>8.050000000000001</v>
+        <v>8.09</v>
       </c>
       <c r="AF40" t="n">
         <v>13</v>
@@ -6116,7 +6116,7 @@
         <v>-24.14</v>
       </c>
       <c r="L48" t="n">
-        <v>-28.91</v>
+        <v>-28.87</v>
       </c>
       <c r="M48" t="n">
         <v>-0.6</v>
@@ -6170,7 +6170,7 @@
         <v>-27.97</v>
       </c>
       <c r="AD48" t="n">
-        <v>-28.91</v>
+        <v>-28.87</v>
       </c>
       <c r="AE48" t="n">
         <v>0.9</v>
@@ -9316,13 +9316,13 @@
         <v>17.29</v>
       </c>
       <c r="AA75" t="n">
-        <v>13.45</v>
+        <v>13.46</v>
       </c>
       <c r="AB75" t="n">
-        <v>13.45</v>
+        <v>13.46</v>
       </c>
       <c r="AC75" t="n">
-        <v>-22.18</v>
+        <v>-22.15</v>
       </c>
       <c r="AD75" t="n">
         <v>-25.97</v>
@@ -9340,7 +9340,7 @@
         <v>1.11</v>
       </c>
       <c r="AL75" t="n">
-        <v>-23.29</v>
+        <v>-23.26</v>
       </c>
       <c r="AM75" t="inlineStr">
         <is>
@@ -11154,7 +11154,7 @@
         <v>3.9</v>
       </c>
       <c r="I91" t="n">
-        <v>-1.2</v>
+        <v>-1.1</v>
       </c>
       <c r="J91" t="n">
         <v>3.16</v>
@@ -11208,10 +11208,10 @@
         <v>80.14</v>
       </c>
       <c r="AA91" t="n">
-        <v>71.14</v>
+        <v>71.15000000000001</v>
       </c>
       <c r="AB91" t="n">
-        <v>71.14</v>
+        <v>71.15000000000001</v>
       </c>
       <c r="AC91" t="n">
         <v>-11.22</v>
@@ -11232,7 +11232,7 @@
         <v>0.95</v>
       </c>
       <c r="AL91" t="n">
-        <v>-12.18</v>
+        <v>-12.17</v>
       </c>
     </row>
     <row r="92">
@@ -16850,7 +16850,7 @@
         <v>-20.5</v>
       </c>
       <c r="I139" t="n">
-        <v>-1.2</v>
+        <v>-1.1</v>
       </c>
       <c r="J139" t="n">
         <v>2.8</v>
@@ -16905,13 +16905,13 @@
         <v>72.19</v>
       </c>
       <c r="AA139" t="n">
-        <v>71.14</v>
+        <v>71.15000000000001</v>
       </c>
       <c r="AB139" t="n">
-        <v>71.14</v>
+        <v>71.15000000000001</v>
       </c>
       <c r="AC139" t="n">
-        <v>-1.45</v>
+        <v>-1.44</v>
       </c>
       <c r="AD139" t="n">
         <v>-2.88</v>
@@ -16929,7 +16929,7 @@
         <v>4.5</v>
       </c>
       <c r="AL139" t="n">
-        <v>-5.95</v>
+        <v>-5.94</v>
       </c>
     </row>
     <row r="140">
@@ -18332,10 +18332,10 @@
         <v>193.01</v>
       </c>
       <c r="AA151" t="n">
-        <v>261.93</v>
+        <v>261.94</v>
       </c>
       <c r="AB151" t="n">
-        <v>261.93</v>
+        <v>261.94</v>
       </c>
       <c r="AC151" t="n">
         <v>35.71</v>
@@ -18356,7 +18356,7 @@
         <v>3.51</v>
       </c>
       <c r="AL151" t="n">
-        <v>32.2</v>
+        <v>32.21</v>
       </c>
       <c r="AM151" t="inlineStr">
         <is>
@@ -21294,7 +21294,7 @@
         <v>-17.98</v>
       </c>
       <c r="AE176" t="n">
-        <v>23.59</v>
+        <v>23.6</v>
       </c>
       <c r="AF176" t="n">
         <v>49</v>
@@ -22009,7 +22009,7 @@
         <v>-13.38</v>
       </c>
       <c r="AD182" t="n">
-        <v>-14.51</v>
+        <v>-14.47</v>
       </c>
       <c r="AE182" t="n">
         <v>21.7</v>
@@ -26814,13 +26814,13 @@
         <v>15.13</v>
       </c>
       <c r="AA223" t="n">
-        <v>13.45</v>
+        <v>13.46</v>
       </c>
       <c r="AB223" t="n">
-        <v>13.45</v>
+        <v>13.46</v>
       </c>
       <c r="AC223" t="n">
-        <v>-11.07</v>
+        <v>-11.04</v>
       </c>
       <c r="AD223" t="n">
         <v>-15.4</v>
@@ -26838,7 +26838,7 @@
         <v>3.51</v>
       </c>
       <c r="AL223" t="n">
-        <v>-14.58</v>
+        <v>-14.55</v>
       </c>
       <c r="AM223" t="inlineStr">
         <is>
@@ -31503,7 +31503,7 @@
         <v>-29.66</v>
       </c>
       <c r="AD263" t="n">
-        <v>-30.32</v>
+        <v>-30.31</v>
       </c>
       <c r="AE263" t="n">
         <v>1.81</v>
@@ -32417,7 +32417,7 @@
       </c>
       <c r="B275" t="inlineStr">
         <is>
-          <t>$46,153.86  (+3.80% price-weighted)</t>
+          <t>$46,153.91  (+3.80% price-weighted)</t>
         </is>
       </c>
     </row>
@@ -32441,7 +32441,7 @@
       </c>
       <c r="B277" t="inlineStr">
         <is>
-          <t>-0.30%</t>
+          <t>-0.29%</t>
         </is>
       </c>
     </row>
@@ -32699,7 +32699,7 @@
         <v>127</v>
       </c>
       <c r="C291" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="D291" t="n">
         <v>43.31</v>
@@ -32946,7 +32946,7 @@
         <v>12</v>
       </c>
       <c r="C303" t="n">
-        <v>-6.52</v>
+        <v>-6.51</v>
       </c>
       <c r="D303" t="n">
         <v>41.67</v>
@@ -33595,7 +33595,7 @@
         <v>46.6</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.3</v>
+        <v>-0.29</v>
       </c>
       <c r="H7" t="n">
         <v>-12.75</v>
@@ -42358,29 +42358,45 @@
           <t>GROWTH</t>
         </is>
       </c>
-      <c r="E119" t="n">
-        <v>55.4</v>
-      </c>
-      <c r="F119" t="n">
-        <v>0.252</v>
-      </c>
-      <c r="G119" t="n">
-        <v>7</v>
-      </c>
-      <c r="H119" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="I119" t="n">
-        <v>11.8</v>
-      </c>
-      <c r="J119" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="K119" t="n">
-        <v>3.16</v>
-      </c>
-      <c r="L119" t="n">
-        <v>43.1</v>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>55.4</t>
+        </is>
+      </c>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>0.252</t>
+        </is>
+      </c>
+      <c r="G119" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="H119" t="inlineStr">
+        <is>
+          <t>1.26</t>
+        </is>
+      </c>
+      <c r="I119" t="inlineStr">
+        <is>
+          <t>11.8</t>
+        </is>
+      </c>
+      <c r="J119" t="inlineStr">
+        <is>
+          <t>3.7</t>
+        </is>
+      </c>
+      <c r="K119" t="inlineStr">
+        <is>
+          <t>3.16</t>
+        </is>
+      </c>
+      <c r="L119" t="inlineStr">
+        <is>
+          <t>43.1</t>
+        </is>
       </c>
       <c r="M119" t="inlineStr">
         <is>
@@ -42792,45 +42808,29 @@
           <t>LEVERAGED</t>
         </is>
       </c>
-      <c r="E125" t="inlineStr">
-        <is>
-          <t>53.7</t>
-        </is>
-      </c>
-      <c r="F125" t="inlineStr">
-        <is>
-          <t>0.273</t>
-        </is>
-      </c>
-      <c r="G125" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="H125" t="inlineStr">
-        <is>
-          <t>1.7</t>
-        </is>
-      </c>
-      <c r="I125" t="inlineStr">
-        <is>
-          <t>10.3</t>
-        </is>
-      </c>
-      <c r="J125" t="inlineStr">
-        <is>
-          <t>5.8</t>
-        </is>
-      </c>
-      <c r="K125" t="inlineStr">
-        <is>
-          <t>-31.45</t>
-        </is>
-      </c>
-      <c r="L125" t="inlineStr">
-        <is>
-          <t>6.6</t>
-        </is>
+      <c r="E125" t="n">
+        <v>53.6</v>
+      </c>
+      <c r="F125" t="n">
+        <v>0.273</v>
+      </c>
+      <c r="G125" t="n">
+        <v>5</v>
+      </c>
+      <c r="H125" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="I125" t="n">
+        <v>9.9</v>
+      </c>
+      <c r="J125" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="K125" t="n">
+        <v>-31.45</v>
+      </c>
+      <c r="L125" t="n">
+        <v>6.6</v>
       </c>
       <c r="M125" t="inlineStr">
         <is>
@@ -42844,7 +42844,7 @@
       </c>
       <c r="O125" t="inlineStr">
         <is>
-          <t>Altman-Z 1.70 in distress zone (&lt;1.81)</t>
+          <t>Altman-Z 1.72 in distress zone (&lt;1.81)</t>
         </is>
       </c>
     </row>
@@ -50352,8 +50352,10 @@
           <t>GROWTH</t>
         </is>
       </c>
-      <c r="L2" t="n">
-        <v>55.4</v>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>55.4</t>
+        </is>
       </c>
     </row>
     <row r="3">
@@ -53714,10 +53716,8 @@
           <t>LEVERAGED</t>
         </is>
       </c>
-      <c r="L60" t="inlineStr">
-        <is>
-          <t>53.7</t>
-        </is>
+      <c r="L60" t="n">
+        <v>53.6</v>
       </c>
     </row>
     <row r="61">

--- a/STS_holy_grail.xlsx
+++ b/STS_holy_grail.xlsx
@@ -37885,45 +37885,29 @@
           <t>CORE</t>
         </is>
       </c>
-      <c r="E58" t="inlineStr">
-        <is>
-          <t>73.1</t>
-        </is>
-      </c>
-      <c r="F58" t="inlineStr">
-        <is>
-          <t>0.253</t>
-        </is>
-      </c>
-      <c r="G58" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="H58" t="inlineStr">
-        <is>
-          <t>12.76</t>
-        </is>
-      </c>
-      <c r="I58" t="inlineStr">
-        <is>
-          <t>1.5</t>
-        </is>
-      </c>
-      <c r="J58" t="inlineStr">
-        <is>
-          <t>8.1</t>
-        </is>
-      </c>
-      <c r="K58" t="inlineStr">
-        <is>
-          <t>0.8</t>
-        </is>
-      </c>
-      <c r="L58" t="inlineStr">
-        <is>
-          <t>40.8</t>
-        </is>
+      <c r="E58" t="n">
+        <v>73.2</v>
+      </c>
+      <c r="F58" t="n">
+        <v>0.253</v>
+      </c>
+      <c r="G58" t="n">
+        <v>8</v>
+      </c>
+      <c r="H58" t="n">
+        <v>12.3</v>
+      </c>
+      <c r="I58" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="J58" t="n">
+        <v>8.1</v>
+      </c>
+      <c r="K58" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="L58" t="n">
+        <v>40.8</v>
       </c>
       <c r="M58" t="inlineStr">
         <is>
@@ -39335,7 +39319,7 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>GTLB</t>
+          <t>DASH</t>
         </is>
       </c>
       <c r="B78" s="15" t="inlineStr">
@@ -39353,54 +39337,38 @@
           <t>GROWTH</t>
         </is>
       </c>
-      <c r="E78" t="inlineStr">
-        <is>
-          <t>66.4</t>
-        </is>
-      </c>
-      <c r="F78" t="inlineStr">
-        <is>
-          <t>0.484</t>
-        </is>
-      </c>
-      <c r="G78" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="H78" t="inlineStr">
-        <is>
-          <t>7.26</t>
-        </is>
-      </c>
-      <c r="I78" t="inlineStr">
-        <is>
-          <t>2.7</t>
-        </is>
-      </c>
-      <c r="J78" t="inlineStr">
-        <is>
-          <t>-1.5</t>
-        </is>
-      </c>
-      <c r="K78" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="L78" t="inlineStr">
-        <is>
-          <t>-7.4</t>
-        </is>
+      <c r="E78" t="n">
+        <v>66.40000000000001</v>
+      </c>
+      <c r="F78" t="n">
+        <v>0.355</v>
+      </c>
+      <c r="G78" t="n">
+        <v>5</v>
+      </c>
+      <c r="H78" t="n">
+        <v>5.89</v>
+      </c>
+      <c r="I78" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="J78" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="K78" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="L78" t="n">
+        <v>5.3</v>
       </c>
       <c r="M78" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Consumer Cyclical</t>
         </is>
       </c>
       <c r="N78" t="inlineStr">
         <is>
-          <t>rev +26%/yr, not yet FCF-safe</t>
+          <t>rev +28%/yr, profitable</t>
         </is>
       </c>
       <c r="O78" t="inlineStr"/>
@@ -39408,84 +39376,80 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>ETSY</t>
-        </is>
-      </c>
-      <c r="B79" s="14" t="inlineStr">
-        <is>
-          <t>FAIL</t>
+          <t>GTLB</t>
+        </is>
+      </c>
+      <c r="B79" s="15" t="inlineStr">
+        <is>
+          <t>PASS</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>FAIL/LEV</t>
+          <t>PASS/GS</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>LEVERAGED</t>
+          <t>GROWTH</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>66.1</t>
+          <t>66.4</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>0.731</t>
+          <t>0.484</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>1.41</t>
+          <t>7.26</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>9.6</t>
+          <t>2.7</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t>14.3</t>
+          <t>-1.5</t>
         </is>
       </c>
       <c r="K79" t="inlineStr">
         <is>
-          <t>-2.8</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="L79" t="inlineStr">
         <is>
-          <t>12.8</t>
+          <t>-7.4</t>
         </is>
       </c>
       <c r="M79" t="inlineStr">
         <is>
-          <t>Consumer Cyclical</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="N79" t="inlineStr">
         <is>
-          <t>distress/leverage flag</t>
-        </is>
-      </c>
-      <c r="O79" t="inlineStr">
-        <is>
-          <t>Altman-Z 1.41 in distress zone (&lt;1.81)</t>
-        </is>
-      </c>
+          <t>rev +26%/yr, not yet FCF-safe</t>
+        </is>
+      </c>
+      <c r="O79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>PLNT</t>
+          <t>ETSY</t>
         </is>
       </c>
       <c r="B80" s="14" t="inlineStr">
@@ -39505,42 +39469,42 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>65.8</t>
+          <t>66.1</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>0.222</t>
+          <t>0.731</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>5</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>1.13</t>
+          <t>1.41</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>6.8</t>
+          <t>9.6</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t>3.9</t>
+          <t>14.3</t>
         </is>
       </c>
       <c r="K80" t="inlineStr">
         <is>
-          <t>-6.01</t>
+          <t>-2.8</t>
         </is>
       </c>
       <c r="L80" t="inlineStr">
         <is>
-          <t>29.8</t>
+          <t>12.8</t>
         </is>
       </c>
       <c r="M80" t="inlineStr">
@@ -39555,87 +39519,91 @@
       </c>
       <c r="O80" t="inlineStr">
         <is>
-          <t>Altman-Z 1.13 in distress zone (&lt;1.81)</t>
+          <t>Altman-Z 1.41 in distress zone (&lt;1.81)</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>COO</t>
-        </is>
-      </c>
-      <c r="B81" s="15" t="inlineStr">
-        <is>
-          <t>PASS</t>
+          <t>PLNT</t>
+        </is>
+      </c>
+      <c r="B81" s="14" t="inlineStr">
+        <is>
+          <t>FAIL</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>FAIL/LEV</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>CORE</t>
+          <t>LEVERAGED</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>65.7</t>
+          <t>65.8</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>0.216</t>
+          <t>0.222</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>2.95</t>
+          <t>1.13</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>4.2</t>
+          <t>6.8</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t>6.7</t>
+          <t>3.9</t>
         </is>
       </c>
       <c r="K81" t="inlineStr">
         <is>
-          <t>0.3</t>
+          <t>-6.01</t>
         </is>
       </c>
       <c r="L81" t="inlineStr">
         <is>
-          <t>16.7</t>
+          <t>29.8</t>
         </is>
       </c>
       <c r="M81" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>Consumer Cyclical</t>
         </is>
       </c>
       <c r="N81" t="inlineStr">
         <is>
-          <t>mature / stable</t>
-        </is>
-      </c>
-      <c r="O81" t="inlineStr"/>
+          <t>distress/leverage flag</t>
+        </is>
+      </c>
+      <c r="O81" t="inlineStr">
+        <is>
+          <t>Altman-Z 1.13 in distress zone (&lt;1.81)</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>DELL</t>
+          <t>COO</t>
         </is>
       </c>
       <c r="B82" s="15" t="inlineStr">
@@ -39660,42 +39628,42 @@
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>0.224</t>
+          <t>0.216</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>3.41</t>
+          <t>2.95</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>2.4</t>
+          <t>4.2</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>5.7</t>
+          <t>6.7</t>
         </is>
       </c>
       <c r="K82" t="inlineStr">
         <is>
-          <t>-12.75</t>
+          <t>0.3</t>
         </is>
       </c>
       <c r="L82" t="inlineStr">
         <is>
-          <t>7.4</t>
+          <t>16.7</t>
         </is>
       </c>
       <c r="M82" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Healthcare</t>
         </is>
       </c>
       <c r="N82" t="inlineStr">
@@ -39708,7 +39676,7 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>PSX</t>
+          <t>DELL</t>
         </is>
       </c>
       <c r="B83" s="15" t="inlineStr">
@@ -39718,12 +39686,12 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>PASS/DECL</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>DECLINING</t>
+          <t>CORE</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
@@ -39733,7 +39701,7 @@
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>0.177</t>
+          <t>0.224</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
@@ -39743,37 +39711,37 @@
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>4.29</t>
+          <t>3.41</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>2.5</t>
+          <t>2.4</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>5.7</t>
         </is>
       </c>
       <c r="K83" t="inlineStr">
         <is>
-          <t>0.68</t>
+          <t>-12.75</t>
         </is>
       </c>
       <c r="L83" t="inlineStr">
         <is>
-          <t>2.6</t>
+          <t>7.4</t>
         </is>
       </c>
       <c r="M83" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="N83" t="inlineStr">
         <is>
-          <t>revenue -8% YoY</t>
+          <t>mature / stable</t>
         </is>
       </c>
       <c r="O83" t="inlineStr"/>
@@ -39781,7 +39749,7 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>VRT</t>
+          <t>PSX</t>
         </is>
       </c>
       <c r="B84" s="15" t="inlineStr">
@@ -39791,12 +39759,12 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>PASS/GS</t>
+          <t>PASS/DECL</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>GROWTH</t>
+          <t>DECLINING</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
@@ -39806,47 +39774,47 @@
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>0.304</t>
+          <t>0.177</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>8.63</t>
+          <t>4.29</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>2.5</t>
         </is>
       </c>
       <c r="J84" t="inlineStr">
         <is>
-          <t>21.2</t>
+          <t>6.0</t>
         </is>
       </c>
       <c r="K84" t="inlineStr">
         <is>
-          <t>0.82</t>
+          <t>0.68</t>
         </is>
       </c>
       <c r="L84" t="inlineStr">
         <is>
-          <t>18.5</t>
+          <t>2.6</t>
         </is>
       </c>
       <c r="M84" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="N84" t="inlineStr">
         <is>
-          <t>rev +28%/yr, profitable</t>
+          <t>revenue -8% YoY</t>
         </is>
       </c>
       <c r="O84" t="inlineStr"/>
@@ -39854,7 +39822,7 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>DASH</t>
+          <t>VRT</t>
         </is>
       </c>
       <c r="B85" s="15" t="inlineStr">
@@ -39874,12 +39842,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>65.5</t>
+          <t>65.7</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>0.355</t>
+          <t>0.304</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
@@ -39889,32 +39857,32 @@
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>6.97</t>
+          <t>8.63</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>1.8</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="J85" t="inlineStr">
         <is>
-          <t>3.4</t>
+          <t>21.2</t>
         </is>
       </c>
       <c r="K85" t="inlineStr">
         <is>
-          <t>0.33</t>
+          <t>0.82</t>
         </is>
       </c>
       <c r="L85" t="inlineStr">
         <is>
-          <t>5.3</t>
+          <t>18.5</t>
         </is>
       </c>
       <c r="M85" t="inlineStr">
         <is>
-          <t>Consumer Cyclical</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="N85" t="inlineStr">
@@ -42808,29 +42776,45 @@
           <t>LEVERAGED</t>
         </is>
       </c>
-      <c r="E125" t="n">
-        <v>53.6</v>
-      </c>
-      <c r="F125" t="n">
-        <v>0.273</v>
-      </c>
-      <c r="G125" t="n">
-        <v>5</v>
-      </c>
-      <c r="H125" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="I125" t="n">
-        <v>9.9</v>
-      </c>
-      <c r="J125" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="K125" t="n">
-        <v>-31.45</v>
-      </c>
-      <c r="L125" t="n">
-        <v>6.6</v>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>53.6</t>
+        </is>
+      </c>
+      <c r="F125" t="inlineStr">
+        <is>
+          <t>0.273</t>
+        </is>
+      </c>
+      <c r="G125" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="H125" t="inlineStr">
+        <is>
+          <t>1.72</t>
+        </is>
+      </c>
+      <c r="I125" t="inlineStr">
+        <is>
+          <t>9.9</t>
+        </is>
+      </c>
+      <c r="J125" t="inlineStr">
+        <is>
+          <t>5.8</t>
+        </is>
+      </c>
+      <c r="K125" t="inlineStr">
+        <is>
+          <t>-31.45</t>
+        </is>
+      </c>
+      <c r="L125" t="inlineStr">
+        <is>
+          <t>6.6</t>
+        </is>
       </c>
       <c r="M125" t="inlineStr">
         <is>
@@ -44901,45 +44885,29 @@
           <t>LEVERAGED</t>
         </is>
       </c>
-      <c r="E154" t="inlineStr">
-        <is>
-          <t>45.4</t>
-        </is>
-      </c>
-      <c r="F154" t="inlineStr">
-        <is>
-          <t>0.29</t>
-        </is>
-      </c>
-      <c r="G154" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="H154" t="inlineStr">
-        <is>
-          <t>0.01</t>
-        </is>
-      </c>
-      <c r="I154" t="inlineStr">
-        <is>
-          <t>16.9</t>
-        </is>
-      </c>
-      <c r="J154" t="inlineStr">
-        <is>
-          <t>-1.6</t>
-        </is>
-      </c>
-      <c r="K154" t="inlineStr">
-        <is>
-          <t>0.39</t>
-        </is>
-      </c>
-      <c r="L154" t="inlineStr">
-        <is>
-          <t>-3.0</t>
-        </is>
+      <c r="E154" t="n">
+        <v>45.4</v>
+      </c>
+      <c r="F154" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="G154" t="n">
+        <v>4</v>
+      </c>
+      <c r="H154" t="n">
+        <v>-0.09</v>
+      </c>
+      <c r="I154" t="n">
+        <v>19.8</v>
+      </c>
+      <c r="J154" t="n">
+        <v>-1.6</v>
+      </c>
+      <c r="K154" t="n">
+        <v>0.39</v>
+      </c>
+      <c r="L154" t="n">
+        <v>-3</v>
       </c>
       <c r="M154" t="inlineStr">
         <is>
@@ -44953,7 +44921,7 @@
       </c>
       <c r="O154" t="inlineStr">
         <is>
-          <t>Altman-Z 0.01 in distress zone (&lt;1.81)</t>
+          <t>Altman-Z -0.09 in distress zone (&lt;1.81)</t>
         </is>
       </c>
     </row>
@@ -46675,7 +46643,7 @@
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>SNPS</t>
+          <t>OXY</t>
         </is>
       </c>
       <c r="B178" s="14" t="inlineStr">
@@ -46685,70 +46653,74 @@
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>FAIL/LEV</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>CORE</t>
+          <t>LEVERAGED</t>
         </is>
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>33.7</t>
+          <t>33.5</t>
         </is>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>0.113</t>
+          <t>0.09</t>
         </is>
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="H178" t="inlineStr">
         <is>
-          <t>3.25</t>
+          <t>1.52</t>
         </is>
       </c>
       <c r="I178" t="inlineStr">
         <is>
-          <t>1.6</t>
+          <t>7.0</t>
         </is>
       </c>
       <c r="J178" t="inlineStr">
         <is>
-          <t>4.1</t>
+          <t>3.8</t>
         </is>
       </c>
       <c r="K178" t="inlineStr">
         <is>
-          <t>0.5</t>
+          <t>0.65</t>
         </is>
       </c>
       <c r="L178" t="inlineStr">
         <is>
-          <t>13.0</t>
+          <t>17.2</t>
         </is>
       </c>
       <c r="M178" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="N178" t="inlineStr">
         <is>
-          <t>mature / stable</t>
-        </is>
-      </c>
-      <c r="O178" t="inlineStr"/>
+          <t>distress/leverage flag</t>
+        </is>
+      </c>
+      <c r="O178" t="inlineStr">
+        <is>
+          <t>Altman-Z 1.52 in distress zone (&lt;1.81)</t>
+        </is>
+      </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>OXY</t>
+          <t>SNPS</t>
         </is>
       </c>
       <c r="B179" s="14" t="inlineStr">
@@ -46758,69 +46730,49 @@
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>FAIL/LEV</t>
+          <t>FAIL</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>LEVERAGED</t>
-        </is>
-      </c>
-      <c r="E179" t="inlineStr">
-        <is>
-          <t>33.5</t>
-        </is>
-      </c>
-      <c r="F179" t="inlineStr">
-        <is>
-          <t>0.09</t>
-        </is>
-      </c>
-      <c r="G179" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="H179" t="inlineStr">
-        <is>
-          <t>1.52</t>
-        </is>
-      </c>
-      <c r="I179" t="inlineStr">
-        <is>
-          <t>7.0</t>
-        </is>
-      </c>
-      <c r="J179" t="inlineStr">
-        <is>
-          <t>3.8</t>
-        </is>
-      </c>
-      <c r="K179" t="inlineStr">
-        <is>
-          <t>0.65</t>
-        </is>
-      </c>
-      <c r="L179" t="inlineStr">
-        <is>
-          <t>17.2</t>
-        </is>
+          <t>CORE</t>
+        </is>
+      </c>
+      <c r="E179" t="n">
+        <v>33.5</v>
+      </c>
+      <c r="F179" t="n">
+        <v>0.113</v>
+      </c>
+      <c r="G179" t="n">
+        <v>3</v>
+      </c>
+      <c r="H179" t="n">
+        <v>3.09</v>
+      </c>
+      <c r="I179" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="J179" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="K179" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="L179" t="n">
+        <v>13</v>
       </c>
       <c r="M179" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="N179" t="inlineStr">
         <is>
-          <t>distress/leverage flag</t>
-        </is>
-      </c>
-      <c r="O179" t="inlineStr">
-        <is>
-          <t>Altman-Z 1.52 in distress zone (&lt;1.81)</t>
-        </is>
-      </c>
+          <t>mature / stable</t>
+        </is>
+      </c>
+      <c r="O179" t="inlineStr"/>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
@@ -48021,7 +47973,7 @@
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>VST</t>
+          <t>KKR</t>
         </is>
       </c>
       <c r="B196" s="14" t="inlineStr">
@@ -48031,74 +47983,54 @@
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>FAIL/LEV</t>
+          <t>FAIL/DECL</t>
         </is>
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>LEVERAGED</t>
-        </is>
-      </c>
-      <c r="E196" t="inlineStr">
-        <is>
-          <t>27.9</t>
-        </is>
-      </c>
-      <c r="F196" t="inlineStr">
-        <is>
-          <t>0.14</t>
-        </is>
-      </c>
-      <c r="G196" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="H196" t="inlineStr">
-        <is>
-          <t>1.34</t>
-        </is>
-      </c>
-      <c r="I196" t="inlineStr">
-        <is>
-          <t>2.6</t>
-        </is>
-      </c>
-      <c r="J196" t="inlineStr">
-        <is>
-          <t>2.1</t>
-        </is>
-      </c>
-      <c r="K196" t="inlineStr">
-        <is>
-          <t>3.94</t>
-        </is>
-      </c>
-      <c r="L196" t="inlineStr">
-        <is>
-          <t>12.0</t>
-        </is>
+          <t>DECLINING</t>
+        </is>
+      </c>
+      <c r="E196" t="n">
+        <v>28</v>
+      </c>
+      <c r="F196" t="n">
+        <v>0.008</v>
+      </c>
+      <c r="G196" t="n">
+        <v>5</v>
+      </c>
+      <c r="H196" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="I196" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="J196" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="K196" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="L196" t="n">
+        <v>2.6</v>
       </c>
       <c r="M196" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>Financial Services</t>
         </is>
       </c>
       <c r="N196" t="inlineStr">
         <is>
-          <t>distress/leverage flag</t>
-        </is>
-      </c>
-      <c r="O196" t="inlineStr">
-        <is>
-          <t>Altman-Z 1.34 in distress zone (&lt;1.81)</t>
-        </is>
-      </c>
+          <t>revenue -11% YoY</t>
+        </is>
+      </c>
+      <c r="O196" t="inlineStr"/>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>KKR</t>
+          <t>VST</t>
         </is>
       </c>
       <c r="B197" s="14" t="inlineStr">
@@ -48108,22 +48040,22 @@
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>FAIL/DECL</t>
+          <t>FAIL/LEV</t>
         </is>
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>DECLINING</t>
+          <t>LEVERAGED</t>
         </is>
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>27.8</t>
+          <t>27.9</t>
         </is>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>0.008</t>
+          <t>0.14</t>
         </is>
       </c>
       <c r="G197" t="inlineStr">
@@ -48133,40 +48065,44 @@
       </c>
       <c r="H197" t="inlineStr">
         <is>
-          <t>0.9</t>
+          <t>1.34</t>
         </is>
       </c>
       <c r="I197" t="inlineStr">
         <is>
-          <t>0.3</t>
+          <t>2.6</t>
         </is>
       </c>
       <c r="J197" t="inlineStr">
         <is>
-          <t>3.3</t>
+          <t>2.1</t>
         </is>
       </c>
       <c r="K197" t="inlineStr">
         <is>
-          <t>1.76</t>
+          <t>3.94</t>
         </is>
       </c>
       <c r="L197" t="inlineStr">
         <is>
-          <t>2.6</t>
+          <t>12.0</t>
         </is>
       </c>
       <c r="M197" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Utilities</t>
         </is>
       </c>
       <c r="N197" t="inlineStr">
         <is>
-          <t>revenue -11% YoY</t>
-        </is>
-      </c>
-      <c r="O197" t="inlineStr"/>
+          <t>distress/leverage flag</t>
+        </is>
+      </c>
+      <c r="O197" t="inlineStr">
+        <is>
+          <t>Altman-Z 1.34 in distress zone (&lt;1.81)</t>
+        </is>
+      </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
@@ -52092,10 +52028,8 @@
           <t>GROWTH</t>
         </is>
       </c>
-      <c r="L32" t="inlineStr">
-        <is>
-          <t>65.5</t>
-        </is>
+      <c r="L32" t="n">
+        <v>66.40000000000001</v>
       </c>
     </row>
     <row r="33">
@@ -53600,10 +53534,8 @@
           <t>DECLINING</t>
         </is>
       </c>
-      <c r="L58" t="inlineStr">
-        <is>
-          <t>27.8</t>
-        </is>
+      <c r="L58" t="n">
+        <v>28</v>
       </c>
     </row>
     <row r="59">
@@ -53658,10 +53590,8 @@
           <t>CORE</t>
         </is>
       </c>
-      <c r="L59" t="inlineStr">
-        <is>
-          <t>73.1</t>
-        </is>
+      <c r="L59" t="n">
+        <v>73.2</v>
       </c>
     </row>
     <row r="60">
@@ -53716,8 +53646,10 @@
           <t>LEVERAGED</t>
         </is>
       </c>
-      <c r="L60" t="n">
-        <v>53.6</v>
+      <c r="L60" t="inlineStr">
+        <is>
+          <t>53.6</t>
+        </is>
       </c>
     </row>
     <row r="61">
@@ -55570,10 +55502,8 @@
           <t>LEVERAGED</t>
         </is>
       </c>
-      <c r="L92" t="inlineStr">
-        <is>
-          <t>45.4</t>
-        </is>
+      <c r="L92" t="n">
+        <v>45.4</v>
       </c>
     </row>
     <row r="93">
@@ -58354,10 +58284,8 @@
           <t>GROWTH</t>
         </is>
       </c>
-      <c r="L140" t="inlineStr">
-        <is>
-          <t>65.5</t>
-        </is>
+      <c r="L140" t="n">
+        <v>66.40000000000001</v>
       </c>
     </row>
     <row r="141">
@@ -58412,10 +58340,8 @@
           <t>LEVERAGED</t>
         </is>
       </c>
-      <c r="L141" t="inlineStr">
-        <is>
-          <t>45.4</t>
-        </is>
+      <c r="L141" t="n">
+        <v>45.4</v>
       </c>
     </row>
     <row r="142">
@@ -58470,10 +58396,8 @@
           <t>CORE</t>
         </is>
       </c>
-      <c r="L142" t="inlineStr">
-        <is>
-          <t>33.7</t>
-        </is>
+      <c r="L142" t="n">
+        <v>33.5</v>
       </c>
     </row>
     <row r="143">

--- a/STS_holy_grail.xlsx
+++ b/STS_holy_grail.xlsx
@@ -1099,7 +1099,7 @@
         <v>4.7</v>
       </c>
       <c r="L2" t="n">
-        <v>-0.89</v>
+        <v>-0.92</v>
       </c>
       <c r="M2" t="n">
         <v>-9.5</v>
@@ -1153,7 +1153,7 @@
         <v>4.49</v>
       </c>
       <c r="AD2" t="n">
-        <v>-0.89</v>
+        <v>-0.92</v>
       </c>
       <c r="AE2" t="n">
         <v>4.9</v>
@@ -2071,7 +2071,7 @@
         <v>-12.2</v>
       </c>
       <c r="L11" t="n">
-        <v>-6.7</v>
+        <v>-6.71</v>
       </c>
       <c r="M11" t="n">
         <v>-12.9</v>
@@ -2120,7 +2120,7 @@
         <v>-6.41</v>
       </c>
       <c r="AD11" t="n">
-        <v>-6.7</v>
+        <v>-6.71</v>
       </c>
       <c r="AE11" t="n">
         <v>4.59</v>
@@ -3249,7 +3249,7 @@
         <v>-15.2</v>
       </c>
       <c r="L22" t="n">
-        <v>-5.77</v>
+        <v>-5.79</v>
       </c>
       <c r="M22" t="n">
         <v>-23</v>
@@ -3298,7 +3298,7 @@
         <v>-5.27</v>
       </c>
       <c r="AD22" t="n">
-        <v>-5.77</v>
+        <v>-5.79</v>
       </c>
       <c r="AE22" t="n">
         <v>1.72</v>
@@ -3896,7 +3896,7 @@
         <v>-5.8</v>
       </c>
       <c r="L28" t="n">
-        <v>-2.1</v>
+        <v>-2.13</v>
       </c>
       <c r="M28" t="n">
         <v>6.7</v>
@@ -3948,7 +3948,7 @@
         <v>2.02</v>
       </c>
       <c r="AD28" t="n">
-        <v>-2.1</v>
+        <v>-2.13</v>
       </c>
       <c r="AE28" t="n">
         <v>6.29</v>
@@ -4581,7 +4581,7 @@
         <v>-7.04</v>
       </c>
       <c r="L34" t="n">
-        <v>-9.66</v>
+        <v>-9.67</v>
       </c>
       <c r="M34" t="n">
         <v>-3.9</v>
@@ -4635,7 +4635,7 @@
         <v>-7.04</v>
       </c>
       <c r="AD34" t="n">
-        <v>-9.66</v>
+        <v>-9.67</v>
       </c>
       <c r="AE34" t="n">
         <v>3.73</v>
@@ -7863,7 +7863,7 @@
         <v>-15.15</v>
       </c>
       <c r="AD62" t="n">
-        <v>-16.08</v>
+        <v>-16.09</v>
       </c>
       <c r="AE62" t="n">
         <v>1.66</v>
@@ -9303,7 +9303,7 @@
         <v>-4.07</v>
       </c>
       <c r="AD74" t="n">
-        <v>-6.78</v>
+        <v>-6.79</v>
       </c>
       <c r="AE74" t="n">
         <v>7.04</v>
@@ -29619,7 +29619,7 @@
         <v>-6.9</v>
       </c>
       <c r="AD246" t="n">
-        <v>-7.04</v>
+        <v>-7.03</v>
       </c>
       <c r="AE246" t="n">
         <v>45.11</v>
@@ -31854,7 +31854,7 @@
         <v>-10.82</v>
       </c>
       <c r="AD265" t="n">
-        <v>-12.02</v>
+        <v>-12</v>
       </c>
       <c r="AE265" t="n">
         <v>18.6</v>
@@ -32445,13 +32445,13 @@
         <v>-14.25</v>
       </c>
       <c r="AE270" t="n">
-        <v>29.93</v>
+        <v>31.82</v>
       </c>
       <c r="AF270" t="n">
         <v>51</v>
       </c>
       <c r="AG270" t="n">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="AJ270" t="n">
         <v>2.55</v>
@@ -33985,7 +33985,7 @@
         <v>23.5</v>
       </c>
       <c r="K5" t="n">
-        <v>17.52</v>
+        <v>17.56</v>
       </c>
       <c r="L5" t="n">
         <v>0</v>
@@ -34065,7 +34065,7 @@
         <v>24.3</v>
       </c>
       <c r="K7" t="n">
-        <v>17.97</v>
+        <v>17.98</v>
       </c>
       <c r="L7" t="n">
         <v>0</v>
@@ -38343,29 +38343,45 @@
           <t>NEW-IPO</t>
         </is>
       </c>
-      <c r="E58" t="n">
-        <v>73.2</v>
-      </c>
-      <c r="F58" t="n">
-        <v>0.292</v>
-      </c>
-      <c r="G58" t="n">
-        <v>7</v>
-      </c>
-      <c r="H58" t="n">
-        <v>12.02</v>
-      </c>
-      <c r="I58" t="n">
-        <v>1</v>
-      </c>
-      <c r="J58" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="K58" t="n">
-        <v>0.86</v>
-      </c>
-      <c r="L58" t="n">
-        <v>34.7</v>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>73.2</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>0.292</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>12.02</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>11.5</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>0.86</t>
+        </is>
+      </c>
+      <c r="L58" t="inlineStr">
+        <is>
+          <t>34.7</t>
+        </is>
       </c>
       <c r="M58" t="inlineStr">
         <is>
@@ -41121,29 +41137,45 @@
           <t>DECLINING</t>
         </is>
       </c>
-      <c r="E96" t="n">
-        <v>61.1</v>
-      </c>
-      <c r="F96" t="n">
-        <v>0.669</v>
-      </c>
-      <c r="G96" t="n">
-        <v>8</v>
-      </c>
-      <c r="H96" t="n">
-        <v>3.47</v>
-      </c>
-      <c r="I96" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="J96" t="n">
-        <v>1</v>
-      </c>
-      <c r="K96" t="n">
-        <v>17.75</v>
-      </c>
-      <c r="L96" t="n">
-        <v>2.2</v>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>61.1</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>0.669</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>3.47</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr">
+        <is>
+          <t>0.8</t>
+        </is>
+      </c>
+      <c r="J96" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="K96" t="inlineStr">
+        <is>
+          <t>17.75</t>
+        </is>
+      </c>
+      <c r="L96" t="inlineStr">
+        <is>
+          <t>2.2</t>
+        </is>
       </c>
       <c r="M96" t="inlineStr">
         <is>
@@ -42638,29 +42670,45 @@
           <t>GROWTH</t>
         </is>
       </c>
-      <c r="E117" t="n">
-        <v>55.6</v>
-      </c>
-      <c r="F117" t="n">
-        <v>0.184</v>
-      </c>
-      <c r="G117" t="n">
-        <v>6</v>
-      </c>
-      <c r="H117" t="n">
-        <v>2.68</v>
-      </c>
-      <c r="I117" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="J117" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="K117" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="L117" t="n">
-        <v>20.4</v>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>55.6</t>
+        </is>
+      </c>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>0.184</t>
+        </is>
+      </c>
+      <c r="G117" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H117" t="inlineStr">
+        <is>
+          <t>2.68</t>
+        </is>
+      </c>
+      <c r="I117" t="inlineStr">
+        <is>
+          <t>4.2</t>
+        </is>
+      </c>
+      <c r="J117" t="inlineStr">
+        <is>
+          <t>2.1</t>
+        </is>
+      </c>
+      <c r="K117" t="inlineStr">
+        <is>
+          <t>1.83</t>
+        </is>
+      </c>
+      <c r="L117" t="inlineStr">
+        <is>
+          <t>20.4</t>
+        </is>
       </c>
       <c r="M117" t="inlineStr">
         <is>
@@ -42841,29 +42889,45 @@
           <t>CORE</t>
         </is>
       </c>
-      <c r="E120" t="n">
-        <v>55.5</v>
-      </c>
-      <c r="F120" t="n">
-        <v>0.158</v>
-      </c>
-      <c r="G120" t="n">
-        <v>6</v>
-      </c>
-      <c r="H120" t="n">
-        <v>2.49</v>
-      </c>
-      <c r="I120" t="n">
-        <v>7</v>
-      </c>
-      <c r="J120" t="n">
-        <v>7</v>
-      </c>
-      <c r="K120" t="n">
-        <v>0.47</v>
-      </c>
-      <c r="L120" t="n">
-        <v>28.3</v>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>55.5</t>
+        </is>
+      </c>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>0.158</t>
+        </is>
+      </c>
+      <c r="G120" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H120" t="inlineStr">
+        <is>
+          <t>2.49</t>
+        </is>
+      </c>
+      <c r="I120" t="inlineStr">
+        <is>
+          <t>7.0</t>
+        </is>
+      </c>
+      <c r="J120" t="inlineStr">
+        <is>
+          <t>7.0</t>
+        </is>
+      </c>
+      <c r="K120" t="inlineStr">
+        <is>
+          <t>0.47</t>
+        </is>
+      </c>
+      <c r="L120" t="inlineStr">
+        <is>
+          <t>28.3</t>
+        </is>
       </c>
       <c r="M120" t="inlineStr">
         <is>
@@ -45461,29 +45525,45 @@
           <t>LEVERAGED</t>
         </is>
       </c>
-      <c r="E156" t="n">
-        <v>45</v>
-      </c>
-      <c r="F156" t="n">
-        <v>0.118</v>
-      </c>
-      <c r="G156" t="n">
-        <v>6</v>
-      </c>
-      <c r="H156" t="n">
-        <v>-0.06</v>
-      </c>
-      <c r="I156" t="n">
-        <v>10.6</v>
-      </c>
-      <c r="J156" t="n">
-        <v>4</v>
-      </c>
-      <c r="K156" t="n">
-        <v>0.96</v>
-      </c>
-      <c r="L156" t="n">
-        <v>16.5</v>
+      <c r="E156" t="inlineStr">
+        <is>
+          <t>45.0</t>
+        </is>
+      </c>
+      <c r="F156" t="inlineStr">
+        <is>
+          <t>0.118</t>
+        </is>
+      </c>
+      <c r="G156" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H156" t="inlineStr">
+        <is>
+          <t>-0.06</t>
+        </is>
+      </c>
+      <c r="I156" t="inlineStr">
+        <is>
+          <t>10.6</t>
+        </is>
+      </c>
+      <c r="J156" t="inlineStr">
+        <is>
+          <t>4.0</t>
+        </is>
+      </c>
+      <c r="K156" t="inlineStr">
+        <is>
+          <t>0.96</t>
+        </is>
+      </c>
+      <c r="L156" t="inlineStr">
+        <is>
+          <t>16.5</t>
+        </is>
       </c>
       <c r="M156" t="inlineStr">
         <is>
@@ -53104,8 +53184,10 @@
           <t>GROWTH</t>
         </is>
       </c>
-      <c r="L40" t="n">
-        <v>55.6</v>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>55.6</t>
+        </is>
       </c>
     </row>
     <row r="41">
@@ -58554,8 +58636,10 @@
           <t>DECLINING</t>
         </is>
       </c>
-      <c r="L134" t="n">
-        <v>61.1</v>
+      <c r="L134" t="inlineStr">
+        <is>
+          <t>61.1</t>
+        </is>
       </c>
     </row>
     <row r="135">
@@ -58610,8 +58694,10 @@
           <t>GROWTH</t>
         </is>
       </c>
-      <c r="L135" t="n">
-        <v>55.6</v>
+      <c r="L135" t="inlineStr">
+        <is>
+          <t>55.6</t>
+        </is>
       </c>
     </row>
     <row r="136">
@@ -58666,8 +58752,10 @@
           <t>CORE</t>
         </is>
       </c>
-      <c r="L136" t="n">
-        <v>55.5</v>
+      <c r="L136" t="inlineStr">
+        <is>
+          <t>55.5</t>
+        </is>
       </c>
     </row>
     <row r="137">
@@ -58722,8 +58810,10 @@
           <t>NEW-IPO</t>
         </is>
       </c>
-      <c r="L137" t="n">
-        <v>73.2</v>
+      <c r="L137" t="inlineStr">
+        <is>
+          <t>73.2</t>
+        </is>
       </c>
     </row>
     <row r="138">
@@ -58778,8 +58868,10 @@
           <t>LEVERAGED</t>
         </is>
       </c>
-      <c r="L138" t="n">
-        <v>45</v>
+      <c r="L138" t="inlineStr">
+        <is>
+          <t>45.0</t>
+        </is>
       </c>
     </row>
     <row r="139">

--- a/STS_holy_grail.xlsx
+++ b/STS_holy_grail.xlsx
@@ -1234,22 +1234,22 @@
         </is>
       </c>
       <c r="T4" t="n">
-        <v>5.28</v>
+        <v>5.29</v>
       </c>
       <c r="U4" t="n">
-        <v>5.28</v>
+        <v>5.29</v>
       </c>
       <c r="V4" t="n">
         <v>-4.16</v>
       </c>
       <c r="X4" t="n">
-        <v>12.39</v>
+        <v>12.38</v>
       </c>
       <c r="Y4" t="n">
         <v>1</v>
       </c>
       <c r="Z4" t="n">
-        <v>12.39</v>
+        <v>12.38</v>
       </c>
       <c r="AA4" t="n">
         <v>11.92</v>
@@ -1264,7 +1264,7 @@
         <v>-4.16</v>
       </c>
       <c r="AE4" t="n">
-        <v>5.28</v>
+        <v>5.29</v>
       </c>
       <c r="AF4" t="n">
         <v>1</v>
@@ -1318,7 +1318,7 @@
         <v>0.4</v>
       </c>
       <c r="L5" t="n">
-        <v>-5.1</v>
+        <v>-5.14</v>
       </c>
       <c r="M5" t="n">
         <v>3.4</v>
@@ -1367,7 +1367,7 @@
         <v>0.95</v>
       </c>
       <c r="AD5" t="n">
-        <v>-5.1</v>
+        <v>-5.14</v>
       </c>
       <c r="AE5" t="n">
         <v>1.76</v>
@@ -1775,10 +1775,10 @@
         </is>
       </c>
       <c r="T9" t="n">
-        <v>6.69</v>
+        <v>6.72</v>
       </c>
       <c r="U9" t="n">
-        <v>6.69</v>
+        <v>6.72</v>
       </c>
       <c r="V9" t="n">
         <v>-5.13</v>
@@ -1805,7 +1805,7 @@
         <v>-5.13</v>
       </c>
       <c r="AE9" t="n">
-        <v>6.69</v>
+        <v>6.72</v>
       </c>
       <c r="AF9" t="n">
         <v>5</v>
@@ -2324,10 +2324,10 @@
         </is>
       </c>
       <c r="T14" t="n">
-        <v>6.41</v>
+        <v>6.42</v>
       </c>
       <c r="U14" t="n">
-        <v>6.41</v>
+        <v>6.42</v>
       </c>
       <c r="V14" t="n">
         <v>-0.24</v>
@@ -2354,7 +2354,7 @@
         <v>-0.24</v>
       </c>
       <c r="AE14" t="n">
-        <v>6.41</v>
+        <v>6.42</v>
       </c>
       <c r="AF14" t="n">
         <v>9</v>
@@ -2408,7 +2408,7 @@
         <v>-12.8</v>
       </c>
       <c r="L15" t="n">
-        <v>-8.66</v>
+        <v>-8.789999999999999</v>
       </c>
       <c r="M15" t="n">
         <v>-12.9</v>
@@ -2457,7 +2457,7 @@
         <v>-8.050000000000001</v>
       </c>
       <c r="AD15" t="n">
-        <v>-8.66</v>
+        <v>-8.789999999999999</v>
       </c>
       <c r="AE15" t="n">
         <v>4.59</v>
@@ -4384,7 +4384,7 @@
         <v>-2.91</v>
       </c>
       <c r="L33" t="n">
-        <v>-5.69</v>
+        <v>-5.71</v>
       </c>
       <c r="M33" t="n">
         <v>-34.1</v>
@@ -4436,7 +4436,7 @@
         <v>-4.65</v>
       </c>
       <c r="AD33" t="n">
-        <v>-5.69</v>
+        <v>-5.71</v>
       </c>
       <c r="AE33" t="n">
         <v>5.22</v>
@@ -6014,7 +6014,7 @@
         <v>4.79</v>
       </c>
       <c r="U47" t="n">
-        <v>14.16</v>
+        <v>14.17</v>
       </c>
       <c r="V47" t="n">
         <v>-5.89</v>
@@ -6044,7 +6044,7 @@
         <v>-5.89</v>
       </c>
       <c r="AE47" t="n">
-        <v>14.16</v>
+        <v>14.17</v>
       </c>
       <c r="AF47" t="n">
         <v>18</v>
@@ -6129,7 +6129,7 @@
         <v>9.52</v>
       </c>
       <c r="U48" t="n">
-        <v>11.16</v>
+        <v>11.19</v>
       </c>
       <c r="V48" t="n">
         <v>-0.79</v>
@@ -6159,7 +6159,7 @@
         <v>-0.79</v>
       </c>
       <c r="AE48" t="n">
-        <v>11.16</v>
+        <v>11.19</v>
       </c>
       <c r="AF48" t="n">
         <v>18</v>
@@ -9528,28 +9528,28 @@
         <v>48</v>
       </c>
       <c r="I77" t="n">
-        <v>-2.9</v>
+        <v>-2.7</v>
       </c>
       <c r="J77" t="n">
-        <v>-7.36</v>
+        <v>-7.6</v>
       </c>
       <c r="K77" t="n">
-        <v>-9.800000000000001</v>
+        <v>-10.04</v>
       </c>
       <c r="L77" t="n">
-        <v>-12.98</v>
+        <v>-13.21</v>
       </c>
       <c r="M77" t="n">
-        <v>15.7</v>
+        <v>16</v>
       </c>
       <c r="N77" t="n">
-        <v>-1.1</v>
+        <v>-0.9</v>
       </c>
       <c r="P77" t="n">
         <v>-20.2</v>
       </c>
       <c r="Q77" t="n">
-        <v>187.03</v>
+        <v>186.54</v>
       </c>
       <c r="R77" t="inlineStr">
         <is>
@@ -9562,10 +9562,10 @@
         </is>
       </c>
       <c r="T77" t="n">
-        <v>2.19</v>
+        <v>1.93</v>
       </c>
       <c r="U77" t="n">
-        <v>2.19</v>
+        <v>1.93</v>
       </c>
       <c r="X77" t="n">
         <v>216.45</v>
@@ -9589,7 +9589,7 @@
         <v>-15.36</v>
       </c>
       <c r="AE77" t="n">
-        <v>2.19</v>
+        <v>1.93</v>
       </c>
       <c r="AF77" t="n">
         <v>29</v>
@@ -10184,7 +10184,7 @@
         <v>-27.99</v>
       </c>
       <c r="AD82" t="n">
-        <v>-28.74</v>
+        <v>-28.8</v>
       </c>
       <c r="AE82" t="n">
         <v>6.36</v>
@@ -17011,28 +17011,28 @@
         <v>15.3</v>
       </c>
       <c r="I140" t="n">
-        <v>-7.1</v>
+        <v>-6.9</v>
       </c>
       <c r="J140" t="n">
-        <v>-0.04</v>
+        <v>-0.29</v>
       </c>
       <c r="K140" t="n">
-        <v>6.29</v>
+        <v>6.03</v>
       </c>
       <c r="L140" t="n">
-        <v>-4.12</v>
+        <v>-4.36</v>
       </c>
       <c r="M140" t="n">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="N140" t="n">
-        <v>-3.7</v>
+        <v>-3.5</v>
       </c>
       <c r="P140" t="n">
         <v>-20.1</v>
       </c>
       <c r="Q140" t="n">
-        <v>382.54</v>
+        <v>381.58</v>
       </c>
       <c r="R140" t="inlineStr">
         <is>
@@ -17045,13 +17045,13 @@
         </is>
       </c>
       <c r="T140" t="n">
-        <v>2.04</v>
+        <v>1.78</v>
       </c>
       <c r="U140" t="n">
-        <v>6.62</v>
+        <v>6.35</v>
       </c>
       <c r="V140" t="n">
-        <v>-4.12</v>
+        <v>-4.36</v>
       </c>
       <c r="X140" t="n">
         <v>397.66</v>
@@ -17072,10 +17072,10 @@
         <v>-10.9</v>
       </c>
       <c r="AD140" t="n">
-        <v>-12.63</v>
+        <v>-12.85</v>
       </c>
       <c r="AE140" t="n">
-        <v>8.029999999999999</v>
+        <v>7.76</v>
       </c>
       <c r="AF140" t="n">
         <v>46</v>
@@ -18437,28 +18437,28 @@
         <v>-9.800000000000001</v>
       </c>
       <c r="I152" t="n">
-        <v>-3.5</v>
+        <v>-3.1</v>
       </c>
       <c r="J152" t="n">
-        <v>7.93</v>
+        <v>7.51</v>
       </c>
       <c r="K152" t="n">
-        <v>-2.15</v>
+        <v>-2.53</v>
       </c>
       <c r="L152" t="n">
-        <v>-2.47</v>
+        <v>-2.85</v>
       </c>
       <c r="M152" t="n">
-        <v>28</v>
+        <v>28.5</v>
       </c>
       <c r="N152" t="n">
-        <v>15.3</v>
+        <v>15.7</v>
       </c>
       <c r="P152" t="n">
         <v>27</v>
       </c>
       <c r="Q152" t="n">
-        <v>87.48</v>
+        <v>87.14</v>
       </c>
       <c r="R152" t="inlineStr">
         <is>
@@ -18471,16 +18471,16 @@
         </is>
       </c>
       <c r="T152" t="n">
-        <v>10.9</v>
+        <v>10.47</v>
       </c>
       <c r="U152" t="n">
-        <v>11.35</v>
+        <v>10.92</v>
       </c>
       <c r="V152" t="n">
-        <v>-0.3</v>
+        <v>-0.6899999999999999</v>
       </c>
       <c r="W152" t="n">
-        <v>-0.3</v>
+        <v>-0.6899999999999999</v>
       </c>
       <c r="X152" t="n">
         <v>112</v>
@@ -18501,10 +18501,10 @@
         <v>0.18</v>
       </c>
       <c r="AD152" t="n">
-        <v>-6.69</v>
+        <v>-7.05</v>
       </c>
       <c r="AE152" t="n">
-        <v>11.35</v>
+        <v>10.92</v>
       </c>
       <c r="AF152" t="n">
         <v>51</v>
@@ -21820,7 +21820,7 @@
         <v>-2.38</v>
       </c>
       <c r="AE180" t="n">
-        <v>83.09999999999999</v>
+        <v>83.12</v>
       </c>
       <c r="AF180" t="n">
         <v>54</v>
@@ -21933,7 +21933,7 @@
         <v>-10.21</v>
       </c>
       <c r="AE181" t="n">
-        <v>34.82</v>
+        <v>34.85</v>
       </c>
       <c r="AF181" t="n">
         <v>54</v>
@@ -27700,7 +27700,7 @@
         <v>-17.71</v>
       </c>
       <c r="AD230" t="n">
-        <v>-18.57</v>
+        <v>-18.64</v>
       </c>
       <c r="AE230" t="n">
         <v>52.35</v>
@@ -33292,7 +33292,7 @@
       </c>
       <c r="B281" t="inlineStr">
         <is>
-          <t>$46,629.13</t>
+          <t>$46,629.12</t>
         </is>
       </c>
     </row>
@@ -33425,7 +33425,7 @@
         <v>38.98</v>
       </c>
       <c r="G290" t="n">
-        <v>-12.44</v>
+        <v>-12.45</v>
       </c>
     </row>
     <row r="291">
@@ -33529,7 +33529,7 @@
         <v>1.03</v>
       </c>
       <c r="G295" t="n">
-        <v>-15.44</v>
+        <v>-15.45</v>
       </c>
     </row>
     <row r="296">
@@ -33551,7 +33551,7 @@
         <v>-0.88</v>
       </c>
       <c r="G296" t="n">
-        <v>-12.54</v>
+        <v>-12.55</v>
       </c>
     </row>
     <row r="297">
@@ -33678,19 +33678,19 @@
         <v>33</v>
       </c>
       <c r="C303" t="n">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="D303" t="n">
         <v>55</v>
       </c>
       <c r="E303" t="n">
-        <v>2.48</v>
+        <v>2.46</v>
       </c>
       <c r="F303" t="n">
         <v>48</v>
       </c>
       <c r="G303" t="n">
-        <v>-9.49</v>
+        <v>-9.51</v>
       </c>
     </row>
     <row r="304">
@@ -33759,7 +33759,7 @@
         <v>55</v>
       </c>
       <c r="E306" t="n">
-        <v>4.6</v>
+        <v>4.59</v>
       </c>
       <c r="F306" t="n">
         <v>57</v>
@@ -33842,7 +33842,7 @@
         <v>-7.74</v>
       </c>
       <c r="F310" t="n">
-        <v>-14.58</v>
+        <v>-14.59</v>
       </c>
     </row>
     <row r="311">
@@ -34374,7 +34374,7 @@
         <v>20.6</v>
       </c>
       <c r="K4" t="n">
-        <v>18.22</v>
+        <v>18.21</v>
       </c>
       <c r="L4" t="n">
         <v>0</v>
@@ -34405,7 +34405,7 @@
         <v>1.2</v>
       </c>
       <c r="H5" t="n">
-        <v>-13.47</v>
+        <v>-13.48</v>
       </c>
       <c r="I5" t="n">
         <v>-39.72</v>
@@ -34485,7 +34485,7 @@
         <v>-0.79</v>
       </c>
       <c r="H7" t="n">
-        <v>-13.81</v>
+        <v>-13.82</v>
       </c>
       <c r="I7" t="n">
         <v>-45.07</v>
@@ -37663,7 +37663,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>FDS</t>
+          <t>MDB</t>
         </is>
       </c>
       <c r="B43" s="14" t="inlineStr">
@@ -37673,62 +37673,46 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>PASS/GS</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>CORE</t>
-        </is>
-      </c>
-      <c r="E43" t="inlineStr">
-        <is>
-          <t>75.6</t>
-        </is>
-      </c>
-      <c r="F43" t="inlineStr">
-        <is>
-          <t>0.284</t>
-        </is>
-      </c>
-      <c r="G43" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="H43" t="inlineStr">
-        <is>
-          <t>4.76</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr">
-        <is>
-          <t>6.2</t>
-        </is>
-      </c>
-      <c r="J43" t="inlineStr">
-        <is>
-          <t>13.8</t>
-        </is>
-      </c>
-      <c r="K43" t="inlineStr">
-        <is>
-          <t>0.71</t>
-        </is>
-      </c>
-      <c r="L43" t="inlineStr">
-        <is>
-          <t>32.2</t>
-        </is>
+          <t>GROWTH</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>75.7</v>
+      </c>
+      <c r="F43" t="n">
+        <v>0.47</v>
+      </c>
+      <c r="G43" t="n">
+        <v>6</v>
+      </c>
+      <c r="H43" t="n">
+        <v>22.1</v>
+      </c>
+      <c r="I43" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="J43" t="n">
+        <v>-16.8</v>
+      </c>
+      <c r="K43" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="L43" t="n">
+        <v>-5.6</v>
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="N43" t="inlineStr">
         <is>
-          <t>mature / stable</t>
+          <t>rev +24%/yr, not yet FCF-safe</t>
         </is>
       </c>
       <c r="O43" t="inlineStr"/>
@@ -37736,7 +37720,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>MDB</t>
+          <t>FDS</t>
         </is>
       </c>
       <c r="B44" s="14" t="inlineStr">
@@ -37746,12 +37730,12 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>PASS/GS</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>GROWTH</t>
+          <t>CORE</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -37761,7 +37745,7 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>0.47</t>
+          <t>0.284</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
@@ -37771,37 +37755,37 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>23.14</t>
+          <t>4.76</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>1.7</t>
+          <t>6.2</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>-16.8</t>
+          <t>13.8</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>0.71</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>-5.6</t>
+          <t>32.2</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Financial Services</t>
         </is>
       </c>
       <c r="N44" t="inlineStr">
         <is>
-          <t>rev +24%/yr, not yet FCF-safe</t>
+          <t>mature / stable</t>
         </is>
       </c>
       <c r="O44" t="inlineStr"/>
@@ -39725,29 +39709,45 @@
           <t>CORE</t>
         </is>
       </c>
-      <c r="E71" t="n">
-        <v>68.7</v>
-      </c>
-      <c r="F71" t="n">
-        <v>0.518</v>
-      </c>
-      <c r="G71" t="n">
-        <v>4</v>
-      </c>
-      <c r="H71" t="n">
-        <v>3.19</v>
-      </c>
-      <c r="I71" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="J71" t="n">
-        <v>75.90000000000001</v>
-      </c>
-      <c r="K71" t="n">
-        <v>0.74</v>
-      </c>
-      <c r="L71" t="n">
-        <v>8.199999999999999</v>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>68.7</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>0.518</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>3.19</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>4.3</t>
+        </is>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>75.9</t>
+        </is>
+      </c>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>0.74</t>
+        </is>
+      </c>
+      <c r="L71" t="inlineStr">
+        <is>
+          <t>8.2</t>
+        </is>
       </c>
       <c r="M71" t="inlineStr">
         <is>
@@ -43902,29 +43902,45 @@
           <t>NEW-IPO</t>
         </is>
       </c>
-      <c r="E128" t="n">
-        <v>53.7</v>
-      </c>
-      <c r="F128" t="n">
-        <v>0.218</v>
-      </c>
-      <c r="G128" t="n">
-        <v>6</v>
-      </c>
-      <c r="H128" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="I128" t="n">
-        <v>7.1</v>
-      </c>
-      <c r="J128" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="K128" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="L128" t="n">
-        <v>2.6</v>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>53.7</t>
+        </is>
+      </c>
+      <c r="F128" t="inlineStr">
+        <is>
+          <t>0.218</t>
+        </is>
+      </c>
+      <c r="G128" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H128" t="inlineStr">
+        <is>
+          <t>2.3</t>
+        </is>
+      </c>
+      <c r="I128" t="inlineStr">
+        <is>
+          <t>7.1</t>
+        </is>
+      </c>
+      <c r="J128" t="inlineStr">
+        <is>
+          <t>1.7</t>
+        </is>
+      </c>
+      <c r="K128" t="inlineStr">
+        <is>
+          <t>1.06</t>
+        </is>
+      </c>
+      <c r="L128" t="inlineStr">
+        <is>
+          <t>2.6</t>
+        </is>
       </c>
       <c r="M128" t="inlineStr">
         <is>
@@ -51596,8 +51612,10 @@
           <t>NEW-IPO</t>
         </is>
       </c>
-      <c r="L2" t="n">
-        <v>53.7</v>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>53.7</t>
+        </is>
       </c>
     </row>
     <row r="3">
@@ -51648,8 +51666,10 @@
           <t>CORE</t>
         </is>
       </c>
-      <c r="L3" t="n">
-        <v>68.7</v>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>68.7</t>
+        </is>
       </c>
     </row>
     <row r="4">
@@ -51704,10 +51724,8 @@
           <t>GROWTH</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>75.6</t>
-        </is>
+      <c r="L4" t="n">
+        <v>75.7</v>
       </c>
     </row>
     <row r="5">
@@ -54720,10 +54738,8 @@
           <t>GROWTH</t>
         </is>
       </c>
-      <c r="L56" t="inlineStr">
-        <is>
-          <t>75.6</t>
-        </is>
+      <c r="L56" t="n">
+        <v>75.7</v>
       </c>
     </row>
     <row r="57">

--- a/STS_holy_grail.xlsx
+++ b/STS_holy_grail.xlsx
@@ -37024,45 +37024,29 @@
           <t>CORE</t>
         </is>
       </c>
-      <c r="E34" t="inlineStr">
-        <is>
-          <t>77.4</t>
-        </is>
-      </c>
-      <c r="F34" t="inlineStr">
-        <is>
-          <t>0.317</t>
-        </is>
-      </c>
-      <c r="G34" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="H34" t="inlineStr">
-        <is>
-          <t>3.14</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>5.0</t>
-        </is>
-      </c>
-      <c r="J34" t="inlineStr">
-        <is>
-          <t>10.7</t>
-        </is>
-      </c>
-      <c r="K34" t="inlineStr">
-        <is>
-          <t>0.47</t>
-        </is>
-      </c>
-      <c r="L34" t="inlineStr">
-        <is>
-          <t>19.8</t>
-        </is>
+      <c r="E34" t="n">
+        <v>77.40000000000001</v>
+      </c>
+      <c r="F34" t="n">
+        <v>0.317</v>
+      </c>
+      <c r="G34" t="n">
+        <v>7</v>
+      </c>
+      <c r="H34" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="I34" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="J34" t="n">
+        <v>10.7</v>
+      </c>
+      <c r="K34" t="n">
+        <v>0.47</v>
+      </c>
+      <c r="L34" t="n">
+        <v>19.8</v>
       </c>
       <c r="M34" t="inlineStr">
         <is>
@@ -37681,29 +37665,45 @@
           <t>GROWTH</t>
         </is>
       </c>
-      <c r="E43" t="n">
-        <v>75.7</v>
-      </c>
-      <c r="F43" t="n">
-        <v>0.47</v>
-      </c>
-      <c r="G43" t="n">
-        <v>6</v>
-      </c>
-      <c r="H43" t="n">
-        <v>22.1</v>
-      </c>
-      <c r="I43" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="J43" t="n">
-        <v>-16.8</v>
-      </c>
-      <c r="K43" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="L43" t="n">
-        <v>-5.6</v>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>75.7</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>0.47</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>22.1</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>1.7</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>-16.8</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>-5.6</t>
+        </is>
       </c>
       <c r="M43" t="inlineStr">
         <is>
@@ -51724,8 +51724,10 @@
           <t>GROWTH</t>
         </is>
       </c>
-      <c r="L4" t="n">
-        <v>75.7</v>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>75.7</t>
+        </is>
       </c>
     </row>
     <row r="5">
@@ -54622,10 +54624,8 @@
           <t>CORE</t>
         </is>
       </c>
-      <c r="L54" t="inlineStr">
-        <is>
-          <t>77.4</t>
-        </is>
+      <c r="L54" t="n">
+        <v>77.40000000000001</v>
       </c>
     </row>
     <row r="55">
@@ -54738,8 +54738,10 @@
           <t>GROWTH</t>
         </is>
       </c>
-      <c r="L56" t="n">
-        <v>75.7</v>
+      <c r="L56" t="inlineStr">
+        <is>
+          <t>75.7</t>
+        </is>
       </c>
     </row>
     <row r="57">

--- a/STS_holy_grail.xlsx
+++ b/STS_holy_grail.xlsx
@@ -45197,7 +45197,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>SPOT</t>
+          <t>MORN</t>
         </is>
       </c>
       <c r="B38" s="16" t="inlineStr">
@@ -45217,12 +45217,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>76.7</t>
+          <t>76.6</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>0.366</t>
+          <t>0.416</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
@@ -45232,32 +45232,32 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>11.54</t>
+          <t>3.95</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>2.7</t>
+          <t>5.9</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>72.7</t>
+          <t>13.5</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>0.23</t>
+          <t>1.03</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>12.8</t>
+          <t>20.6</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>Communication Services</t>
+          <t>Financial Services</t>
         </is>
       </c>
       <c r="N38" t="inlineStr">
@@ -45270,7 +45270,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>MORN</t>
+          <t>SPOT</t>
         </is>
       </c>
       <c r="B39" s="16" t="inlineStr">
@@ -45288,49 +45288,33 @@
           <t>CORE</t>
         </is>
       </c>
-      <c r="E39" t="inlineStr">
-        <is>
-          <t>76.6</t>
-        </is>
-      </c>
-      <c r="F39" t="inlineStr">
-        <is>
-          <t>0.416</t>
-        </is>
-      </c>
-      <c r="G39" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="H39" t="inlineStr">
-        <is>
-          <t>3.95</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t>5.9</t>
-        </is>
-      </c>
-      <c r="J39" t="inlineStr">
-        <is>
-          <t>13.5</t>
-        </is>
-      </c>
-      <c r="K39" t="inlineStr">
-        <is>
-          <t>1.03</t>
-        </is>
-      </c>
-      <c r="L39" t="inlineStr">
-        <is>
-          <t>20.6</t>
-        </is>
+      <c r="E39" t="n">
+        <v>76.59999999999999</v>
+      </c>
+      <c r="F39" t="n">
+        <v>0.366</v>
+      </c>
+      <c r="G39" t="n">
+        <v>6</v>
+      </c>
+      <c r="H39" t="n">
+        <v>11.68</v>
+      </c>
+      <c r="I39" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="J39" t="n">
+        <v>72.7</v>
+      </c>
+      <c r="K39" t="n">
+        <v>0.23</v>
+      </c>
+      <c r="L39" t="n">
+        <v>12.8</v>
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Communication Services</t>
         </is>
       </c>
       <c r="N39" t="inlineStr">
@@ -49228,157 +49212,138 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>TCOM</t>
-        </is>
-      </c>
-      <c r="B93" s="15" t="inlineStr">
-        <is>
-          <t>FAIL</t>
+          <t>ARWR</t>
+        </is>
+      </c>
+      <c r="B93" s="14" t="inlineStr">
+        <is>
+          <t>WATCH</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>FAIL/LEV</t>
+          <t>WATCH/GS</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>LEVERAGED</t>
-        </is>
-      </c>
-      <c r="E93" t="inlineStr">
-        <is>
-          <t>63.5</t>
-        </is>
-      </c>
-      <c r="F93" t="inlineStr">
-        <is>
-          <t>0.188</t>
-        </is>
-      </c>
-      <c r="G93" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="H93" t="inlineStr">
-        <is>
-          <t>1.48</t>
-        </is>
-      </c>
-      <c r="I93" t="inlineStr">
-        <is>
-          <t>53.3</t>
-        </is>
-      </c>
-      <c r="J93" t="inlineStr">
-        <is>
-          <t>46.8</t>
-        </is>
-      </c>
-      <c r="K93" t="inlineStr">
-        <is>
-          <t>0.18</t>
-        </is>
-      </c>
-      <c r="L93" t="inlineStr">
-        <is>
-          <t>27.4</t>
-        </is>
+          <t>GROWTH</t>
+        </is>
+      </c>
+      <c r="E93" t="n">
+        <v>64.2</v>
+      </c>
+      <c r="G93" t="n">
+        <v>5</v>
+      </c>
+      <c r="H93" t="n">
+        <v>5.97</v>
+      </c>
+      <c r="I93" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="J93" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="K93" t="n">
+        <v>0.79</v>
+      </c>
+      <c r="L93" t="n">
+        <v>11.9</v>
       </c>
       <c r="M93" t="inlineStr">
         <is>
-          <t>Consumer Cyclical</t>
+          <t>Healthcare</t>
         </is>
       </c>
       <c r="N93" t="inlineStr">
         <is>
-          <t>distress/leverage flag</t>
-        </is>
-      </c>
-      <c r="O93" t="inlineStr">
-        <is>
-          <t>Altman-Z 1.48 in distress zone (&lt;1.81)</t>
-        </is>
-      </c>
+          <t>rev +51%/yr, not yet FCF-safe</t>
+        </is>
+      </c>
+      <c r="O93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>CAT</t>
-        </is>
-      </c>
-      <c r="B94" s="14" t="inlineStr">
-        <is>
-          <t>WATCH</t>
+          <t>TCOM</t>
+        </is>
+      </c>
+      <c r="B94" s="15" t="inlineStr">
+        <is>
+          <t>FAIL</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>WATCH</t>
+          <t>FAIL/LEV</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>CORE</t>
+          <t>LEVERAGED</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>63.4</t>
+          <t>63.5</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>0.218</t>
+          <t>0.188</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>5.11</t>
+          <t>1.48</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>53.3</t>
         </is>
       </c>
       <c r="J94" t="inlineStr">
         <is>
-          <t>24.0</t>
+          <t>46.8</t>
         </is>
       </c>
       <c r="K94" t="inlineStr">
         <is>
-          <t>2.03</t>
+          <t>0.18</t>
         </is>
       </c>
       <c r="L94" t="inlineStr">
         <is>
-          <t>16.5</t>
+          <t>27.4</t>
         </is>
       </c>
       <c r="M94" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Consumer Cyclical</t>
         </is>
       </c>
       <c r="N94" t="inlineStr">
         <is>
-          <t>mature / stable</t>
-        </is>
-      </c>
-      <c r="O94" t="inlineStr"/>
+          <t>distress/leverage flag</t>
+        </is>
+      </c>
+      <c r="O94" t="inlineStr">
+        <is>
+          <t>Altman-Z 1.48 in distress zone (&lt;1.81)</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>MTZ</t>
+          <t>CAT</t>
         </is>
       </c>
       <c r="B95" s="14" t="inlineStr">
@@ -49388,52 +49353,52 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>WATCH/IPO</t>
+          <t>WATCH</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>NEW-IPO</t>
+          <t>CORE</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>63.2</t>
+          <t>63.4</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>0.181</t>
+          <t>0.218</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>6</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>3.77</t>
+          <t>5.11</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>1.6</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="J95" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>24.0</t>
         </is>
       </c>
       <c r="K95" t="inlineStr">
         <is>
-          <t>0.86</t>
+          <t>2.03</t>
         </is>
       </c>
       <c r="L95" t="inlineStr">
         <is>
-          <t>4.6</t>
+          <t>16.5</t>
         </is>
       </c>
       <c r="M95" t="inlineStr">
@@ -49443,7 +49408,7 @@
       </c>
       <c r="N95" t="inlineStr">
         <is>
-          <t>&lt;3yr public history</t>
+          <t>mature / stable</t>
         </is>
       </c>
       <c r="O95" t="inlineStr"/>
@@ -49451,7 +49416,7 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>UNH</t>
+          <t>MTZ</t>
         </is>
       </c>
       <c r="B96" s="14" t="inlineStr">
@@ -49461,62 +49426,62 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>WATCH</t>
+          <t>WATCH/IPO</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>CORE</t>
+          <t>NEW-IPO</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>62.6</t>
+          <t>63.2</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>0.268</t>
+          <t>0.181</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>8</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>2.95</t>
+          <t>3.77</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>4.8</t>
+          <t>1.6</t>
         </is>
       </c>
       <c r="J96" t="inlineStr">
         <is>
-          <t>4.7</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="K96" t="inlineStr">
         <is>
-          <t>0.83</t>
+          <t>0.86</t>
         </is>
       </c>
       <c r="L96" t="inlineStr">
         <is>
-          <t>4.2</t>
+          <t>4.6</t>
         </is>
       </c>
       <c r="M96" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="N96" t="inlineStr">
         <is>
-          <t>mature / stable</t>
+          <t>&lt;3yr public history</t>
         </is>
       </c>
       <c r="O96" t="inlineStr"/>
@@ -49524,7 +49489,7 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>COHR</t>
+          <t>UNH</t>
         </is>
       </c>
       <c r="B97" s="14" t="inlineStr">
@@ -49544,12 +49509,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>61.3</t>
+          <t>62.6</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>0.146</t>
+          <t>0.268</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
@@ -49559,32 +49524,32 @@
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>5.95</t>
+          <t>2.95</t>
         </is>
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>-1.8</t>
+          <t>4.8</t>
         </is>
       </c>
       <c r="J97" t="inlineStr">
         <is>
-          <t>5.5</t>
+          <t>4.7</t>
         </is>
       </c>
       <c r="K97" t="inlineStr">
         <is>
-          <t>0.32</t>
+          <t>0.83</t>
         </is>
       </c>
       <c r="L97" t="inlineStr">
         <is>
-          <t>12.7</t>
+          <t>4.2</t>
         </is>
       </c>
       <c r="M97" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Healthcare</t>
         </is>
       </c>
       <c r="N97" t="inlineStr">
@@ -49597,7 +49562,7 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>VLO</t>
+          <t>COHR</t>
         </is>
       </c>
       <c r="B98" s="14" t="inlineStr">
@@ -49607,12 +49572,12 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>WATCH/DECL</t>
+          <t>WATCH</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>DECLINING</t>
+          <t>CORE</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
@@ -49622,7 +49587,7 @@
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>0.093</t>
+          <t>0.146</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
@@ -49632,37 +49597,37 @@
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>5.81</t>
+          <t>5.95</t>
         </is>
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>4.5</t>
+          <t>-1.8</t>
         </is>
       </c>
       <c r="J98" t="inlineStr">
         <is>
-          <t>6.4</t>
+          <t>5.5</t>
         </is>
       </c>
       <c r="K98" t="inlineStr">
         <is>
-          <t>0.49</t>
+          <t>0.32</t>
         </is>
       </c>
       <c r="L98" t="inlineStr">
         <is>
-          <t>3.5</t>
+          <t>12.7</t>
         </is>
       </c>
       <c r="M98" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="N98" t="inlineStr">
         <is>
-          <t>revenue -6% YoY</t>
+          <t>mature / stable</t>
         </is>
       </c>
       <c r="O98" t="inlineStr"/>
@@ -49670,7 +49635,7 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>CPRI</t>
+          <t>VLO</t>
         </is>
       </c>
       <c r="B99" s="14" t="inlineStr">
@@ -49690,52 +49655,52 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>61.1</t>
+          <t>61.3</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>0.669</t>
+          <t>0.093</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>6</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>3.47</t>
+          <t>5.81</t>
         </is>
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>0.8</t>
+          <t>4.5</t>
         </is>
       </c>
       <c r="J99" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>6.4</t>
         </is>
       </c>
       <c r="K99" t="inlineStr">
         <is>
-          <t>17.75</t>
+          <t>0.49</t>
         </is>
       </c>
       <c r="L99" t="inlineStr">
         <is>
-          <t>2.2</t>
+          <t>3.5</t>
         </is>
       </c>
       <c r="M99" t="inlineStr">
         <is>
-          <t>Consumer Cyclical</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="N99" t="inlineStr">
         <is>
-          <t>revenue -4% YoY</t>
+          <t>revenue -6% YoY</t>
         </is>
       </c>
       <c r="O99" t="inlineStr"/>
@@ -49743,7 +49708,7 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>KEYS</t>
+          <t>CPRI</t>
         </is>
       </c>
       <c r="B100" s="14" t="inlineStr">
@@ -49753,62 +49718,62 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>WATCH</t>
+          <t>WATCH/DECL</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>CORE</t>
+          <t>DECLINING</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>60.8</t>
+          <t>61.1</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>0.295</t>
+          <t>0.669</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>8</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>8.62</t>
+          <t>3.47</t>
         </is>
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t>2.1</t>
+          <t>0.8</t>
         </is>
       </c>
       <c r="J100" t="inlineStr">
         <is>
-          <t>12.3</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="K100" t="inlineStr">
         <is>
-          <t>0.47</t>
+          <t>17.75</t>
         </is>
       </c>
       <c r="L100" t="inlineStr">
         <is>
-          <t>16.3</t>
+          <t>2.2</t>
         </is>
       </c>
       <c r="M100" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Consumer Cyclical</t>
         </is>
       </c>
       <c r="N100" t="inlineStr">
         <is>
-          <t>mature / stable</t>
+          <t>revenue -4% YoY</t>
         </is>
       </c>
       <c r="O100" t="inlineStr"/>
@@ -49816,7 +49781,7 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>MU</t>
+          <t>KEYS</t>
         </is>
       </c>
       <c r="B101" s="14" t="inlineStr">
@@ -49826,12 +49791,12 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>WATCH/GS</t>
+          <t>WATCH</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>GROWTH</t>
+          <t>CORE</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
@@ -49841,37 +49806,37 @@
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>0.18</t>
+          <t>0.295</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>5</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>27.3</t>
+          <t>8.62</t>
         </is>
       </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>2.1</t>
         </is>
       </c>
       <c r="J101" t="inlineStr">
         <is>
-          <t>21.2</t>
+          <t>12.3</t>
         </is>
       </c>
       <c r="K101" t="inlineStr">
         <is>
-          <t>0.28</t>
+          <t>0.47</t>
         </is>
       </c>
       <c r="L101" t="inlineStr">
         <is>
-          <t>26.2</t>
+          <t>16.3</t>
         </is>
       </c>
       <c r="M101" t="inlineStr">
@@ -49881,7 +49846,7 @@
       </c>
       <c r="N101" t="inlineStr">
         <is>
-          <t>rev +7%/yr, profitable</t>
+          <t>mature / stable</t>
         </is>
       </c>
       <c r="O101" t="inlineStr"/>
@@ -49889,7 +49854,7 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>MPC</t>
+          <t>MU</t>
         </is>
       </c>
       <c r="B102" s="14" t="inlineStr">
@@ -49899,22 +49864,22 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>WATCH/DECL</t>
+          <t>WATCH/GS</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>DECLINING</t>
+          <t>GROWTH</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>60.3</t>
+          <t>60.8</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>0.119</t>
+          <t>0.18</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
@@ -49924,37 +49889,37 @@
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>3.76</t>
+          <t>27.3</t>
         </is>
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t>4.3</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="J102" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>21.2</t>
         </is>
       </c>
       <c r="K102" t="inlineStr">
         <is>
-          <t>1.98</t>
+          <t>0.28</t>
         </is>
       </c>
       <c r="L102" t="inlineStr">
         <is>
-          <t>4.3</t>
+          <t>26.2</t>
         </is>
       </c>
       <c r="M102" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="N102" t="inlineStr">
         <is>
-          <t>revenue -4% YoY</t>
+          <t>rev +7%/yr, profitable</t>
         </is>
       </c>
       <c r="O102" t="inlineStr"/>
@@ -49962,7 +49927,7 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>XOM</t>
+          <t>MPC</t>
         </is>
       </c>
       <c r="B103" s="14" t="inlineStr">
@@ -49987,37 +49952,37 @@
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>0.159</t>
+          <t>0.119</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>4.75</t>
+          <t>3.76</t>
         </is>
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t>3.6</t>
+          <t>4.3</t>
         </is>
       </c>
       <c r="J103" t="inlineStr">
         <is>
-          <t>69.4</t>
+          <t>6.0</t>
         </is>
       </c>
       <c r="K103" t="inlineStr">
         <is>
-          <t>0.17</t>
+          <t>1.98</t>
         </is>
       </c>
       <c r="L103" t="inlineStr">
         <is>
-          <t>10.5</t>
+          <t>4.3</t>
         </is>
       </c>
       <c r="M103" t="inlineStr">
@@ -50027,7 +49992,7 @@
       </c>
       <c r="N103" t="inlineStr">
         <is>
-          <t>revenue -5% YoY</t>
+          <t>revenue -4% YoY</t>
         </is>
       </c>
       <c r="O103" t="inlineStr"/>
@@ -50035,7 +50000,7 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>XOM</t>
         </is>
       </c>
       <c r="B104" s="14" t="inlineStr">
@@ -50045,62 +50010,62 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>WATCH</t>
+          <t>WATCH/DECL</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>CORE</t>
+          <t>DECLINING</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>60.1</t>
+          <t>60.3</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>0.201</t>
+          <t>0.159</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>2.95</t>
+          <t>4.75</t>
         </is>
       </c>
       <c r="I104" t="inlineStr">
         <is>
-          <t>2.1</t>
+          <t>3.6</t>
         </is>
       </c>
       <c r="J104" t="inlineStr">
         <is>
-          <t>-15.5</t>
+          <t>69.4</t>
         </is>
       </c>
       <c r="K104" t="inlineStr">
         <is>
-          <t>0.69</t>
+          <t>0.17</t>
         </is>
       </c>
       <c r="L104" t="inlineStr">
         <is>
-          <t>-25.9</t>
+          <t>10.5</t>
         </is>
       </c>
       <c r="M104" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="N104" t="inlineStr">
         <is>
-          <t>mature / stable</t>
+          <t>revenue -5% YoY</t>
         </is>
       </c>
       <c r="O104" t="inlineStr"/>
@@ -50108,7 +50073,7 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>APA</t>
+          <t>U</t>
         </is>
       </c>
       <c r="B105" s="14" t="inlineStr">
@@ -50118,62 +50083,62 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>WATCH/DECL</t>
+          <t>WATCH</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>DECLINING</t>
+          <t>CORE</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>59.8</t>
+          <t>60.1</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>0.204</t>
+          <t>0.201</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>1.84</t>
+          <t>2.95</t>
         </is>
       </c>
       <c r="I105" t="inlineStr">
         <is>
-          <t>11.6</t>
+          <t>2.1</t>
         </is>
       </c>
       <c r="J105" t="inlineStr">
         <is>
-          <t>11.0</t>
+          <t>-15.5</t>
         </is>
       </c>
       <c r="K105" t="inlineStr">
         <is>
-          <t>0.75</t>
+          <t>0.69</t>
         </is>
       </c>
       <c r="L105" t="inlineStr">
         <is>
-          <t>30.8</t>
+          <t>-25.9</t>
         </is>
       </c>
       <c r="M105" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="N105" t="inlineStr">
         <is>
-          <t>revenue -8% YoY</t>
+          <t>mature / stable</t>
         </is>
       </c>
       <c r="O105" t="inlineStr"/>
@@ -50181,7 +50146,7 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>CRWD</t>
+          <t>APA</t>
         </is>
       </c>
       <c r="B106" s="14" t="inlineStr">
@@ -50191,62 +50156,62 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>WATCH/SPEC</t>
+          <t>WATCH/DECL</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>SPECULATIVE</t>
+          <t>DECLINING</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>59.5</t>
+          <t>59.8</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>0.324</t>
+          <t>0.204</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>7</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>24.97</t>
+          <t>1.84</t>
         </is>
       </c>
       <c r="I106" t="inlineStr">
         <is>
-          <t>0.5</t>
+          <t>11.6</t>
         </is>
       </c>
       <c r="J106" t="inlineStr">
         <is>
-          <t>-3.5</t>
+          <t>11.0</t>
         </is>
       </c>
       <c r="K106" t="inlineStr">
         <is>
-          <t>0.19</t>
+          <t>0.75</t>
         </is>
       </c>
       <c r="L106" t="inlineStr">
         <is>
-          <t>-6.1</t>
+          <t>30.8</t>
         </is>
       </c>
       <c r="M106" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="N106" t="inlineStr">
         <is>
-          <t>pre-commercial (P/S 56)</t>
+          <t>revenue -8% YoY</t>
         </is>
       </c>
       <c r="O106" t="inlineStr"/>
@@ -50254,22 +50219,22 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>DKNG</t>
-        </is>
-      </c>
-      <c r="B107" s="15" t="inlineStr">
-        <is>
-          <t>FAIL</t>
+          <t>CRWD</t>
+        </is>
+      </c>
+      <c r="B107" s="14" t="inlineStr">
+        <is>
+          <t>WATCH</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>FAIL/GS</t>
+          <t>WATCH/SPEC</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>GROWTH</t>
+          <t>SPECULATIVE</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
@@ -50279,69 +50244,65 @@
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>0.551</t>
+          <t>0.324</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>4</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>0.97</t>
+          <t>24.97</t>
         </is>
       </c>
       <c r="I107" t="inlineStr">
         <is>
-          <t>4.8</t>
+          <t>0.5</t>
         </is>
       </c>
       <c r="J107" t="inlineStr">
         <is>
-          <t>-0.8</t>
+          <t>-3.5</t>
         </is>
       </c>
       <c r="K107" t="inlineStr">
         <is>
-          <t>2.99</t>
+          <t>0.19</t>
         </is>
       </c>
       <c r="L107" t="inlineStr">
         <is>
-          <t>-0.3</t>
+          <t>-6.1</t>
         </is>
       </c>
       <c r="M107" t="inlineStr">
         <is>
-          <t>Consumer Cyclical</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="N107" t="inlineStr">
         <is>
-          <t>rev +27%/yr, profitable</t>
-        </is>
-      </c>
-      <c r="O107" t="inlineStr">
-        <is>
-          <t>Altman-Z 0.97 in distress zone (&lt;1.81)</t>
-        </is>
-      </c>
+          <t>pre-commercial (P/S 56)</t>
+        </is>
+      </c>
+      <c r="O107" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>NVO</t>
-        </is>
-      </c>
-      <c r="B108" s="14" t="inlineStr">
-        <is>
-          <t>WATCH</t>
+          <t>DKNG</t>
+        </is>
+      </c>
+      <c r="B108" s="15" t="inlineStr">
+        <is>
+          <t>FAIL</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>WATCH/GS</t>
+          <t>FAIL/GS</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -50351,115 +50312,119 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>59.2</t>
+          <t>59.5</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>0.461</t>
+          <t>0.551</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>2.09</t>
+          <t>0.97</t>
         </is>
       </c>
       <c r="I108" t="inlineStr">
         <is>
-          <t>17.0</t>
+          <t>4.8</t>
         </is>
       </c>
       <c r="J108" t="inlineStr">
         <is>
-          <t>32.0</t>
+          <t>-0.8</t>
         </is>
       </c>
       <c r="K108" t="inlineStr">
         <is>
-          <t>0.67</t>
+          <t>2.99</t>
         </is>
       </c>
       <c r="L108" t="inlineStr">
         <is>
-          <t>41.3</t>
+          <t>-0.3</t>
         </is>
       </c>
       <c r="M108" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>Consumer Cyclical</t>
         </is>
       </c>
       <c r="N108" t="inlineStr">
         <is>
-          <t>rev +20%/yr, profitable</t>
-        </is>
-      </c>
-      <c r="O108" t="inlineStr"/>
+          <t>rev +27%/yr, profitable</t>
+        </is>
+      </c>
+      <c r="O108" t="inlineStr">
+        <is>
+          <t>Altman-Z 0.97 in distress zone (&lt;1.81)</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>DVA</t>
-        </is>
-      </c>
-      <c r="B109" s="15" t="inlineStr">
-        <is>
-          <t>FAIL</t>
+          <t>NVO</t>
+        </is>
+      </c>
+      <c r="B109" s="14" t="inlineStr">
+        <is>
+          <t>WATCH</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>FAIL/LEV</t>
+          <t>WATCH/GS</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>LEVERAGED</t>
+          <t>GROWTH</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>58.9</t>
+          <t>59.2</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>0.252</t>
+          <t>0.461</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>1.61</t>
+          <t>2.09</t>
         </is>
       </c>
       <c r="I109" t="inlineStr">
         <is>
-          <t>11.2</t>
+          <t>17.0</t>
         </is>
       </c>
       <c r="J109" t="inlineStr">
         <is>
-          <t>3.3</t>
+          <t>32.0</t>
         </is>
       </c>
       <c r="K109" t="inlineStr">
         <is>
-          <t>-19.77</t>
+          <t>0.67</t>
         </is>
       </c>
       <c r="L109" t="inlineStr">
         <is>
-          <t>14.7</t>
+          <t>41.3</t>
         </is>
       </c>
       <c r="M109" t="inlineStr">
@@ -50469,34 +50434,30 @@
       </c>
       <c r="N109" t="inlineStr">
         <is>
-          <t>distress/leverage flag</t>
-        </is>
-      </c>
-      <c r="O109" t="inlineStr">
-        <is>
-          <t>Altman-Z 1.61 in distress zone (&lt;1.81)</t>
-        </is>
-      </c>
+          <t>rev +20%/yr, profitable</t>
+        </is>
+      </c>
+      <c r="O109" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>ELF</t>
-        </is>
-      </c>
-      <c r="B110" s="14" t="inlineStr">
-        <is>
-          <t>WATCH</t>
+          <t>DVA</t>
+        </is>
+      </c>
+      <c r="B110" s="15" t="inlineStr">
+        <is>
+          <t>FAIL</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>WATCH</t>
+          <t>FAIL/LEV</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>CORE</t>
+          <t>LEVERAGED</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
@@ -50506,55 +50467,59 @@
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>0.483</t>
+          <t>0.252</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>6</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>3.76</t>
+          <t>1.61</t>
         </is>
       </c>
       <c r="I110" t="inlineStr">
         <is>
-          <t>3.2</t>
+          <t>11.2</t>
         </is>
       </c>
       <c r="J110" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>3.3</t>
         </is>
       </c>
       <c r="K110" t="inlineStr">
         <is>
-          <t>0.81</t>
+          <t>-19.77</t>
         </is>
       </c>
       <c r="L110" t="inlineStr">
         <is>
-          <t>8.0</t>
+          <t>14.7</t>
         </is>
       </c>
       <c r="M110" t="inlineStr">
         <is>
-          <t>Consumer Defensive</t>
+          <t>Healthcare</t>
         </is>
       </c>
       <c r="N110" t="inlineStr">
         <is>
-          <t>mature / stable</t>
-        </is>
-      </c>
-      <c r="O110" t="inlineStr"/>
+          <t>distress/leverage flag</t>
+        </is>
+      </c>
+      <c r="O110" t="inlineStr">
+        <is>
+          <t>Altman-Z 1.61 in distress zone (&lt;1.81)</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>NTR</t>
+          <t>ELF</t>
         </is>
       </c>
       <c r="B111" s="14" t="inlineStr">
@@ -50574,47 +50539,47 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>58.2</t>
+          <t>58.9</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>0.16</t>
+          <t>0.483</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>3</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>1.94</t>
+          <t>3.76</t>
         </is>
       </c>
       <c r="I111" t="inlineStr">
         <is>
-          <t>5.7</t>
+          <t>3.2</t>
         </is>
       </c>
       <c r="J111" t="inlineStr">
         <is>
-          <t>5.2</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="K111" t="inlineStr">
         <is>
-          <t>0.47</t>
+          <t>0.81</t>
         </is>
       </c>
       <c r="L111" t="inlineStr">
         <is>
-          <t>14.4</t>
+          <t>8.0</t>
         </is>
       </c>
       <c r="M111" t="inlineStr">
         <is>
-          <t>Basic Materials</t>
+          <t>Consumer Defensive</t>
         </is>
       </c>
       <c r="N111" t="inlineStr">
@@ -50627,7 +50592,7 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>FUTU</t>
+          <t>NTR</t>
         </is>
       </c>
       <c r="B112" s="14" t="inlineStr">
@@ -50637,58 +50602,62 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>WATCH/GS</t>
+          <t>WATCH</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>GROWTH</t>
+          <t>CORE</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>57.9</t>
+          <t>58.2</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>0.087</t>
+          <t>0.16</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>8</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>0.7</t>
+          <t>1.94</t>
         </is>
       </c>
       <c r="I112" t="inlineStr">
         <is>
-          <t>264.2</t>
-        </is>
-      </c>
-      <c r="J112" t="inlineStr"/>
+          <t>5.7</t>
+        </is>
+      </c>
+      <c r="J112" t="inlineStr">
+        <is>
+          <t>5.2</t>
+        </is>
+      </c>
       <c r="K112" t="inlineStr">
         <is>
-          <t>0.44</t>
+          <t>0.47</t>
         </is>
       </c>
       <c r="L112" t="inlineStr">
         <is>
-          <t>61.6</t>
+          <t>14.4</t>
         </is>
       </c>
       <c r="M112" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Basic Materials</t>
         </is>
       </c>
       <c r="N112" t="inlineStr">
         <is>
-          <t>rev +68%/yr, profitable</t>
+          <t>mature / stable</t>
         </is>
       </c>
       <c r="O112" t="inlineStr"/>
@@ -50696,7 +50665,7 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>IRDM</t>
+          <t>FUTU</t>
         </is>
       </c>
       <c r="B113" s="14" t="inlineStr">
@@ -50706,62 +50675,58 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>WATCH</t>
+          <t>WATCH/GS</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>CORE</t>
+          <t>GROWTH</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>57.8</t>
+          <t>57.9</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>0.246</t>
+          <t>0.087</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>1.98</t>
+          <t>0.7</t>
         </is>
       </c>
       <c r="I113" t="inlineStr">
         <is>
-          <t>5.9</t>
-        </is>
-      </c>
-      <c r="J113" t="inlineStr">
-        <is>
-          <t>2.6</t>
-        </is>
-      </c>
+          <t>264.2</t>
+        </is>
+      </c>
+      <c r="J113" t="inlineStr"/>
       <c r="K113" t="inlineStr">
         <is>
-          <t>3.81</t>
+          <t>0.44</t>
         </is>
       </c>
       <c r="L113" t="inlineStr">
         <is>
-          <t>27.1</t>
+          <t>61.6</t>
         </is>
       </c>
       <c r="M113" t="inlineStr">
         <is>
-          <t>Communication Services</t>
+          <t>Financial Services</t>
         </is>
       </c>
       <c r="N113" t="inlineStr">
         <is>
-          <t>mature / stable</t>
+          <t>rev +68%/yr, profitable</t>
         </is>
       </c>
       <c r="O113" t="inlineStr"/>
@@ -50769,7 +50734,7 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>ARWR</t>
+          <t>IRDM</t>
         </is>
       </c>
       <c r="B114" s="14" t="inlineStr">
@@ -50779,58 +50744,62 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>WATCH/GS</t>
+          <t>WATCH</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>GROWTH</t>
+          <t>CORE</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>57.6</t>
-        </is>
-      </c>
-      <c r="F114" t="inlineStr"/>
+          <t>57.8</t>
+        </is>
+      </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>0.246</t>
+        </is>
+      </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>7.9</t>
+          <t>1.98</t>
         </is>
       </c>
       <c r="I114" t="inlineStr">
         <is>
-          <t>1.3</t>
+          <t>5.9</t>
         </is>
       </c>
       <c r="J114" t="inlineStr">
         <is>
-          <t>1.6</t>
+          <t>2.6</t>
         </is>
       </c>
       <c r="K114" t="inlineStr">
         <is>
-          <t>0.79</t>
+          <t>3.81</t>
         </is>
       </c>
       <c r="L114" t="inlineStr">
         <is>
-          <t>11.9</t>
+          <t>27.1</t>
         </is>
       </c>
       <c r="M114" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>Communication Services</t>
         </is>
       </c>
       <c r="N114" t="inlineStr">
         <is>
-          <t>rev +23258%/yr, not yet FCF-safe</t>
+          <t>mature / stable</t>
         </is>
       </c>
       <c r="O114" t="inlineStr"/>
@@ -61257,10 +61226,8 @@
           <t>CORE</t>
         </is>
       </c>
-      <c r="L29" t="inlineStr">
-        <is>
-          <t>76.7</t>
-        </is>
+      <c r="L29" t="n">
+        <v>76.59999999999999</v>
       </c>
     </row>
     <row r="30">
@@ -62533,10 +62500,8 @@
           <t>GROWTH</t>
         </is>
       </c>
-      <c r="L51" t="inlineStr">
-        <is>
-          <t>57.6</t>
-        </is>
+      <c r="L51" t="n">
+        <v>64.2</v>
       </c>
     </row>
     <row r="52">
@@ -66883,10 +66848,8 @@
           <t>CORE</t>
         </is>
       </c>
-      <c r="L126" t="inlineStr">
-        <is>
-          <t>76.7</t>
-        </is>
+      <c r="L126" t="n">
+        <v>76.59999999999999</v>
       </c>
     </row>
     <row r="127">

--- a/STS_holy_grail.xlsx
+++ b/STS_holy_grail.xlsx
@@ -51995,29 +51995,45 @@
           <t>DECLINING</t>
         </is>
       </c>
-      <c r="E105" t="n">
-        <v>60.1</v>
-      </c>
-      <c r="F105" t="n">
-        <v>0.093</v>
-      </c>
-      <c r="G105" t="n">
-        <v>6</v>
-      </c>
-      <c r="H105" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="I105" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="J105" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="K105" t="n">
-        <v>0.49</v>
-      </c>
-      <c r="L105" t="n">
-        <v>3.5</v>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>60.1</t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>0.093</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H105" t="inlineStr">
+        <is>
+          <t>6.2</t>
+        </is>
+      </c>
+      <c r="I105" t="inlineStr">
+        <is>
+          <t>3.8</t>
+        </is>
+      </c>
+      <c r="J105" t="inlineStr">
+        <is>
+          <t>6.4</t>
+        </is>
+      </c>
+      <c r="K105" t="inlineStr">
+        <is>
+          <t>0.49</t>
+        </is>
+      </c>
+      <c r="L105" t="inlineStr">
+        <is>
+          <t>3.5</t>
+        </is>
       </c>
       <c r="M105" t="inlineStr">
         <is>
@@ -69230,8 +69246,10 @@
           <t>DECLINING</t>
         </is>
       </c>
-      <c r="L132" t="n">
-        <v>60.1</v>
+      <c r="L132" t="inlineStr">
+        <is>
+          <t>60.1</t>
+        </is>
       </c>
     </row>
     <row r="133">

--- a/STS_holy_grail.xlsx
+++ b/STS_holy_grail.xlsx
@@ -880,7 +880,7 @@
     <col width="6" customWidth="1" min="15" max="15"/>
     <col width="12" customWidth="1" min="16" max="16"/>
     <col width="17" customWidth="1" min="17" max="17"/>
-    <col width="9" customWidth="1" min="18" max="18"/>
+    <col width="10" customWidth="1" min="18" max="18"/>
     <col width="60" customWidth="1" min="19" max="19"/>
     <col width="12" customWidth="1" min="20" max="20"/>
     <col width="12" customWidth="1" min="21" max="21"/>
@@ -1163,45 +1163,21 @@
           <t>FAIL/GS</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>D200G</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>Pending</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>G</t>
-        </is>
-      </c>
       <c r="G2" t="n">
         <v>3.2</v>
       </c>
       <c r="H2" t="n">
         <v>-1.3</v>
       </c>
-      <c r="M2" t="n">
-        <v>8.1</v>
-      </c>
-      <c r="P2" t="n">
-        <v>8.1</v>
-      </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>NO PRICE</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
           <t>RE-QUAL D200G 2026-10-15</t>
         </is>
-      </c>
-      <c r="AI2" t="n">
-        <v>35.09000015258789</v>
       </c>
     </row>
     <row r="3">
@@ -1218,50 +1194,21 @@
           <t>WATCH</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>DLB</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>Pending</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>G</t>
-        </is>
-      </c>
       <c r="G3" t="n">
         <v>2.7</v>
       </c>
       <c r="H3" t="n">
         <v>2.1</v>
       </c>
-      <c r="M3" t="n">
-        <v>-9.699999999999999</v>
-      </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>WR20</t>
-        </is>
-      </c>
-      <c r="P3" t="n">
-        <v>-25.7</v>
-      </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>NO PRICE</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
           <t>RE-QUAL WR20 2026-10-15</t>
         </is>
-      </c>
-      <c r="AI3" t="n">
-        <v>39.22999954223633</v>
       </c>
     </row>
     <row r="4">
@@ -1308,9 +1255,6 @@
       <c r="M4" t="n">
         <v>1.5</v>
       </c>
-      <c r="N4" t="n">
-        <v>11.5</v>
-      </c>
       <c r="P4" t="n">
         <v>-22.3</v>
       </c>
@@ -1438,9 +1382,6 @@
       <c r="M5" t="n">
         <v>1.2</v>
       </c>
-      <c r="N5" t="n">
-        <v>2.8</v>
-      </c>
       <c r="P5" t="n">
         <v>2.8</v>
       </c>
@@ -1562,9 +1503,6 @@
       <c r="M6" t="n">
         <v>-8.300000000000001</v>
       </c>
-      <c r="N6" t="n">
-        <v>-3.2</v>
-      </c>
       <c r="O6" t="inlineStr">
         <is>
           <t>WR20</t>
@@ -1697,9 +1635,6 @@
       <c r="M7" t="n">
         <v>20.1</v>
       </c>
-      <c r="N7" t="n">
-        <v>24.4</v>
-      </c>
       <c r="P7" t="n">
         <v>2.6</v>
       </c>
@@ -1821,9 +1756,6 @@
       <c r="M8" t="n">
         <v>-8.4</v>
       </c>
-      <c r="N8" t="n">
-        <v>-6.1</v>
-      </c>
       <c r="P8" t="n">
         <v>-13.4</v>
       </c>
@@ -1951,9 +1883,6 @@
       <c r="M9" t="n">
         <v>3.6</v>
       </c>
-      <c r="N9" t="n">
-        <v>10.9</v>
-      </c>
       <c r="P9" t="n">
         <v>-6.7</v>
       </c>
@@ -2076,14 +2005,11 @@
         <v>35</v>
       </c>
       <c r="L10" t="n">
-        <v>-4.35</v>
+        <v>-4.37</v>
       </c>
       <c r="M10" t="n">
         <v>-9.199999999999999</v>
       </c>
-      <c r="N10" t="n">
-        <v>-5</v>
-      </c>
       <c r="O10" t="inlineStr">
         <is>
           <t>WR40</t>
@@ -2148,7 +2074,7 @@
         <v>4.03</v>
       </c>
       <c r="AL10" t="n">
-        <v>-4.35</v>
+        <v>-4.37</v>
       </c>
       <c r="AM10" t="n">
         <v>4.3</v>
@@ -2210,9 +2136,6 @@
       <c r="M11" t="n">
         <v>1</v>
       </c>
-      <c r="N11" t="n">
-        <v>5.2</v>
-      </c>
       <c r="P11" t="n">
         <v>-5.4</v>
       </c>
@@ -2334,9 +2257,6 @@
       <c r="M12" t="n">
         <v>-5.1</v>
       </c>
-      <c r="N12" t="n">
-        <v>0.7</v>
-      </c>
       <c r="O12" t="inlineStr">
         <is>
           <t>WR20</t>
@@ -2469,9 +2389,6 @@
       <c r="M13" t="n">
         <v>-22.7</v>
       </c>
-      <c r="N13" t="n">
-        <v>-25.4</v>
-      </c>
       <c r="P13" t="n">
         <v>-32.1</v>
       </c>
@@ -2593,9 +2510,6 @@
       <c r="M14" t="n">
         <v>-3.2</v>
       </c>
-      <c r="N14" t="n">
-        <v>-24</v>
-      </c>
       <c r="O14" t="inlineStr">
         <is>
           <t>WR20</t>
@@ -2727,9 +2641,6 @@
       <c r="M15" t="n">
         <v>1.5</v>
       </c>
-      <c r="N15" t="n">
-        <v>-3.2</v>
-      </c>
       <c r="P15" t="n">
         <v>-12.8</v>
       </c>
@@ -2857,9 +2768,6 @@
       <c r="M16" t="n">
         <v>0.3</v>
       </c>
-      <c r="N16" t="n">
-        <v>0</v>
-      </c>
       <c r="P16" t="n">
         <v>-14.8</v>
       </c>
@@ -2987,9 +2895,6 @@
       <c r="M17" t="n">
         <v>-0.6</v>
       </c>
-      <c r="N17" t="n">
-        <v>8.6</v>
-      </c>
       <c r="P17" t="n">
         <v>-3.8</v>
       </c>
@@ -3120,9 +3025,6 @@
       <c r="M18" t="n">
         <v>2.2</v>
       </c>
-      <c r="N18" t="n">
-        <v>18.8</v>
-      </c>
       <c r="P18" t="n">
         <v>-16.6</v>
       </c>
@@ -3253,9 +3155,6 @@
       <c r="M19" t="n">
         <v>-8</v>
       </c>
-      <c r="N19" t="n">
-        <v>-7</v>
-      </c>
       <c r="P19" t="n">
         <v>-9.199999999999999</v>
       </c>
@@ -3377,9 +3276,6 @@
       <c r="M20" t="n">
         <v>-29.1</v>
       </c>
-      <c r="N20" t="n">
-        <v>-20.6</v>
-      </c>
       <c r="P20" t="n">
         <v>-29.3</v>
       </c>
@@ -3510,9 +3406,6 @@
       <c r="M21" t="n">
         <v>-0.3</v>
       </c>
-      <c r="N21" t="n">
-        <v>5.9</v>
-      </c>
       <c r="P21" t="n">
         <v>-1.9</v>
       </c>
@@ -3640,9 +3533,6 @@
       <c r="M22" t="n">
         <v>5.1</v>
       </c>
-      <c r="N22" t="n">
-        <v>7.9</v>
-      </c>
       <c r="P22" t="n">
         <v>-1</v>
       </c>
@@ -3773,9 +3663,6 @@
       <c r="M23" t="n">
         <v>3.4</v>
       </c>
-      <c r="N23" t="n">
-        <v>7.7</v>
-      </c>
       <c r="P23" t="n">
         <v>-2.8</v>
       </c>
@@ -3909,9 +3796,6 @@
       <c r="M24" t="n">
         <v>-8.800000000000001</v>
       </c>
-      <c r="N24" t="n">
-        <v>-2.7</v>
-      </c>
       <c r="O24" t="inlineStr">
         <is>
           <t>WR20</t>
@@ -4047,9 +3931,6 @@
       <c r="M25" t="n">
         <v>-35.8</v>
       </c>
-      <c r="N25" t="n">
-        <v>-35.9</v>
-      </c>
       <c r="P25" t="n">
         <v>-38.7</v>
       </c>
@@ -4174,9 +4055,6 @@
       <c r="M26" t="n">
         <v>-6.9</v>
       </c>
-      <c r="N26" t="n">
-        <v>1.3</v>
-      </c>
       <c r="P26" t="n">
         <v>-7.1</v>
       </c>
@@ -4310,9 +4188,6 @@
       <c r="M27" t="n">
         <v>-12.6</v>
       </c>
-      <c r="N27" t="n">
-        <v>2.4</v>
-      </c>
       <c r="P27" t="n">
         <v>-15</v>
       </c>
@@ -4354,7 +4229,7 @@
         <v>10.82</v>
       </c>
       <c r="AC27" t="n">
-        <v>15.79</v>
+        <v>15.81</v>
       </c>
       <c r="AD27" t="n">
         <v>-5.13</v>
@@ -4384,7 +4259,7 @@
         <v>-5.13</v>
       </c>
       <c r="AM27" t="n">
-        <v>15.79</v>
+        <v>15.81</v>
       </c>
       <c r="AN27" t="n">
         <v>14</v>
@@ -4446,9 +4321,6 @@
       <c r="M28" t="n">
         <v>-8.6</v>
       </c>
-      <c r="N28" t="n">
-        <v>-32.1</v>
-      </c>
       <c r="O28" t="inlineStr">
         <is>
           <t>WR20</t>
@@ -4589,9 +4461,6 @@
       <c r="M29" t="n">
         <v>-3.7</v>
       </c>
-      <c r="N29" t="n">
-        <v>-6</v>
-      </c>
       <c r="O29" t="inlineStr">
         <is>
           <t>WR20</t>
@@ -4721,9 +4590,6 @@
       <c r="M30" t="n">
         <v>3.6</v>
       </c>
-      <c r="N30" t="n">
-        <v>17.5</v>
-      </c>
       <c r="P30" t="n">
         <v>-8.6</v>
       </c>
@@ -4857,9 +4723,6 @@
       <c r="M31" t="n">
         <v>1.2</v>
       </c>
-      <c r="N31" t="n">
-        <v>-3.8</v>
-      </c>
       <c r="P31" t="n">
         <v>-9.1</v>
       </c>
@@ -4993,9 +4856,6 @@
       <c r="M32" t="n">
         <v>-25.1</v>
       </c>
-      <c r="N32" t="n">
-        <v>-18.2</v>
-      </c>
       <c r="P32" t="n">
         <v>-26.9</v>
       </c>
@@ -5126,9 +4986,6 @@
       <c r="M33" t="n">
         <v>-12.9</v>
       </c>
-      <c r="N33" t="n">
-        <v>-13.5</v>
-      </c>
       <c r="P33" t="n">
         <v>-19.3</v>
       </c>
@@ -5253,9 +5110,6 @@
       <c r="M34" t="n">
         <v>17.3</v>
       </c>
-      <c r="N34" t="n">
-        <v>20.3</v>
-      </c>
       <c r="P34" t="n">
         <v>11.4</v>
       </c>
@@ -5380,9 +5234,6 @@
       <c r="M35" t="n">
         <v>-12.3</v>
       </c>
-      <c r="N35" t="n">
-        <v>-0.8</v>
-      </c>
       <c r="P35" t="n">
         <v>-16.1</v>
       </c>
@@ -5516,9 +5367,6 @@
       <c r="M36" t="n">
         <v>-18.4</v>
       </c>
-      <c r="N36" t="n">
-        <v>-23.4</v>
-      </c>
       <c r="P36" t="n">
         <v>-19.9</v>
       </c>
@@ -5643,9 +5491,6 @@
       <c r="M37" t="n">
         <v>-17</v>
       </c>
-      <c r="N37" t="n">
-        <v>-11.5</v>
-      </c>
       <c r="P37" t="n">
         <v>-20.1</v>
       </c>
@@ -5776,9 +5621,6 @@
       <c r="M38" t="n">
         <v>7.7</v>
       </c>
-      <c r="N38" t="n">
-        <v>12.8</v>
-      </c>
       <c r="P38" t="n">
         <v>5.6</v>
       </c>
@@ -5909,9 +5751,6 @@
       <c r="M39" t="n">
         <v>3.5</v>
       </c>
-      <c r="N39" t="n">
-        <v>19.9</v>
-      </c>
       <c r="P39" t="n">
         <v>-30.3</v>
       </c>
@@ -6045,9 +5884,6 @@
       <c r="M40" t="n">
         <v>2.4</v>
       </c>
-      <c r="N40" t="n">
-        <v>9.1</v>
-      </c>
       <c r="P40" t="n">
         <v>-4.8</v>
       </c>
@@ -6172,9 +6008,6 @@
       <c r="M41" t="n">
         <v>-17.5</v>
       </c>
-      <c r="N41" t="n">
-        <v>-15.2</v>
-      </c>
       <c r="P41" t="n">
         <v>-20</v>
       </c>
@@ -6305,9 +6138,6 @@
       <c r="M42" t="n">
         <v>4.6</v>
       </c>
-      <c r="N42" t="n">
-        <v>7.2</v>
-      </c>
       <c r="P42" t="n">
         <v>-8.6</v>
       </c>
@@ -6435,9 +6265,6 @@
       <c r="M43" t="n">
         <v>-10.8</v>
       </c>
-      <c r="N43" t="n">
-        <v>32.4</v>
-      </c>
       <c r="P43" t="n">
         <v>-27.7</v>
       </c>
@@ -6579,9 +6406,6 @@
       <c r="M44" t="n">
         <v>-23</v>
       </c>
-      <c r="N44" t="n">
-        <v>-19.8</v>
-      </c>
       <c r="P44" t="n">
         <v>-28</v>
       </c>
@@ -6709,9 +6533,6 @@
       <c r="M45" t="n">
         <v>-10.3</v>
       </c>
-      <c r="N45" t="n">
-        <v>3.9</v>
-      </c>
       <c r="P45" t="n">
         <v>-19.9</v>
       </c>
@@ -6853,9 +6674,6 @@
       <c r="M46" t="n">
         <v>-5.4</v>
       </c>
-      <c r="N46" t="n">
-        <v>-10.4</v>
-      </c>
       <c r="P46" t="n">
         <v>-12.5</v>
       </c>
@@ -6988,9 +6806,6 @@
       <c r="M47" t="n">
         <v>-5.7</v>
       </c>
-      <c r="N47" t="n">
-        <v>-1.2</v>
-      </c>
       <c r="O47" t="inlineStr">
         <is>
           <t>WR20</t>
@@ -7123,9 +6938,6 @@
       <c r="M48" t="n">
         <v>10</v>
       </c>
-      <c r="N48" t="n">
-        <v>-13</v>
-      </c>
       <c r="P48" t="n">
         <v>7.9</v>
       </c>
@@ -7272,9 +7084,6 @@
       <c r="M49" t="n">
         <v>1.2</v>
       </c>
-      <c r="N49" t="n">
-        <v>10.9</v>
-      </c>
       <c r="P49" t="n">
         <v>-32.7</v>
       </c>
@@ -7413,9 +7222,6 @@
       <c r="M50" t="n">
         <v>6.7</v>
       </c>
-      <c r="N50" t="n">
-        <v>9.5</v>
-      </c>
       <c r="P50" t="n">
         <v>6.2</v>
       </c>
@@ -7557,9 +7363,6 @@
       <c r="M51" t="n">
         <v>-34.1</v>
       </c>
-      <c r="N51" t="n">
-        <v>-29.1</v>
-      </c>
       <c r="P51" t="n">
         <v>-36.2</v>
       </c>
@@ -7698,9 +7501,6 @@
       <c r="M52" t="n">
         <v>-3.6</v>
       </c>
-      <c r="N52" t="n">
-        <v>0.7</v>
-      </c>
       <c r="O52" t="inlineStr">
         <is>
           <t>WR30</t>
@@ -7847,9 +7647,6 @@
       <c r="M53" t="n">
         <v>5.1</v>
       </c>
-      <c r="N53" t="n">
-        <v>-1.3</v>
-      </c>
       <c r="P53" t="n">
         <v>2.1</v>
       </c>
@@ -7991,9 +7788,6 @@
       <c r="M54" t="n">
         <v>1.9</v>
       </c>
-      <c r="N54" t="n">
-        <v>7.2</v>
-      </c>
       <c r="P54" t="n">
         <v>-19.9</v>
       </c>
@@ -8135,9 +7929,6 @@
       <c r="M55" t="n">
         <v>-10.3</v>
       </c>
-      <c r="N55" t="n">
-        <v>-3.2</v>
-      </c>
       <c r="P55" t="n">
         <v>-41.2</v>
       </c>
@@ -8270,9 +8061,6 @@
       <c r="M56" t="n">
         <v>-3.1</v>
       </c>
-      <c r="N56" t="n">
-        <v>18.8</v>
-      </c>
       <c r="O56" t="inlineStr">
         <is>
           <t>WR30</t>
@@ -8419,9 +8207,6 @@
       <c r="M57" t="n">
         <v>9.9</v>
       </c>
-      <c r="N57" t="n">
-        <v>9.4</v>
-      </c>
       <c r="P57" t="n">
         <v>-21</v>
       </c>
@@ -8565,9 +8350,6 @@
       <c r="M58" t="n">
         <v>6.2</v>
       </c>
-      <c r="N58" t="n">
-        <v>4.4</v>
-      </c>
       <c r="P58" t="n">
         <v>-12.3</v>
       </c>
@@ -8695,9 +8477,6 @@
       <c r="M59" t="n">
         <v>31.8</v>
       </c>
-      <c r="N59" t="n">
-        <v>30.6</v>
-      </c>
       <c r="P59" t="n">
         <v>26.6</v>
       </c>
@@ -8771,7 +8550,7 @@
         <v>-11.66</v>
       </c>
       <c r="AM59" t="n">
-        <v>5.48</v>
+        <v>5.5</v>
       </c>
       <c r="AN59" t="n">
         <v>24</v>
@@ -8836,9 +8615,6 @@
       <c r="M60" t="n">
         <v>-3.3</v>
       </c>
-      <c r="N60" t="n">
-        <v>-13.1</v>
-      </c>
       <c r="O60" t="inlineStr">
         <is>
           <t>WR20</t>
@@ -8976,9 +8752,6 @@
       <c r="M61" t="n">
         <v>16.3</v>
       </c>
-      <c r="N61" t="n">
-        <v>-18.9</v>
-      </c>
       <c r="P61" t="n">
         <v>13.8</v>
       </c>
@@ -9111,9 +8884,6 @@
       <c r="M62" t="n">
         <v>1.4</v>
       </c>
-      <c r="N62" t="n">
-        <v>-8.800000000000001</v>
-      </c>
       <c r="P62" t="n">
         <v>-9.800000000000001</v>
       </c>
@@ -9173,7 +8943,7 @@
         <v>-13.47</v>
       </c>
       <c r="AL62" t="n">
-        <v>-16.29</v>
+        <v>-16.3</v>
       </c>
       <c r="AM62" t="n">
         <v>0.74</v>
@@ -9246,9 +9016,6 @@
       <c r="M63" t="n">
         <v>0.4</v>
       </c>
-      <c r="N63" t="n">
-        <v>13.6</v>
-      </c>
       <c r="P63" t="n">
         <v>2.1</v>
       </c>
@@ -9390,9 +9157,6 @@
       <c r="M64" t="n">
         <v>-30.4</v>
       </c>
-      <c r="N64" t="n">
-        <v>-33</v>
-      </c>
       <c r="P64" t="n">
         <v>-33.7</v>
       </c>
@@ -9520,9 +9284,6 @@
       <c r="M65" t="n">
         <v>-4.9</v>
       </c>
-      <c r="N65" t="n">
-        <v>-5.7</v>
-      </c>
       <c r="P65" t="n">
         <v>-6.3</v>
       </c>
@@ -9650,28 +9411,25 @@
         <v>-9.6</v>
       </c>
       <c r="I66" t="n">
-        <v>-3.4</v>
+        <v>-3.2</v>
       </c>
       <c r="J66" t="n">
-        <v>5.48</v>
+        <v>5.19</v>
       </c>
       <c r="K66" t="n">
-        <v>7.06</v>
+        <v>6.76</v>
       </c>
       <c r="L66" t="n">
-        <v>-0.79</v>
+        <v>-1.07</v>
       </c>
       <c r="M66" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="N66" t="n">
-        <v>2.7</v>
+        <v>4.9</v>
       </c>
       <c r="P66" t="n">
         <v>3.8</v>
       </c>
       <c r="Q66" t="n">
-        <v>74.11</v>
+        <v>73.90000000000001</v>
       </c>
       <c r="R66" t="inlineStr">
         <is>
@@ -9707,16 +9465,16 @@
         </is>
       </c>
       <c r="AB66" t="n">
-        <v>9.52</v>
+        <v>9.220000000000001</v>
       </c>
       <c r="AC66" t="n">
-        <v>11.19</v>
+        <v>10.88</v>
       </c>
       <c r="AD66" t="n">
-        <v>-0.79</v>
+        <v>-1.07</v>
       </c>
       <c r="AE66" t="n">
-        <v>-0.79</v>
+        <v>-1.07</v>
       </c>
       <c r="AF66" t="n">
         <v>77.5</v>
@@ -9740,7 +9498,7 @@
         <v>-2.53</v>
       </c>
       <c r="AM66" t="n">
-        <v>11.19</v>
+        <v>10.88</v>
       </c>
       <c r="AN66" t="n">
         <v>27</v>
@@ -9805,9 +9563,6 @@
       <c r="M67" t="n">
         <v>4.1</v>
       </c>
-      <c r="N67" t="n">
-        <v>-12.5</v>
-      </c>
       <c r="P67" t="n">
         <v>-6.5</v>
       </c>
@@ -9940,9 +9695,6 @@
       <c r="M68" t="n">
         <v>-3.6</v>
       </c>
-      <c r="N68" t="n">
-        <v>32.8</v>
-      </c>
       <c r="O68" t="inlineStr">
         <is>
           <t>WR20</t>
@@ -10089,9 +9841,6 @@
       <c r="M69" t="n">
         <v>-32.6</v>
       </c>
-      <c r="N69" t="n">
-        <v>-27.2</v>
-      </c>
       <c r="P69" t="n">
         <v>-40.5</v>
       </c>
@@ -10219,9 +9968,6 @@
       <c r="M70" t="n">
         <v>-4.7</v>
       </c>
-      <c r="N70" t="n">
-        <v>-15.6</v>
-      </c>
       <c r="O70" t="inlineStr">
         <is>
           <t>WR30</t>
@@ -10297,7 +10043,7 @@
         <v>-15.67</v>
       </c>
       <c r="AL70" t="n">
-        <v>-19.73</v>
+        <v>-19.98</v>
       </c>
       <c r="AM70" t="n">
         <v>6.65</v>
@@ -10370,9 +10116,6 @@
       <c r="M71" t="n">
         <v>-5.7</v>
       </c>
-      <c r="N71" t="n">
-        <v>-44.9</v>
-      </c>
       <c r="O71" t="inlineStr">
         <is>
           <t>WR20</t>
@@ -10524,9 +10267,6 @@
       <c r="M72" t="n">
         <v>-29.7</v>
       </c>
-      <c r="N72" t="n">
-        <v>-25.6</v>
-      </c>
       <c r="P72" t="n">
         <v>-44.3</v>
       </c>
@@ -10654,9 +10394,6 @@
       <c r="M73" t="n">
         <v>0.3</v>
       </c>
-      <c r="N73" t="n">
-        <v>-56.1</v>
-      </c>
       <c r="P73" t="n">
         <v>-32.8</v>
       </c>
@@ -10716,7 +10453,7 @@
         <v>-57.74</v>
       </c>
       <c r="AL73" t="n">
-        <v>-63.57</v>
+        <v>-63.53</v>
       </c>
       <c r="AM73" t="n">
         <v>0.01</v>
@@ -10789,9 +10526,6 @@
       <c r="M74" t="n">
         <v>10.7</v>
       </c>
-      <c r="N74" t="n">
-        <v>7.7</v>
-      </c>
       <c r="P74" t="n">
         <v>-10.6</v>
       </c>
@@ -10938,9 +10672,6 @@
       <c r="M75" t="n">
         <v>9.800000000000001</v>
       </c>
-      <c r="N75" t="n">
-        <v>-1.7</v>
-      </c>
       <c r="P75" t="n">
         <v>8.5</v>
       </c>
@@ -11082,9 +10813,6 @@
       <c r="M76" t="n">
         <v>3.3</v>
       </c>
-      <c r="N76" t="n">
-        <v>14.7</v>
-      </c>
       <c r="P76" t="n">
         <v>-14.5</v>
       </c>
@@ -11223,9 +10951,6 @@
       <c r="M77" t="n">
         <v>-0.9</v>
       </c>
-      <c r="N77" t="n">
-        <v>6.1</v>
-      </c>
       <c r="P77" t="n">
         <v>-12.1</v>
       </c>
@@ -11367,9 +11092,6 @@
       <c r="M78" t="n">
         <v>53.6</v>
       </c>
-      <c r="N78" t="n">
-        <v>47.6</v>
-      </c>
       <c r="P78" t="n">
         <v>-11.8</v>
       </c>
@@ -11502,9 +11224,6 @@
       <c r="M79" t="n">
         <v>-20.5</v>
       </c>
-      <c r="N79" t="n">
-        <v>-30.1</v>
-      </c>
       <c r="P79" t="n">
         <v>-27.1</v>
       </c>
@@ -11637,9 +11356,6 @@
       <c r="M80" t="n">
         <v>1.1</v>
       </c>
-      <c r="N80" t="n">
-        <v>-19.9</v>
-      </c>
       <c r="P80" t="n">
         <v>-9.199999999999999</v>
       </c>
@@ -11786,9 +11502,6 @@
       <c r="M81" t="n">
         <v>-5</v>
       </c>
-      <c r="N81" t="n">
-        <v>11.5</v>
-      </c>
       <c r="O81" t="inlineStr">
         <is>
           <t>WR40</t>
@@ -11935,9 +11648,6 @@
       <c r="M82" t="n">
         <v>-4.1</v>
       </c>
-      <c r="N82" t="n">
-        <v>19.9</v>
-      </c>
       <c r="O82" t="inlineStr">
         <is>
           <t>WR30</t>
@@ -12084,9 +11794,6 @@
       <c r="M83" t="n">
         <v>1.4</v>
       </c>
-      <c r="N83" t="n">
-        <v>-6.2</v>
-      </c>
       <c r="P83" t="n">
         <v>-3.5</v>
       </c>
@@ -12214,9 +11921,6 @@
       <c r="M84" t="n">
         <v>4</v>
       </c>
-      <c r="N84" t="n">
-        <v>-13.1</v>
-      </c>
       <c r="P84" t="n">
         <v>-14.9</v>
       </c>
@@ -12349,9 +12053,6 @@
       <c r="M85" t="n">
         <v>24.9</v>
       </c>
-      <c r="N85" t="n">
-        <v>30.9</v>
-      </c>
       <c r="P85" t="n">
         <v>-0.9</v>
       </c>
@@ -12493,9 +12194,6 @@
       <c r="M86" t="n">
         <v>-1.2</v>
       </c>
-      <c r="N86" t="n">
-        <v>-25.4</v>
-      </c>
       <c r="P86" t="n">
         <v>-10.6</v>
       </c>
@@ -12642,9 +12340,6 @@
       <c r="M87" t="n">
         <v>-9.699999999999999</v>
       </c>
-      <c r="N87" t="n">
-        <v>-14.7</v>
-      </c>
       <c r="O87" t="inlineStr">
         <is>
           <t>WR30</t>
@@ -12782,9 +12477,6 @@
       <c r="M88" t="n">
         <v>9.1</v>
       </c>
-      <c r="N88" t="n">
-        <v>-7.2</v>
-      </c>
       <c r="P88" t="n">
         <v>8.6</v>
       </c>
@@ -12931,9 +12623,6 @@
       <c r="M89" t="n">
         <v>-0.4</v>
       </c>
-      <c r="N89" t="n">
-        <v>7.2</v>
-      </c>
       <c r="O89" t="inlineStr">
         <is>
           <t>WR20</t>
@@ -13080,9 +12769,6 @@
       <c r="M90" t="n">
         <v>15</v>
       </c>
-      <c r="N90" t="n">
-        <v>14.5</v>
-      </c>
       <c r="P90" t="n">
         <v>11.6</v>
       </c>
@@ -13110,6 +12796,9 @@
       </c>
       <c r="W90" t="b">
         <v>0</v>
+      </c>
+      <c r="X90" s="13" t="n">
+        <v>46399</v>
       </c>
       <c r="Z90" t="n">
         <v>0</v>
@@ -13207,9 +12896,6 @@
       <c r="M91" t="n">
         <v>6.2</v>
       </c>
-      <c r="N91" t="n">
-        <v>-11.2</v>
-      </c>
       <c r="P91" t="n">
         <v>-3.5</v>
       </c>
@@ -13342,9 +13028,6 @@
       <c r="M92" t="n">
         <v>-4.6</v>
       </c>
-      <c r="N92" t="n">
-        <v>0.7</v>
-      </c>
       <c r="O92" t="inlineStr">
         <is>
           <t>WR30</t>
@@ -13496,9 +13179,6 @@
       <c r="M93" t="n">
         <v>6.9</v>
       </c>
-      <c r="N93" t="n">
-        <v>-3.4</v>
-      </c>
       <c r="P93" t="n">
         <v>5.4</v>
       </c>
@@ -13640,9 +13320,6 @@
       <c r="M94" t="n">
         <v>-8.5</v>
       </c>
-      <c r="N94" t="n">
-        <v>-18.1</v>
-      </c>
       <c r="O94" t="inlineStr">
         <is>
           <t>WR20</t>
@@ -13707,7 +13384,7 @@
         <v>-19.43</v>
       </c>
       <c r="AL94" t="n">
-        <v>-25.92</v>
+        <v>-26</v>
       </c>
       <c r="AM94" t="n">
         <v>4.08</v>
@@ -13780,9 +13457,6 @@
       <c r="M95" t="n">
         <v>16</v>
       </c>
-      <c r="N95" t="n">
-        <v>13.3</v>
-      </c>
       <c r="P95" t="n">
         <v>-20.2</v>
       </c>
@@ -13915,9 +13589,6 @@
       <c r="M96" t="n">
         <v>-8</v>
       </c>
-      <c r="N96" t="n">
-        <v>18.8</v>
-      </c>
       <c r="O96" t="inlineStr">
         <is>
           <t>WR40</t>
@@ -14064,9 +13735,6 @@
       <c r="M97" t="n">
         <v>4.3</v>
       </c>
-      <c r="N97" t="n">
-        <v>-17.9</v>
-      </c>
       <c r="P97" t="n">
         <v>-8.9</v>
       </c>
@@ -14199,9 +13867,6 @@
       <c r="M98" t="n">
         <v>32.9</v>
       </c>
-      <c r="N98" t="n">
-        <v>36.4</v>
-      </c>
       <c r="P98" t="n">
         <v>8.300000000000001</v>
       </c>
@@ -14343,9 +14008,6 @@
       <c r="M99" t="n">
         <v>1.8</v>
       </c>
-      <c r="N99" t="n">
-        <v>-1.2</v>
-      </c>
       <c r="P99" t="n">
         <v>-29.3</v>
       </c>
@@ -14489,9 +14151,6 @@
       <c r="M100" t="n">
         <v>9</v>
       </c>
-      <c r="N100" t="n">
-        <v>-16.1</v>
-      </c>
       <c r="P100" t="n">
         <v>-13.5</v>
       </c>
@@ -14635,9 +14294,6 @@
       <c r="M101" t="n">
         <v>5.4</v>
       </c>
-      <c r="N101" t="n">
-        <v>-24</v>
-      </c>
       <c r="P101" t="n">
         <v>-20</v>
       </c>
@@ -14784,9 +14440,6 @@
       <c r="M102" t="n">
         <v>8.699999999999999</v>
       </c>
-      <c r="N102" t="n">
-        <v>9.300000000000001</v>
-      </c>
       <c r="P102" t="n">
         <v>7.8</v>
       </c>
@@ -14928,9 +14581,6 @@
       <c r="M103" t="n">
         <v>4.2</v>
       </c>
-      <c r="N103" t="n">
-        <v>-13.1</v>
-      </c>
       <c r="P103" t="n">
         <v>-31.3</v>
       </c>
@@ -15074,9 +14724,6 @@
       <c r="M104" t="n">
         <v>8.699999999999999</v>
       </c>
-      <c r="N104" t="n">
-        <v>-9.5</v>
-      </c>
       <c r="P104" t="n">
         <v>-7.7</v>
       </c>
@@ -15218,9 +14865,6 @@
       <c r="M105" t="n">
         <v>4.9</v>
       </c>
-      <c r="N105" t="n">
-        <v>-13.2</v>
-      </c>
       <c r="P105" t="n">
         <v>-9</v>
       </c>
@@ -15367,9 +15011,6 @@
       <c r="M106" t="n">
         <v>8.9</v>
       </c>
-      <c r="N106" t="n">
-        <v>-10.7</v>
-      </c>
       <c r="P106" t="n">
         <v>-5.4</v>
       </c>
@@ -15516,9 +15157,6 @@
       <c r="M107" t="n">
         <v>-10.4</v>
       </c>
-      <c r="N107" t="n">
-        <v>-37.1</v>
-      </c>
       <c r="P107" t="n">
         <v>-13.3</v>
       </c>
@@ -15651,9 +15289,6 @@
       <c r="M108" t="n">
         <v>-9.5</v>
       </c>
-      <c r="N108" t="n">
-        <v>-16</v>
-      </c>
       <c r="P108" t="n">
         <v>-16.6</v>
       </c>
@@ -15786,9 +15421,6 @@
       <c r="M109" t="n">
         <v>30.3</v>
       </c>
-      <c r="N109" t="n">
-        <v>33.7</v>
-      </c>
       <c r="P109" t="n">
         <v>20.7</v>
       </c>
@@ -15935,9 +15567,6 @@
       <c r="M110" t="n">
         <v>3.7</v>
       </c>
-      <c r="N110" t="n">
-        <v>-17.8</v>
-      </c>
       <c r="P110" t="n">
         <v>1.7</v>
       </c>
@@ -16084,9 +15713,6 @@
       <c r="M111" t="n">
         <v>-12.7</v>
       </c>
-      <c r="N111" t="n">
-        <v>-24.5</v>
-      </c>
       <c r="P111" t="n">
         <v>-15.8</v>
       </c>
@@ -16219,9 +15845,6 @@
       <c r="M112" t="n">
         <v>-29.6</v>
       </c>
-      <c r="N112" t="n">
-        <v>-23.9</v>
-      </c>
       <c r="P112" t="n">
         <v>-39.2</v>
       </c>
@@ -16354,9 +15977,6 @@
       <c r="M113" t="n">
         <v>-19.2</v>
       </c>
-      <c r="N113" t="n">
-        <v>-30.4</v>
-      </c>
       <c r="P113" t="n">
         <v>-21.1</v>
       </c>
@@ -16489,9 +16109,6 @@
       <c r="M114" t="n">
         <v>48</v>
       </c>
-      <c r="N114" t="n">
-        <v>52.7</v>
-      </c>
       <c r="P114" t="n">
         <v>11.9</v>
       </c>
@@ -16633,9 +16250,6 @@
       <c r="M115" t="n">
         <v>-25.1</v>
       </c>
-      <c r="N115" t="n">
-        <v>-23.7</v>
-      </c>
       <c r="P115" t="n">
         <v>-31.4</v>
       </c>
@@ -16779,9 +16393,6 @@
       <c r="M116" t="n">
         <v>-9.5</v>
       </c>
-      <c r="N116" t="n">
-        <v>-12.5</v>
-      </c>
       <c r="O116" t="inlineStr">
         <is>
           <t>WR20</t>
@@ -16919,9 +16530,6 @@
       <c r="M117" t="n">
         <v>3.9</v>
       </c>
-      <c r="N117" t="n">
-        <v>12.5</v>
-      </c>
       <c r="P117" t="n">
         <v>-18</v>
       </c>
@@ -17065,9 +16673,6 @@
       <c r="M118" t="n">
         <v>31.7</v>
       </c>
-      <c r="N118" t="n">
-        <v>58.5</v>
-      </c>
       <c r="P118" t="n">
         <v>27</v>
       </c>
@@ -17209,9 +16814,6 @@
       <c r="M119" t="n">
         <v>4.4</v>
       </c>
-      <c r="N119" t="n">
-        <v>18.4</v>
-      </c>
       <c r="P119" t="n">
         <v>-31</v>
       </c>
@@ -17353,9 +16955,6 @@
       <c r="M120" t="n">
         <v>-0.7</v>
       </c>
-      <c r="N120" t="n">
-        <v>-42.6</v>
-      </c>
       <c r="O120" t="inlineStr">
         <is>
           <t>WR40</t>
@@ -17504,9 +17103,6 @@
       <c r="M121" t="n">
         <v>-5.6</v>
       </c>
-      <c r="N121" t="n">
-        <v>-46.6</v>
-      </c>
       <c r="O121" t="inlineStr">
         <is>
           <t>WR20</t>
@@ -17644,9 +17240,6 @@
       <c r="M122" t="n">
         <v>3.8</v>
       </c>
-      <c r="N122" t="n">
-        <v>32.8</v>
-      </c>
       <c r="P122" t="n">
         <v>-41.2</v>
       </c>
@@ -17793,9 +17386,6 @@
       <c r="M123" t="n">
         <v>-5.3</v>
       </c>
-      <c r="N123" t="n">
-        <v>-22.9</v>
-      </c>
       <c r="O123" t="inlineStr">
         <is>
           <t>WR20</t>
@@ -17933,9 +17523,6 @@
       <c r="M124" t="n">
         <v>0.8</v>
       </c>
-      <c r="N124" t="n">
-        <v>10.8</v>
-      </c>
       <c r="P124" t="n">
         <v>-13</v>
       </c>
@@ -18077,9 +17664,6 @@
       <c r="M125" t="n">
         <v>3.7</v>
       </c>
-      <c r="N125" t="n">
-        <v>8.1</v>
-      </c>
       <c r="P125" t="n">
         <v>-20.6</v>
       </c>
@@ -18212,9 +17796,6 @@
       <c r="M126" t="n">
         <v>3</v>
       </c>
-      <c r="N126" t="n">
-        <v>16.2</v>
-      </c>
       <c r="P126" t="n">
         <v>-30.4</v>
       </c>
@@ -18353,9 +17934,6 @@
       <c r="M127" t="n">
         <v>1.5</v>
       </c>
-      <c r="N127" t="n">
-        <v>-32.1</v>
-      </c>
       <c r="P127" t="n">
         <v>-24.7</v>
       </c>
@@ -18499,9 +18077,6 @@
       <c r="M128" t="n">
         <v>7.1</v>
       </c>
-      <c r="N128" t="n">
-        <v>-9.6</v>
-      </c>
       <c r="P128" t="n">
         <v>1.9</v>
       </c>
@@ -18645,9 +18220,6 @@
       <c r="M129" t="n">
         <v>-2.7</v>
       </c>
-      <c r="N129" t="n">
-        <v>-26.1</v>
-      </c>
       <c r="O129" t="inlineStr">
         <is>
           <t>WR30</t>
@@ -18799,9 +18371,6 @@
       <c r="M130" t="n">
         <v>1.7</v>
       </c>
-      <c r="N130" t="n">
-        <v>-20.5</v>
-      </c>
       <c r="P130" t="n">
         <v>-1.6</v>
       </c>
@@ -18948,9 +18517,6 @@
       <c r="M131" t="n">
         <v>4.8</v>
       </c>
-      <c r="N131" t="n">
-        <v>29.1</v>
-      </c>
       <c r="P131" t="n">
         <v>-33.7</v>
       </c>
@@ -19092,9 +18658,6 @@
       <c r="M132" t="n">
         <v>1.7</v>
       </c>
-      <c r="N132" t="n">
-        <v>-25.2</v>
-      </c>
       <c r="P132" t="n">
         <v>-12.3</v>
       </c>
@@ -19154,7 +18717,7 @@
         <v>-24.68</v>
       </c>
       <c r="AL132" t="n">
-        <v>-30.14</v>
+        <v>-30.13</v>
       </c>
       <c r="AM132" t="n">
         <v>1.78</v>
@@ -19227,9 +18790,6 @@
       <c r="M133" t="n">
         <v>52.9</v>
       </c>
-      <c r="N133" t="n">
-        <v>63.7</v>
-      </c>
       <c r="P133" t="n">
         <v>18.6</v>
       </c>
@@ -19371,9 +18931,6 @@
       <c r="M134" t="n">
         <v>1.4</v>
       </c>
-      <c r="N134" t="n">
-        <v>-3</v>
-      </c>
       <c r="P134" t="n">
         <v>-14.9</v>
       </c>
@@ -19515,9 +19072,6 @@
       <c r="M135" t="n">
         <v>52.3</v>
       </c>
-      <c r="N135" t="n">
-        <v>74.2</v>
-      </c>
       <c r="P135" t="n">
         <v>18</v>
       </c>
@@ -19659,9 +19213,6 @@
       <c r="M136" t="n">
         <v>-1.3</v>
       </c>
-      <c r="N136" t="n">
-        <v>7.2</v>
-      </c>
       <c r="P136" t="n">
         <v>-19.9</v>
       </c>
@@ -19803,9 +19354,6 @@
       <c r="M137" t="n">
         <v>37</v>
       </c>
-      <c r="N137" t="n">
-        <v>30.8</v>
-      </c>
       <c r="P137" t="n">
         <v>5.2</v>
       </c>
@@ -19947,9 +19495,6 @@
       <c r="M138" t="n">
         <v>13.5</v>
       </c>
-      <c r="N138" t="n">
-        <v>37.4</v>
-      </c>
       <c r="P138" t="n">
         <v>-21.7</v>
       </c>
@@ -20096,9 +19641,6 @@
       <c r="M139" t="n">
         <v>-11.1</v>
       </c>
-      <c r="N139" t="n">
-        <v>-3.2</v>
-      </c>
       <c r="P139" t="n">
         <v>-25.3</v>
       </c>
@@ -20240,9 +19782,6 @@
       <c r="M140" t="n">
         <v>9.699999999999999</v>
       </c>
-      <c r="N140" t="n">
-        <v>-1.8</v>
-      </c>
       <c r="P140" t="n">
         <v>3.2</v>
       </c>
@@ -20381,9 +19920,6 @@
       <c r="M141" t="n">
         <v>-24.2</v>
       </c>
-      <c r="N141" t="n">
-        <v>-34.3</v>
-      </c>
       <c r="P141" t="n">
         <v>-24.4</v>
       </c>
@@ -20530,9 +20066,6 @@
       <c r="M142" t="n">
         <v>5.1</v>
       </c>
-      <c r="N142" t="n">
-        <v>31.4</v>
-      </c>
       <c r="P142" t="n">
         <v>-32.6</v>
       </c>
@@ -20674,9 +20207,6 @@
       <c r="M143" t="n">
         <v>-14.4</v>
       </c>
-      <c r="N143" t="n">
-        <v>0</v>
-      </c>
       <c r="P143" t="n">
         <v>-14.3</v>
       </c>
@@ -20818,9 +20348,6 @@
       <c r="M144" t="n">
         <v>18.1</v>
       </c>
-      <c r="N144" t="n">
-        <v>6.8</v>
-      </c>
       <c r="P144" t="n">
         <v>16.9</v>
       </c>
@@ -20948,9 +20475,6 @@
       <c r="M145" t="n">
         <v>-11.4</v>
       </c>
-      <c r="N145" t="n">
-        <v>19.9</v>
-      </c>
       <c r="P145" t="n">
         <v>-30.7</v>
       </c>
@@ -21092,9 +20616,6 @@
       <c r="M146" t="n">
         <v>10.3</v>
       </c>
-      <c r="N146" t="n">
-        <v>15.9</v>
-      </c>
       <c r="P146" t="n">
         <v>10.8</v>
       </c>
@@ -21236,9 +20757,6 @@
       <c r="M147" t="n">
         <v>30.9</v>
       </c>
-      <c r="N147" t="n">
-        <v>23.6</v>
-      </c>
       <c r="P147" t="n">
         <v>12.6</v>
       </c>
@@ -21377,9 +20895,6 @@
       <c r="M148" t="n">
         <v>-22.2</v>
       </c>
-      <c r="N148" t="n">
-        <v>-6</v>
-      </c>
       <c r="P148" t="n">
         <v>-24.1</v>
       </c>
@@ -21521,9 +21036,6 @@
       <c r="M149" t="n">
         <v>-25.3</v>
       </c>
-      <c r="N149" t="n">
-        <v>-3.2</v>
-      </c>
       <c r="P149" t="n">
         <v>-50.8</v>
       </c>
@@ -21670,9 +21182,6 @@
       <c r="M150" t="n">
         <v>14.7</v>
       </c>
-      <c r="N150" t="n">
-        <v>-10.4</v>
-      </c>
       <c r="P150" t="n">
         <v>-0.5</v>
       </c>
@@ -21816,9 +21325,6 @@
       <c r="M151" t="n">
         <v>0.4</v>
       </c>
-      <c r="N151" t="n">
-        <v>26.1</v>
-      </c>
       <c r="P151" t="n">
         <v>-36.9</v>
       </c>
@@ -21960,9 +21466,6 @@
       <c r="M152" t="n">
         <v>-11.6</v>
       </c>
-      <c r="N152" t="n">
-        <v>-13.1</v>
-      </c>
       <c r="P152" t="n">
         <v>-32.4</v>
       </c>
@@ -22109,9 +21612,6 @@
       <c r="M153" t="n">
         <v>-4</v>
       </c>
-      <c r="N153" t="n">
-        <v>9.4</v>
-      </c>
       <c r="O153" t="inlineStr">
         <is>
           <t>WR20</t>
@@ -22258,9 +21758,6 @@
       <c r="M154" t="n">
         <v>-3</v>
       </c>
-      <c r="N154" t="n">
-        <v>44.2</v>
-      </c>
       <c r="O154" t="inlineStr">
         <is>
           <t>WR20</t>
@@ -22407,9 +21904,6 @@
       <c r="M155" t="n">
         <v>-29.1</v>
       </c>
-      <c r="N155" t="n">
-        <v>-25.6</v>
-      </c>
       <c r="P155" t="n">
         <v>-45.6</v>
       </c>
@@ -22542,9 +22036,6 @@
       <c r="M156" t="n">
         <v>-11.2</v>
       </c>
-      <c r="N156" t="n">
-        <v>-18.7</v>
-      </c>
       <c r="P156" t="n">
         <v>-31.4</v>
       </c>
@@ -22677,9 +22168,6 @@
       <c r="M157" t="n">
         <v>23.1</v>
       </c>
-      <c r="N157" t="n">
-        <v>10.6</v>
-      </c>
       <c r="P157" t="n">
         <v>21</v>
       </c>
@@ -22818,9 +22306,6 @@
       <c r="M158" t="n">
         <v>4.2</v>
       </c>
-      <c r="N158" t="n">
-        <v>5.2</v>
-      </c>
       <c r="P158" t="n">
         <v>-20.1</v>
       </c>
@@ -22959,9 +22444,6 @@
       <c r="M159" t="n">
         <v>7.3</v>
       </c>
-      <c r="N159" t="n">
-        <v>13.6</v>
-      </c>
       <c r="P159" t="n">
         <v>-6.2</v>
       </c>
@@ -23103,9 +22585,6 @@
       <c r="M160" t="n">
         <v>-24</v>
       </c>
-      <c r="N160" t="n">
-        <v>-13.6</v>
-      </c>
       <c r="P160" t="n">
         <v>-25.9</v>
       </c>
@@ -23252,7 +22731,7 @@
         <v>46241</v>
       </c>
       <c r="Z161" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AB161" t="n">
         <v>26.14</v>
@@ -23276,13 +22755,13 @@
         <v>8.76</v>
       </c>
       <c r="AI161" t="n">
-        <v>7.06</v>
+        <v>7.26</v>
       </c>
       <c r="AJ161" t="n">
-        <v>7.06</v>
+        <v>7.26</v>
       </c>
       <c r="AK161" t="n">
-        <v>-19.4</v>
+        <v>-17.12</v>
       </c>
       <c r="AL161" t="n">
         <v>-24.31</v>
@@ -23291,16 +22770,16 @@
         <v>26.14</v>
       </c>
       <c r="AN161" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AO161" t="n">
         <v>4</v>
       </c>
       <c r="AR161" t="n">
-        <v>4.92</v>
+        <v>4.42</v>
       </c>
       <c r="AT161" t="n">
-        <v>-24.32</v>
+        <v>-21.54</v>
       </c>
       <c r="AU161" t="inlineStr">
         <is>
@@ -23358,9 +22837,6 @@
       <c r="M162" t="n">
         <v>-14.9</v>
       </c>
-      <c r="N162" t="n">
-        <v>-16.8</v>
-      </c>
       <c r="P162" t="n">
         <v>-27</v>
       </c>
@@ -23504,9 +22980,6 @@
       <c r="M163" t="n">
         <v>47.6</v>
       </c>
-      <c r="N163" t="n">
-        <v>44.2</v>
-      </c>
       <c r="P163" t="n">
         <v>31.8</v>
       </c>
@@ -23648,9 +23121,6 @@
       <c r="M164" t="n">
         <v>25</v>
       </c>
-      <c r="N164" t="n">
-        <v>22.3</v>
-      </c>
       <c r="P164" t="n">
         <v>-6.8</v>
       </c>
@@ -23792,9 +23262,6 @@
       <c r="M165" t="n">
         <v>-21.4</v>
       </c>
-      <c r="N165" t="n">
-        <v>-12.5</v>
-      </c>
       <c r="P165" t="n">
         <v>-27.7</v>
       </c>
@@ -23936,9 +23403,6 @@
       <c r="M166" t="n">
         <v>-12.9</v>
       </c>
-      <c r="N166" t="n">
-        <v>5</v>
-      </c>
       <c r="P166" t="n">
         <v>-17.4</v>
       </c>
@@ -24080,9 +23544,6 @@
       <c r="M167" t="n">
         <v>-8.4</v>
       </c>
-      <c r="N167" t="n">
-        <v>12.5</v>
-      </c>
       <c r="O167" t="inlineStr">
         <is>
           <t>WR20</t>
@@ -24229,9 +23690,6 @@
       <c r="M168" t="n">
         <v>-3.5</v>
       </c>
-      <c r="N168" t="n">
-        <v>4.4</v>
-      </c>
       <c r="O168" t="inlineStr">
         <is>
           <t>WR20</t>
@@ -24378,9 +23836,6 @@
       <c r="M169" t="n">
         <v>-24.2</v>
       </c>
-      <c r="N169" t="n">
-        <v>-20.7</v>
-      </c>
       <c r="P169" t="n">
         <v>-25.7</v>
       </c>
@@ -24524,9 +23979,6 @@
       <c r="M170" t="n">
         <v>-28.8</v>
       </c>
-      <c r="N170" t="n">
-        <v>-14.7</v>
-      </c>
       <c r="P170" t="n">
         <v>-42.4</v>
       </c>
@@ -24668,9 +24120,6 @@
       <c r="M171" t="n">
         <v>28.5</v>
       </c>
-      <c r="N171" t="n">
-        <v>11.3</v>
-      </c>
       <c r="P171" t="n">
         <v>27</v>
       </c>
@@ -24812,9 +24261,6 @@
       <c r="M172" t="n">
         <v>52.9</v>
       </c>
-      <c r="N172" t="n">
-        <v>76.7</v>
-      </c>
       <c r="P172" t="n">
         <v>5.4</v>
       </c>
@@ -24962,9 +24408,6 @@
       <c r="M173" t="n">
         <v>-37.8</v>
       </c>
-      <c r="N173" t="n">
-        <v>-11.6</v>
-      </c>
       <c r="P173" t="n">
         <v>-50.4</v>
       </c>
@@ -25112,9 +24555,6 @@
       <c r="M174" t="n">
         <v>-14.6</v>
       </c>
-      <c r="N174" t="n">
-        <v>-3</v>
-      </c>
       <c r="P174" t="n">
         <v>-14.7</v>
       </c>
@@ -25262,9 +24702,6 @@
       <c r="M175" t="n">
         <v>9</v>
       </c>
-      <c r="N175" t="n">
-        <v>-17.9</v>
-      </c>
       <c r="P175" t="n">
         <v>-7.5</v>
       </c>
@@ -25408,9 +24845,6 @@
       <c r="M176" t="n">
         <v>46.7</v>
       </c>
-      <c r="N176" t="n">
-        <v>9.800000000000001</v>
-      </c>
       <c r="P176" t="n">
         <v>42.3</v>
       </c>
@@ -25563,9 +24997,6 @@
       <c r="M177" t="n">
         <v>48.1</v>
       </c>
-      <c r="N177" t="n">
-        <v>37.8</v>
-      </c>
       <c r="P177" t="n">
         <v>45.4</v>
       </c>
@@ -25713,9 +25144,6 @@
       <c r="M178" t="n">
         <v>56.6</v>
       </c>
-      <c r="N178" t="n">
-        <v>-13</v>
-      </c>
       <c r="P178" t="n">
         <v>50.5</v>
       </c>
@@ -25863,9 +25291,6 @@
       <c r="M179" t="n">
         <v>78.8</v>
       </c>
-      <c r="N179" t="n">
-        <v>15.7</v>
-      </c>
       <c r="P179" t="n">
         <v>73.3</v>
       </c>
@@ -26018,9 +25443,6 @@
       <c r="M180" t="n">
         <v>51.9</v>
       </c>
-      <c r="N180" t="n">
-        <v>21.2</v>
-      </c>
       <c r="P180" t="n">
         <v>49.5</v>
       </c>
@@ -26173,9 +25595,6 @@
       <c r="M181" t="n">
         <v>82.09999999999999</v>
       </c>
-      <c r="N181" t="n">
-        <v>30.3</v>
-      </c>
       <c r="P181" t="n">
         <v>75.8</v>
       </c>
@@ -26323,9 +25742,6 @@
       <c r="M182" t="n">
         <v>63.2</v>
       </c>
-      <c r="N182" t="n">
-        <v>51.4</v>
-      </c>
       <c r="P182" t="n">
         <v>43.2</v>
       </c>
@@ -26468,9 +25884,6 @@
       <c r="M183" t="n">
         <v>35.3</v>
       </c>
-      <c r="N183" t="n">
-        <v>8.5</v>
-      </c>
       <c r="P183" t="n">
         <v>24.9</v>
       </c>
@@ -26623,9 +26036,6 @@
       <c r="M184" t="n">
         <v>65.3</v>
       </c>
-      <c r="N184" t="n">
-        <v>2.8</v>
-      </c>
       <c r="P184" t="n">
         <v>53.9</v>
       </c>
@@ -26773,9 +26183,6 @@
       <c r="M185" t="n">
         <v>19.3</v>
       </c>
-      <c r="N185" t="n">
-        <v>-9.5</v>
-      </c>
       <c r="P185" t="n">
         <v>15.7</v>
       </c>
@@ -26923,9 +26330,6 @@
       <c r="M186" t="n">
         <v>51.8</v>
       </c>
-      <c r="N186" t="n">
-        <v>-1.7</v>
-      </c>
       <c r="P186" t="n">
         <v>46.3</v>
       </c>
@@ -27070,9 +26474,6 @@
       <c r="M187" t="n">
         <v>51.3</v>
       </c>
-      <c r="N187" t="n">
-        <v>13.1</v>
-      </c>
       <c r="P187" t="n">
         <v>48.1</v>
       </c>
@@ -27220,9 +26621,6 @@
       <c r="M188" t="n">
         <v>32.8</v>
       </c>
-      <c r="N188" t="n">
-        <v>12.2</v>
-      </c>
       <c r="P188" t="n">
         <v>24</v>
       </c>
@@ -27370,9 +26768,6 @@
       <c r="M189" t="n">
         <v>98.2</v>
       </c>
-      <c r="N189" t="n">
-        <v>51.8</v>
-      </c>
       <c r="P189" t="n">
         <v>70.09999999999999</v>
       </c>
@@ -27515,9 +26910,6 @@
       <c r="M190" t="n">
         <v>40.9</v>
       </c>
-      <c r="N190" t="n">
-        <v>-3.3</v>
-      </c>
       <c r="P190" t="n">
         <v>40</v>
       </c>
@@ -27662,9 +27054,6 @@
       <c r="M191" t="n">
         <v>51.1</v>
       </c>
-      <c r="N191" t="n">
-        <v>-7.2</v>
-      </c>
       <c r="P191" t="n">
         <v>36.8</v>
       </c>
@@ -27817,9 +27206,6 @@
       <c r="M192" t="n">
         <v>37.5</v>
       </c>
-      <c r="N192" t="n">
-        <v>-3.4</v>
-      </c>
       <c r="P192" t="n">
         <v>31.2</v>
       </c>
@@ -27958,9 +27344,6 @@
       <c r="M193" t="n">
         <v>-14.6</v>
       </c>
-      <c r="N193" t="n">
-        <v>18.4</v>
-      </c>
       <c r="P193" t="n">
         <v>-45.2</v>
       </c>
@@ -28113,9 +27496,6 @@
       <c r="M194" t="n">
         <v>16.5</v>
       </c>
-      <c r="N194" t="n">
-        <v>-14.8</v>
-      </c>
       <c r="P194" t="n">
         <v>12.5</v>
       </c>
@@ -28263,9 +27643,6 @@
       <c r="M195" t="n">
         <v>-8.800000000000001</v>
       </c>
-      <c r="N195" t="n">
-        <v>-24</v>
-      </c>
       <c r="P195" t="n">
         <v>-12.3</v>
       </c>
@@ -28418,9 +27795,6 @@
       <c r="M196" t="n">
         <v>41.1</v>
       </c>
-      <c r="N196" t="n">
-        <v>209.3</v>
-      </c>
       <c r="P196" t="n">
         <v>20.1</v>
       </c>
@@ -28568,9 +27942,6 @@
       <c r="M197" t="n">
         <v>9.9</v>
       </c>
-      <c r="N197" t="n">
-        <v>-10.7</v>
-      </c>
       <c r="P197" t="n">
         <v>10.1</v>
       </c>
@@ -28718,9 +28089,6 @@
       <c r="M198" t="n">
         <v>-27.9</v>
       </c>
-      <c r="N198" t="n">
-        <v>-42.6</v>
-      </c>
       <c r="P198" t="n">
         <v>-29.5</v>
       </c>
@@ -28873,9 +28241,6 @@
       <c r="M199" t="n">
         <v>-28.3</v>
       </c>
-      <c r="N199" t="n">
-        <v>8.1</v>
-      </c>
       <c r="P199" t="n">
         <v>-29.8</v>
       </c>
@@ -29018,9 +28383,6 @@
       <c r="M200" t="n">
         <v>19.8</v>
       </c>
-      <c r="N200" t="n">
-        <v>-0.2</v>
-      </c>
       <c r="P200" t="n">
         <v>15.6</v>
       </c>
@@ -29163,9 +28525,6 @@
       <c r="M201" t="n">
         <v>37.4</v>
       </c>
-      <c r="N201" t="n">
-        <v>-1.3</v>
-      </c>
       <c r="P201" t="n">
         <v>31.2</v>
       </c>
@@ -29310,9 +28669,6 @@
       <c r="M202" t="n">
         <v>73.3</v>
       </c>
-      <c r="N202" t="n">
-        <v>43.2</v>
-      </c>
       <c r="P202" t="n">
         <v>67.09999999999999</v>
       </c>
@@ -29460,9 +28816,6 @@
       <c r="M203" t="n">
         <v>8.699999999999999</v>
       </c>
-      <c r="N203" t="n">
-        <v>-30.4</v>
-      </c>
       <c r="P203" t="n">
         <v>4.4</v>
       </c>
@@ -29612,9 +28965,6 @@
       <c r="M204" t="n">
         <v>-20.5</v>
       </c>
-      <c r="N204" t="n">
-        <v>-20.7</v>
-      </c>
       <c r="P204" t="n">
         <v>-34.2</v>
       </c>
@@ -29752,9 +29102,6 @@
       <c r="M205" t="n">
         <v>-15.1</v>
       </c>
-      <c r="N205" t="n">
-        <v>-46.6</v>
-      </c>
       <c r="P205" t="n">
         <v>-13.4</v>
       </c>
@@ -29907,9 +29254,6 @@
       <c r="M206" t="n">
         <v>22.6</v>
       </c>
-      <c r="N206" t="n">
-        <v>-9.6</v>
-      </c>
       <c r="P206" t="n">
         <v>18.2</v>
       </c>
@@ -30048,9 +29392,6 @@
       <c r="M207" t="n">
         <v>26.4</v>
       </c>
-      <c r="N207" t="n">
-        <v>-25.7</v>
-      </c>
       <c r="P207" t="n">
         <v>14.8</v>
       </c>
@@ -30194,9 +29535,6 @@
       <c r="M208" t="n">
         <v>-28.1</v>
       </c>
-      <c r="N208" t="n">
-        <v>-56.1</v>
-      </c>
       <c r="P208" t="n">
         <v>-42.6</v>
       </c>
@@ -30270,7 +29608,7 @@
         <v>-49.19</v>
       </c>
       <c r="AL208" t="n">
-        <v>-56.19</v>
+        <v>-56.15</v>
       </c>
       <c r="AM208" t="n">
         <v>20.63</v>
@@ -30349,9 +29687,6 @@
       <c r="M209" t="n">
         <v>3.7</v>
       </c>
-      <c r="N209" t="n">
-        <v>-25.2</v>
-      </c>
       <c r="P209" t="n">
         <v>-1.3</v>
       </c>
@@ -30416,7 +29751,7 @@
         <v>-25.65</v>
       </c>
       <c r="AL209" t="n">
-        <v>-31.04</v>
+        <v>-31.03</v>
       </c>
       <c r="AM209" t="n">
         <v>4.41</v>
@@ -30495,9 +29830,6 @@
       <c r="M210" t="n">
         <v>61.4</v>
       </c>
-      <c r="N210" t="n">
-        <v>17.9</v>
-      </c>
       <c r="P210" t="n">
         <v>59.4</v>
       </c>
@@ -30642,9 +29974,6 @@
       <c r="M211" t="n">
         <v>-8.199999999999999</v>
       </c>
-      <c r="N211" t="n">
-        <v>45.9</v>
-      </c>
       <c r="O211" t="inlineStr">
         <is>
           <t>WR40</t>
@@ -30797,9 +30126,6 @@
       <c r="M212" t="n">
         <v>1.4</v>
       </c>
-      <c r="N212" t="n">
-        <v>-20.5</v>
-      </c>
       <c r="P212" t="n">
         <v>-1.3</v>
       </c>
@@ -30952,9 +30278,6 @@
       <c r="M213" t="n">
         <v>1.6</v>
       </c>
-      <c r="N213" t="n">
-        <v>-25.4</v>
-      </c>
       <c r="P213" t="n">
         <v>-7.1</v>
       </c>
@@ -31107,9 +30430,6 @@
       <c r="M214" t="n">
         <v>-34.2</v>
       </c>
-      <c r="N214" t="n">
-        <v>-15.6</v>
-      </c>
       <c r="P214" t="n">
         <v>-35.9</v>
       </c>
@@ -31252,9 +30572,6 @@
       <c r="M215" t="n">
         <v>-11.8</v>
       </c>
-      <c r="N215" t="n">
-        <v>-32.1</v>
-      </c>
       <c r="P215" t="n">
         <v>-15.2</v>
       </c>
@@ -31407,9 +30724,6 @@
       <c r="M216" t="n">
         <v>-30.4</v>
       </c>
-      <c r="N216" t="n">
-        <v>-22.9</v>
-      </c>
       <c r="P216" t="n">
         <v>-44.5</v>
       </c>
@@ -31553,9 +30867,6 @@
       <c r="M217" t="n">
         <v>2.3</v>
       </c>
-      <c r="N217" t="n">
-        <v>-44.9</v>
-      </c>
       <c r="P217" t="n">
         <v>-4.2</v>
       </c>
@@ -31708,9 +31019,6 @@
       <c r="M218" t="n">
         <v>-24.2</v>
       </c>
-      <c r="N218" t="n">
-        <v>-15.3</v>
-      </c>
       <c r="P218" t="n">
         <v>-37.2</v>
       </c>
@@ -31858,9 +31166,6 @@
       <c r="M219" t="n">
         <v>-1.1</v>
       </c>
-      <c r="N219" t="n">
-        <v>-13.2</v>
-      </c>
       <c r="P219" t="n">
         <v>-16.6</v>
       </c>
@@ -32008,9 +31313,6 @@
       <c r="M220" t="n">
         <v>-18.3</v>
       </c>
-      <c r="N220" t="n">
-        <v>90.09999999999999</v>
-      </c>
       <c r="P220" t="n">
         <v>-36.7</v>
       </c>
@@ -32087,7 +31389,7 @@
         <v>-12.09</v>
       </c>
       <c r="AM220" t="n">
-        <v>138.65</v>
+        <v>138.74</v>
       </c>
       <c r="AN220" t="n">
         <v>63</v>
@@ -32158,9 +31460,6 @@
       <c r="M221" t="n">
         <v>-28.4</v>
       </c>
-      <c r="N221" t="n">
-        <v>-24.3</v>
-      </c>
       <c r="P221" t="n">
         <v>-36.4</v>
       </c>
@@ -32313,9 +31612,6 @@
       <c r="M222" t="n">
         <v>-26.9</v>
       </c>
-      <c r="N222" t="n">
-        <v>21.6</v>
-      </c>
       <c r="P222" t="n">
         <v>-37.1</v>
       </c>
@@ -32387,7 +31683,7 @@
         <v>-6.68</v>
       </c>
       <c r="AM222" t="n">
-        <v>51.25</v>
+        <v>51.28</v>
       </c>
       <c r="AN222" t="n">
         <v>63</v>
@@ -32458,9 +31754,6 @@
       <c r="M223" t="n">
         <v>-11.5</v>
       </c>
-      <c r="N223" t="n">
-        <v>12.9</v>
-      </c>
       <c r="P223" t="n">
         <v>-33.1</v>
       </c>
@@ -32593,9 +31886,6 @@
       <c r="M224" t="n">
         <v>-22.5</v>
       </c>
-      <c r="N224" t="n">
-        <v>-24.7</v>
-      </c>
       <c r="P224" t="n">
         <v>-25.8</v>
       </c>
@@ -32748,9 +32038,6 @@
       <c r="M225" t="n">
         <v>1.1</v>
       </c>
-      <c r="N225" t="n">
-        <v>4.8</v>
-      </c>
       <c r="P225" t="n">
         <v>-22.3</v>
       </c>
@@ -33043,9 +32330,6 @@
       <c r="M227" t="n">
         <v>-34.3</v>
       </c>
-      <c r="N227" t="n">
-        <v>-35.4</v>
-      </c>
       <c r="P227" t="n">
         <v>-41.1</v>
       </c>
@@ -33193,9 +32477,6 @@
       <c r="M228" t="n">
         <v>11.2</v>
       </c>
-      <c r="N228" t="n">
-        <v>-5.8</v>
-      </c>
       <c r="P228" t="n">
         <v>10.3</v>
       </c>
@@ -33487,9 +32768,6 @@
       <c r="M230" t="n">
         <v>-25.2</v>
       </c>
-      <c r="N230" t="n">
-        <v>-26.1</v>
-      </c>
       <c r="P230" t="n">
         <v>-25.6</v>
       </c>
@@ -33642,9 +32920,6 @@
       <c r="M231" t="n">
         <v>-29.2</v>
       </c>
-      <c r="N231" t="n">
-        <v>-5</v>
-      </c>
       <c r="P231" t="n">
         <v>-50.8</v>
       </c>
@@ -33794,9 +33069,6 @@
       <c r="M232" t="n">
         <v>22.2</v>
       </c>
-      <c r="N232" t="n">
-        <v>-19.9</v>
-      </c>
       <c r="P232" t="n">
         <v>20.3</v>
       </c>
@@ -33941,9 +33213,6 @@
       <c r="M233" t="n">
         <v>7.4</v>
       </c>
-      <c r="N233" t="n">
-        <v>-8.1</v>
-      </c>
       <c r="P233" t="n">
         <v>5</v>
       </c>
@@ -34088,9 +33357,6 @@
       <c r="M234" t="n">
         <v>64.90000000000001</v>
       </c>
-      <c r="N234" t="n">
-        <v>47.4</v>
-      </c>
       <c r="P234" t="n">
         <v>51.1</v>
       </c>
@@ -34233,9 +33499,6 @@
       <c r="M235" t="n">
         <v>22.5</v>
       </c>
-      <c r="N235" t="n">
-        <v>10</v>
-      </c>
       <c r="P235" t="n">
         <v>17.1</v>
       </c>
@@ -34366,9 +33629,6 @@
       <c r="M236" t="n">
         <v>-28.7</v>
       </c>
-      <c r="N236" t="n">
-        <v>0.7</v>
-      </c>
       <c r="P236" t="n">
         <v>-39.4</v>
       </c>
@@ -34511,9 +33771,6 @@
       <c r="M237" t="n">
         <v>3.4</v>
       </c>
-      <c r="N237" t="n">
-        <v>22.1</v>
-      </c>
       <c r="P237" t="n">
         <v>-17.1</v>
       </c>
@@ -34656,9 +33913,6 @@
       <c r="M238" t="n">
         <v>-30.2</v>
       </c>
-      <c r="N238" t="n">
-        <v>-44.5</v>
-      </c>
       <c r="P238" t="n">
         <v>-33.9</v>
       </c>
@@ -34811,9 +34065,6 @@
       <c r="M239" t="n">
         <v>-24.2</v>
       </c>
-      <c r="N239" t="n">
-        <v>-35.6</v>
-      </c>
       <c r="P239" t="n">
         <v>-32.4</v>
       </c>
@@ -34952,9 +34203,6 @@
       <c r="M240" t="n">
         <v>13.7</v>
       </c>
-      <c r="N240" t="n">
-        <v>-17</v>
-      </c>
       <c r="P240" t="n">
         <v>-28.1</v>
       </c>
@@ -35098,9 +34346,6 @@
       <c r="M241" t="n">
         <v>55.8</v>
       </c>
-      <c r="N241" t="n">
-        <v>9.300000000000001</v>
-      </c>
       <c r="P241" t="n">
         <v>35.7</v>
       </c>
@@ -35239,9 +34484,6 @@
       <c r="M242" t="n">
         <v>-20.1</v>
       </c>
-      <c r="N242" t="n">
-        <v>-29.6</v>
-      </c>
       <c r="P242" t="n">
         <v>-21.7</v>
       </c>
@@ -35270,9 +34512,6 @@
       <c r="W242" t="b">
         <v>0</v>
       </c>
-      <c r="X242" s="13" t="n">
-        <v>46310</v>
-      </c>
       <c r="Y242" s="13" t="n">
         <v>46225</v>
       </c>
@@ -35315,7 +34554,7 @@
         <v>-8.73</v>
       </c>
       <c r="AL242" t="n">
-        <v>-12.21</v>
+        <v>-12.27</v>
       </c>
       <c r="AM242" t="n">
         <v>24.31</v>
@@ -35389,9 +34628,6 @@
       <c r="M243" t="n">
         <v>-0.4</v>
       </c>
-      <c r="N243" t="n">
-        <v>8.1</v>
-      </c>
       <c r="O243" t="inlineStr">
         <is>
           <t>WR20</t>
@@ -35549,9 +34785,6 @@
       <c r="M244" t="n">
         <v>58.8</v>
       </c>
-      <c r="N244" t="n">
-        <v>39.3</v>
-      </c>
       <c r="P244" t="n">
         <v>44.2</v>
       </c>
@@ -35699,9 +34932,6 @@
       <c r="M245" t="n">
         <v>28.6</v>
       </c>
-      <c r="N245" t="n">
-        <v>17</v>
-      </c>
       <c r="P245" t="n">
         <v>21.9</v>
       </c>
@@ -35844,9 +35074,6 @@
       <c r="M246" t="n">
         <v>69.59999999999999</v>
       </c>
-      <c r="N246" t="n">
-        <v>42.5</v>
-      </c>
       <c r="P246" t="n">
         <v>31.9</v>
       </c>
@@ -35994,9 +35221,6 @@
       <c r="M247" t="n">
         <v>25.2</v>
       </c>
-      <c r="N247" t="n">
-        <v>-6.7</v>
-      </c>
       <c r="P247" t="n">
         <v>23.7</v>
       </c>
@@ -36144,9 +35368,6 @@
       <c r="M248" t="n">
         <v>-5.5</v>
       </c>
-      <c r="N248" t="n">
-        <v>-16.1</v>
-      </c>
       <c r="O248" t="inlineStr">
         <is>
           <t>WR30</t>
@@ -36304,9 +35525,6 @@
       <c r="M249" t="n">
         <v>15.6</v>
       </c>
-      <c r="N249" t="n">
-        <v>-37.1</v>
-      </c>
       <c r="P249" t="n">
         <v>13.1</v>
       </c>
@@ -36456,9 +35674,6 @@
       <c r="M250" t="n">
         <v>-29.9</v>
       </c>
-      <c r="N250" t="n">
-        <v>-7.4</v>
-      </c>
       <c r="P250" t="n">
         <v>-41.6</v>
       </c>
@@ -36606,9 +35821,6 @@
       <c r="M251" t="n">
         <v>39.4</v>
       </c>
-      <c r="N251" t="n">
-        <v>49.7</v>
-      </c>
       <c r="P251" t="n">
         <v>13.8</v>
       </c>
@@ -36751,9 +35963,6 @@
       <c r="M252" t="n">
         <v>-4.2</v>
       </c>
-      <c r="N252" t="n">
-        <v>-14.8</v>
-      </c>
       <c r="O252" t="inlineStr">
         <is>
           <t>WR30</t>
@@ -36903,9 +36112,6 @@
       <c r="M253" t="n">
         <v>4.1</v>
       </c>
-      <c r="N253" t="n">
-        <v>1.4</v>
-      </c>
       <c r="P253" t="n">
         <v>-6.3</v>
       </c>
@@ -37048,9 +36254,6 @@
       <c r="M254" t="n">
         <v>-21.7</v>
       </c>
-      <c r="N254" t="n">
-        <v>29.1</v>
-      </c>
       <c r="P254" t="n">
         <v>-33.7</v>
       </c>
@@ -37193,9 +36396,6 @@
       <c r="M255" t="n">
         <v>-38.3</v>
       </c>
-      <c r="N255" t="n">
-        <v>-9.699999999999999</v>
-      </c>
       <c r="P255" t="n">
         <v>-48.2</v>
       </c>
@@ -37343,9 +36543,6 @@
       <c r="M256" t="n">
         <v>-0.4</v>
       </c>
-      <c r="N256" t="n">
-        <v>-18.6</v>
-      </c>
       <c r="P256" t="n">
         <v>-14.2</v>
       </c>
@@ -37498,9 +36695,6 @@
       <c r="M257" t="n">
         <v>-12</v>
       </c>
-      <c r="N257" t="n">
-        <v>-22.9</v>
-      </c>
       <c r="P257" t="n">
         <v>-24.6</v>
       </c>
@@ -37647,9 +36841,6 @@
       <c r="M258" t="n">
         <v>-19.7</v>
       </c>
-      <c r="N258" t="n">
-        <v>-35.7</v>
-      </c>
       <c r="P258" t="n">
         <v>-21.6</v>
       </c>
@@ -37718,7 +36909,7 @@
         <v>-18.59</v>
       </c>
       <c r="AL258" t="n">
-        <v>-21.23</v>
+        <v>-21.26</v>
       </c>
       <c r="AM258" t="n">
         <v>19.06</v>
@@ -37794,9 +36985,6 @@
       <c r="M259" t="n">
         <v>-6.4</v>
       </c>
-      <c r="N259" t="n">
-        <v>19.7</v>
-      </c>
       <c r="P259" t="n">
         <v>-12.3</v>
       </c>
@@ -37939,9 +37127,6 @@
       <c r="M260" t="n">
         <v>4.6</v>
       </c>
-      <c r="N260" t="n">
-        <v>6.1</v>
-      </c>
       <c r="P260" t="n">
         <v>1.5</v>
       </c>
@@ -38089,9 +37274,6 @@
       <c r="M261" t="n">
         <v>-0.2</v>
       </c>
-      <c r="N261" t="n">
-        <v>60.5</v>
-      </c>
       <c r="O261" t="inlineStr">
         <is>
           <t>WR20</t>
@@ -38244,9 +37426,6 @@
       <c r="M262" t="n">
         <v>0.9</v>
       </c>
-      <c r="N262" t="n">
-        <v>10.8</v>
-      </c>
       <c r="P262" t="n">
         <v>-29.6</v>
       </c>
@@ -38391,9 +37570,6 @@
       <c r="M263" t="n">
         <v>16.5</v>
       </c>
-      <c r="N263" t="n">
-        <v>-17.8</v>
-      </c>
       <c r="P263" t="n">
         <v>11.6</v>
       </c>
@@ -38538,9 +37714,6 @@
       <c r="M264" t="n">
         <v>-9.6</v>
       </c>
-      <c r="N264" t="n">
-        <v>16.2</v>
-      </c>
       <c r="O264" t="inlineStr">
         <is>
           <t>WR30</t>
@@ -38693,9 +37866,6 @@
       <c r="M265" t="n">
         <v>-11.3</v>
       </c>
-      <c r="N265" t="n">
-        <v>-20.8</v>
-      </c>
       <c r="P265" t="n">
         <v>-25.4</v>
       </c>
@@ -38840,9 +38010,6 @@
       <c r="M266" t="n">
         <v>14.9</v>
       </c>
-      <c r="N266" t="n">
-        <v>4.1</v>
-      </c>
       <c r="P266" t="n">
         <v>14.1</v>
       </c>
@@ -38985,9 +38152,6 @@
       <c r="M267" t="n">
         <v>-32.8</v>
       </c>
-      <c r="N267" t="n">
-        <v>-33.2</v>
-      </c>
       <c r="P267" t="n">
         <v>-50.4</v>
       </c>
@@ -39137,9 +38301,6 @@
       <c r="M268" t="n">
         <v>-40.3</v>
       </c>
-      <c r="N268" t="n">
-        <v>-39.5</v>
-      </c>
       <c r="P268" t="n">
         <v>-41.9</v>
       </c>
@@ -39292,9 +38453,6 @@
       <c r="M269" t="n">
         <v>-48.5</v>
       </c>
-      <c r="N269" t="n">
-        <v>-47.7</v>
-      </c>
       <c r="P269" t="n">
         <v>-48.8</v>
       </c>
@@ -39447,9 +38605,6 @@
       <c r="M270" t="n">
         <v>-26.7</v>
       </c>
-      <c r="N270" t="n">
-        <v>-36.2</v>
-      </c>
       <c r="P270" t="n">
         <v>-36.4</v>
       </c>
@@ -39593,9 +38748,6 @@
       <c r="M271" t="n">
         <v>-0.5</v>
       </c>
-      <c r="N271" t="n">
-        <v>69.40000000000001</v>
-      </c>
       <c r="O271" t="inlineStr">
         <is>
           <t>WR20</t>
@@ -39748,9 +38900,6 @@
       <c r="M272" t="n">
         <v>7.1</v>
       </c>
-      <c r="N272" t="n">
-        <v>48.4</v>
-      </c>
       <c r="P272" t="n">
         <v>-17.9</v>
       </c>
@@ -39898,9 +39047,6 @@
       <c r="M273" t="n">
         <v>7.6</v>
       </c>
-      <c r="N273" t="n">
-        <v>14.7</v>
-      </c>
       <c r="P273" t="n">
         <v>-26.5</v>
       </c>
@@ -40043,9 +39189,6 @@
       <c r="M274" t="n">
         <v>-2.1</v>
       </c>
-      <c r="N274" t="n">
-        <v>9.1</v>
-      </c>
       <c r="O274" t="inlineStr">
         <is>
           <t>WR30</t>
@@ -40198,9 +39341,6 @@
       <c r="M275" t="n">
         <v>-9</v>
       </c>
-      <c r="N275" t="n">
-        <v>-2.7</v>
-      </c>
       <c r="P275" t="n">
         <v>-18</v>
       </c>
@@ -40350,9 +39490,6 @@
       <c r="M276" t="n">
         <v>-42.2</v>
       </c>
-      <c r="N276" t="n">
-        <v>-37.2</v>
-      </c>
       <c r="P276" t="n">
         <v>-46.7</v>
       </c>
@@ -40426,7 +39563,7 @@
         <v>-13.59</v>
       </c>
       <c r="AL276" t="n">
-        <v>-18.36</v>
+        <v>-18.35</v>
       </c>
       <c r="AM276" t="n">
         <v>45.74</v>
@@ -40505,9 +39642,6 @@
       <c r="M277" t="n">
         <v>-3.4</v>
       </c>
-      <c r="N277" t="n">
-        <v>-23.2</v>
-      </c>
       <c r="P277" t="n">
         <v>-10.1</v>
       </c>
@@ -40660,9 +39794,6 @@
       <c r="M278" t="n">
         <v>2.9</v>
       </c>
-      <c r="N278" t="n">
-        <v>-13.8</v>
-      </c>
       <c r="P278" t="n">
         <v>-0.1</v>
       </c>
@@ -40815,9 +39946,6 @@
       <c r="M279" t="n">
         <v>-8.800000000000001</v>
       </c>
-      <c r="N279" t="n">
-        <v>-9.5</v>
-      </c>
       <c r="P279" t="n">
         <v>-10.8</v>
       </c>
@@ -40959,9 +40087,6 @@
       <c r="M280" t="n">
         <v>0.2</v>
       </c>
-      <c r="N280" t="n">
-        <v>-6.4</v>
-      </c>
       <c r="P280" t="n">
         <v>-7.8</v>
       </c>
@@ -41104,9 +40229,6 @@
       <c r="M281" t="n">
         <v>21.4</v>
       </c>
-      <c r="N281" t="n">
-        <v>10.3</v>
-      </c>
       <c r="P281" t="n">
         <v>19.8</v>
       </c>
@@ -41246,9 +40368,6 @@
       <c r="M282" t="n">
         <v>13.6</v>
       </c>
-      <c r="N282" t="n">
-        <v>31</v>
-      </c>
       <c r="P282" t="n">
         <v>6.5</v>
       </c>
@@ -41391,9 +40510,6 @@
       <c r="M283" t="n">
         <v>-8.6</v>
       </c>
-      <c r="N283" t="n">
-        <v>-18.8</v>
-      </c>
       <c r="P283" t="n">
         <v>-12.7</v>
       </c>
@@ -41541,9 +40657,6 @@
       <c r="M284" t="n">
         <v>23.7</v>
       </c>
-      <c r="N284" t="n">
-        <v>-8.4</v>
-      </c>
       <c r="P284" t="n">
         <v>20.2</v>
       </c>
@@ -41688,9 +40801,6 @@
       <c r="M285" t="n">
         <v>-43.3</v>
       </c>
-      <c r="N285" t="n">
-        <v>11.5</v>
-      </c>
       <c r="P285" t="n">
         <v>-55.7</v>
       </c>
@@ -41838,9 +40948,6 @@
       <c r="M286" t="n">
         <v>29.3</v>
       </c>
-      <c r="N286" t="n">
-        <v>-9.300000000000001</v>
-      </c>
       <c r="P286" t="n">
         <v>5.2</v>
       </c>
@@ -41984,9 +41091,6 @@
       <c r="M287" t="n">
         <v>-0.9</v>
       </c>
-      <c r="N287" t="n">
-        <v>-7.9</v>
-      </c>
       <c r="O287" t="inlineStr">
         <is>
           <t>WR20</t>
@@ -42139,9 +41243,6 @@
       <c r="M288" t="n">
         <v>23</v>
       </c>
-      <c r="N288" t="n">
-        <v>-25.2</v>
-      </c>
       <c r="P288" t="n">
         <v>5.7</v>
       </c>
@@ -42280,9 +41381,6 @@
       <c r="M289" t="n">
         <v>12.2</v>
       </c>
-      <c r="N289" t="n">
-        <v>-3.8</v>
-      </c>
       <c r="P289" t="n">
         <v>8.800000000000001</v>
       </c>
@@ -42430,9 +41528,6 @@
       <c r="M290" t="n">
         <v>45.6</v>
       </c>
-      <c r="N290" t="n">
-        <v>15.8</v>
-      </c>
       <c r="P290" t="n">
         <v>25</v>
       </c>
@@ -42576,9 +41671,6 @@
       <c r="M291" t="n">
         <v>-20</v>
       </c>
-      <c r="N291" t="n">
-        <v>-18.1</v>
-      </c>
       <c r="P291" t="n">
         <v>-33</v>
       </c>
@@ -42652,7 +41744,7 @@
         <v>-13.38</v>
       </c>
       <c r="AL291" t="n">
-        <v>-20.35</v>
+        <v>-20.44</v>
       </c>
       <c r="AM291" t="n">
         <v>11.91</v>
@@ -42731,9 +41823,6 @@
       <c r="M292" t="n">
         <v>56.3</v>
       </c>
-      <c r="N292" t="n">
-        <v>52.8</v>
-      </c>
       <c r="P292" t="n">
         <v>34.3</v>
       </c>
@@ -42886,9 +41975,6 @@
       <c r="M293" t="n">
         <v>-9</v>
       </c>
-      <c r="N293" t="n">
-        <v>35.8</v>
-      </c>
       <c r="O293" t="inlineStr">
         <is>
           <t>WR20</t>
@@ -43041,9 +42127,6 @@
       <c r="M294" t="n">
         <v>-25.3</v>
       </c>
-      <c r="N294" t="n">
-        <v>32.8</v>
-      </c>
       <c r="P294" t="n">
         <v>-43.3</v>
       </c>
@@ -43190,9 +42273,6 @@
       </c>
       <c r="M295" t="n">
         <v>-4.1</v>
-      </c>
-      <c r="N295" t="n">
-        <v>-19.5</v>
       </c>
       <c r="O295" t="inlineStr">
         <is>
@@ -43341,7 +42421,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>292 (+2 pending)</t>
+          <t>292 (+0 pending)</t>
         </is>
       </c>
     </row>
@@ -43365,7 +42445,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>$49,544.27  (+0.17% price-weighted)</t>
+          <t>$49,544.47  (+0.17% price-weighted)</t>
         </is>
       </c>
     </row>
@@ -43377,7 +42457,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>-0.04%  &lt;- judge the system by this line</t>
+          <t>-0.03%  &lt;- judge the system by this line</t>
         </is>
       </c>
     </row>
@@ -43389,7 +42469,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-2.21%</t>
+          <t>-2.20%</t>
         </is>
       </c>
     </row>
@@ -43502,10 +42582,10 @@
         <v>74</v>
       </c>
       <c r="C13" t="n">
-        <v>-0.87</v>
+        <v>-0.84</v>
       </c>
       <c r="D13" t="n">
-        <v>-3.16</v>
+        <v>-3.12</v>
       </c>
       <c r="E13" t="n">
         <v>5.06</v>
@@ -43690,13 +42770,13 @@
         <v>1</v>
       </c>
       <c r="C21" t="n">
-        <v>-19.4</v>
+        <v>-17.12</v>
       </c>
       <c r="D21" t="n">
         <v>0</v>
       </c>
       <c r="E21" t="n">
-        <v>-24.32</v>
+        <v>-21.54</v>
       </c>
       <c r="G21" t="n">
         <v>-24.31</v>
@@ -43788,13 +42868,13 @@
         <v>65</v>
       </c>
       <c r="E26" t="n">
-        <v>4.32</v>
+        <v>4.31</v>
       </c>
       <c r="F26" t="n">
         <v>58</v>
       </c>
       <c r="G26" t="n">
-        <v>-8.6</v>
+        <v>-8.609999999999999</v>
       </c>
     </row>
     <row r="27">
@@ -43924,7 +43004,7 @@
         <v>10.7</v>
       </c>
       <c r="F32" t="n">
-        <v>-13.72</v>
+        <v>-13.73</v>
       </c>
     </row>
     <row r="33">
@@ -43946,7 +43026,7 @@
         <v>-4.52</v>
       </c>
       <c r="F33" t="n">
-        <v>-16.48</v>
+        <v>-16.51</v>
       </c>
     </row>
     <row r="34">
@@ -44572,7 +43652,7 @@
         <v>129</v>
       </c>
       <c r="D6" t="n">
-        <v>-6.64</v>
+        <v>-6.63</v>
       </c>
       <c r="E6" t="n">
         <v>-8.74</v>
@@ -44581,13 +43661,13 @@
         <v>34.1</v>
       </c>
       <c r="G6" t="n">
-        <v>-8.73</v>
+        <v>-8.710000000000001</v>
       </c>
       <c r="H6" t="n">
-        <v>-19.35</v>
+        <v>-19.36</v>
       </c>
       <c r="I6" t="n">
-        <v>-63.57</v>
+        <v>-63.53</v>
       </c>
       <c r="J6" t="n">
         <v>43.4</v>
@@ -44615,7 +43695,7 @@
         <v>292</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.04</v>
+        <v>-0.03</v>
       </c>
       <c r="E7" t="n">
         <v>-0.91</v>
@@ -44624,13 +43704,13 @@
         <v>47.9</v>
       </c>
       <c r="G7" t="n">
-        <v>-2.21</v>
+        <v>-2.2</v>
       </c>
       <c r="H7" t="n">
         <v>-15.89</v>
       </c>
       <c r="I7" t="n">
-        <v>-63.57</v>
+        <v>-63.53</v>
       </c>
       <c r="J7" t="n">
         <v>33.6</v>
@@ -44656,7 +43736,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Avg drawdown (MAE%, less-negative is better): PASS -12.49 vs FAIL -19.35  -&gt;  PASS better</t>
+          <t>Avg drawdown (MAE%, less-negative is better): PASS -12.49 vs FAIL -19.36  -&gt;  PASS better</t>
         </is>
       </c>
     </row>
@@ -44670,7 +43750,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Avg return %: PASS 6.3 vs FAIL -6.64  -&gt;  PASS better</t>
+          <t>Avg return %: PASS 6.3 vs FAIL -6.63  -&gt;  PASS better</t>
         </is>
       </c>
     </row>
@@ -46083,29 +45163,45 @@
           <t>DECLINING</t>
         </is>
       </c>
-      <c r="E19" t="n">
-        <v>83.8</v>
-      </c>
-      <c r="F19" t="n">
-        <v>0.432</v>
-      </c>
-      <c r="G19" t="n">
-        <v>8</v>
-      </c>
-      <c r="H19" t="n">
-        <v>7.66</v>
-      </c>
-      <c r="I19" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="J19" t="n">
-        <v>11.8</v>
-      </c>
-      <c r="K19" t="n">
-        <v>0.9399999999999999</v>
-      </c>
-      <c r="L19" t="n">
-        <v>18.8</v>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>83.8</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>0.432</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>7.66</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>2.3</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>11.8</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>0.94</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>18.8</t>
+        </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
@@ -56161,45 +55257,29 @@
           <t>CORE</t>
         </is>
       </c>
-      <c r="E157" t="inlineStr">
-        <is>
-          <t>47.1</t>
-        </is>
-      </c>
-      <c r="F157" t="inlineStr">
-        <is>
-          <t>0.206</t>
-        </is>
-      </c>
-      <c r="G157" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="H157" t="inlineStr">
-        <is>
-          <t>3.49</t>
-        </is>
-      </c>
-      <c r="I157" t="inlineStr">
-        <is>
-          <t>1.1</t>
-        </is>
-      </c>
-      <c r="J157" t="inlineStr">
-        <is>
-          <t>5.7</t>
-        </is>
-      </c>
-      <c r="K157" t="inlineStr">
-        <is>
-          <t>1.75</t>
-        </is>
-      </c>
-      <c r="L157" t="inlineStr">
-        <is>
-          <t>24.7</t>
-        </is>
+      <c r="E157" t="n">
+        <v>47.2</v>
+      </c>
+      <c r="F157" t="n">
+        <v>0.206</v>
+      </c>
+      <c r="G157" t="n">
+        <v>5</v>
+      </c>
+      <c r="H157" t="n">
+        <v>3.56</v>
+      </c>
+      <c r="I157" t="n">
+        <v>1</v>
+      </c>
+      <c r="J157" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="K157" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="L157" t="n">
+        <v>24.7</v>
       </c>
       <c r="M157" t="inlineStr">
         <is>
@@ -62040,7 +61120,11 @@
           <t>1</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr"/>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
       <c r="E2" t="inlineStr">
         <is>
           <t>2.7</t>
@@ -62094,7 +61178,11 @@
           <t>1</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr"/>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
       <c r="E3" t="inlineStr">
         <is>
           <t>3.2</t>
@@ -64852,10 +63940,8 @@
           <t>CORE</t>
         </is>
       </c>
-      <c r="L50" t="inlineStr">
-        <is>
-          <t>47.1</t>
-        </is>
+      <c r="L50" t="n">
+        <v>47.2</v>
       </c>
     </row>
     <row r="51">
@@ -68796,8 +67882,10 @@
           <t>DECLINING</t>
         </is>
       </c>
-      <c r="L118" t="n">
-        <v>83.8</v>
+      <c r="L118" t="inlineStr">
+        <is>
+          <t>83.8</t>
+        </is>
       </c>
     </row>
     <row r="119">

--- a/STS_holy_grail.xlsx
+++ b/STS_holy_grail.xlsx
@@ -55257,29 +55257,45 @@
           <t>CORE</t>
         </is>
       </c>
-      <c r="E157" t="n">
-        <v>47.2</v>
-      </c>
-      <c r="F157" t="n">
-        <v>0.206</v>
-      </c>
-      <c r="G157" t="n">
-        <v>5</v>
-      </c>
-      <c r="H157" t="n">
-        <v>3.56</v>
-      </c>
-      <c r="I157" t="n">
-        <v>1</v>
-      </c>
-      <c r="J157" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="K157" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="L157" t="n">
-        <v>24.7</v>
+      <c r="E157" t="inlineStr">
+        <is>
+          <t>47.2</t>
+        </is>
+      </c>
+      <c r="F157" t="inlineStr">
+        <is>
+          <t>0.206</t>
+        </is>
+      </c>
+      <c r="G157" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="H157" t="inlineStr">
+        <is>
+          <t>3.56</t>
+        </is>
+      </c>
+      <c r="I157" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="J157" t="inlineStr">
+        <is>
+          <t>5.7</t>
+        </is>
+      </c>
+      <c r="K157" t="inlineStr">
+        <is>
+          <t>1.75</t>
+        </is>
+      </c>
+      <c r="L157" t="inlineStr">
+        <is>
+          <t>24.7</t>
+        </is>
       </c>
       <c r="M157" t="inlineStr">
         <is>
@@ -63940,8 +63956,10 @@
           <t>CORE</t>
         </is>
       </c>
-      <c r="L50" t="n">
-        <v>47.2</v>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>47.2</t>
+        </is>
       </c>
     </row>
     <row r="51">

--- a/STS_holy_grail.xlsx
+++ b/STS_holy_grail.xlsx
@@ -1201,7 +1201,7 @@
         </is>
       </c>
       <c r="AI2" t="n">
-        <v>89.84999999999999</v>
+        <v>89.84999847412109</v>
       </c>
     </row>
     <row r="3">
@@ -2061,7 +2061,7 @@
         <v>-8.800000000000001</v>
       </c>
       <c r="I10" t="n">
-        <v>-10.1</v>
+        <v>-8.6</v>
       </c>
       <c r="L10" t="n">
         <v>-1.66</v>
@@ -2070,7 +2070,7 @@
         <v>-8.4</v>
       </c>
       <c r="N10" t="n">
-        <v>-6.1</v>
+        <v>-4.1</v>
       </c>
       <c r="P10" t="n">
         <v>-13.4</v>
@@ -2107,7 +2107,7 @@
         <v>46310</v>
       </c>
       <c r="Z10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB10" t="n">
         <v>6.21</v>
@@ -2128,13 +2128,13 @@
         <v>13.84</v>
       </c>
       <c r="AI10" t="n">
-        <v>14.18</v>
+        <v>14.47</v>
       </c>
       <c r="AJ10" t="n">
-        <v>14.18</v>
+        <v>14.47</v>
       </c>
       <c r="AK10" t="n">
-        <v>2.46</v>
+        <v>4.55</v>
       </c>
       <c r="AL10" t="n">
         <v>-1.66</v>
@@ -2143,16 +2143,16 @@
         <v>6.21</v>
       </c>
       <c r="AN10" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AO10" t="n">
         <v>1</v>
       </c>
       <c r="AR10" t="n">
-        <v>-0.4</v>
+        <v>-1.51</v>
       </c>
       <c r="AT10" t="n">
-        <v>2.86</v>
+        <v>6.06</v>
       </c>
     </row>
     <row r="11">
@@ -3372,7 +3372,7 @@
         <v>14.7</v>
       </c>
       <c r="I20" t="n">
-        <v>26.2</v>
+        <v>30.1</v>
       </c>
       <c r="L20" t="n">
         <v>-2.24</v>
@@ -3381,13 +3381,13 @@
         <v>2.1</v>
       </c>
       <c r="N20" t="n">
-        <v>18.7</v>
+        <v>21.3</v>
       </c>
       <c r="P20" t="n">
-        <v>-16.7</v>
+        <v>-16.6</v>
       </c>
       <c r="Q20" t="n">
-        <v>191.37</v>
+        <v>191.33</v>
       </c>
       <c r="R20" t="inlineStr">
         <is>
@@ -3418,13 +3418,13 @@
         <v>46303</v>
       </c>
       <c r="Z20" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AB20" t="n">
-        <v>16.59</v>
+        <v>18.39</v>
       </c>
       <c r="AC20" t="n">
-        <v>16.59</v>
+        <v>18.39</v>
       </c>
       <c r="AD20" t="n">
         <v>-2.24</v>
@@ -3442,31 +3442,31 @@
         <v>195.43</v>
       </c>
       <c r="AI20" t="n">
-        <v>224.92</v>
+        <v>229.68</v>
       </c>
       <c r="AJ20" t="n">
-        <v>224.92</v>
+        <v>229.68</v>
       </c>
       <c r="AK20" t="n">
-        <v>15.09</v>
+        <v>17.53</v>
       </c>
       <c r="AL20" t="n">
         <v>-2.24</v>
       </c>
       <c r="AM20" t="n">
-        <v>16.59</v>
+        <v>18.39</v>
       </c>
       <c r="AN20" t="n">
+        <v>9</v>
+      </c>
+      <c r="AO20" t="n">
         <v>8</v>
       </c>
-      <c r="AO20" t="n">
-        <v>7</v>
-      </c>
       <c r="AR20" t="n">
-        <v>-0.82</v>
+        <v>-1.91</v>
       </c>
       <c r="AT20" t="n">
-        <v>15.91</v>
+        <v>19.44</v>
       </c>
     </row>
     <row r="21">
@@ -4164,7 +4164,7 @@
         <v>2.8</v>
       </c>
       <c r="I26" t="n">
-        <v>11.5</v>
+        <v>15.6</v>
       </c>
       <c r="J26" t="n">
         <v>2.42</v>
@@ -4176,7 +4176,7 @@
         <v>-8.800000000000001</v>
       </c>
       <c r="N26" t="n">
-        <v>-2.7</v>
+        <v>-2.9</v>
       </c>
       <c r="O26" t="inlineStr">
         <is>
@@ -4187,7 +4187,7 @@
         <v>-25.6</v>
       </c>
       <c r="Q26" t="n">
-        <v>19.05</v>
+        <v>19.04</v>
       </c>
       <c r="R26" t="inlineStr">
         <is>
@@ -4218,7 +4218,7 @@
         <v>46295</v>
       </c>
       <c r="Z26" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AB26" t="n">
         <v>6.86</v>
@@ -4239,13 +4239,13 @@
         <v>17.36</v>
       </c>
       <c r="AI26" t="n">
-        <v>18.05</v>
+        <v>17.98</v>
       </c>
       <c r="AJ26" t="n">
-        <v>18.05</v>
+        <v>17.98</v>
       </c>
       <c r="AK26" t="n">
-        <v>3.97</v>
+        <v>3.57</v>
       </c>
       <c r="AL26" t="n">
         <v>-1.61</v>
@@ -4254,16 +4254,16 @@
         <v>6.86</v>
       </c>
       <c r="AN26" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AO26" t="n">
         <v>1</v>
       </c>
       <c r="AR26" t="n">
-        <v>0.65</v>
+        <v>-0.47</v>
       </c>
       <c r="AT26" t="n">
-        <v>3.33</v>
+        <v>4.04</v>
       </c>
     </row>
     <row r="27">
@@ -5381,7 +5381,7 @@
         <v>-0.9</v>
       </c>
       <c r="I35" t="n">
-        <v>-11.3</v>
+        <v>-14</v>
       </c>
       <c r="J35" t="n">
         <v>-3.75</v>
@@ -5393,7 +5393,7 @@
         <v>-12.9</v>
       </c>
       <c r="N35" t="n">
-        <v>-13.5</v>
+        <v>-14.9</v>
       </c>
       <c r="P35" t="n">
         <v>-19.3</v>
@@ -5445,13 +5445,13 @@
         <v>115.12</v>
       </c>
       <c r="AI35" t="n">
-        <v>111.13</v>
+        <v>109.11</v>
       </c>
       <c r="AJ35" t="n">
-        <v>111.13</v>
+        <v>109.11</v>
       </c>
       <c r="AK35" t="n">
-        <v>-3.47</v>
+        <v>-5.22</v>
       </c>
       <c r="AL35" t="n">
         <v>-9.01</v>
@@ -5460,16 +5460,16 @@
         <v>4.59</v>
       </c>
       <c r="AN35" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AO35" t="n">
         <v>1</v>
       </c>
       <c r="AR35" t="n">
-        <v>0.72</v>
+        <v>-0.39</v>
       </c>
       <c r="AT35" t="n">
-        <v>-4.19</v>
+        <v>-4.83</v>
       </c>
     </row>
     <row r="36">
@@ -5493,7 +5493,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Extended</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -5508,7 +5508,7 @@
         <v>20.7</v>
       </c>
       <c r="I36" t="n">
-        <v>-4.1</v>
+        <v>-3.7</v>
       </c>
       <c r="J36" t="n">
         <v>-1.49</v>
@@ -5520,7 +5520,7 @@
         <v>17.3</v>
       </c>
       <c r="N36" t="n">
-        <v>20.3</v>
+        <v>19.8</v>
       </c>
       <c r="P36" t="n">
         <v>11.4</v>
@@ -5553,6 +5553,9 @@
       <c r="X36" s="13" t="n">
         <v>46331</v>
       </c>
+      <c r="Y36" s="13" t="n">
+        <v>46311</v>
+      </c>
       <c r="Z36" t="n">
         <v>0</v>
       </c>
@@ -5560,7 +5563,10 @@
         <v>1.83</v>
       </c>
       <c r="AC36" t="n">
-        <v>4.98</v>
+        <v>6.26</v>
+      </c>
+      <c r="AD36" t="n">
+        <v>-10.54</v>
       </c>
       <c r="AF36" t="n">
         <v>166.56</v>
@@ -5572,31 +5578,31 @@
         <v>166.56</v>
       </c>
       <c r="AI36" t="n">
-        <v>174.28</v>
+        <v>173.7</v>
       </c>
       <c r="AJ36" t="n">
-        <v>174.28</v>
+        <v>173.7</v>
       </c>
       <c r="AK36" t="n">
-        <v>4.63</v>
+        <v>4.29</v>
       </c>
       <c r="AL36" t="n">
         <v>-10.54</v>
       </c>
       <c r="AM36" t="n">
-        <v>4.98</v>
+        <v>6.26</v>
       </c>
       <c r="AN36" t="n">
+        <v>20</v>
+      </c>
+      <c r="AO36" t="n">
         <v>19</v>
       </c>
-      <c r="AO36" t="n">
-        <v>18</v>
-      </c>
       <c r="AR36" t="n">
-        <v>0.72</v>
+        <v>-0.39</v>
       </c>
       <c r="AT36" t="n">
-        <v>3.91</v>
+        <v>4.68</v>
       </c>
     </row>
     <row r="37">
@@ -6149,7 +6155,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Extended</t>
+          <t>Retired</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -6164,11 +6170,14 @@
         <v>31.3</v>
       </c>
       <c r="I41" t="n">
-        <v>19.6</v>
+        <v>12.2</v>
       </c>
       <c r="J41" t="n">
         <v>1.47</v>
       </c>
+      <c r="K41" t="n">
+        <v>4.33</v>
+      </c>
       <c r="L41" t="n">
         <v>-5.99</v>
       </c>
@@ -6176,7 +6185,7 @@
         <v>3.5</v>
       </c>
       <c r="N41" t="n">
-        <v>19.9</v>
+        <v>11.8</v>
       </c>
       <c r="P41" t="n">
         <v>-30.3</v>
@@ -6213,7 +6222,12 @@
         <v>46301</v>
       </c>
       <c r="Z41" t="n">
-        <v>7</v>
+        <v>8</v>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>ran</t>
+        </is>
       </c>
       <c r="AB41" t="n">
         <v>4.88</v>
@@ -6237,13 +6251,13 @@
         <v>10.85</v>
       </c>
       <c r="AI41" t="n">
-        <v>12.16</v>
+        <v>11.32</v>
       </c>
       <c r="AJ41" t="n">
-        <v>12.16</v>
+        <v>11.32</v>
       </c>
       <c r="AK41" t="n">
-        <v>12.07</v>
+        <v>4.33</v>
       </c>
       <c r="AL41" t="n">
         <v>-5.99</v>
@@ -6252,16 +6266,16 @@
         <v>18.71</v>
       </c>
       <c r="AN41" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AO41" t="n">
         <v>16</v>
       </c>
       <c r="AR41" t="n">
-        <v>1.38</v>
+        <v>0.25</v>
       </c>
       <c r="AT41" t="n">
-        <v>10.7</v>
+        <v>4.08</v>
       </c>
     </row>
     <row r="42">
@@ -6986,7 +7000,7 @@
         <v>4.6</v>
       </c>
       <c r="I47" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="J47" t="n">
         <v>-3.41</v>
@@ -7001,7 +7015,7 @@
         <v>-10.3</v>
       </c>
       <c r="N47" t="n">
-        <v>3.9</v>
+        <v>1.8</v>
       </c>
       <c r="P47" t="n">
         <v>-19.9</v>
@@ -7038,7 +7052,7 @@
         <v>46301</v>
       </c>
       <c r="Z47" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA47" t="inlineStr">
         <is>
@@ -7067,31 +7081,31 @@
         <v>218.76</v>
       </c>
       <c r="AI47" t="n">
-        <v>245.16</v>
+        <v>239.9</v>
       </c>
       <c r="AJ47" t="n">
-        <v>245.16</v>
+        <v>239.9</v>
       </c>
       <c r="AK47" t="n">
-        <v>12.07</v>
+        <v>9.66</v>
       </c>
       <c r="AL47" t="n">
         <v>-8.949999999999999</v>
       </c>
       <c r="AM47" t="n">
-        <v>12.79</v>
+        <v>15.08</v>
       </c>
       <c r="AN47" t="n">
+        <v>22</v>
+      </c>
+      <c r="AO47" t="n">
         <v>21</v>
       </c>
-      <c r="AO47" t="n">
-        <v>20</v>
-      </c>
       <c r="AR47" t="n">
-        <v>1.38</v>
+        <v>0.26</v>
       </c>
       <c r="AT47" t="n">
-        <v>10.68</v>
+        <v>9.4</v>
       </c>
     </row>
     <row r="48">
@@ -7265,7 +7279,7 @@
         <v>10.5</v>
       </c>
       <c r="I49" t="n">
-        <v>-5.2</v>
+        <v>-7.5</v>
       </c>
       <c r="J49" t="n">
         <v>-3.62</v>
@@ -7280,7 +7294,7 @@
         <v>-5.7</v>
       </c>
       <c r="N49" t="n">
-        <v>-1.2</v>
+        <v>-3.5</v>
       </c>
       <c r="O49" t="inlineStr">
         <is>
@@ -7337,31 +7351,31 @@
         <v>250.35</v>
       </c>
       <c r="AI49" t="n">
-        <v>251.67</v>
+        <v>245.2</v>
       </c>
       <c r="AJ49" t="n">
-        <v>251.67</v>
+        <v>245.2</v>
       </c>
       <c r="AK49" t="n">
-        <v>0.53</v>
+        <v>-2.06</v>
       </c>
       <c r="AL49" t="n">
         <v>-10.26</v>
       </c>
       <c r="AM49" t="n">
-        <v>1.73</v>
+        <v>2.46</v>
       </c>
       <c r="AN49" t="n">
+        <v>22</v>
+      </c>
+      <c r="AO49" t="n">
         <v>21</v>
       </c>
-      <c r="AO49" t="n">
-        <v>3</v>
-      </c>
       <c r="AR49" t="n">
-        <v>1.38</v>
+        <v>0.26</v>
       </c>
       <c r="AT49" t="n">
-        <v>-0.86</v>
+        <v>-2.32</v>
       </c>
     </row>
     <row r="50">
@@ -8547,7 +8561,7 @@
         <v>35.1</v>
       </c>
       <c r="I58" t="n">
-        <v>26.2</v>
+        <v>30.1</v>
       </c>
       <c r="J58" t="n">
         <v>-7.78</v>
@@ -8562,7 +8576,7 @@
         <v>-3.2</v>
       </c>
       <c r="N58" t="n">
-        <v>18.7</v>
+        <v>21.3</v>
       </c>
       <c r="O58" t="inlineStr">
         <is>
@@ -8570,10 +8584,10 @@
         </is>
       </c>
       <c r="P58" t="n">
-        <v>-34</v>
+        <v>-33.9</v>
       </c>
       <c r="Q58" t="n">
-        <v>196.88</v>
+        <v>196.83</v>
       </c>
       <c r="R58" t="inlineStr">
         <is>
@@ -8604,7 +8618,7 @@
         <v>46296</v>
       </c>
       <c r="Z58" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AA58" t="inlineStr">
         <is>
@@ -8633,31 +8647,31 @@
         <v>190.53</v>
       </c>
       <c r="AI58" t="n">
-        <v>224.92</v>
+        <v>229.68</v>
       </c>
       <c r="AJ58" t="n">
-        <v>224.92</v>
+        <v>229.68</v>
       </c>
       <c r="AK58" t="n">
-        <v>18.05</v>
+        <v>20.55</v>
       </c>
       <c r="AL58" t="n">
         <v>-10.39</v>
       </c>
       <c r="AM58" t="n">
-        <v>19.59</v>
+        <v>21.43</v>
       </c>
       <c r="AN58" t="n">
+        <v>24</v>
+      </c>
+      <c r="AO58" t="n">
         <v>23</v>
       </c>
-      <c r="AO58" t="n">
-        <v>22</v>
-      </c>
       <c r="AR58" t="n">
-        <v>1.79</v>
+        <v>0.66</v>
       </c>
       <c r="AT58" t="n">
-        <v>16.26</v>
+        <v>19.89</v>
       </c>
     </row>
     <row r="59">
@@ -9253,7 +9267,7 @@
         <v>15.1</v>
       </c>
       <c r="I63" t="n">
-        <v>-32.1</v>
+        <v>-33.6</v>
       </c>
       <c r="J63" t="n">
         <v>-21.29</v>
@@ -9268,7 +9282,7 @@
         <v>16.3</v>
       </c>
       <c r="N63" t="n">
-        <v>-18.9</v>
+        <v>-22.5</v>
       </c>
       <c r="P63" t="n">
         <v>13.8</v>
@@ -9320,31 +9334,31 @@
         <v>83.75</v>
       </c>
       <c r="AI63" t="n">
-        <v>58.5</v>
+        <v>55.9</v>
       </c>
       <c r="AJ63" t="n">
-        <v>58.5</v>
+        <v>55.9</v>
       </c>
       <c r="AK63" t="n">
-        <v>-30.15</v>
+        <v>-33.25</v>
       </c>
       <c r="AL63" t="n">
-        <v>-31.77</v>
+        <v>-33.34</v>
       </c>
       <c r="AM63" t="n">
         <v>2.66</v>
       </c>
       <c r="AN63" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AO63" t="n">
         <v>0</v>
       </c>
       <c r="AR63" t="n">
-        <v>1.18</v>
+        <v>0.06</v>
       </c>
       <c r="AT63" t="n">
-        <v>-31.32</v>
+        <v>-33.31</v>
       </c>
       <c r="AU63" t="inlineStr">
         <is>
@@ -9388,7 +9402,7 @@
         <v>11.1</v>
       </c>
       <c r="I64" t="n">
-        <v>-17</v>
+        <v>-16.6</v>
       </c>
       <c r="J64" t="n">
         <v>-8.85</v>
@@ -9403,7 +9417,7 @@
         <v>1.4</v>
       </c>
       <c r="N64" t="n">
-        <v>-8.800000000000001</v>
+        <v>-10.1</v>
       </c>
       <c r="P64" t="n">
         <v>-9.800000000000001</v>
@@ -9455,13 +9469,13 @@
         <v>131.78</v>
       </c>
       <c r="AI64" t="n">
-        <v>114.03</v>
+        <v>112.27</v>
       </c>
       <c r="AJ64" t="n">
-        <v>114.03</v>
+        <v>112.27</v>
       </c>
       <c r="AK64" t="n">
-        <v>-13.47</v>
+        <v>-14.8</v>
       </c>
       <c r="AL64" t="n">
         <v>-16.3</v>
@@ -9470,16 +9484,16 @@
         <v>0.74</v>
       </c>
       <c r="AN64" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AO64" t="n">
         <v>1</v>
       </c>
       <c r="AR64" t="n">
-        <v>2.07</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="AT64" t="n">
-        <v>-15.54</v>
+        <v>-15.74</v>
       </c>
       <c r="AU64" t="inlineStr">
         <is>
@@ -9523,7 +9537,7 @@
         <v>-19.9</v>
       </c>
       <c r="I65" t="n">
-        <v>0.6</v>
+        <v>1.1</v>
       </c>
       <c r="J65" t="n">
         <v>7.04</v>
@@ -9538,7 +9552,7 @@
         <v>0.4</v>
       </c>
       <c r="N65" t="n">
-        <v>13.6</v>
+        <v>10.8</v>
       </c>
       <c r="P65" t="n">
         <v>2.1</v>
@@ -9575,7 +9589,7 @@
         <v>46276</v>
       </c>
       <c r="Z65" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AA65" t="inlineStr">
         <is>
@@ -9604,13 +9618,13 @@
         <v>66.86</v>
       </c>
       <c r="AI65" t="n">
-        <v>75.92</v>
+        <v>74.01000000000001</v>
       </c>
       <c r="AJ65" t="n">
-        <v>75.92</v>
+        <v>74.01000000000001</v>
       </c>
       <c r="AK65" t="n">
-        <v>13.55</v>
+        <v>10.69</v>
       </c>
       <c r="AL65" t="n">
         <v>-1.24</v>
@@ -9619,16 +9633,16 @@
         <v>21.85</v>
       </c>
       <c r="AN65" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AO65" t="n">
         <v>22</v>
       </c>
       <c r="AR65" t="n">
-        <v>2.07</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="AT65" t="n">
-        <v>11.48</v>
+        <v>9.76</v>
       </c>
     </row>
     <row r="66">
@@ -9667,7 +9681,7 @@
         <v>-9.1</v>
       </c>
       <c r="I66" t="n">
-        <v>-14.2</v>
+        <v>-13.1</v>
       </c>
       <c r="J66" t="n">
         <v>-5.75</v>
@@ -9682,7 +9696,7 @@
         <v>-30.4</v>
       </c>
       <c r="N66" t="n">
-        <v>-33</v>
+        <v>-34.5</v>
       </c>
       <c r="P66" t="n">
         <v>-33.7</v>
@@ -9734,31 +9748,31 @@
         <v>15.93</v>
       </c>
       <c r="AI66" t="n">
-        <v>14.43</v>
+        <v>14.07</v>
       </c>
       <c r="AJ66" t="n">
-        <v>14.43</v>
+        <v>14.07</v>
       </c>
       <c r="AK66" t="n">
-        <v>-9.390000000000001</v>
+        <v>-11.65</v>
       </c>
       <c r="AL66" t="n">
-        <v>-11.84</v>
+        <v>-12.34</v>
       </c>
       <c r="AM66" t="n">
         <v>0.85</v>
       </c>
       <c r="AN66" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AO66" t="n">
         <v>0</v>
       </c>
       <c r="AR66" t="n">
-        <v>1.26</v>
+        <v>0.14</v>
       </c>
       <c r="AT66" t="n">
-        <v>-10.65</v>
+        <v>-11.79</v>
       </c>
     </row>
     <row r="67">
@@ -9941,10 +9955,10 @@
         <v>-9.6</v>
       </c>
       <c r="I68" t="n">
-        <v>-4.6</v>
+        <v>-4.3</v>
       </c>
       <c r="J68" t="n">
-        <v>5.48</v>
+        <v>5.19</v>
       </c>
       <c r="K68" t="n">
         <v>7.06</v>
@@ -9953,16 +9967,16 @@
         <v>-1.07</v>
       </c>
       <c r="M68" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="N68" t="n">
-        <v>-0.8</v>
+        <v>-0.7</v>
       </c>
       <c r="P68" t="n">
         <v>3.7</v>
       </c>
       <c r="Q68" t="n">
-        <v>74.01000000000001</v>
+        <v>73.97</v>
       </c>
       <c r="R68" t="inlineStr">
         <is>
@@ -9978,7 +9992,7 @@
         <v>46213</v>
       </c>
       <c r="U68" t="n">
-        <v>-1.81</v>
+        <v>-1.53</v>
       </c>
       <c r="V68" t="n">
         <v>42</v>
@@ -10082,7 +10096,7 @@
         <v>9.699999999999999</v>
       </c>
       <c r="I69" t="n">
-        <v>-22.3</v>
+        <v>-22.1</v>
       </c>
       <c r="J69" t="n">
         <v>-10.83</v>
@@ -10097,7 +10111,7 @@
         <v>4.1</v>
       </c>
       <c r="N69" t="n">
-        <v>-12.5</v>
+        <v>-14.4</v>
       </c>
       <c r="P69" t="n">
         <v>-6.5</v>
@@ -10149,13 +10163,13 @@
         <v>133.75</v>
       </c>
       <c r="AI69" t="n">
-        <v>109.2</v>
+        <v>106.61</v>
       </c>
       <c r="AJ69" t="n">
-        <v>109.2</v>
+        <v>106.61</v>
       </c>
       <c r="AK69" t="n">
-        <v>-18.36</v>
+        <v>-20.29</v>
       </c>
       <c r="AL69" t="n">
         <v>-21.17</v>
@@ -10164,16 +10178,16 @@
         <v>0.08</v>
       </c>
       <c r="AN69" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AO69" t="n">
         <v>0</v>
       </c>
       <c r="AR69" t="n">
-        <v>1.26</v>
+        <v>0.14</v>
       </c>
       <c r="AT69" t="n">
-        <v>-19.62</v>
+        <v>-20.43</v>
       </c>
       <c r="AU69" t="inlineStr">
         <is>
@@ -10533,7 +10547,7 @@
         <v>-38.2</v>
       </c>
       <c r="Q72" t="n">
-        <v>167.32</v>
+        <v>167.31</v>
       </c>
       <c r="R72" t="inlineStr">
         <is>
@@ -10812,7 +10826,7 @@
         <v>1.3</v>
       </c>
       <c r="I74" t="n">
-        <v>-12.7</v>
+        <v>-7.6</v>
       </c>
       <c r="J74" t="n">
         <v>-6.82</v>
@@ -10827,7 +10841,7 @@
         <v>-29.7</v>
       </c>
       <c r="N74" t="n">
-        <v>-25.6</v>
+        <v>-24.9</v>
       </c>
       <c r="P74" t="n">
         <v>-44.3</v>
@@ -10879,13 +10893,13 @@
         <v>46.92</v>
       </c>
       <c r="AI74" t="n">
-        <v>44.14</v>
+        <v>44.39</v>
       </c>
       <c r="AJ74" t="n">
-        <v>44.14</v>
+        <v>44.39</v>
       </c>
       <c r="AK74" t="n">
-        <v>-5.92</v>
+        <v>-5.39</v>
       </c>
       <c r="AL74" t="n">
         <v>-11.79</v>
@@ -10894,16 +10908,16 @@
         <v>2.43</v>
       </c>
       <c r="AN74" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AO74" t="n">
         <v>0</v>
       </c>
       <c r="AR74" t="n">
-        <v>0.22</v>
+        <v>-0.89</v>
       </c>
       <c r="AT74" t="n">
-        <v>-6.14</v>
+        <v>-4.5</v>
       </c>
     </row>
     <row r="75">
@@ -11226,7 +11240,7 @@
         <v>-26.6</v>
       </c>
       <c r="I77" t="n">
-        <v>-10.8</v>
+        <v>-15.1</v>
       </c>
       <c r="J77" t="n">
         <v>-5.89</v>
@@ -11241,7 +11255,7 @@
         <v>9.800000000000001</v>
       </c>
       <c r="N77" t="n">
-        <v>-1.7</v>
+        <v>-6.6</v>
       </c>
       <c r="P77" t="n">
         <v>8.5</v>
@@ -11278,7 +11292,7 @@
         <v>46273</v>
       </c>
       <c r="Z77" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AA77" t="inlineStr">
         <is>
@@ -11307,31 +11321,31 @@
         <v>443.5</v>
       </c>
       <c r="AI77" t="n">
-        <v>430.01</v>
+        <v>409.29</v>
       </c>
       <c r="AJ77" t="n">
-        <v>430.01</v>
+        <v>409.29</v>
       </c>
       <c r="AK77" t="n">
-        <v>-3.04</v>
+        <v>-7.71</v>
       </c>
       <c r="AL77" t="n">
-        <v>-7.21</v>
+        <v>-8.17</v>
       </c>
       <c r="AM77" t="n">
         <v>23.39</v>
       </c>
       <c r="AN77" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="AO77" t="n">
         <v>21</v>
       </c>
       <c r="AR77" t="n">
-        <v>1.48</v>
+        <v>0.35</v>
       </c>
       <c r="AT77" t="n">
-        <v>-4.52</v>
+        <v>-8.07</v>
       </c>
     </row>
     <row r="78">
@@ -11793,7 +11807,7 @@
         <v>-17.1</v>
       </c>
       <c r="I81" t="n">
-        <v>-8.699999999999999</v>
+        <v>-10.4</v>
       </c>
       <c r="J81" t="n">
         <v>-7.68</v>
@@ -11808,7 +11822,7 @@
         <v>-20.5</v>
       </c>
       <c r="N81" t="n">
-        <v>-30.1</v>
+        <v>-32</v>
       </c>
       <c r="P81" t="n">
         <v>-27.1</v>
@@ -11860,31 +11874,31 @@
         <v>97.91</v>
       </c>
       <c r="AI81" t="n">
-        <v>82.56</v>
+        <v>80.14</v>
       </c>
       <c r="AJ81" t="n">
-        <v>82.56</v>
+        <v>80.14</v>
       </c>
       <c r="AK81" t="n">
-        <v>-15.68</v>
+        <v>-18.15</v>
       </c>
       <c r="AL81" t="n">
-        <v>-18.29</v>
+        <v>-18.62</v>
       </c>
       <c r="AM81" t="n">
         <v>1.77</v>
       </c>
       <c r="AN81" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="AO81" t="n">
         <v>4</v>
       </c>
       <c r="AR81" t="n">
-        <v>0.83</v>
+        <v>-0.28</v>
       </c>
       <c r="AT81" t="n">
-        <v>-16.51</v>
+        <v>-17.86</v>
       </c>
       <c r="AU81" t="inlineStr">
         <is>
@@ -12226,7 +12240,7 @@
         <v>5.8</v>
       </c>
       <c r="I84" t="n">
-        <v>19.6</v>
+        <v>12.2</v>
       </c>
       <c r="J84" t="n">
         <v>8.66</v>
@@ -12241,7 +12255,7 @@
         <v>-4.1</v>
       </c>
       <c r="N84" t="n">
-        <v>19.9</v>
+        <v>11.8</v>
       </c>
       <c r="O84" t="inlineStr">
         <is>
@@ -12283,7 +12297,7 @@
         <v>46262</v>
       </c>
       <c r="Z84" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="AA84" t="inlineStr">
         <is>
@@ -12312,13 +12326,13 @@
         <v>10.28</v>
       </c>
       <c r="AI84" t="n">
-        <v>12.16</v>
+        <v>11.32</v>
       </c>
       <c r="AJ84" t="n">
-        <v>12.16</v>
+        <v>11.32</v>
       </c>
       <c r="AK84" t="n">
-        <v>18.29</v>
+        <v>10.12</v>
       </c>
       <c r="AL84" t="n">
         <v>-2.14</v>
@@ -12327,16 +12341,16 @@
         <v>25.29</v>
       </c>
       <c r="AN84" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="AO84" t="n">
         <v>30</v>
       </c>
       <c r="AR84" t="n">
-        <v>0.25</v>
+        <v>-0.86</v>
       </c>
       <c r="AT84" t="n">
-        <v>18.04</v>
+        <v>10.97</v>
       </c>
     </row>
     <row r="85">
@@ -12375,7 +12389,7 @@
         <v>-4.2</v>
       </c>
       <c r="I85" t="n">
-        <v>-2.4</v>
+        <v>-7.1</v>
       </c>
       <c r="J85" t="n">
         <v>-7.73</v>
@@ -12390,7 +12404,7 @@
         <v>1.4</v>
       </c>
       <c r="N85" t="n">
-        <v>-6.2</v>
+        <v>-10.4</v>
       </c>
       <c r="P85" t="n">
         <v>-3.5</v>
@@ -12442,31 +12456,31 @@
         <v>372.92</v>
       </c>
       <c r="AI85" t="n">
-        <v>344.33</v>
+        <v>328.75</v>
       </c>
       <c r="AJ85" t="n">
-        <v>344.33</v>
+        <v>328.75</v>
       </c>
       <c r="AK85" t="n">
-        <v>-7.67</v>
+        <v>-11.84</v>
       </c>
       <c r="AL85" t="n">
-        <v>-10.27</v>
+        <v>-11.89</v>
       </c>
       <c r="AM85" t="n">
         <v>2.12</v>
       </c>
       <c r="AN85" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="AO85" t="n">
         <v>26</v>
       </c>
       <c r="AR85" t="n">
-        <v>0.25</v>
+        <v>-0.86</v>
       </c>
       <c r="AT85" t="n">
-        <v>-7.92</v>
+        <v>-10.99</v>
       </c>
     </row>
     <row r="86">
@@ -14209,7 +14223,7 @@
         <v>44.3</v>
       </c>
       <c r="I98" t="n">
-        <v>26.2</v>
+        <v>30.1</v>
       </c>
       <c r="J98" t="n">
         <v>-3.81</v>
@@ -14221,10 +14235,10 @@
         <v>-5.71</v>
       </c>
       <c r="M98" t="n">
-        <v>-8.1</v>
+        <v>-8</v>
       </c>
       <c r="N98" t="n">
-        <v>18.7</v>
+        <v>21.3</v>
       </c>
       <c r="O98" t="inlineStr">
         <is>
@@ -14235,7 +14249,7 @@
         <v>-43.6</v>
       </c>
       <c r="Q98" t="n">
-        <v>200.84</v>
+        <v>200.8</v>
       </c>
       <c r="R98" t="inlineStr">
         <is>
@@ -14266,7 +14280,7 @@
         <v>46279</v>
       </c>
       <c r="Z98" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AA98" t="inlineStr">
         <is>
@@ -14295,31 +14309,31 @@
         <v>184.64</v>
       </c>
       <c r="AI98" t="n">
-        <v>224.92</v>
+        <v>229.68</v>
       </c>
       <c r="AJ98" t="n">
-        <v>224.92</v>
+        <v>229.68</v>
       </c>
       <c r="AK98" t="n">
-        <v>21.82</v>
+        <v>24.39</v>
       </c>
       <c r="AL98" t="n">
         <v>-7.53</v>
       </c>
       <c r="AM98" t="n">
-        <v>23.41</v>
+        <v>25.3</v>
       </c>
       <c r="AN98" t="n">
+        <v>39</v>
+      </c>
+      <c r="AO98" t="n">
         <v>38</v>
       </c>
-      <c r="AO98" t="n">
-        <v>37</v>
-      </c>
       <c r="AR98" t="n">
-        <v>1.17</v>
+        <v>0.05</v>
       </c>
       <c r="AT98" t="n">
-        <v>20.65</v>
+        <v>24.35</v>
       </c>
     </row>
     <row r="99">
@@ -14637,7 +14651,7 @@
         <v>37.7</v>
       </c>
       <c r="I101" t="n">
-        <v>-5.2</v>
+        <v>-7.5</v>
       </c>
       <c r="J101" t="n">
         <v>-6.45</v>
@@ -14652,7 +14666,7 @@
         <v>1.8</v>
       </c>
       <c r="N101" t="n">
-        <v>-1.2</v>
+        <v>-3.5</v>
       </c>
       <c r="P101" t="n">
         <v>-29.3</v>
@@ -14689,7 +14703,7 @@
         <v>46261</v>
       </c>
       <c r="Z101" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="AA101" t="inlineStr">
         <is>
@@ -14715,13 +14729,13 @@
         <v>275</v>
       </c>
       <c r="AI101" t="n">
-        <v>251.67</v>
+        <v>245.2</v>
       </c>
       <c r="AJ101" t="n">
-        <v>251.67</v>
+        <v>245.2</v>
       </c>
       <c r="AK101" t="n">
-        <v>-8.48</v>
+        <v>-10.84</v>
       </c>
       <c r="AL101" t="n">
         <v>-18.3</v>
@@ -14730,16 +14744,16 @@
         <v>7.1</v>
       </c>
       <c r="AN101" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="AO101" t="n">
         <v>6</v>
       </c>
       <c r="AR101" t="n">
-        <v>1.17</v>
+        <v>0.05</v>
       </c>
       <c r="AT101" t="n">
-        <v>-9.65</v>
+        <v>-10.88</v>
       </c>
       <c r="AU101" t="inlineStr">
         <is>
@@ -15517,7 +15531,7 @@
         <v>-7.1</v>
       </c>
       <c r="I107" t="n">
-        <v>-12.5</v>
+        <v>-17.8</v>
       </c>
       <c r="J107" t="n">
         <v>2.22</v>
@@ -15532,7 +15546,7 @@
         <v>4.9</v>
       </c>
       <c r="N107" t="n">
-        <v>-13.2</v>
+        <v>-14.6</v>
       </c>
       <c r="P107" t="n">
         <v>-9</v>
@@ -15569,7 +15583,7 @@
         <v>46258</v>
       </c>
       <c r="Z107" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="AA107" t="inlineStr">
         <is>
@@ -15598,31 +15612,31 @@
         <v>50.78</v>
       </c>
       <c r="AI107" t="n">
-        <v>42.34</v>
+        <v>41.62</v>
       </c>
       <c r="AJ107" t="n">
-        <v>42.34</v>
+        <v>41.62</v>
       </c>
       <c r="AK107" t="n">
-        <v>-16.62</v>
+        <v>-18.04</v>
       </c>
       <c r="AL107" t="n">
-        <v>-18.59</v>
+        <v>-19.22</v>
       </c>
       <c r="AM107" t="n">
         <v>11.12</v>
       </c>
       <c r="AN107" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="AO107" t="n">
         <v>20</v>
       </c>
       <c r="AR107" t="n">
-        <v>1.01</v>
+        <v>-0.11</v>
       </c>
       <c r="AT107" t="n">
-        <v>-17.63</v>
+        <v>-17.93</v>
       </c>
       <c r="AU107" t="inlineStr">
         <is>
@@ -16234,7 +16248,7 @@
         <v>-9.1</v>
       </c>
       <c r="I112" t="n">
-        <v>-15.7</v>
+        <v>-17.8</v>
       </c>
       <c r="J112" t="n">
         <v>-5.07</v>
@@ -16249,7 +16263,7 @@
         <v>3.7</v>
       </c>
       <c r="N112" t="n">
-        <v>-17.8</v>
+        <v>-21.8</v>
       </c>
       <c r="P112" t="n">
         <v>1.7</v>
@@ -16286,7 +16300,7 @@
         <v>46287</v>
       </c>
       <c r="Z112" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AA112" t="inlineStr">
         <is>
@@ -16315,13 +16329,13 @@
         <v>112.19</v>
       </c>
       <c r="AI112" t="n">
-        <v>92.31999999999999</v>
+        <v>87.81</v>
       </c>
       <c r="AJ112" t="n">
-        <v>92.31999999999999</v>
+        <v>87.81</v>
       </c>
       <c r="AK112" t="n">
-        <v>-17.71</v>
+        <v>-21.73</v>
       </c>
       <c r="AL112" t="n">
         <v>-23.2</v>
@@ -16330,16 +16344,16 @@
         <v>14.5</v>
       </c>
       <c r="AN112" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="AO112" t="n">
         <v>25</v>
       </c>
       <c r="AR112" t="n">
-        <v>1.01</v>
+        <v>-0.11</v>
       </c>
       <c r="AT112" t="n">
-        <v>-18.72</v>
+        <v>-21.62</v>
       </c>
       <c r="AU112" t="inlineStr">
         <is>
@@ -16383,7 +16397,7 @@
         <v>-31.8</v>
       </c>
       <c r="I113" t="n">
-        <v>-15.8</v>
+        <v>-14.2</v>
       </c>
       <c r="J113" t="n">
         <v>-7.89</v>
@@ -16398,7 +16412,7 @@
         <v>-12.7</v>
       </c>
       <c r="N113" t="n">
-        <v>-24.5</v>
+        <v>-24.3</v>
       </c>
       <c r="P113" t="n">
         <v>-15.8</v>
@@ -16450,13 +16464,13 @@
         <v>50.2</v>
       </c>
       <c r="AI113" t="n">
-        <v>41.1</v>
+        <v>41.16</v>
       </c>
       <c r="AJ113" t="n">
-        <v>41.1</v>
+        <v>41.16</v>
       </c>
       <c r="AK113" t="n">
-        <v>-18.13</v>
+        <v>-18.01</v>
       </c>
       <c r="AL113" t="n">
         <v>-27.27</v>
@@ -16465,16 +16479,16 @@
         <v>4.72</v>
       </c>
       <c r="AN113" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="AO113" t="n">
         <v>3</v>
       </c>
       <c r="AR113" t="n">
-        <v>1.01</v>
+        <v>-0.11</v>
       </c>
       <c r="AT113" t="n">
-        <v>-19.14</v>
+        <v>-17.9</v>
       </c>
       <c r="AU113" t="inlineStr">
         <is>
@@ -16932,7 +16946,7 @@
         <v>-11.7</v>
       </c>
       <c r="I117" t="n">
-        <v>-6.2</v>
+        <v>-6.7</v>
       </c>
       <c r="J117" t="n">
         <v>2.64</v>
@@ -16944,7 +16958,7 @@
         <v>-5.11</v>
       </c>
       <c r="M117" t="n">
-        <v>-25.2</v>
+        <v>-25.1</v>
       </c>
       <c r="N117" t="n">
         <v>-23.7</v>
@@ -16953,7 +16967,7 @@
         <v>-31.5</v>
       </c>
       <c r="Q117" t="n">
-        <v>86.54000000000001</v>
+        <v>86.53</v>
       </c>
       <c r="R117" t="inlineStr">
         <is>
@@ -16984,7 +16998,7 @@
         <v>46262</v>
       </c>
       <c r="Z117" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="AA117" t="inlineStr">
         <is>
@@ -17010,13 +17024,13 @@
         <v>64.77</v>
       </c>
       <c r="AI117" t="n">
-        <v>59.09</v>
+        <v>58.94</v>
       </c>
       <c r="AJ117" t="n">
-        <v>59.09</v>
+        <v>58.94</v>
       </c>
       <c r="AK117" t="n">
-        <v>-8.77</v>
+        <v>-9</v>
       </c>
       <c r="AL117" t="n">
         <v>-13.39</v>
@@ -17025,16 +17039,16 @@
         <v>8.279999999999999</v>
       </c>
       <c r="AN117" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="AO117" t="n">
         <v>6</v>
       </c>
       <c r="AR117" t="n">
-        <v>1.01</v>
+        <v>-0.11</v>
       </c>
       <c r="AT117" t="n">
-        <v>-9.779999999999999</v>
+        <v>-8.890000000000001</v>
       </c>
       <c r="AU117" t="inlineStr">
         <is>
@@ -21247,7 +21261,7 @@
         <v>-10</v>
       </c>
       <c r="I147" t="n">
-        <v>19.6</v>
+        <v>12.2</v>
       </c>
       <c r="J147" t="n">
         <v>3.54</v>
@@ -21262,7 +21276,7 @@
         <v>-11.4</v>
       </c>
       <c r="N147" t="n">
-        <v>19.9</v>
+        <v>11.8</v>
       </c>
       <c r="P147" t="n">
         <v>-30.7</v>
@@ -21299,7 +21313,7 @@
         <v>46245</v>
       </c>
       <c r="Z147" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="AA147" t="inlineStr">
         <is>
@@ -21328,13 +21342,13 @@
         <v>10.03</v>
       </c>
       <c r="AI147" t="n">
-        <v>12.16</v>
+        <v>11.32</v>
       </c>
       <c r="AJ147" t="n">
-        <v>12.16</v>
+        <v>11.32</v>
       </c>
       <c r="AK147" t="n">
-        <v>21.3</v>
+        <v>12.92</v>
       </c>
       <c r="AL147" t="n">
         <v>-5.44</v>
@@ -21343,16 +21357,16 @@
         <v>28.48</v>
       </c>
       <c r="AN147" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="AO147" t="n">
         <v>47</v>
       </c>
       <c r="AR147" t="n">
-        <v>-0.28</v>
+        <v>-1.38</v>
       </c>
       <c r="AT147" t="n">
-        <v>21.57</v>
+        <v>14.3</v>
       </c>
     </row>
     <row r="148">
@@ -21969,7 +21983,7 @@
         <v>9.4</v>
       </c>
       <c r="I152" t="n">
-        <v>-9</v>
+        <v>-9.699999999999999</v>
       </c>
       <c r="J152" t="n">
         <v>-8.5</v>
@@ -21984,7 +21998,7 @@
         <v>14.7</v>
       </c>
       <c r="N152" t="n">
-        <v>-10.4</v>
+        <v>-13.2</v>
       </c>
       <c r="P152" t="n">
         <v>-0.5</v>
@@ -22021,7 +22035,7 @@
         <v>46238</v>
       </c>
       <c r="Z152" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="AA152" t="inlineStr">
         <is>
@@ -22047,13 +22061,13 @@
         <v>15.77</v>
       </c>
       <c r="AI152" t="n">
-        <v>12.28</v>
+        <v>11.88</v>
       </c>
       <c r="AJ152" t="n">
-        <v>12.28</v>
+        <v>11.88</v>
       </c>
       <c r="AK152" t="n">
-        <v>-22.13</v>
+        <v>-24.67</v>
       </c>
       <c r="AL152" t="n">
         <v>-26.13</v>
@@ -22062,16 +22076,16 @@
         <v>8.5</v>
       </c>
       <c r="AN152" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="AO152" t="n">
         <v>2</v>
       </c>
       <c r="AR152" t="n">
-        <v>3.24</v>
+        <v>2.1</v>
       </c>
       <c r="AT152" t="n">
-        <v>-25.37</v>
+        <v>-26.76</v>
       </c>
       <c r="AU152" t="inlineStr">
         <is>
@@ -23258,7 +23272,7 @@
         <v>-7.4</v>
       </c>
       <c r="I161" t="n">
-        <v>0.6</v>
+        <v>1.1</v>
       </c>
       <c r="J161" t="n">
         <v>10.43</v>
@@ -23273,7 +23287,7 @@
         <v>7.3</v>
       </c>
       <c r="N161" t="n">
-        <v>13.6</v>
+        <v>10.8</v>
       </c>
       <c r="P161" t="n">
         <v>-6.2</v>
@@ -23310,7 +23324,7 @@
         <v>46237</v>
       </c>
       <c r="Z161" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="AA161" t="inlineStr">
         <is>
@@ -23339,13 +23353,13 @@
         <v>70.92</v>
       </c>
       <c r="AI161" t="n">
-        <v>75.92</v>
+        <v>74.01000000000001</v>
       </c>
       <c r="AJ161" t="n">
-        <v>75.92</v>
+        <v>74.01000000000001</v>
       </c>
       <c r="AK161" t="n">
-        <v>7.05</v>
+        <v>4.36</v>
       </c>
       <c r="AL161" t="n">
         <v>-6.9</v>
@@ -23354,16 +23368,16 @@
         <v>27.52</v>
       </c>
       <c r="AN161" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="AO161" t="n">
         <v>21</v>
       </c>
       <c r="AR161" t="n">
-        <v>5.12</v>
+        <v>3.95</v>
       </c>
       <c r="AT161" t="n">
-        <v>1.93</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="162">
@@ -23947,7 +23961,7 @@
         <v>25.1</v>
       </c>
       <c r="I166" t="n">
-        <v>-0.8</v>
+        <v>-1.8</v>
       </c>
       <c r="J166" t="n">
         <v>10.45</v>
@@ -23962,7 +23976,7 @@
         <v>25</v>
       </c>
       <c r="N166" t="n">
-        <v>22.3</v>
+        <v>19.9</v>
       </c>
       <c r="P166" t="n">
         <v>-6.8</v>
@@ -23999,7 +24013,7 @@
         <v>46233</v>
       </c>
       <c r="Z166" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="AA166" t="inlineStr">
         <is>
@@ -24028,13 +24042,13 @@
         <v>24.39</v>
       </c>
       <c r="AI166" t="n">
-        <v>25.76</v>
+        <v>25.28</v>
       </c>
       <c r="AJ166" t="n">
-        <v>25.76</v>
+        <v>25.28</v>
       </c>
       <c r="AK166" t="n">
-        <v>5.61</v>
+        <v>3.65</v>
       </c>
       <c r="AL166" t="n">
         <v>-7.51</v>
@@ -24043,16 +24057,16 @@
         <v>22.95</v>
       </c>
       <c r="AN166" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="AO166" t="n">
         <v>1</v>
       </c>
       <c r="AR166" t="n">
-        <v>4.56</v>
+        <v>3.4</v>
       </c>
       <c r="AT166" t="n">
-        <v>1.06</v>
+        <v>0.24</v>
       </c>
     </row>
     <row r="167">
@@ -24677,7 +24691,7 @@
         <v>-11.5</v>
       </c>
       <c r="I171" t="n">
-        <v>-1.1</v>
+        <v>3.5</v>
       </c>
       <c r="J171" t="n">
         <v>-18.43</v>
@@ -24692,7 +24706,7 @@
         <v>-24.2</v>
       </c>
       <c r="N171" t="n">
-        <v>-20.7</v>
+        <v>-21.2</v>
       </c>
       <c r="P171" t="n">
         <v>-25.7</v>
@@ -24729,7 +24743,7 @@
         <v>46230</v>
       </c>
       <c r="Z171" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="AA171" t="inlineStr">
         <is>
@@ -24755,13 +24769,13 @@
         <v>268.74</v>
       </c>
       <c r="AI171" t="n">
-        <v>234.03</v>
+        <v>231.83</v>
       </c>
       <c r="AJ171" t="n">
-        <v>234.03</v>
+        <v>231.83</v>
       </c>
       <c r="AK171" t="n">
-        <v>-12.92</v>
+        <v>-13.73</v>
       </c>
       <c r="AL171" t="n">
         <v>-26.39</v>
@@ -24770,16 +24784,16 @@
         <v>8.130000000000001</v>
       </c>
       <c r="AN171" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="AO171" t="n">
         <v>3</v>
       </c>
       <c r="AR171" t="n">
-        <v>4.77</v>
+        <v>3.61</v>
       </c>
       <c r="AT171" t="n">
-        <v>-17.68</v>
+        <v>-17.34</v>
       </c>
       <c r="AU171" t="inlineStr">
         <is>
@@ -25895,7 +25909,7 @@
         <v>45.4</v>
       </c>
       <c r="Q179" t="n">
-        <v>130.31</v>
+        <v>130.3</v>
       </c>
       <c r="R179" t="inlineStr">
         <is>
@@ -27234,7 +27248,7 @@
         <v>24.3</v>
       </c>
       <c r="I188" t="n">
-        <v>-10.8</v>
+        <v>-15.1</v>
       </c>
       <c r="J188" t="n">
         <v>-5.03</v>
@@ -27249,7 +27263,7 @@
         <v>51.8</v>
       </c>
       <c r="N188" t="n">
-        <v>-1.7</v>
+        <v>-6.6</v>
       </c>
       <c r="P188" t="n">
         <v>46.3</v>
@@ -27281,7 +27295,7 @@
         <v>46226</v>
       </c>
       <c r="Z188" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="AA188" t="inlineStr">
         <is>
@@ -27307,22 +27321,22 @@
         <v>545.05</v>
       </c>
       <c r="AI188" t="n">
-        <v>430.01</v>
+        <v>409.29</v>
       </c>
       <c r="AJ188" t="n">
-        <v>430.01</v>
+        <v>409.29</v>
       </c>
       <c r="AK188" t="n">
-        <v>-21.11</v>
+        <v>-24.91</v>
       </c>
       <c r="AL188" t="n">
-        <v>-24.5</v>
+        <v>-25.28</v>
       </c>
       <c r="AM188" t="n">
         <v>5.66</v>
       </c>
       <c r="AN188" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="AO188" t="n">
         <v>3</v>
@@ -27331,13 +27345,13 @@
         <v>-14.83</v>
       </c>
       <c r="AR188" t="n">
-        <v>3.57</v>
+        <v>2.42</v>
       </c>
       <c r="AS188" t="n">
         <v>4.4</v>
       </c>
       <c r="AT188" t="n">
-        <v>-24.67</v>
+        <v>-27.33</v>
       </c>
       <c r="AU188" t="inlineStr">
         <is>
@@ -29621,7 +29635,7 @@
         <v>13.9</v>
       </c>
       <c r="I204" t="n">
-        <v>23</v>
+        <v>15.1</v>
       </c>
       <c r="J204" t="n">
         <v>-6.26</v>
@@ -29636,7 +29650,7 @@
         <v>73.3</v>
       </c>
       <c r="N204" t="n">
-        <v>43.2</v>
+        <v>34.1</v>
       </c>
       <c r="P204" t="n">
         <v>67.09999999999999</v>
@@ -29668,7 +29682,7 @@
         <v>46224</v>
       </c>
       <c r="Z204" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="AA204" t="inlineStr">
         <is>
@@ -29697,13 +29711,13 @@
         <v>517</v>
       </c>
       <c r="AI204" t="n">
-        <v>562.23</v>
+        <v>528.75</v>
       </c>
       <c r="AJ204" t="n">
-        <v>562.23</v>
+        <v>528.75</v>
       </c>
       <c r="AK204" t="n">
-        <v>8.75</v>
+        <v>2.27</v>
       </c>
       <c r="AL204" t="n">
         <v>-17.98</v>
@@ -29712,7 +29726,7 @@
         <v>27.37</v>
       </c>
       <c r="AN204" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="AO204" t="n">
         <v>55</v>
@@ -29721,13 +29735,13 @@
         <v>17.12</v>
       </c>
       <c r="AR204" t="n">
-        <v>3.57</v>
+        <v>2.42</v>
       </c>
       <c r="AS204" t="n">
         <v>4.4</v>
       </c>
       <c r="AT204" t="n">
-        <v>5.18</v>
+        <v>-0.15</v>
       </c>
       <c r="AU204" t="inlineStr">
         <is>
@@ -31439,7 +31453,7 @@
         <v>-35.9</v>
       </c>
       <c r="Q216" t="n">
-        <v>188.74</v>
+        <v>188.73</v>
       </c>
       <c r="R216" t="inlineStr">
         <is>
@@ -32169,7 +32183,7 @@
         <v>3.7</v>
       </c>
       <c r="I221" t="n">
-        <v>-12.5</v>
+        <v>-17.8</v>
       </c>
       <c r="J221" t="n">
         <v>4.03</v>
@@ -32184,7 +32198,7 @@
         <v>-1.1</v>
       </c>
       <c r="N221" t="n">
-        <v>-13.2</v>
+        <v>-14.6</v>
       </c>
       <c r="P221" t="n">
         <v>-16.6</v>
@@ -32216,7 +32230,7 @@
         <v>46231</v>
       </c>
       <c r="Z221" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="AA221" t="inlineStr">
         <is>
@@ -32245,22 +32259,22 @@
         <v>50.22</v>
       </c>
       <c r="AI221" t="n">
-        <v>42.34</v>
+        <v>41.62</v>
       </c>
       <c r="AJ221" t="n">
-        <v>42.34</v>
+        <v>41.62</v>
       </c>
       <c r="AK221" t="n">
-        <v>-15.69</v>
+        <v>-17.12</v>
       </c>
       <c r="AL221" t="n">
-        <v>-17.68</v>
+        <v>-18.32</v>
       </c>
       <c r="AM221" t="n">
         <v>12.36</v>
       </c>
       <c r="AN221" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="AO221" t="n">
         <v>43</v>
@@ -32269,13 +32283,13 @@
         <v>-12.74</v>
       </c>
       <c r="AR221" t="n">
-        <v>3.57</v>
+        <v>2.42</v>
       </c>
       <c r="AS221" t="n">
         <v>4.4</v>
       </c>
       <c r="AT221" t="n">
-        <v>-19.26</v>
+        <v>-19.55</v>
       </c>
       <c r="AU221" t="inlineStr">
         <is>
@@ -33059,7 +33073,7 @@
         <v>24.8</v>
       </c>
       <c r="I227" t="n">
-        <v>7.4</v>
+        <v>6</v>
       </c>
       <c r="J227" t="n">
         <v>0.72</v>
@@ -33074,7 +33088,7 @@
         <v>1.1</v>
       </c>
       <c r="N227" t="n">
-        <v>4.8</v>
+        <v>3.2</v>
       </c>
       <c r="P227" t="n">
         <v>-22.3</v>
@@ -33131,13 +33145,13 @@
         <v>20.61</v>
       </c>
       <c r="AI227" t="n">
-        <v>20.44</v>
+        <v>20.14</v>
       </c>
       <c r="AJ227" t="n">
-        <v>20.44</v>
+        <v>20.14</v>
       </c>
       <c r="AK227" t="n">
-        <v>-0.82</v>
+        <v>-2.27</v>
       </c>
       <c r="AL227" t="n">
         <v>-23.57</v>
@@ -33146,7 +33160,7 @@
         <v>3.55</v>
       </c>
       <c r="AN227" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="AO227" t="n">
         <v>12</v>
@@ -33155,13 +33169,13 @@
         <v>-12.66</v>
       </c>
       <c r="AR227" t="n">
-        <v>3.57</v>
+        <v>2.42</v>
       </c>
       <c r="AS227" t="n">
         <v>4.4</v>
       </c>
       <c r="AT227" t="n">
-        <v>-4.38</v>
+        <v>-4.69</v>
       </c>
       <c r="AU227" t="inlineStr">
         <is>
@@ -34967,7 +34981,7 @@
         <v>-40.6</v>
       </c>
       <c r="I240" t="n">
-        <v>-30.6</v>
+        <v>-35.1</v>
       </c>
       <c r="J240" t="n">
         <v>9.31</v>
@@ -34982,7 +34996,7 @@
         <v>-30.2</v>
       </c>
       <c r="N240" t="n">
-        <v>-44.5</v>
+        <v>-49.2</v>
       </c>
       <c r="P240" t="n">
         <v>-33.9</v>
@@ -35019,7 +35033,7 @@
         <v>46224</v>
       </c>
       <c r="Z240" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="AA240" t="inlineStr">
         <is>
@@ -35048,13 +35062,13 @@
         <v>58.11</v>
       </c>
       <c r="AI240" t="n">
-        <v>44.46</v>
+        <v>40.66</v>
       </c>
       <c r="AJ240" t="n">
-        <v>44.46</v>
+        <v>40.66</v>
       </c>
       <c r="AK240" t="n">
-        <v>-23.49</v>
+        <v>-30.03</v>
       </c>
       <c r="AL240" t="n">
         <v>-31.39</v>
@@ -35063,7 +35077,7 @@
         <v>29.2</v>
       </c>
       <c r="AN240" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="AO240" t="n">
         <v>17</v>
@@ -35072,13 +35086,13 @@
         <v>-19.01</v>
       </c>
       <c r="AR240" t="n">
-        <v>3.57</v>
+        <v>2.42</v>
       </c>
       <c r="AS240" t="n">
         <v>4.4</v>
       </c>
       <c r="AT240" t="n">
-        <v>-27.06</v>
+        <v>-32.45</v>
       </c>
       <c r="AU240" t="inlineStr">
         <is>
@@ -35550,7 +35564,7 @@
         <v>-37.4</v>
       </c>
       <c r="I244" t="n">
-        <v>-19.1</v>
+        <v>-15.6</v>
       </c>
       <c r="J244" t="n">
         <v>1.06</v>
@@ -35565,7 +35579,7 @@
         <v>-20.1</v>
       </c>
       <c r="N244" t="n">
-        <v>-29.6</v>
+        <v>-27.7</v>
       </c>
       <c r="P244" t="n">
         <v>-21.7</v>
@@ -35599,7 +35613,7 @@
         <v>46225</v>
       </c>
       <c r="Z244" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="AA244" t="inlineStr">
         <is>
@@ -35628,13 +35642,13 @@
         <v>44.28</v>
       </c>
       <c r="AI244" t="n">
-        <v>40.42</v>
+        <v>41.45</v>
       </c>
       <c r="AJ244" t="n">
-        <v>40.42</v>
+        <v>41.45</v>
       </c>
       <c r="AK244" t="n">
-        <v>-8.73</v>
+        <v>-6.4</v>
       </c>
       <c r="AL244" t="n">
         <v>-12.27</v>
@@ -35643,7 +35657,7 @@
         <v>24.31</v>
       </c>
       <c r="AN244" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="AO244" t="n">
         <v>17</v>
@@ -35652,13 +35666,13 @@
         <v>-6.31</v>
       </c>
       <c r="AR244" t="n">
-        <v>3.57</v>
+        <v>2.42</v>
       </c>
       <c r="AS244" t="n">
         <v>4.4</v>
       </c>
       <c r="AT244" t="n">
-        <v>-12.29</v>
+        <v>-8.82</v>
       </c>
     </row>
     <row r="245">
@@ -36935,7 +36949,7 @@
         <v>13.8</v>
       </c>
       <c r="Q253" t="n">
-        <v>117.55</v>
+        <v>117.54</v>
       </c>
       <c r="R253" t="inlineStr">
         <is>
@@ -37651,7 +37665,7 @@
         <v>19.4</v>
       </c>
       <c r="I258" t="n">
-        <v>-9</v>
+        <v>-10.1</v>
       </c>
       <c r="J258" t="n">
         <v>9.869999999999999</v>
@@ -37666,7 +37680,7 @@
         <v>-0.4</v>
       </c>
       <c r="N258" t="n">
-        <v>-18.6</v>
+        <v>-21.5</v>
       </c>
       <c r="P258" t="n">
         <v>-14.2</v>
@@ -37703,7 +37717,7 @@
         <v>46230</v>
       </c>
       <c r="Z258" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="AA258" t="inlineStr">
         <is>
@@ -37732,22 +37746,22 @@
         <v>45.7</v>
       </c>
       <c r="AI258" t="n">
-        <v>36.5</v>
+        <v>35.13</v>
       </c>
       <c r="AJ258" t="n">
-        <v>36.5</v>
+        <v>35.13</v>
       </c>
       <c r="AK258" t="n">
-        <v>-20.13</v>
+        <v>-23.13</v>
       </c>
       <c r="AL258" t="n">
-        <v>-22.04</v>
+        <v>-23.68</v>
       </c>
       <c r="AM258" t="n">
         <v>17.33</v>
       </c>
       <c r="AN258" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="AO258" t="n">
         <v>12</v>
@@ -37756,13 +37770,13 @@
         <v>-17.26</v>
       </c>
       <c r="AR258" t="n">
-        <v>3.57</v>
+        <v>2.42</v>
       </c>
       <c r="AS258" t="n">
         <v>4.4</v>
       </c>
       <c r="AT258" t="n">
-        <v>-23.7</v>
+        <v>-25.55</v>
       </c>
       <c r="AU258" t="inlineStr">
         <is>
@@ -37955,7 +37969,7 @@
         <v>2.4</v>
       </c>
       <c r="I260" t="n">
-        <v>-24.2</v>
+        <v>-26.2</v>
       </c>
       <c r="J260" t="n">
         <v>-1.89</v>
@@ -37970,7 +37984,7 @@
         <v>-19.7</v>
       </c>
       <c r="N260" t="n">
-        <v>-35.7</v>
+        <v>-37.4</v>
       </c>
       <c r="P260" t="n">
         <v>-21.6</v>
@@ -38002,7 +38016,7 @@
         <v>46240</v>
       </c>
       <c r="Z260" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="AA260" t="inlineStr">
         <is>
@@ -38031,22 +38045,22 @@
         <v>120.59</v>
       </c>
       <c r="AI260" t="n">
-        <v>98.18000000000001</v>
+        <v>95.48</v>
       </c>
       <c r="AJ260" t="n">
-        <v>98.18000000000001</v>
+        <v>95.48</v>
       </c>
       <c r="AK260" t="n">
-        <v>-18.59</v>
+        <v>-20.83</v>
       </c>
       <c r="AL260" t="n">
-        <v>-21.26</v>
+        <v>-21.5</v>
       </c>
       <c r="AM260" t="n">
         <v>19.06</v>
       </c>
       <c r="AN260" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="AO260" t="n">
         <v>25</v>
@@ -38055,13 +38069,13 @@
         <v>-19.03</v>
       </c>
       <c r="AR260" t="n">
-        <v>3.57</v>
+        <v>2.42</v>
       </c>
       <c r="AS260" t="n">
         <v>4.4</v>
       </c>
       <c r="AT260" t="n">
-        <v>-22.15</v>
+        <v>-23.25</v>
       </c>
       <c r="AU260" t="inlineStr">
         <is>
@@ -38699,7 +38713,7 @@
         <v>2.3</v>
       </c>
       <c r="I265" t="n">
-        <v>-15.7</v>
+        <v>-17.8</v>
       </c>
       <c r="J265" t="n">
         <v>-2.12</v>
@@ -38714,7 +38728,7 @@
         <v>16.5</v>
       </c>
       <c r="N265" t="n">
-        <v>-17.8</v>
+        <v>-21.8</v>
       </c>
       <c r="P265" t="n">
         <v>11.6</v>
@@ -38746,7 +38760,7 @@
         <v>46224</v>
       </c>
       <c r="Z265" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="AA265" t="inlineStr">
         <is>
@@ -38772,13 +38786,13 @@
         <v>120.43</v>
       </c>
       <c r="AI265" t="n">
-        <v>92.31999999999999</v>
+        <v>87.81</v>
       </c>
       <c r="AJ265" t="n">
-        <v>92.31999999999999</v>
+        <v>87.81</v>
       </c>
       <c r="AK265" t="n">
-        <v>-23.34</v>
+        <v>-27.09</v>
       </c>
       <c r="AL265" t="n">
         <v>-28.46</v>
@@ -38787,7 +38801,7 @@
         <v>6.67</v>
       </c>
       <c r="AN265" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="AO265" t="n">
         <v>48</v>
@@ -38796,13 +38810,13 @@
         <v>-17.02</v>
       </c>
       <c r="AR265" t="n">
-        <v>3.57</v>
+        <v>2.42</v>
       </c>
       <c r="AS265" t="n">
         <v>4.4</v>
       </c>
       <c r="AT265" t="n">
-        <v>-26.91</v>
+        <v>-29.51</v>
       </c>
       <c r="AU265" t="inlineStr">
         <is>
@@ -40056,7 +40070,7 @@
         <v>25.8</v>
       </c>
       <c r="I274" t="n">
-        <v>46.6</v>
+        <v>48.4</v>
       </c>
       <c r="J274" t="n">
         <v>12.95</v>
@@ -40071,7 +40085,7 @@
         <v>7.1</v>
       </c>
       <c r="N274" t="n">
-        <v>48.4</v>
+        <v>49.5</v>
       </c>
       <c r="P274" t="n">
         <v>-17.9</v>
@@ -40108,7 +40122,7 @@
         <v>46231</v>
       </c>
       <c r="Z274" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="AA274" t="inlineStr">
         <is>
@@ -40137,13 +40151,13 @@
         <v>96.34</v>
       </c>
       <c r="AI274" t="n">
-        <v>151.99</v>
+        <v>153.26</v>
       </c>
       <c r="AJ274" t="n">
-        <v>151.99</v>
+        <v>153.26</v>
       </c>
       <c r="AK274" t="n">
-        <v>57.76</v>
+        <v>59.08</v>
       </c>
       <c r="AL274" t="n">
         <v>-6.51</v>
@@ -40152,7 +40166,7 @@
         <v>62.67</v>
       </c>
       <c r="AN274" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="AO274" t="n">
         <v>62</v>
@@ -40161,13 +40175,13 @@
         <v>56.61</v>
       </c>
       <c r="AR274" t="n">
-        <v>3.57</v>
+        <v>2.42</v>
       </c>
       <c r="AS274" t="n">
         <v>4.4</v>
       </c>
       <c r="AT274" t="n">
-        <v>54.2</v>
+        <v>56.66</v>
       </c>
     </row>
     <row r="275">
@@ -40506,7 +40520,7 @@
         <v>5.5</v>
       </c>
       <c r="I277" t="n">
-        <v>11.5</v>
+        <v>15.6</v>
       </c>
       <c r="J277" t="n">
         <v>1.46</v>
@@ -40521,7 +40535,7 @@
         <v>-9.1</v>
       </c>
       <c r="N277" t="n">
-        <v>-2.7</v>
+        <v>-2.9</v>
       </c>
       <c r="P277" t="n">
         <v>-18</v>
@@ -40558,7 +40572,7 @@
         <v>46295</v>
       </c>
       <c r="Z277" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AA277" t="inlineStr">
         <is>
@@ -40584,13 +40598,13 @@
         <v>17.49</v>
       </c>
       <c r="AI277" t="n">
-        <v>18.05</v>
+        <v>17.98</v>
       </c>
       <c r="AJ277" t="n">
-        <v>18.05</v>
+        <v>17.98</v>
       </c>
       <c r="AK277" t="n">
-        <v>3.2</v>
+        <v>2.8</v>
       </c>
       <c r="AL277" t="n">
         <v>-19.94</v>
@@ -40599,7 +40613,7 @@
         <v>6.06</v>
       </c>
       <c r="AN277" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="AO277" t="n">
         <v>51</v>
@@ -40608,13 +40622,13 @@
         <v>1.66</v>
       </c>
       <c r="AR277" t="n">
-        <v>3.57</v>
+        <v>2.42</v>
       </c>
       <c r="AS277" t="n">
         <v>4.4</v>
       </c>
       <c r="AT277" t="n">
-        <v>-0.37</v>
+        <v>0.38</v>
       </c>
       <c r="AU277" t="inlineStr">
         <is>
@@ -40658,7 +40672,7 @@
         <v>-17.5</v>
       </c>
       <c r="I278" t="n">
-        <v>-26.2</v>
+        <v>-21.3</v>
       </c>
       <c r="J278" t="n">
         <v>11.63</v>
@@ -40673,7 +40687,7 @@
         <v>-42.2</v>
       </c>
       <c r="N278" t="n">
-        <v>-37.2</v>
+        <v>-37.7</v>
       </c>
       <c r="P278" t="n">
         <v>-46.7</v>
@@ -40710,7 +40724,7 @@
         <v>46224</v>
       </c>
       <c r="Z278" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="AA278" t="inlineStr">
         <is>
@@ -40739,13 +40753,13 @@
         <v>142.6</v>
       </c>
       <c r="AI278" t="n">
-        <v>123.22</v>
+        <v>121.79</v>
       </c>
       <c r="AJ278" t="n">
-        <v>123.22</v>
+        <v>121.79</v>
       </c>
       <c r="AK278" t="n">
-        <v>-13.59</v>
+        <v>-14.59</v>
       </c>
       <c r="AL278" t="n">
         <v>-18.35</v>
@@ -40754,7 +40768,7 @@
         <v>45.74</v>
       </c>
       <c r="AN278" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="AO278" t="n">
         <v>19</v>
@@ -40763,13 +40777,13 @@
         <v>-10.85</v>
       </c>
       <c r="AR278" t="n">
-        <v>3.57</v>
+        <v>2.42</v>
       </c>
       <c r="AS278" t="n">
         <v>4.4</v>
       </c>
       <c r="AT278" t="n">
-        <v>-17.16</v>
+        <v>-17.01</v>
       </c>
       <c r="AU278" t="inlineStr">
         <is>
@@ -40813,7 +40827,7 @@
         <v>-18.1</v>
       </c>
       <c r="I279" t="n">
-        <v>-20.1</v>
+        <v>-18.1</v>
       </c>
       <c r="J279" t="n">
         <v>-5.59</v>
@@ -40828,7 +40842,7 @@
         <v>-3.4</v>
       </c>
       <c r="N279" t="n">
-        <v>-23.2</v>
+        <v>-20.6</v>
       </c>
       <c r="P279" t="n">
         <v>-10.1</v>
@@ -40865,7 +40879,7 @@
         <v>46247</v>
       </c>
       <c r="Z279" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="AA279" t="inlineStr">
         <is>
@@ -40894,13 +40908,13 @@
         <v>68.29000000000001</v>
       </c>
       <c r="AI279" t="n">
-        <v>55.4</v>
+        <v>57.25</v>
       </c>
       <c r="AJ279" t="n">
-        <v>55.4</v>
+        <v>57.25</v>
       </c>
       <c r="AK279" t="n">
-        <v>-18.88</v>
+        <v>-16.17</v>
       </c>
       <c r="AL279" t="n">
         <v>-27.26</v>
@@ -40909,7 +40923,7 @@
         <v>10.77</v>
       </c>
       <c r="AN279" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="AO279" t="n">
         <v>19</v>
@@ -40918,13 +40932,13 @@
         <v>-22.42</v>
       </c>
       <c r="AR279" t="n">
-        <v>3.57</v>
+        <v>2.42</v>
       </c>
       <c r="AS279" t="n">
         <v>4.4</v>
       </c>
       <c r="AT279" t="n">
-        <v>-22.44</v>
+        <v>-18.59</v>
       </c>
       <c r="AU279" t="inlineStr">
         <is>
@@ -40968,7 +40982,7 @@
         <v>1.6</v>
       </c>
       <c r="I280" t="n">
-        <v>-18.9</v>
+        <v>7.9</v>
       </c>
       <c r="J280" t="n">
         <v>4.01</v>
@@ -40983,13 +40997,13 @@
         <v>2.9</v>
       </c>
       <c r="N280" t="n">
-        <v>-13.9</v>
+        <v>-12.9</v>
       </c>
       <c r="P280" t="n">
         <v>-0.1</v>
       </c>
       <c r="Q280" t="n">
-        <v>51.74</v>
+        <v>51.73</v>
       </c>
       <c r="R280" t="inlineStr">
         <is>
@@ -41020,7 +41034,7 @@
         <v>46225</v>
       </c>
       <c r="Z280" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="AA280" t="inlineStr">
         <is>
@@ -41049,13 +41063,13 @@
         <v>53.22</v>
       </c>
       <c r="AI280" t="n">
-        <v>43.92</v>
+        <v>44.45</v>
       </c>
       <c r="AJ280" t="n">
-        <v>43.92</v>
+        <v>44.45</v>
       </c>
       <c r="AK280" t="n">
-        <v>-17.47</v>
+        <v>-16.48</v>
       </c>
       <c r="AL280" t="n">
         <v>-28.93</v>
@@ -41064,7 +41078,7 @@
         <v>12.6</v>
       </c>
       <c r="AN280" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="AO280" t="n">
         <v>12</v>
@@ -41073,13 +41087,13 @@
         <v>-21.31</v>
       </c>
       <c r="AR280" t="n">
-        <v>3.57</v>
+        <v>2.42</v>
       </c>
       <c r="AS280" t="n">
         <v>4.4</v>
       </c>
       <c r="AT280" t="n">
-        <v>-21.04</v>
+        <v>-18.9</v>
       </c>
       <c r="AU280" t="inlineStr">
         <is>
@@ -41554,7 +41568,7 @@
         <v>2.1</v>
       </c>
       <c r="I284" t="n">
-        <v>11.1</v>
+        <v>13.2</v>
       </c>
       <c r="J284" t="n">
         <v>6.91</v>
@@ -41569,7 +41583,7 @@
         <v>13.6</v>
       </c>
       <c r="N284" t="n">
-        <v>31</v>
+        <v>35.9</v>
       </c>
       <c r="P284" t="n">
         <v>6.5</v>
@@ -41601,7 +41615,7 @@
         <v>46225</v>
       </c>
       <c r="Z284" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="AA284" t="inlineStr">
         <is>
@@ -41630,37 +41644,37 @@
         <v>34.49</v>
       </c>
       <c r="AI284" t="n">
-        <v>47.23</v>
+        <v>49.15</v>
       </c>
       <c r="AJ284" t="n">
-        <v>47.23</v>
+        <v>49.15</v>
       </c>
       <c r="AK284" t="n">
-        <v>36.95</v>
+        <v>42.52</v>
       </c>
       <c r="AL284" t="n">
         <v>-1.07</v>
       </c>
       <c r="AM284" t="n">
-        <v>40.92</v>
+        <v>42.84</v>
       </c>
       <c r="AN284" t="n">
+        <v>64</v>
+      </c>
+      <c r="AO284" t="n">
         <v>63</v>
-      </c>
-      <c r="AO284" t="n">
-        <v>61</v>
       </c>
       <c r="AP284" t="n">
         <v>39.21</v>
       </c>
       <c r="AR284" t="n">
-        <v>3.57</v>
+        <v>2.42</v>
       </c>
       <c r="AS284" t="n">
         <v>4.4</v>
       </c>
       <c r="AT284" t="n">
-        <v>33.38</v>
+        <v>40.1</v>
       </c>
     </row>
     <row r="285">
@@ -41849,7 +41863,7 @@
         <v>-3.5</v>
       </c>
       <c r="I286" t="n">
-        <v>-7.4</v>
+        <v>-7.9</v>
       </c>
       <c r="J286" t="n">
         <v>-6.74</v>
@@ -41864,7 +41878,7 @@
         <v>23.7</v>
       </c>
       <c r="N286" t="n">
-        <v>-8.4</v>
+        <v>-9.1</v>
       </c>
       <c r="P286" t="n">
         <v>20.2</v>
@@ -41896,7 +41910,7 @@
         <v>46238</v>
       </c>
       <c r="Z286" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="AA286" t="inlineStr">
         <is>
@@ -41922,13 +41936,13 @@
         <v>890</v>
       </c>
       <c r="AI286" t="n">
-        <v>735.64</v>
+        <v>730.76</v>
       </c>
       <c r="AJ286" t="n">
-        <v>735.64</v>
+        <v>730.76</v>
       </c>
       <c r="AK286" t="n">
-        <v>-17.34</v>
+        <v>-17.89</v>
       </c>
       <c r="AL286" t="n">
         <v>-20.9</v>
@@ -41937,7 +41951,7 @@
         <v>5.06</v>
       </c>
       <c r="AN286" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="AO286" t="n">
         <v>11</v>
@@ -41946,13 +41960,13 @@
         <v>-13.17</v>
       </c>
       <c r="AR286" t="n">
-        <v>3.57</v>
+        <v>2.42</v>
       </c>
       <c r="AS286" t="n">
         <v>4.4</v>
       </c>
       <c r="AT286" t="n">
-        <v>-20.91</v>
+        <v>-20.31</v>
       </c>
       <c r="AU286" t="inlineStr">
         <is>
@@ -42523,7 +42537,7 @@
         <v>-38.26</v>
       </c>
       <c r="AL290" t="n">
-        <v>-38.63</v>
+        <v>-38.62</v>
       </c>
       <c r="AM290" t="n">
         <v>1.81</v>
@@ -43687,7 +43701,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>$48,115.83  (-2.87% price-weighted)</t>
+          <t>$47,981.63  (-3.14% price-weighted)</t>
         </is>
       </c>
     </row>
@@ -43699,7 +43713,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>-2.89%  &lt;- judge the system by this line</t>
+          <t>-3.15%  &lt;- judge the system by this line</t>
         </is>
       </c>
     </row>
@@ -43711,7 +43725,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-4.09%</t>
+          <t>-4.18%</t>
         </is>
       </c>
     </row>
@@ -43799,19 +43813,19 @@
         <v>190</v>
       </c>
       <c r="C12" t="n">
-        <v>-0.64</v>
+        <v>-0.82</v>
       </c>
       <c r="D12" t="n">
-        <v>-1.84</v>
+        <v>-1.8</v>
       </c>
       <c r="E12" t="n">
         <v>1.96</v>
       </c>
       <c r="F12" t="n">
-        <v>48.42</v>
+        <v>47.89</v>
       </c>
       <c r="G12" t="n">
-        <v>-13.43</v>
+        <v>-13.46</v>
       </c>
     </row>
     <row r="13">
@@ -43824,10 +43838,10 @@
         <v>75</v>
       </c>
       <c r="C13" t="n">
-        <v>-4.95</v>
+        <v>-5.38</v>
       </c>
       <c r="D13" t="n">
-        <v>-6.22</v>
+        <v>-6.54</v>
       </c>
       <c r="E13" t="n">
         <v>5.06</v>
@@ -43836,7 +43850,7 @@
         <v>30.67</v>
       </c>
       <c r="G13" t="n">
-        <v>-20.01</v>
+        <v>-20.04</v>
       </c>
     </row>
     <row r="14">
@@ -43849,10 +43863,10 @@
         <v>29</v>
       </c>
       <c r="C14" t="n">
-        <v>-12.3</v>
+        <v>-12.7</v>
       </c>
       <c r="D14" t="n">
-        <v>-13.37</v>
+        <v>-13.69</v>
       </c>
       <c r="E14" t="n">
         <v>7.06</v>
@@ -43861,7 +43875,7 @@
         <v>24.14</v>
       </c>
       <c r="G14" t="n">
-        <v>-21.64</v>
+        <v>-21.67</v>
       </c>
     </row>
     <row r="15"/>
@@ -43912,19 +43926,19 @@
         <v>95</v>
       </c>
       <c r="C17" t="n">
-        <v>-6.55</v>
+        <v>-6.91</v>
       </c>
       <c r="D17" t="n">
         <v>28.42</v>
       </c>
       <c r="E17" t="n">
-        <v>-7.55</v>
+        <v>-7.75</v>
       </c>
       <c r="F17" t="n">
         <v>3.79</v>
       </c>
       <c r="G17" t="n">
-        <v>-17.9</v>
+        <v>-17.93</v>
       </c>
     </row>
     <row r="18">
@@ -43937,19 +43951,19 @@
         <v>42</v>
       </c>
       <c r="C18" t="n">
-        <v>-2.06</v>
+        <v>-2.36</v>
       </c>
       <c r="D18" t="n">
         <v>54.76</v>
       </c>
       <c r="E18" t="n">
-        <v>-3.41</v>
+        <v>-3.46</v>
       </c>
       <c r="F18" t="n">
         <v>3.32</v>
       </c>
       <c r="G18" t="n">
-        <v>-13.1</v>
+        <v>-13.18</v>
       </c>
     </row>
     <row r="19">
@@ -43987,19 +44001,19 @@
         <v>138</v>
       </c>
       <c r="C20" t="n">
-        <v>-1.47</v>
+        <v>-1.69</v>
       </c>
       <c r="D20" t="n">
-        <v>44.2</v>
+        <v>43.48</v>
       </c>
       <c r="E20" t="n">
-        <v>-2.8</v>
+        <v>-2.83</v>
       </c>
       <c r="F20" t="n">
         <v>4.07</v>
       </c>
       <c r="G20" t="n">
-        <v>-15.84</v>
+        <v>-15.87</v>
       </c>
     </row>
     <row r="21">
@@ -44076,13 +44090,13 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C25" t="n">
-        <v>-0.23</v>
+        <v>-0.21</v>
       </c>
       <c r="D25" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E25" t="n">
         <v>3.83</v>
@@ -44091,7 +44105,7 @@
         <v>64</v>
       </c>
       <c r="G25" t="n">
-        <v>-13.5</v>
+        <v>-13.4</v>
       </c>
     </row>
     <row r="26">
@@ -44176,7 +44190,7 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="C29" t="n">
         <v>2.26</v>
@@ -44185,13 +44199,13 @@
         <v>61</v>
       </c>
       <c r="E29" t="n">
-        <v>6.52</v>
+        <v>6.51</v>
       </c>
       <c r="F29" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="G29" t="n">
-        <v>-10.72</v>
+        <v>-10.7</v>
       </c>
     </row>
     <row r="30"/>
@@ -44237,13 +44251,13 @@
         <v>5</v>
       </c>
       <c r="C32" t="n">
-        <v>7.1</v>
+        <v>7.62</v>
       </c>
       <c r="D32" t="n">
         <v>80</v>
       </c>
       <c r="E32" t="n">
-        <v>7.26</v>
+        <v>8</v>
       </c>
       <c r="F32" t="n">
         <v>-13.73</v>
@@ -44259,13 +44273,13 @@
         <v>11</v>
       </c>
       <c r="C33" t="n">
-        <v>-5.72</v>
+        <v>-6.24</v>
       </c>
       <c r="D33" t="n">
         <v>36.36</v>
       </c>
       <c r="E33" t="n">
-        <v>-6.62</v>
+        <v>-6.93</v>
       </c>
       <c r="F33" t="n">
         <v>-16.65</v>
@@ -44281,13 +44295,13 @@
         <v>26</v>
       </c>
       <c r="C34" t="n">
-        <v>-0.13</v>
+        <v>-0.25</v>
       </c>
       <c r="D34" t="n">
-        <v>46.15</v>
+        <v>42.31</v>
       </c>
       <c r="E34" t="n">
-        <v>-0.78</v>
+        <v>-0.8</v>
       </c>
       <c r="F34" t="n">
         <v>-15.12</v>
@@ -44808,19 +44822,19 @@
         <v>109</v>
       </c>
       <c r="D4" t="n">
-        <v>3.51</v>
+        <v>3.32</v>
       </c>
       <c r="E4" t="n">
-        <v>0.53</v>
+        <v>0.39</v>
       </c>
       <c r="F4" t="n">
-        <v>51.4</v>
+        <v>50.5</v>
       </c>
       <c r="G4" t="n">
-        <v>2.27</v>
+        <v>2.26</v>
       </c>
       <c r="H4" t="n">
-        <v>-12.59</v>
+        <v>-12.62</v>
       </c>
       <c r="I4" t="n">
         <v>-43.08</v>
@@ -44829,7 +44843,7 @@
         <v>22.9</v>
       </c>
       <c r="K4" t="n">
-        <v>20.2</v>
+        <v>20.29</v>
       </c>
       <c r="L4" t="n">
         <v>43</v>
@@ -44851,7 +44865,7 @@
         <v>55</v>
       </c>
       <c r="D5" t="n">
-        <v>0.49</v>
+        <v>0.29</v>
       </c>
       <c r="E5" t="n">
         <v>1.08</v>
@@ -44860,10 +44874,10 @@
         <v>50.9</v>
       </c>
       <c r="G5" t="n">
-        <v>-0.85</v>
+        <v>-0.84</v>
       </c>
       <c r="H5" t="n">
-        <v>-14.3</v>
+        <v>-14.33</v>
       </c>
       <c r="I5" t="n">
         <v>-45.62</v>
@@ -44872,7 +44886,7 @@
         <v>32.7</v>
       </c>
       <c r="K5" t="n">
-        <v>19.53</v>
+        <v>19.57</v>
       </c>
       <c r="L5" t="n">
         <v>26</v>
@@ -44894,19 +44908,19 @@
         <v>130</v>
       </c>
       <c r="D6" t="n">
-        <v>-9.68</v>
+        <v>-10.04</v>
       </c>
       <c r="E6" t="n">
-        <v>-10.93</v>
+        <v>-11.47</v>
       </c>
       <c r="F6" t="n">
         <v>29.2</v>
       </c>
       <c r="G6" t="n">
-        <v>-10.81</v>
+        <v>-11</v>
       </c>
       <c r="H6" t="n">
-        <v>-19.4</v>
+        <v>-19.43</v>
       </c>
       <c r="I6" t="n">
         <v>-63.53</v>
@@ -44937,19 +44951,19 @@
         <v>294</v>
       </c>
       <c r="D7" t="n">
-        <v>-2.89</v>
+        <v>-3.15</v>
       </c>
       <c r="E7" t="n">
-        <v>-4.32</v>
+        <v>-4.6</v>
       </c>
       <c r="F7" t="n">
-        <v>41.5</v>
+        <v>41.2</v>
       </c>
       <c r="G7" t="n">
-        <v>-4.09</v>
+        <v>-4.18</v>
       </c>
       <c r="H7" t="n">
-        <v>-15.92</v>
+        <v>-15.95</v>
       </c>
       <c r="I7" t="n">
         <v>-63.53</v>
@@ -44958,7 +44972,7 @@
         <v>34</v>
       </c>
       <c r="K7" t="n">
-        <v>19.68</v>
+        <v>19.72</v>
       </c>
       <c r="L7" t="n">
         <v>124</v>
@@ -44978,7 +44992,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Avg drawdown (MAE%, less-negative is better): PASS -12.59 vs FAIL -19.4  -&gt;  PASS better</t>
+          <t>Avg drawdown (MAE%, less-negative is better): PASS -12.62 vs FAIL -19.43  -&gt;  PASS better</t>
         </is>
       </c>
     </row>
@@ -44992,14 +45006,14 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Avg return %: PASS 3.51 vs FAIL -9.68  -&gt;  PASS better</t>
+          <t>Avg return %: PASS 3.32 vs FAIL -10.04  -&gt;  PASS better</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Win rate %: PASS 51.4 vs FAIL 29.2  -&gt;  PASS better</t>
+          <t>Win rate %: PASS 50.5 vs FAIL 29.2  -&gt;  PASS better</t>
         </is>
       </c>
     </row>
@@ -47062,29 +47076,45 @@
           <t>CORE</t>
         </is>
       </c>
-      <c r="E28" t="n">
-        <v>80.7</v>
-      </c>
-      <c r="F28" t="n">
-        <v>0.526</v>
-      </c>
-      <c r="G28" t="n">
-        <v>7</v>
-      </c>
-      <c r="H28" t="n">
-        <v>4</v>
-      </c>
-      <c r="I28" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="J28" t="n">
-        <v>66.40000000000001</v>
-      </c>
-      <c r="K28" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="L28" t="n">
-        <v>24.9</v>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>80.7</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>0.526</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>4.0</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>4.7</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>66.4</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>0.9</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>24.9</t>
+        </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
@@ -51945,29 +51975,45 @@
           <t>LEVERAGED</t>
         </is>
       </c>
-      <c r="E95" t="n">
-        <v>63.5</v>
-      </c>
-      <c r="F95" t="n">
-        <v>0.188</v>
-      </c>
-      <c r="G95" t="n">
-        <v>7</v>
-      </c>
-      <c r="H95" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="I95" t="n">
-        <v>53.9</v>
-      </c>
-      <c r="J95" t="n">
-        <v>46.8</v>
-      </c>
-      <c r="K95" t="n">
-        <v>0.18</v>
-      </c>
-      <c r="L95" t="n">
-        <v>27.4</v>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>63.5</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>0.188</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>1.48</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr">
+        <is>
+          <t>53.9</t>
+        </is>
+      </c>
+      <c r="J95" t="inlineStr">
+        <is>
+          <t>46.8</t>
+        </is>
+      </c>
+      <c r="K95" t="inlineStr">
+        <is>
+          <t>0.18</t>
+        </is>
+      </c>
+      <c r="L95" t="inlineStr">
+        <is>
+          <t>27.4</t>
+        </is>
       </c>
       <c r="M95" t="inlineStr">
         <is>
@@ -57367,26 +57413,41 @@
           <t>DECLINING</t>
         </is>
       </c>
-      <c r="E169" t="n">
-        <v>42.2</v>
-      </c>
-      <c r="F169" t="n">
-        <v>0.098</v>
-      </c>
-      <c r="G169" t="n">
-        <v>4</v>
-      </c>
-      <c r="H169" t="n">
-        <v>3.68</v>
-      </c>
-      <c r="I169" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="K169" t="n">
-        <v>0.27</v>
-      </c>
-      <c r="L169" t="n">
-        <v>8</v>
+      <c r="E169" t="inlineStr">
+        <is>
+          <t>42.2</t>
+        </is>
+      </c>
+      <c r="F169" t="inlineStr">
+        <is>
+          <t>0.098</t>
+        </is>
+      </c>
+      <c r="G169" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="H169" t="inlineStr">
+        <is>
+          <t>3.68</t>
+        </is>
+      </c>
+      <c r="I169" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+      <c r="J169" t="inlineStr"/>
+      <c r="K169" t="inlineStr">
+        <is>
+          <t>0.27</t>
+        </is>
+      </c>
+      <c r="L169" t="inlineStr">
+        <is>
+          <t>8.0</t>
+        </is>
       </c>
       <c r="M169" t="inlineStr">
         <is>
@@ -59375,29 +59436,45 @@
           <t>NEW-IPO</t>
         </is>
       </c>
-      <c r="E196" t="n">
-        <v>30.3</v>
-      </c>
-      <c r="F196" t="n">
-        <v>0.08699999999999999</v>
-      </c>
-      <c r="G196" t="n">
-        <v>4</v>
-      </c>
-      <c r="H196" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="I196" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="J196" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="K196" t="n">
-        <v>0.82</v>
-      </c>
-      <c r="L196" t="n">
-        <v>30.2</v>
+      <c r="E196" t="inlineStr">
+        <is>
+          <t>30.3</t>
+        </is>
+      </c>
+      <c r="F196" t="inlineStr">
+        <is>
+          <t>0.087</t>
+        </is>
+      </c>
+      <c r="G196" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="H196" t="inlineStr">
+        <is>
+          <t>1.81</t>
+        </is>
+      </c>
+      <c r="I196" t="inlineStr">
+        <is>
+          <t>5.4</t>
+        </is>
+      </c>
+      <c r="J196" t="inlineStr">
+        <is>
+          <t>5.1</t>
+        </is>
+      </c>
+      <c r="K196" t="inlineStr">
+        <is>
+          <t>0.82</t>
+        </is>
+      </c>
+      <c r="L196" t="inlineStr">
+        <is>
+          <t>30.2</t>
+        </is>
       </c>
       <c r="M196" t="inlineStr">
         <is>
@@ -62250,12 +62327,22 @@
           <t>NEW-IPO</t>
         </is>
       </c>
-      <c r="E235" t="n">
-        <v>0</v>
-      </c>
-      <c r="G235" t="n">
-        <v>0</v>
-      </c>
+      <c r="E235" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="F235" t="inlineStr"/>
+      <c r="G235" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H235" t="inlineStr"/>
+      <c r="I235" t="inlineStr"/>
+      <c r="J235" t="inlineStr"/>
+      <c r="K235" t="inlineStr"/>
+      <c r="L235" t="inlineStr"/>
       <c r="M235" t="inlineStr">
         <is>
           <t>Consumer Defensive</t>
@@ -62464,8 +62551,10 @@
           <t>NEW-IPO</t>
         </is>
       </c>
-      <c r="L3" t="n">
-        <v>30.3</v>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>30.3</t>
+        </is>
       </c>
     </row>
     <row r="4">
@@ -64840,8 +64929,10 @@
           <t>DECLINING</t>
         </is>
       </c>
-      <c r="L44" t="n">
-        <v>42.2</v>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>42.2</t>
+        </is>
       </c>
     </row>
     <row r="45">
@@ -64954,8 +65045,10 @@
           <t>NEW-IPO</t>
         </is>
       </c>
-      <c r="L46" t="n">
-        <v>0</v>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
       </c>
     </row>
     <row r="47">
@@ -65010,8 +65103,10 @@
           <t>CORE</t>
         </is>
       </c>
-      <c r="L47" t="n">
-        <v>80.7</v>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>80.7</t>
+        </is>
       </c>
     </row>
     <row r="48">
@@ -65066,8 +65161,10 @@
           <t>LEVERAGED</t>
         </is>
       </c>
-      <c r="L48" t="n">
-        <v>63.5</v>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>63.5</t>
+        </is>
       </c>
     </row>
     <row r="49">

--- a/STS_holy_grail.xlsx
+++ b/STS_holy_grail.xlsx
@@ -880,7 +880,7 @@
     <col width="6" customWidth="1" min="15" max="15"/>
     <col width="12" customWidth="1" min="16" max="16"/>
     <col width="17" customWidth="1" min="17" max="17"/>
-    <col width="9" customWidth="1" min="18" max="18"/>
+    <col width="10" customWidth="1" min="18" max="18"/>
     <col width="60" customWidth="1" min="19" max="19"/>
     <col width="12" customWidth="1" min="20" max="20"/>
     <col width="12" customWidth="1" min="21" max="21"/>
@@ -1163,45 +1163,21 @@
           <t>PASS/SPEC</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>D200G</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>Pending</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>G</t>
-        </is>
-      </c>
       <c r="G2" t="n">
         <v>6.1</v>
       </c>
       <c r="H2" t="n">
         <v>-9.800000000000001</v>
       </c>
-      <c r="M2" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="P2" t="n">
-        <v>2.3</v>
-      </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>NO PRICE</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
           <t>RE-QUAL D200G 2026-10-22</t>
         </is>
-      </c>
-      <c r="AI2" t="n">
-        <v>257.8200073242188</v>
       </c>
     </row>
     <row r="3">
@@ -1218,45 +1194,21 @@
           <t>PASS/IPO</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>D200G</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>Pending</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>G</t>
-        </is>
-      </c>
       <c r="G3" t="n">
         <v>6</v>
       </c>
       <c r="H3" t="n">
         <v>-14.5</v>
       </c>
-      <c r="M3" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="P3" t="n">
-        <v>2.4</v>
-      </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>NO PRICE</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
           <t>RE-QUAL D200G 2026-10-22</t>
         </is>
-      </c>
-      <c r="AI3" t="n">
-        <v>1260.930053710938</v>
       </c>
     </row>
     <row r="4">
@@ -1273,50 +1225,21 @@
           <t>FAIL/LEV</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>DLB</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>Pending</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>G</t>
-        </is>
-      </c>
       <c r="G4" t="n">
         <v>5</v>
       </c>
       <c r="H4" t="n">
         <v>-1.7</v>
       </c>
-      <c r="M4" t="n">
-        <v>-8.1</v>
-      </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>WR20</t>
-        </is>
-      </c>
-      <c r="P4" t="n">
-        <v>-21.8</v>
-      </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>NO PRICE</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
           <t>RE-QUAL WR20 2026-10-22</t>
         </is>
-      </c>
-      <c r="AI4" t="n">
-        <v>50.81999969482422</v>
       </c>
     </row>
     <row r="5">
@@ -1333,50 +1256,21 @@
           <t>WATCH/DECL</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>DLB</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>Pending</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>G</t>
-        </is>
-      </c>
       <c r="G5" t="n">
         <v>2.3</v>
       </c>
       <c r="H5" t="n">
         <v>21.7</v>
       </c>
-      <c r="M5" t="n">
-        <v>-9.800000000000001</v>
-      </c>
-      <c r="O5" t="inlineStr">
-        <is>
-          <t>WR30</t>
-        </is>
-      </c>
-      <c r="P5" t="n">
-        <v>-36.2</v>
-      </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>NO PRICE</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
           <t>RE-QUAL WR30 2026-10-22</t>
         </is>
-      </c>
-      <c r="AI5" t="n">
-        <v>16.36000061035156</v>
       </c>
     </row>
     <row r="6">
@@ -1393,50 +1287,21 @@
           <t>PASS/DECL</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>DLB</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>Pending</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>G</t>
-        </is>
-      </c>
       <c r="G6" t="n">
         <v>2.2</v>
       </c>
       <c r="H6" t="n">
         <v>6.1</v>
       </c>
-      <c r="M6" t="n">
-        <v>-2.3</v>
-      </c>
-      <c r="O6" t="inlineStr">
-        <is>
-          <t>WR20</t>
-        </is>
-      </c>
-      <c r="P6" t="n">
-        <v>-24.9</v>
-      </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>NO PRICE</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
           <t>RE-QUAL WR20 2026-10-22</t>
         </is>
-      </c>
-      <c r="AI6" t="n">
-        <v>197.2100067138672</v>
       </c>
     </row>
     <row r="7">
@@ -1453,45 +1318,21 @@
           <t>PASS/DECL</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>S2</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>Pending</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>G</t>
-        </is>
-      </c>
       <c r="G7" t="n">
         <v>2.1</v>
       </c>
       <c r="H7" t="n">
         <v>1.7</v>
       </c>
-      <c r="M7" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="P7" t="n">
-        <v>15.5</v>
-      </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>NO PRICE</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
           <t>auto-added 2026-10-22</t>
         </is>
-      </c>
-      <c r="AI7" t="n">
-        <v>72.62000274658203</v>
       </c>
     </row>
     <row r="8">
@@ -1508,50 +1349,21 @@
           <t>FAIL/DECL</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>DLB</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>Pending</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>G</t>
-        </is>
-      </c>
       <c r="G8" t="n">
         <v>2.1</v>
       </c>
       <c r="H8" t="n">
         <v>-1.1</v>
       </c>
-      <c r="M8" t="n">
-        <v>-7.2</v>
-      </c>
-      <c r="O8" t="inlineStr">
-        <is>
-          <t>WR20</t>
-        </is>
-      </c>
-      <c r="P8" t="n">
-        <v>-20.2</v>
-      </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>NO PRICE</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
         <is>
           <t>RE-QUAL WR20 2026-10-22</t>
         </is>
-      </c>
-      <c r="AI8" t="n">
-        <v>84.44999694824219</v>
       </c>
     </row>
     <row r="9">
@@ -1598,9 +1410,6 @@
       <c r="M9" t="n">
         <v>-7</v>
       </c>
-      <c r="N9" t="n">
-        <v>-3.1</v>
-      </c>
       <c r="O9" t="inlineStr">
         <is>
           <t>WR30</t>
@@ -1728,14 +1537,11 @@
         <v>-14.9</v>
       </c>
       <c r="L10" t="n">
-        <v>-7.42</v>
+        <v>-7.43</v>
       </c>
       <c r="M10" t="n">
         <v>0</v>
       </c>
-      <c r="N10" t="n">
-        <v>-6.9</v>
-      </c>
       <c r="P10" t="n">
         <v>-1.6</v>
       </c>
@@ -1795,7 +1601,7 @@
         <v>-6.63</v>
       </c>
       <c r="AL10" t="n">
-        <v>-7.42</v>
+        <v>-7.43</v>
       </c>
       <c r="AM10" t="n">
         <v>1.75</v>
@@ -1857,9 +1663,6 @@
       <c r="M11" t="n">
         <v>0.7</v>
       </c>
-      <c r="N11" t="n">
-        <v>-9.300000000000001</v>
-      </c>
       <c r="P11" t="n">
         <v>-4.9</v>
       </c>
@@ -1981,9 +1784,6 @@
       <c r="M12" t="n">
         <v>11.4</v>
       </c>
-      <c r="N12" t="n">
-        <v>-0.1</v>
-      </c>
       <c r="P12" t="n">
         <v>6.3</v>
       </c>
@@ -2105,9 +1905,6 @@
       <c r="M13" t="n">
         <v>6.2</v>
       </c>
-      <c r="N13" t="n">
-        <v>3.6</v>
-      </c>
       <c r="P13" t="n">
         <v>-2.6</v>
       </c>
@@ -2235,9 +2032,6 @@
       <c r="M14" t="n">
         <v>-8.1</v>
       </c>
-      <c r="N14" t="n">
-        <v>6.9</v>
-      </c>
       <c r="O14" t="inlineStr">
         <is>
           <t>WR20</t>
@@ -2373,9 +2167,6 @@
       <c r="M15" t="n">
         <v>1.5</v>
       </c>
-      <c r="N15" t="n">
-        <v>7.7</v>
-      </c>
       <c r="P15" t="n">
         <v>-22.3</v>
       </c>
@@ -2506,9 +2297,6 @@
       <c r="M16" t="n">
         <v>1.2</v>
       </c>
-      <c r="N16" t="n">
-        <v>-5.7</v>
-      </c>
       <c r="P16" t="n">
         <v>2.8</v>
       </c>
@@ -2636,9 +2424,6 @@
       <c r="M17" t="n">
         <v>-8.300000000000001</v>
       </c>
-      <c r="N17" t="n">
-        <v>11.5</v>
-      </c>
       <c r="O17" t="inlineStr">
         <is>
           <t>WR20</t>
@@ -2682,10 +2467,10 @@
         <v>5</v>
       </c>
       <c r="AB17" t="n">
-        <v>19.74</v>
+        <v>19.77</v>
       </c>
       <c r="AC17" t="n">
-        <v>19.74</v>
+        <v>19.77</v>
       </c>
       <c r="AD17" t="n">
         <v>-1.74</v>
@@ -2715,7 +2500,7 @@
         <v>-1.74</v>
       </c>
       <c r="AM17" t="n">
-        <v>19.74</v>
+        <v>19.77</v>
       </c>
       <c r="AN17" t="n">
         <v>7</v>
@@ -2774,9 +2559,6 @@
       <c r="M18" t="n">
         <v>20.1</v>
       </c>
-      <c r="N18" t="n">
-        <v>26.4</v>
-      </c>
       <c r="P18" t="n">
         <v>2.6</v>
       </c>
@@ -2904,9 +2686,6 @@
       <c r="M19" t="n">
         <v>-8.4</v>
       </c>
-      <c r="N19" t="n">
-        <v>0.1</v>
-      </c>
       <c r="P19" t="n">
         <v>-13.4</v>
       </c>
@@ -3034,9 +2813,6 @@
       <c r="M20" t="n">
         <v>3.6</v>
       </c>
-      <c r="N20" t="n">
-        <v>25</v>
-      </c>
       <c r="P20" t="n">
         <v>-6.7</v>
       </c>
@@ -3075,10 +2851,10 @@
         <v>5</v>
       </c>
       <c r="AB20" t="n">
-        <v>20.06</v>
+        <v>20.1</v>
       </c>
       <c r="AC20" t="n">
-        <v>20.06</v>
+        <v>20.1</v>
       </c>
       <c r="AD20" t="n">
         <v>0</v>
@@ -3108,7 +2884,7 @@
         <v>0</v>
       </c>
       <c r="AM20" t="n">
-        <v>20.06</v>
+        <v>20.1</v>
       </c>
       <c r="AN20" t="n">
         <v>7</v>
@@ -3167,9 +2943,6 @@
       <c r="M21" t="n">
         <v>-9.199999999999999</v>
       </c>
-      <c r="N21" t="n">
-        <v>1.6</v>
-      </c>
       <c r="O21" t="inlineStr">
         <is>
           <t>WR40</t>
@@ -3302,9 +3075,6 @@
       <c r="M22" t="n">
         <v>1</v>
       </c>
-      <c r="N22" t="n">
-        <v>20.2</v>
-      </c>
       <c r="P22" t="n">
         <v>-5.4</v>
       </c>
@@ -3438,9 +3208,6 @@
       <c r="M23" t="n">
         <v>-5.1</v>
       </c>
-      <c r="N23" t="n">
-        <v>-6.5</v>
-      </c>
       <c r="O23" t="inlineStr">
         <is>
           <t>WR20</t>
@@ -3576,9 +3343,6 @@
       <c r="M24" t="n">
         <v>-22.7</v>
       </c>
-      <c r="N24" t="n">
-        <v>-30.8</v>
-      </c>
       <c r="P24" t="n">
         <v>-32.1</v>
       </c>
@@ -3703,9 +3467,6 @@
       <c r="M25" t="n">
         <v>-3.2</v>
       </c>
-      <c r="N25" t="n">
-        <v>-33.5</v>
-      </c>
       <c r="O25" t="inlineStr">
         <is>
           <t>WR20</t>
@@ -3840,9 +3601,6 @@
       <c r="M26" t="n">
         <v>1.5</v>
       </c>
-      <c r="N26" t="n">
-        <v>-9.4</v>
-      </c>
       <c r="P26" t="n">
         <v>-12.8</v>
       </c>
@@ -3973,9 +3731,6 @@
       <c r="M27" t="n">
         <v>0.3</v>
       </c>
-      <c r="N27" t="n">
-        <v>-8.5</v>
-      </c>
       <c r="P27" t="n">
         <v>-14.8</v>
       </c>
@@ -4106,9 +3861,6 @@
       <c r="M28" t="n">
         <v>-0.6</v>
       </c>
-      <c r="N28" t="n">
-        <v>16.3</v>
-      </c>
       <c r="P28" t="n">
         <v>-3.8</v>
       </c>
@@ -4242,9 +3994,6 @@
       <c r="M29" t="n">
         <v>2.2</v>
       </c>
-      <c r="N29" t="n">
-        <v>37</v>
-      </c>
       <c r="P29" t="n">
         <v>-16.6</v>
       </c>
@@ -4373,14 +4122,11 @@
         <v>-0.41</v>
       </c>
       <c r="L30" t="n">
-        <v>-3.4</v>
+        <v>-3.36</v>
       </c>
       <c r="M30" t="n">
         <v>-8</v>
       </c>
-      <c r="N30" t="n">
-        <v>-9.6</v>
-      </c>
       <c r="P30" t="n">
         <v>-9.199999999999999</v>
       </c>
@@ -4440,7 +4186,7 @@
         <v>-2.13</v>
       </c>
       <c r="AL30" t="n">
-        <v>-3.4</v>
+        <v>-3.36</v>
       </c>
       <c r="AM30" t="n">
         <v>4.75</v>
@@ -4505,9 +4251,6 @@
       <c r="M31" t="n">
         <v>-29.1</v>
       </c>
-      <c r="N31" t="n">
-        <v>-17</v>
-      </c>
       <c r="P31" t="n">
         <v>-29.3</v>
       </c>
@@ -4630,25 +4373,22 @@
         <v>-6.5</v>
       </c>
       <c r="I32" t="n">
-        <v>1.6</v>
+        <v>2.3</v>
       </c>
       <c r="J32" t="n">
-        <v>6.91</v>
+        <v>6.15</v>
       </c>
       <c r="L32" t="n">
-        <v>-1.34</v>
+        <v>-2.04</v>
       </c>
       <c r="M32" t="n">
-        <v>-0.3</v>
-      </c>
-      <c r="N32" t="n">
-        <v>7.6</v>
+        <v>0.4</v>
       </c>
       <c r="P32" t="n">
         <v>-1.9</v>
       </c>
       <c r="Q32" t="n">
-        <v>86.98</v>
+        <v>86.36</v>
       </c>
       <c r="R32" t="inlineStr">
         <is>
@@ -4682,13 +4422,13 @@
         <v>5</v>
       </c>
       <c r="AB32" t="n">
-        <v>7.68</v>
+        <v>6.92</v>
       </c>
       <c r="AC32" t="n">
-        <v>9.890000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="AD32" t="n">
-        <v>-1.34</v>
+        <v>-2.04</v>
       </c>
       <c r="AF32" t="n">
         <v>86.69</v>
@@ -4709,16 +4449,16 @@
         <v>8.99</v>
       </c>
       <c r="AL32" t="n">
-        <v>-1.34</v>
+        <v>-2.04</v>
       </c>
       <c r="AM32" t="n">
-        <v>9.890000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="AN32" t="n">
         <v>14</v>
       </c>
       <c r="AO32" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AR32" t="n">
         <v>-0.74</v>
@@ -4774,9 +4514,6 @@
       <c r="M33" t="n">
         <v>5.1</v>
       </c>
-      <c r="N33" t="n">
-        <v>7.1</v>
-      </c>
       <c r="P33" t="n">
         <v>-1</v>
       </c>
@@ -4910,9 +4647,6 @@
       <c r="M34" t="n">
         <v>3.4</v>
       </c>
-      <c r="N34" t="n">
-        <v>7</v>
-      </c>
       <c r="P34" t="n">
         <v>-2.8</v>
       </c>
@@ -5046,9 +4780,6 @@
       <c r="M35" t="n">
         <v>-8.800000000000001</v>
       </c>
-      <c r="N35" t="n">
-        <v>-2.4</v>
-      </c>
       <c r="O35" t="inlineStr">
         <is>
           <t>WR20</t>
@@ -5184,9 +4915,6 @@
       <c r="M36" t="n">
         <v>-35.8</v>
       </c>
-      <c r="N36" t="n">
-        <v>-35.3</v>
-      </c>
       <c r="P36" t="n">
         <v>-38.7</v>
       </c>
@@ -5311,9 +5039,6 @@
       <c r="M37" t="n">
         <v>-6.9</v>
       </c>
-      <c r="N37" t="n">
-        <v>-0.1</v>
-      </c>
       <c r="P37" t="n">
         <v>-7.1</v>
       </c>
@@ -5373,10 +5098,10 @@
         <v>1714.99</v>
       </c>
       <c r="AI37" t="n">
-        <v>1824.95</v>
+        <v>1824.96</v>
       </c>
       <c r="AJ37" t="n">
-        <v>1824.95</v>
+        <v>1824.96</v>
       </c>
       <c r="AK37" t="n">
         <v>6.41</v>
@@ -5447,9 +5172,6 @@
       <c r="M38" t="n">
         <v>-12.6</v>
       </c>
-      <c r="N38" t="n">
-        <v>2.9</v>
-      </c>
       <c r="P38" t="n">
         <v>-15</v>
       </c>
@@ -5583,9 +5305,6 @@
       <c r="M39" t="n">
         <v>-8.6</v>
       </c>
-      <c r="N39" t="n">
-        <v>-36.6</v>
-      </c>
       <c r="O39" t="inlineStr">
         <is>
           <t>WR20</t>
@@ -5726,9 +5445,6 @@
       <c r="M40" t="n">
         <v>-3.7</v>
       </c>
-      <c r="N40" t="n">
-        <v>-3.5</v>
-      </c>
       <c r="O40" t="inlineStr">
         <is>
           <t>WR20</t>
@@ -5864,9 +5580,6 @@
       <c r="M41" t="n">
         <v>3.6</v>
       </c>
-      <c r="N41" t="n">
-        <v>18.1</v>
-      </c>
       <c r="P41" t="n">
         <v>-8.6</v>
       </c>
@@ -5908,7 +5621,7 @@
         <v>3.54</v>
       </c>
       <c r="AC41" t="n">
-        <v>14.92</v>
+        <v>14.97</v>
       </c>
       <c r="AD41" t="n">
         <v>-6.76</v>
@@ -5938,7 +5651,7 @@
         <v>-6.76</v>
       </c>
       <c r="AM41" t="n">
-        <v>14.92</v>
+        <v>14.97</v>
       </c>
       <c r="AN41" t="n">
         <v>20</v>
@@ -6003,9 +5716,6 @@
       <c r="M42" t="n">
         <v>1.2</v>
       </c>
-      <c r="N42" t="n">
-        <v>-10.6</v>
-      </c>
       <c r="P42" t="n">
         <v>-9.1</v>
       </c>
@@ -6079,7 +5789,7 @@
         <v>-8.619999999999999</v>
       </c>
       <c r="AL42" t="n">
-        <v>-10.14</v>
+        <v>-10.24</v>
       </c>
       <c r="AM42" t="n">
         <v>16.71</v>
@@ -6147,9 +5857,6 @@
       <c r="M43" t="n">
         <v>-25.1</v>
       </c>
-      <c r="N43" t="n">
-        <v>-11.4</v>
-      </c>
       <c r="P43" t="n">
         <v>-26.9</v>
       </c>
@@ -6291,9 +5998,6 @@
       <c r="M44" t="n">
         <v>-12.9</v>
       </c>
-      <c r="N44" t="n">
-        <v>-20</v>
-      </c>
       <c r="P44" t="n">
         <v>-19.3</v>
       </c>
@@ -6421,9 +6125,6 @@
       <c r="M45" t="n">
         <v>17.3</v>
       </c>
-      <c r="N45" t="n">
-        <v>20.5</v>
-      </c>
       <c r="P45" t="n">
         <v>11.4</v>
       </c>
@@ -6562,9 +6263,6 @@
       <c r="M46" t="n">
         <v>-12.3</v>
       </c>
-      <c r="N46" t="n">
-        <v>-5.4</v>
-      </c>
       <c r="P46" t="n">
         <v>-16.1</v>
       </c>
@@ -6706,9 +6404,6 @@
       <c r="M47" t="n">
         <v>-18.4</v>
       </c>
-      <c r="N47" t="n">
-        <v>-17.4</v>
-      </c>
       <c r="P47" t="n">
         <v>-19.9</v>
       </c>
@@ -6836,9 +6531,6 @@
       <c r="M48" t="n">
         <v>-17</v>
       </c>
-      <c r="N48" t="n">
-        <v>-14.1</v>
-      </c>
       <c r="P48" t="n">
         <v>-20.1</v>
       </c>
@@ -6977,9 +6669,6 @@
       <c r="M49" t="n">
         <v>7.7</v>
       </c>
-      <c r="N49" t="n">
-        <v>15.3</v>
-      </c>
       <c r="P49" t="n">
         <v>5.6</v>
       </c>
@@ -7118,9 +6807,6 @@
       <c r="M50" t="n">
         <v>3.5</v>
       </c>
-      <c r="N50" t="n">
-        <v>19.3</v>
-      </c>
       <c r="P50" t="n">
         <v>-30.3</v>
       </c>
@@ -7262,9 +6948,6 @@
       <c r="M51" t="n">
         <v>2.4</v>
       </c>
-      <c r="N51" t="n">
-        <v>13.5</v>
-      </c>
       <c r="P51" t="n">
         <v>-4.8</v>
       </c>
@@ -7403,9 +7086,6 @@
       <c r="M52" t="n">
         <v>-17.5</v>
       </c>
-      <c r="N52" t="n">
-        <v>-7.2</v>
-      </c>
       <c r="P52" t="n">
         <v>-20</v>
       </c>
@@ -7544,9 +7224,6 @@
       <c r="M53" t="n">
         <v>4.6</v>
       </c>
-      <c r="N53" t="n">
-        <v>17.5</v>
-      </c>
       <c r="P53" t="n">
         <v>-8.6</v>
       </c>
@@ -7574,9 +7251,6 @@
       </c>
       <c r="W53" t="b">
         <v>1</v>
-      </c>
-      <c r="X53" s="13" t="n">
-        <v>46317</v>
       </c>
       <c r="Y53" s="13" t="n">
         <v>46317</v>
@@ -7688,9 +7362,6 @@
       <c r="M54" t="n">
         <v>-10.8</v>
       </c>
-      <c r="N54" t="n">
-        <v>32.5</v>
-      </c>
       <c r="P54" t="n">
         <v>-27.7</v>
       </c>
@@ -7832,9 +7503,6 @@
       <c r="M55" t="n">
         <v>-23</v>
       </c>
-      <c r="N55" t="n">
-        <v>-19.1</v>
-      </c>
       <c r="P55" t="n">
         <v>-28</v>
       </c>
@@ -7962,9 +7630,6 @@
       <c r="M56" t="n">
         <v>-10.3</v>
       </c>
-      <c r="N56" t="n">
-        <v>8.6</v>
-      </c>
       <c r="P56" t="n">
         <v>-19.9</v>
       </c>
@@ -8106,9 +7771,6 @@
       <c r="M57" t="n">
         <v>-5.4</v>
       </c>
-      <c r="N57" t="n">
-        <v>-3.3</v>
-      </c>
       <c r="P57" t="n">
         <v>-12.5</v>
       </c>
@@ -8241,9 +7903,6 @@
       <c r="M58" t="n">
         <v>-5.7</v>
       </c>
-      <c r="N58" t="n">
-        <v>7.1</v>
-      </c>
       <c r="O58" t="inlineStr">
         <is>
           <t>WR20</t>
@@ -8387,9 +8046,6 @@
       <c r="M59" t="n">
         <v>10</v>
       </c>
-      <c r="N59" t="n">
-        <v>-14.4</v>
-      </c>
       <c r="P59" t="n">
         <v>7.9</v>
       </c>
@@ -8536,9 +8192,6 @@
       <c r="M60" t="n">
         <v>1.2</v>
       </c>
-      <c r="N60" t="n">
-        <v>25</v>
-      </c>
       <c r="P60" t="n">
         <v>-32.7</v>
       </c>
@@ -8615,7 +8268,7 @@
         <v>-12.2</v>
       </c>
       <c r="AM60" t="n">
-        <v>18.62</v>
+        <v>18.65</v>
       </c>
       <c r="AN60" t="n">
         <v>27</v>
@@ -8680,9 +8333,6 @@
       <c r="M61" t="n">
         <v>6.7</v>
       </c>
-      <c r="N61" t="n">
-        <v>15.5</v>
-      </c>
       <c r="P61" t="n">
         <v>6.2</v>
       </c>
@@ -8759,7 +8409,7 @@
         <v>-2.13</v>
       </c>
       <c r="AM61" t="n">
-        <v>12.01</v>
+        <v>12.39</v>
       </c>
       <c r="AN61" t="n">
         <v>27</v>
@@ -8824,9 +8474,6 @@
       <c r="M62" t="n">
         <v>-34.1</v>
       </c>
-      <c r="N62" t="n">
-        <v>-24</v>
-      </c>
       <c r="P62" t="n">
         <v>-36.2</v>
       </c>
@@ -8965,9 +8612,6 @@
       <c r="M63" t="n">
         <v>-3.6</v>
       </c>
-      <c r="N63" t="n">
-        <v>-6.5</v>
-      </c>
       <c r="O63" t="inlineStr">
         <is>
           <t>WR30</t>
@@ -9114,9 +8758,6 @@
       <c r="M64" t="n">
         <v>5.1</v>
       </c>
-      <c r="N64" t="n">
-        <v>-18.6</v>
-      </c>
       <c r="P64" t="n">
         <v>2.1</v>
       </c>
@@ -9260,9 +8901,6 @@
       <c r="M65" t="n">
         <v>1.9</v>
       </c>
-      <c r="N65" t="n">
-        <v>15.1</v>
-      </c>
       <c r="P65" t="n">
         <v>-19.9</v>
       </c>
@@ -9404,9 +9042,6 @@
       <c r="M66" t="n">
         <v>-10.3</v>
       </c>
-      <c r="N66" t="n">
-        <v>11.5</v>
-      </c>
       <c r="P66" t="n">
         <v>-41.2</v>
       </c>
@@ -9483,7 +9118,7 @@
         <v>-14.74</v>
       </c>
       <c r="AM66" t="n">
-        <v>13.7</v>
+        <v>13.73</v>
       </c>
       <c r="AN66" t="n">
         <v>28</v>
@@ -9553,9 +9188,6 @@
       <c r="M67" t="n">
         <v>-3.1</v>
       </c>
-      <c r="N67" t="n">
-        <v>37</v>
-      </c>
       <c r="O67" t="inlineStr">
         <is>
           <t>WR30</t>
@@ -9702,9 +9334,6 @@
       <c r="M68" t="n">
         <v>9.9</v>
       </c>
-      <c r="N68" t="n">
-        <v>11.9</v>
-      </c>
       <c r="P68" t="n">
         <v>-21</v>
       </c>
@@ -9848,9 +9477,6 @@
       <c r="M69" t="n">
         <v>6.2</v>
       </c>
-      <c r="N69" t="n">
-        <v>1</v>
-      </c>
       <c r="P69" t="n">
         <v>-12.3</v>
       </c>
@@ -9978,9 +9604,6 @@
       <c r="M70" t="n">
         <v>31.8</v>
       </c>
-      <c r="N70" t="n">
-        <v>30.3</v>
-      </c>
       <c r="P70" t="n">
         <v>26.6</v>
       </c>
@@ -10119,9 +9742,6 @@
       <c r="M71" t="n">
         <v>-3.3</v>
       </c>
-      <c r="N71" t="n">
-        <v>-4.7</v>
-      </c>
       <c r="O71" t="inlineStr">
         <is>
           <t>WR20</t>
@@ -10259,9 +9879,6 @@
       <c r="M72" t="n">
         <v>16.3</v>
       </c>
-      <c r="N72" t="n">
-        <v>-18.8</v>
-      </c>
       <c r="P72" t="n">
         <v>13.8</v>
       </c>
@@ -10394,9 +10011,6 @@
       <c r="M73" t="n">
         <v>1.4</v>
       </c>
-      <c r="N73" t="n">
-        <v>-0.2</v>
-      </c>
       <c r="P73" t="n">
         <v>-9.800000000000001</v>
       </c>
@@ -10529,9 +10143,6 @@
       <c r="M74" t="n">
         <v>0.4</v>
       </c>
-      <c r="N74" t="n">
-        <v>8.5</v>
-      </c>
       <c r="P74" t="n">
         <v>2.1</v>
       </c>
@@ -10673,9 +10284,6 @@
       <c r="M75" t="n">
         <v>-30.4</v>
       </c>
-      <c r="N75" t="n">
-        <v>-36.6</v>
-      </c>
       <c r="P75" t="n">
         <v>-33.7</v>
       </c>
@@ -10735,7 +10343,7 @@
         <v>-15.42</v>
       </c>
       <c r="AL75" t="n">
-        <v>-16.86</v>
+        <v>-17.24</v>
       </c>
       <c r="AM75" t="n">
         <v>0.85</v>
@@ -10808,9 +10416,6 @@
       <c r="M76" t="n">
         <v>-4.9</v>
       </c>
-      <c r="N76" t="n">
-        <v>-5.6</v>
-      </c>
       <c r="P76" t="n">
         <v>-6.3</v>
       </c>
@@ -10952,9 +10557,6 @@
       <c r="M77" t="n">
         <v>4.9</v>
       </c>
-      <c r="N77" t="n">
-        <v>4.3</v>
-      </c>
       <c r="P77" t="n">
         <v>3.8</v>
       </c>
@@ -11093,9 +10695,6 @@
       <c r="M78" t="n">
         <v>4.1</v>
       </c>
-      <c r="N78" t="n">
-        <v>-4</v>
-      </c>
       <c r="P78" t="n">
         <v>-6.5</v>
       </c>
@@ -11228,9 +10827,6 @@
       <c r="M79" t="n">
         <v>-3.6</v>
       </c>
-      <c r="N79" t="n">
-        <v>43.4</v>
-      </c>
       <c r="O79" t="inlineStr">
         <is>
           <t>WR20</t>
@@ -11312,7 +10908,7 @@
         <v>-3.87</v>
       </c>
       <c r="AM79" t="n">
-        <v>45.59</v>
+        <v>45.63</v>
       </c>
       <c r="AN79" t="n">
         <v>33</v>
@@ -11377,9 +10973,6 @@
       <c r="M80" t="n">
         <v>-32.6</v>
       </c>
-      <c r="N80" t="n">
-        <v>-22.6</v>
-      </c>
       <c r="P80" t="n">
         <v>-40.5</v>
       </c>
@@ -11453,7 +11046,7 @@
         <v>-12.47</v>
       </c>
       <c r="AM80" t="n">
-        <v>8.779999999999999</v>
+        <v>8.789999999999999</v>
       </c>
       <c r="AN80" t="n">
         <v>33</v>
@@ -11518,9 +11111,6 @@
       <c r="M81" t="n">
         <v>-4.7</v>
       </c>
-      <c r="N81" t="n">
-        <v>-20.4</v>
-      </c>
       <c r="O81" t="inlineStr">
         <is>
           <t>WR30</t>
@@ -11596,7 +11186,7 @@
         <v>-21.27</v>
       </c>
       <c r="AL81" t="n">
-        <v>-23.01</v>
+        <v>-23.02</v>
       </c>
       <c r="AM81" t="n">
         <v>6.65</v>
@@ -11669,9 +11259,6 @@
       <c r="M82" t="n">
         <v>-5.7</v>
       </c>
-      <c r="N82" t="n">
-        <v>-53.8</v>
-      </c>
       <c r="O82" t="inlineStr">
         <is>
           <t>WR20</t>
@@ -11823,9 +11410,6 @@
       <c r="M83" t="n">
         <v>-29.7</v>
       </c>
-      <c r="N83" t="n">
-        <v>-20.8</v>
-      </c>
       <c r="P83" t="n">
         <v>-44.3</v>
       </c>
@@ -11953,9 +11537,6 @@
       <c r="M84" t="n">
         <v>0.3</v>
       </c>
-      <c r="N84" t="n">
-        <v>-60.1</v>
-      </c>
       <c r="P84" t="n">
         <v>-32.8</v>
       </c>
@@ -12088,9 +11669,6 @@
       <c r="M85" t="n">
         <v>10.7</v>
       </c>
-      <c r="N85" t="n">
-        <v>7</v>
-      </c>
       <c r="P85" t="n">
         <v>-10.6</v>
       </c>
@@ -12237,9 +11815,6 @@
       <c r="M86" t="n">
         <v>9.800000000000001</v>
       </c>
-      <c r="N86" t="n">
-        <v>-14.8</v>
-      </c>
       <c r="P86" t="n">
         <v>8.5</v>
       </c>
@@ -12313,7 +11888,7 @@
         <v>-15.31</v>
       </c>
       <c r="AL86" t="n">
-        <v>-15.4</v>
+        <v>-15.41</v>
       </c>
       <c r="AM86" t="n">
         <v>23.39</v>
@@ -12386,9 +11961,6 @@
       <c r="M87" t="n">
         <v>3.3</v>
       </c>
-      <c r="N87" t="n">
-        <v>15.5</v>
-      </c>
       <c r="P87" t="n">
         <v>-14.5</v>
       </c>
@@ -12530,9 +12102,6 @@
       <c r="M88" t="n">
         <v>-0.9</v>
       </c>
-      <c r="N88" t="n">
-        <v>2.8</v>
-      </c>
       <c r="P88" t="n">
         <v>-12.1</v>
       </c>
@@ -12674,9 +12243,6 @@
       <c r="M89" t="n">
         <v>53.6</v>
       </c>
-      <c r="N89" t="n">
-        <v>47.9</v>
-      </c>
       <c r="P89" t="n">
         <v>-11.8</v>
       </c>
@@ -12809,9 +12375,6 @@
       <c r="M90" t="n">
         <v>-20.5</v>
       </c>
-      <c r="N90" t="n">
-        <v>-33.1</v>
-      </c>
       <c r="P90" t="n">
         <v>-27.1</v>
       </c>
@@ -12944,9 +12507,6 @@
       <c r="M91" t="n">
         <v>1.1</v>
       </c>
-      <c r="N91" t="n">
-        <v>-27.3</v>
-      </c>
       <c r="P91" t="n">
         <v>-9.199999999999999</v>
       </c>
@@ -13093,9 +12653,6 @@
       <c r="M92" t="n">
         <v>-5</v>
       </c>
-      <c r="N92" t="n">
-        <v>7.7</v>
-      </c>
       <c r="O92" t="inlineStr">
         <is>
           <t>WR40</t>
@@ -13242,9 +12799,6 @@
       <c r="M93" t="n">
         <v>-4.1</v>
       </c>
-      <c r="N93" t="n">
-        <v>19.3</v>
-      </c>
       <c r="O93" t="inlineStr">
         <is>
           <t>WR30</t>
@@ -13391,9 +12945,6 @@
       <c r="M94" t="n">
         <v>1.4</v>
       </c>
-      <c r="N94" t="n">
-        <v>-11.9</v>
-      </c>
       <c r="P94" t="n">
         <v>-3.5</v>
       </c>
@@ -13526,9 +13077,6 @@
       <c r="M95" t="n">
         <v>4</v>
       </c>
-      <c r="N95" t="n">
-        <v>-6.7</v>
-      </c>
       <c r="P95" t="n">
         <v>-14.9</v>
       </c>
@@ -13661,9 +13209,6 @@
       <c r="M96" t="n">
         <v>24.9</v>
       </c>
-      <c r="N96" t="n">
-        <v>41.7</v>
-      </c>
       <c r="P96" t="n">
         <v>-0.9</v>
       </c>
@@ -13805,9 +13350,6 @@
       <c r="M97" t="n">
         <v>-1.2</v>
       </c>
-      <c r="N97" t="n">
-        <v>-34.6</v>
-      </c>
       <c r="P97" t="n">
         <v>-10.6</v>
       </c>
@@ -13954,9 +13496,6 @@
       <c r="M98" t="n">
         <v>-9.699999999999999</v>
       </c>
-      <c r="N98" t="n">
-        <v>-22.1</v>
-      </c>
       <c r="O98" t="inlineStr">
         <is>
           <t>WR30</t>
@@ -14021,7 +13560,7 @@
         <v>-20.65</v>
       </c>
       <c r="AL98" t="n">
-        <v>-21.24</v>
+        <v>-21.25</v>
       </c>
       <c r="AM98" t="n">
         <v>3.01</v>
@@ -14094,9 +13633,6 @@
       <c r="M99" t="n">
         <v>9.1</v>
       </c>
-      <c r="N99" t="n">
-        <v>-22.3</v>
-      </c>
       <c r="P99" t="n">
         <v>8.6</v>
       </c>
@@ -14243,9 +13779,6 @@
       <c r="M100" t="n">
         <v>-0.4</v>
       </c>
-      <c r="N100" t="n">
-        <v>15.1</v>
-      </c>
       <c r="O100" t="inlineStr">
         <is>
           <t>WR20</t>
@@ -14392,9 +13925,6 @@
       <c r="M101" t="n">
         <v>15</v>
       </c>
-      <c r="N101" t="n">
-        <v>18.9</v>
-      </c>
       <c r="P101" t="n">
         <v>11.6</v>
       </c>
@@ -14533,9 +14063,6 @@
       <c r="M102" t="n">
         <v>6.2</v>
       </c>
-      <c r="N102" t="n">
-        <v>-10.1</v>
-      </c>
       <c r="P102" t="n">
         <v>-3.5</v>
       </c>
@@ -14668,9 +14195,6 @@
       <c r="M103" t="n">
         <v>-4.6</v>
       </c>
-      <c r="N103" t="n">
-        <v>-6.5</v>
-      </c>
       <c r="O103" t="inlineStr">
         <is>
           <t>WR30</t>
@@ -14822,9 +14346,6 @@
       <c r="M104" t="n">
         <v>6.9</v>
       </c>
-      <c r="N104" t="n">
-        <v>-18.5</v>
-      </c>
       <c r="P104" t="n">
         <v>5.4</v>
       </c>
@@ -14898,7 +14419,7 @@
         <v>-17.88</v>
       </c>
       <c r="AL104" t="n">
-        <v>-18.6</v>
+        <v>-18.59</v>
       </c>
       <c r="AM104" t="n">
         <v>15.92</v>
@@ -14971,9 +14492,6 @@
       <c r="M105" t="n">
         <v>-8.5</v>
       </c>
-      <c r="N105" t="n">
-        <v>-18.5</v>
-      </c>
       <c r="O105" t="inlineStr">
         <is>
           <t>WR20</t>
@@ -15111,9 +14629,6 @@
       <c r="M106" t="n">
         <v>16</v>
       </c>
-      <c r="N106" t="n">
-        <v>21</v>
-      </c>
       <c r="P106" t="n">
         <v>-20.2</v>
       </c>
@@ -15246,9 +14761,6 @@
       <c r="M107" t="n">
         <v>-8</v>
       </c>
-      <c r="N107" t="n">
-        <v>37</v>
-      </c>
       <c r="O107" t="inlineStr">
         <is>
           <t>WR40</t>
@@ -15395,9 +14907,6 @@
       <c r="M108" t="n">
         <v>4.3</v>
       </c>
-      <c r="N108" t="n">
-        <v>-23.1</v>
-      </c>
       <c r="P108" t="n">
         <v>-8.9</v>
       </c>
@@ -15530,9 +15039,6 @@
       <c r="M109" t="n">
         <v>32.9</v>
       </c>
-      <c r="N109" t="n">
-        <v>29.9</v>
-      </c>
       <c r="P109" t="n">
         <v>8.300000000000001</v>
       </c>
@@ -15674,9 +15180,6 @@
       <c r="M110" t="n">
         <v>1.8</v>
       </c>
-      <c r="N110" t="n">
-        <v>7.1</v>
-      </c>
       <c r="P110" t="n">
         <v>-29.3</v>
       </c>
@@ -15820,9 +15323,6 @@
       <c r="M111" t="n">
         <v>9</v>
       </c>
-      <c r="N111" t="n">
-        <v>-23.4</v>
-      </c>
       <c r="P111" t="n">
         <v>-13.5</v>
       </c>
@@ -15966,9 +15466,6 @@
       <c r="M112" t="n">
         <v>5.4</v>
       </c>
-      <c r="N112" t="n">
-        <v>-33.5</v>
-      </c>
       <c r="P112" t="n">
         <v>-20</v>
       </c>
@@ -16115,9 +15612,6 @@
       <c r="M113" t="n">
         <v>8.699999999999999</v>
       </c>
-      <c r="N113" t="n">
-        <v>6.5</v>
-      </c>
       <c r="P113" t="n">
         <v>7.8</v>
       </c>
@@ -16259,9 +15753,6 @@
       <c r="M114" t="n">
         <v>4.2</v>
       </c>
-      <c r="N114" t="n">
-        <v>-4.7</v>
-      </c>
       <c r="P114" t="n">
         <v>-31.3</v>
       </c>
@@ -16405,9 +15896,6 @@
       <c r="M115" t="n">
         <v>8.699999999999999</v>
       </c>
-      <c r="N115" t="n">
-        <v>-19.5</v>
-      </c>
       <c r="P115" t="n">
         <v>-7.7</v>
       </c>
@@ -16554,9 +16042,6 @@
       <c r="M116" t="n">
         <v>4.9</v>
       </c>
-      <c r="N116" t="n">
-        <v>-10.9</v>
-      </c>
       <c r="P116" t="n">
         <v>-9</v>
       </c>
@@ -16703,9 +16188,6 @@
       <c r="M117" t="n">
         <v>8.9</v>
       </c>
-      <c r="N117" t="n">
-        <v>-19.7</v>
-      </c>
       <c r="P117" t="n">
         <v>-5.4</v>
       </c>
@@ -16852,9 +16334,6 @@
       <c r="M118" t="n">
         <v>-10.4</v>
       </c>
-      <c r="N118" t="n">
-        <v>-43.5</v>
-      </c>
       <c r="P118" t="n">
         <v>-13.3</v>
       </c>
@@ -16914,7 +16393,7 @@
         <v>-36.54</v>
       </c>
       <c r="AL118" t="n">
-        <v>-37.26</v>
+        <v>-37.27</v>
       </c>
       <c r="AM118" t="n">
         <v>3.06</v>
@@ -16987,9 +16466,6 @@
       <c r="M119" t="n">
         <v>-9.5</v>
       </c>
-      <c r="N119" t="n">
-        <v>-13.9</v>
-      </c>
       <c r="P119" t="n">
         <v>-16.6</v>
       </c>
@@ -17122,9 +16598,6 @@
       <c r="M120" t="n">
         <v>30.3</v>
       </c>
-      <c r="N120" t="n">
-        <v>34.7</v>
-      </c>
       <c r="P120" t="n">
         <v>20.7</v>
       </c>
@@ -17271,9 +16744,6 @@
       <c r="M121" t="n">
         <v>3.7</v>
       </c>
-      <c r="N121" t="n">
-        <v>-18.9</v>
-      </c>
       <c r="P121" t="n">
         <v>1.7</v>
       </c>
@@ -17420,9 +16890,6 @@
       <c r="M122" t="n">
         <v>-12.7</v>
       </c>
-      <c r="N122" t="n">
-        <v>-22.6</v>
-      </c>
       <c r="P122" t="n">
         <v>-15.8</v>
       </c>
@@ -17555,9 +17022,6 @@
       <c r="M123" t="n">
         <v>-29.6</v>
       </c>
-      <c r="N123" t="n">
-        <v>-16.1</v>
-      </c>
       <c r="P123" t="n">
         <v>-39.2</v>
       </c>
@@ -17690,9 +17154,6 @@
       <c r="M124" t="n">
         <v>-19.2</v>
       </c>
-      <c r="N124" t="n">
-        <v>-30</v>
-      </c>
       <c r="P124" t="n">
         <v>-21.1</v>
       </c>
@@ -17825,9 +17286,6 @@
       <c r="M125" t="n">
         <v>48</v>
       </c>
-      <c r="N125" t="n">
-        <v>47.2</v>
-      </c>
       <c r="P125" t="n">
         <v>11.9</v>
       </c>
@@ -17969,9 +17427,6 @@
       <c r="M126" t="n">
         <v>-25.1</v>
       </c>
-      <c r="N126" t="n">
-        <v>-20.5</v>
-      </c>
       <c r="P126" t="n">
         <v>-31.4</v>
       </c>
@@ -18115,9 +17570,6 @@
       <c r="M127" t="n">
         <v>-9.5</v>
       </c>
-      <c r="N127" t="n">
-        <v>-18.6</v>
-      </c>
       <c r="O127" t="inlineStr">
         <is>
           <t>WR20</t>
@@ -18255,9 +17707,6 @@
       <c r="M128" t="n">
         <v>3.9</v>
       </c>
-      <c r="N128" t="n">
-        <v>14.7</v>
-      </c>
       <c r="P128" t="n">
         <v>-18</v>
       </c>
@@ -18401,9 +17850,6 @@
       <c r="M129" t="n">
         <v>31.7</v>
       </c>
-      <c r="N129" t="n">
-        <v>56.4</v>
-      </c>
       <c r="P129" t="n">
         <v>27</v>
       </c>
@@ -18545,9 +17991,6 @@
       <c r="M130" t="n">
         <v>4.4</v>
       </c>
-      <c r="N130" t="n">
-        <v>13.3</v>
-      </c>
       <c r="P130" t="n">
         <v>-31</v>
       </c>
@@ -18689,9 +18132,6 @@
       <c r="M131" t="n">
         <v>-0.7</v>
       </c>
-      <c r="N131" t="n">
-        <v>-47.8</v>
-      </c>
       <c r="O131" t="inlineStr">
         <is>
           <t>WR40</t>
@@ -18840,9 +18280,6 @@
       <c r="M132" t="n">
         <v>-5.6</v>
       </c>
-      <c r="N132" t="n">
-        <v>-51.6</v>
-      </c>
       <c r="O132" t="inlineStr">
         <is>
           <t>WR20</t>
@@ -18980,9 +18417,6 @@
       <c r="M133" t="n">
         <v>3.8</v>
       </c>
-      <c r="N133" t="n">
-        <v>43.4</v>
-      </c>
       <c r="P133" t="n">
         <v>-41.2</v>
       </c>
@@ -19059,7 +18493,7 @@
         <v>-16.21</v>
       </c>
       <c r="AM133" t="n">
-        <v>26.91</v>
+        <v>26.94</v>
       </c>
       <c r="AN133" t="n">
         <v>49</v>
@@ -19129,9 +18563,6 @@
       <c r="M134" t="n">
         <v>-5.3</v>
       </c>
-      <c r="N134" t="n">
-        <v>-15.1</v>
-      </c>
       <c r="O134" t="inlineStr">
         <is>
           <t>WR20</t>
@@ -19269,9 +18700,6 @@
       <c r="M135" t="n">
         <v>0.8</v>
       </c>
-      <c r="N135" t="n">
-        <v>3.4</v>
-      </c>
       <c r="P135" t="n">
         <v>-13</v>
       </c>
@@ -19413,9 +18841,6 @@
       <c r="M136" t="n">
         <v>3.7</v>
       </c>
-      <c r="N136" t="n">
-        <v>9.699999999999999</v>
-      </c>
       <c r="P136" t="n">
         <v>-20.6</v>
       </c>
@@ -19548,9 +18973,6 @@
       <c r="M137" t="n">
         <v>3</v>
       </c>
-      <c r="N137" t="n">
-        <v>24.7</v>
-      </c>
       <c r="P137" t="n">
         <v>-30.4</v>
       </c>
@@ -19692,9 +19114,6 @@
       <c r="M138" t="n">
         <v>1.5</v>
       </c>
-      <c r="N138" t="n">
-        <v>-36.6</v>
-      </c>
       <c r="P138" t="n">
         <v>-24.7</v>
       </c>
@@ -19838,9 +19257,6 @@
       <c r="M139" t="n">
         <v>7.1</v>
       </c>
-      <c r="N139" t="n">
-        <v>-10.7</v>
-      </c>
       <c r="P139" t="n">
         <v>1.9</v>
       </c>
@@ -19984,9 +19400,6 @@
       <c r="M140" t="n">
         <v>-2.7</v>
       </c>
-      <c r="N140" t="n">
-        <v>-31.1</v>
-      </c>
       <c r="O140" t="inlineStr">
         <is>
           <t>WR30</t>
@@ -20138,9 +19551,6 @@
       <c r="M141" t="n">
         <v>1.7</v>
       </c>
-      <c r="N141" t="n">
-        <v>-33.9</v>
-      </c>
       <c r="P141" t="n">
         <v>-1.6</v>
       </c>
@@ -20287,9 +19697,6 @@
       <c r="M142" t="n">
         <v>4.8</v>
       </c>
-      <c r="N142" t="n">
-        <v>36.4</v>
-      </c>
       <c r="P142" t="n">
         <v>-33.7</v>
       </c>
@@ -20431,9 +19838,6 @@
       <c r="M143" t="n">
         <v>1.7</v>
       </c>
-      <c r="N143" t="n">
-        <v>-23.8</v>
-      </c>
       <c r="P143" t="n">
         <v>-12.3</v>
       </c>
@@ -20566,9 +19970,6 @@
       <c r="M144" t="n">
         <v>52.9</v>
       </c>
-      <c r="N144" t="n">
-        <v>53.3</v>
-      </c>
       <c r="P144" t="n">
         <v>18.6</v>
       </c>
@@ -20596,9 +19997,6 @@
       </c>
       <c r="W144" t="b">
         <v>1</v>
-      </c>
-      <c r="X144" s="13" t="n">
-        <v>46317</v>
       </c>
       <c r="Y144" s="13" t="n">
         <v>46265</v>
@@ -20710,9 +20108,6 @@
       <c r="M145" t="n">
         <v>1.4</v>
       </c>
-      <c r="N145" t="n">
-        <v>-5.7</v>
-      </c>
       <c r="P145" t="n">
         <v>-14.9</v>
       </c>
@@ -20854,9 +20249,6 @@
       <c r="M146" t="n">
         <v>52.3</v>
       </c>
-      <c r="N146" t="n">
-        <v>63.2</v>
-      </c>
       <c r="P146" t="n">
         <v>18</v>
       </c>
@@ -20998,9 +20390,6 @@
       <c r="M147" t="n">
         <v>-1.3</v>
       </c>
-      <c r="N147" t="n">
-        <v>17.5</v>
-      </c>
       <c r="P147" t="n">
         <v>-19.9</v>
       </c>
@@ -21028,9 +20417,6 @@
       </c>
       <c r="W147" t="b">
         <v>1</v>
-      </c>
-      <c r="X147" s="13" t="n">
-        <v>46317</v>
       </c>
       <c r="Y147" s="13" t="n">
         <v>46253</v>
@@ -21142,9 +20528,6 @@
       <c r="M148" t="n">
         <v>37</v>
       </c>
-      <c r="N148" t="n">
-        <v>24.3</v>
-      </c>
       <c r="P148" t="n">
         <v>5.2</v>
       </c>
@@ -21286,9 +20669,6 @@
       <c r="M149" t="n">
         <v>13.5</v>
       </c>
-      <c r="N149" t="n">
-        <v>30</v>
-      </c>
       <c r="P149" t="n">
         <v>-21.7</v>
       </c>
@@ -21435,9 +20815,6 @@
       <c r="M150" t="n">
         <v>-11.1</v>
       </c>
-      <c r="N150" t="n">
-        <v>-9.4</v>
-      </c>
       <c r="P150" t="n">
         <v>-25.3</v>
       </c>
@@ -21579,9 +20956,6 @@
       <c r="M151" t="n">
         <v>9.699999999999999</v>
       </c>
-      <c r="N151" t="n">
-        <v>-3.9</v>
-      </c>
       <c r="P151" t="n">
         <v>3.2</v>
       </c>
@@ -21720,9 +21094,6 @@
       <c r="M152" t="n">
         <v>-24.2</v>
       </c>
-      <c r="N152" t="n">
-        <v>-28.4</v>
-      </c>
       <c r="P152" t="n">
         <v>-24.4</v>
       </c>
@@ -21869,9 +21240,6 @@
       <c r="M153" t="n">
         <v>5.1</v>
       </c>
-      <c r="N153" t="n">
-        <v>28.2</v>
-      </c>
       <c r="P153" t="n">
         <v>-32.6</v>
       </c>
@@ -22013,9 +21381,6 @@
       <c r="M154" t="n">
         <v>-14.4</v>
       </c>
-      <c r="N154" t="n">
-        <v>-8.5</v>
-      </c>
       <c r="P154" t="n">
         <v>-14.3</v>
       </c>
@@ -22157,9 +21522,6 @@
       <c r="M155" t="n">
         <v>18.1</v>
       </c>
-      <c r="N155" t="n">
-        <v>5.6</v>
-      </c>
       <c r="P155" t="n">
         <v>16.9</v>
       </c>
@@ -22287,9 +21649,6 @@
       <c r="M156" t="n">
         <v>-11.4</v>
       </c>
-      <c r="N156" t="n">
-        <v>19.3</v>
-      </c>
       <c r="P156" t="n">
         <v>-30.7</v>
       </c>
@@ -22431,9 +21790,6 @@
       <c r="M157" t="n">
         <v>10.3</v>
       </c>
-      <c r="N157" t="n">
-        <v>17.6</v>
-      </c>
       <c r="P157" t="n">
         <v>10.8</v>
       </c>
@@ -22507,7 +21863,7 @@
         <v>-6.54</v>
       </c>
       <c r="AM157" t="n">
-        <v>18.6</v>
+        <v>18.66</v>
       </c>
       <c r="AN157" t="n">
         <v>56</v>
@@ -22572,9 +21928,6 @@
       <c r="M158" t="n">
         <v>30.9</v>
       </c>
-      <c r="N158" t="n">
-        <v>26.7</v>
-      </c>
       <c r="P158" t="n">
         <v>12.6</v>
       </c>
@@ -22713,9 +22066,6 @@
       <c r="M159" t="n">
         <v>-22.2</v>
       </c>
-      <c r="N159" t="n">
-        <v>-3.5</v>
-      </c>
       <c r="P159" t="n">
         <v>-24.1</v>
       </c>
@@ -22857,9 +22207,6 @@
       <c r="M160" t="n">
         <v>-25.3</v>
       </c>
-      <c r="N160" t="n">
-        <v>11.5</v>
-      </c>
       <c r="P160" t="n">
         <v>-50.8</v>
       </c>
@@ -22936,7 +22283,7 @@
         <v>-19.66</v>
       </c>
       <c r="AM160" t="n">
-        <v>28.49</v>
+        <v>28.52</v>
       </c>
       <c r="AN160" t="n">
         <v>58</v>
@@ -23006,9 +22353,6 @@
       <c r="M161" t="n">
         <v>14.7</v>
       </c>
-      <c r="N161" t="n">
-        <v>-7.5</v>
-      </c>
       <c r="P161" t="n">
         <v>-0.5</v>
       </c>
@@ -23152,9 +22496,6 @@
       <c r="M162" t="n">
         <v>0.4</v>
       </c>
-      <c r="N162" t="n">
-        <v>34.9</v>
-      </c>
       <c r="P162" t="n">
         <v>-36.9</v>
       </c>
@@ -23296,9 +22637,6 @@
       <c r="M163" t="n">
         <v>-11.6</v>
       </c>
-      <c r="N163" t="n">
-        <v>-4.7</v>
-      </c>
       <c r="P163" t="n">
         <v>-32.4</v>
       </c>
@@ -23445,9 +22783,6 @@
       <c r="M164" t="n">
         <v>-4</v>
       </c>
-      <c r="N164" t="n">
-        <v>11.9</v>
-      </c>
       <c r="O164" t="inlineStr">
         <is>
           <t>WR20</t>
@@ -23594,9 +22929,6 @@
       <c r="M165" t="n">
         <v>-3</v>
       </c>
-      <c r="N165" t="n">
-        <v>56</v>
-      </c>
       <c r="O165" t="inlineStr">
         <is>
           <t>WR20</t>
@@ -23743,9 +23075,6 @@
       <c r="M166" t="n">
         <v>-29.1</v>
       </c>
-      <c r="N166" t="n">
-        <v>-19</v>
-      </c>
       <c r="P166" t="n">
         <v>-45.6</v>
       </c>
@@ -23878,9 +23207,6 @@
       <c r="M167" t="n">
         <v>-11.2</v>
       </c>
-      <c r="N167" t="n">
-        <v>-12.5</v>
-      </c>
       <c r="P167" t="n">
         <v>-31.4</v>
       </c>
@@ -24013,9 +23339,6 @@
       <c r="M168" t="n">
         <v>23.1</v>
       </c>
-      <c r="N168" t="n">
-        <v>9.699999999999999</v>
-      </c>
       <c r="P168" t="n">
         <v>21</v>
       </c>
@@ -24154,9 +23477,6 @@
       <c r="M169" t="n">
         <v>4.2</v>
       </c>
-      <c r="N169" t="n">
-        <v>20.2</v>
-      </c>
       <c r="P169" t="n">
         <v>-20.1</v>
       </c>
@@ -24298,9 +23618,6 @@
       <c r="M170" t="n">
         <v>7.3</v>
       </c>
-      <c r="N170" t="n">
-        <v>8.5</v>
-      </c>
       <c r="P170" t="n">
         <v>-6.2</v>
       </c>
@@ -24442,9 +23759,6 @@
       <c r="M171" t="n">
         <v>-24</v>
       </c>
-      <c r="N171" t="n">
-        <v>-9.800000000000001</v>
-      </c>
       <c r="P171" t="n">
         <v>-25.9</v>
       </c>
@@ -24700,9 +24014,6 @@
       <c r="M173" t="n">
         <v>-14.9</v>
       </c>
-      <c r="N173" t="n">
-        <v>-2.3</v>
-      </c>
       <c r="P173" t="n">
         <v>-27</v>
       </c>
@@ -24852,9 +24163,6 @@
       <c r="M174" t="n">
         <v>47.6</v>
       </c>
-      <c r="N174" t="n">
-        <v>38.7</v>
-      </c>
       <c r="P174" t="n">
         <v>31.8</v>
       </c>
@@ -25002,9 +24310,6 @@
       <c r="M175" t="n">
         <v>25</v>
       </c>
-      <c r="N175" t="n">
-        <v>21</v>
-      </c>
       <c r="P175" t="n">
         <v>-6.8</v>
       </c>
@@ -25152,9 +24457,6 @@
       <c r="M176" t="n">
         <v>-21.4</v>
       </c>
-      <c r="N176" t="n">
-        <v>-18.6</v>
-      </c>
       <c r="P176" t="n">
         <v>-27.7</v>
       </c>
@@ -25302,9 +24604,6 @@
       <c r="M177" t="n">
         <v>-12.9</v>
       </c>
-      <c r="N177" t="n">
-        <v>-5.1</v>
-      </c>
       <c r="P177" t="n">
         <v>-17.4</v>
       </c>
@@ -25452,9 +24751,6 @@
       <c r="M178" t="n">
         <v>-8.4</v>
       </c>
-      <c r="N178" t="n">
-        <v>14.7</v>
-      </c>
       <c r="O178" t="inlineStr">
         <is>
           <t>WR20</t>
@@ -25607,9 +24903,6 @@
       <c r="M179" t="n">
         <v>-3.5</v>
       </c>
-      <c r="N179" t="n">
-        <v>1</v>
-      </c>
       <c r="O179" t="inlineStr">
         <is>
           <t>WR20</t>
@@ -25762,9 +25055,6 @@
       <c r="M180" t="n">
         <v>-24.2</v>
       </c>
-      <c r="N180" t="n">
-        <v>-21.9</v>
-      </c>
       <c r="P180" t="n">
         <v>-25.7</v>
       </c>
@@ -25914,9 +25204,6 @@
       <c r="M181" t="n">
         <v>-28.8</v>
       </c>
-      <c r="N181" t="n">
-        <v>-22.1</v>
-      </c>
       <c r="P181" t="n">
         <v>-42.4</v>
       </c>
@@ -26064,9 +25351,6 @@
       <c r="M182" t="n">
         <v>28.5</v>
       </c>
-      <c r="N182" t="n">
-        <v>5.4</v>
-      </c>
       <c r="P182" t="n">
         <v>27</v>
       </c>
@@ -26214,9 +25498,6 @@
       <c r="M183" t="n">
         <v>52.9</v>
       </c>
-      <c r="N183" t="n">
-        <v>66.7</v>
-      </c>
       <c r="P183" t="n">
         <v>5.4</v>
       </c>
@@ -26364,9 +25645,6 @@
       <c r="M184" t="n">
         <v>-37.8</v>
       </c>
-      <c r="N184" t="n">
-        <v>-3.1</v>
-      </c>
       <c r="P184" t="n">
         <v>-50.4</v>
       </c>
@@ -26514,9 +25792,6 @@
       <c r="M185" t="n">
         <v>-14.6</v>
       </c>
-      <c r="N185" t="n">
-        <v>-5.7</v>
-      </c>
       <c r="P185" t="n">
         <v>-14.7</v>
       </c>
@@ -26664,9 +25939,6 @@
       <c r="M186" t="n">
         <v>9</v>
       </c>
-      <c r="N186" t="n">
-        <v>-23.1</v>
-      </c>
       <c r="P186" t="n">
         <v>-7.5</v>
       </c>
@@ -26810,9 +26082,6 @@
       <c r="M187" t="n">
         <v>46.7</v>
       </c>
-      <c r="N187" t="n">
-        <v>-6.9</v>
-      </c>
       <c r="P187" t="n">
         <v>42.3</v>
       </c>
@@ -26965,9 +26234,6 @@
       <c r="M188" t="n">
         <v>48.1</v>
       </c>
-      <c r="N188" t="n">
-        <v>25</v>
-      </c>
       <c r="P188" t="n">
         <v>45.4</v>
       </c>
@@ -27115,9 +26381,6 @@
       <c r="M189" t="n">
         <v>56.6</v>
       </c>
-      <c r="N189" t="n">
-        <v>-14.4</v>
-      </c>
       <c r="P189" t="n">
         <v>50.5</v>
       </c>
@@ -27265,9 +26528,6 @@
       <c r="M190" t="n">
         <v>78.8</v>
       </c>
-      <c r="N190" t="n">
-        <v>2.4</v>
-      </c>
       <c r="P190" t="n">
         <v>73.3</v>
       </c>
@@ -27420,9 +26680,6 @@
       <c r="M191" t="n">
         <v>51.9</v>
       </c>
-      <c r="N191" t="n">
-        <v>2.3</v>
-      </c>
       <c r="P191" t="n">
         <v>49.5</v>
       </c>
@@ -27575,9 +26832,6 @@
       <c r="M192" t="n">
         <v>82.09999999999999</v>
       </c>
-      <c r="N192" t="n">
-        <v>17.5</v>
-      </c>
       <c r="P192" t="n">
         <v>75.8</v>
       </c>
@@ -27725,9 +26979,6 @@
       <c r="M193" t="n">
         <v>63.2</v>
       </c>
-      <c r="N193" t="n">
-        <v>40.3</v>
-      </c>
       <c r="P193" t="n">
         <v>43.2</v>
       </c>
@@ -27870,9 +27121,6 @@
       <c r="M194" t="n">
         <v>35.3</v>
       </c>
-      <c r="N194" t="n">
-        <v>-9.300000000000001</v>
-      </c>
       <c r="P194" t="n">
         <v>24.9</v>
       </c>
@@ -28025,9 +27273,6 @@
       <c r="M195" t="n">
         <v>65.3</v>
       </c>
-      <c r="N195" t="n">
-        <v>-5.7</v>
-      </c>
       <c r="P195" t="n">
         <v>53.9</v>
       </c>
@@ -28175,9 +27420,6 @@
       <c r="M196" t="n">
         <v>19.3</v>
       </c>
-      <c r="N196" t="n">
-        <v>-19.5</v>
-      </c>
       <c r="P196" t="n">
         <v>15.7</v>
       </c>
@@ -28325,9 +27567,6 @@
       <c r="M197" t="n">
         <v>51.8</v>
       </c>
-      <c r="N197" t="n">
-        <v>-14.8</v>
-      </c>
       <c r="P197" t="n">
         <v>46.3</v>
       </c>
@@ -28393,7 +27632,7 @@
         <v>-31.09</v>
       </c>
       <c r="AL197" t="n">
-        <v>-31.16</v>
+        <v>-31.17</v>
       </c>
       <c r="AM197" t="n">
         <v>5.66</v>
@@ -28472,9 +27711,6 @@
       <c r="M198" t="n">
         <v>51.3</v>
       </c>
-      <c r="N198" t="n">
-        <v>-0.1</v>
-      </c>
       <c r="P198" t="n">
         <v>48.1</v>
       </c>
@@ -28622,9 +27858,6 @@
       <c r="M199" t="n">
         <v>32.8</v>
       </c>
-      <c r="N199" t="n">
-        <v>-4.3</v>
-      </c>
       <c r="P199" t="n">
         <v>24</v>
       </c>
@@ -28772,9 +28005,6 @@
       <c r="M200" t="n">
         <v>98.5</v>
       </c>
-      <c r="N200" t="n">
-        <v>41.6</v>
-      </c>
       <c r="P200" t="n">
         <v>70.09999999999999</v>
       </c>
@@ -28917,9 +28147,6 @@
       <c r="M201" t="n">
         <v>40.9</v>
       </c>
-      <c r="N201" t="n">
-        <v>-25.1</v>
-      </c>
       <c r="P201" t="n">
         <v>40</v>
       </c>
@@ -29064,9 +28291,6 @@
       <c r="M202" t="n">
         <v>51.1</v>
       </c>
-      <c r="N202" t="n">
-        <v>-22.3</v>
-      </c>
       <c r="P202" t="n">
         <v>36.8</v>
       </c>
@@ -29219,9 +28443,6 @@
       <c r="M203" t="n">
         <v>37.5</v>
       </c>
-      <c r="N203" t="n">
-        <v>-18.5</v>
-      </c>
       <c r="P203" t="n">
         <v>31.2</v>
       </c>
@@ -29360,9 +28581,6 @@
       <c r="M204" t="n">
         <v>-14.6</v>
       </c>
-      <c r="N204" t="n">
-        <v>13.3</v>
-      </c>
       <c r="P204" t="n">
         <v>-45.2</v>
       </c>
@@ -29515,9 +28733,6 @@
       <c r="M205" t="n">
         <v>16.5</v>
       </c>
-      <c r="N205" t="n">
-        <v>-29.6</v>
-      </c>
       <c r="P205" t="n">
         <v>12.5</v>
       </c>
@@ -29665,9 +28880,6 @@
       <c r="M206" t="n">
         <v>-8.800000000000001</v>
       </c>
-      <c r="N206" t="n">
-        <v>-33.5</v>
-      </c>
       <c r="P206" t="n">
         <v>-12.3</v>
       </c>
@@ -29820,9 +29032,6 @@
       <c r="M207" t="n">
         <v>41.1</v>
       </c>
-      <c r="N207" t="n">
-        <v>149.1</v>
-      </c>
       <c r="P207" t="n">
         <v>20.1</v>
       </c>
@@ -29970,9 +29179,6 @@
       <c r="M208" t="n">
         <v>9.9</v>
       </c>
-      <c r="N208" t="n">
-        <v>-19.7</v>
-      </c>
       <c r="P208" t="n">
         <v>10.1</v>
       </c>
@@ -30120,9 +29326,6 @@
       <c r="M209" t="n">
         <v>-27.9</v>
       </c>
-      <c r="N209" t="n">
-        <v>-47.8</v>
-      </c>
       <c r="P209" t="n">
         <v>-29.5</v>
       </c>
@@ -30275,9 +29478,6 @@
       <c r="M210" t="n">
         <v>-28.3</v>
       </c>
-      <c r="N210" t="n">
-        <v>3.6</v>
-      </c>
       <c r="P210" t="n">
         <v>-29.8</v>
       </c>
@@ -30420,9 +29620,6 @@
       <c r="M211" t="n">
         <v>19.8</v>
       </c>
-      <c r="N211" t="n">
-        <v>-11</v>
-      </c>
       <c r="P211" t="n">
         <v>15.6</v>
       </c>
@@ -30565,9 +29762,6 @@
       <c r="M212" t="n">
         <v>37.4</v>
       </c>
-      <c r="N212" t="n">
-        <v>-18.6</v>
-      </c>
       <c r="P212" t="n">
         <v>31.2</v>
       </c>
@@ -30709,9 +29903,6 @@
       <c r="M213" t="n">
         <v>73.3</v>
       </c>
-      <c r="N213" t="n">
-        <v>26.8</v>
-      </c>
       <c r="P213" t="n">
         <v>67.09999999999999</v>
       </c>
@@ -30859,9 +30050,6 @@
       <c r="M214" t="n">
         <v>8.699999999999999</v>
       </c>
-      <c r="N214" t="n">
-        <v>-37.5</v>
-      </c>
       <c r="P214" t="n">
         <v>4.4</v>
       </c>
@@ -31011,9 +30199,6 @@
       <c r="M215" t="n">
         <v>-20.5</v>
       </c>
-      <c r="N215" t="n">
-        <v>-22.1</v>
-      </c>
       <c r="P215" t="n">
         <v>-34.2</v>
       </c>
@@ -31151,9 +30336,6 @@
       <c r="M216" t="n">
         <v>-15.1</v>
       </c>
-      <c r="N216" t="n">
-        <v>-51.6</v>
-      </c>
       <c r="P216" t="n">
         <v>-13.4</v>
       </c>
@@ -31306,9 +30488,6 @@
       <c r="M217" t="n">
         <v>22.6</v>
       </c>
-      <c r="N217" t="n">
-        <v>-10.7</v>
-      </c>
       <c r="P217" t="n">
         <v>18.2</v>
       </c>
@@ -31447,9 +30626,6 @@
       <c r="M218" t="n">
         <v>26.4</v>
       </c>
-      <c r="N218" t="n">
-        <v>-22.2</v>
-      </c>
       <c r="P218" t="n">
         <v>14.8</v>
       </c>
@@ -31593,9 +30769,6 @@
       <c r="M219" t="n">
         <v>-28.1</v>
       </c>
-      <c r="N219" t="n">
-        <v>-60.1</v>
-      </c>
       <c r="P219" t="n">
         <v>-42.6</v>
       </c>
@@ -31748,9 +30921,6 @@
       <c r="M220" t="n">
         <v>3.7</v>
       </c>
-      <c r="N220" t="n">
-        <v>-23.8</v>
-      </c>
       <c r="P220" t="n">
         <v>-1.3</v>
       </c>
@@ -31894,9 +31064,6 @@
       <c r="M221" t="n">
         <v>61.4</v>
       </c>
-      <c r="N221" t="n">
-        <v>12.8</v>
-      </c>
       <c r="P221" t="n">
         <v>59.4</v>
       </c>
@@ -32041,9 +31208,6 @@
       <c r="M222" t="n">
         <v>-8.199999999999999</v>
       </c>
-      <c r="N222" t="n">
-        <v>42.9</v>
-      </c>
       <c r="O222" t="inlineStr">
         <is>
           <t>WR40</t>
@@ -32196,9 +31360,6 @@
       <c r="M223" t="n">
         <v>1.4</v>
       </c>
-      <c r="N223" t="n">
-        <v>-33.9</v>
-      </c>
       <c r="P223" t="n">
         <v>-1.3</v>
       </c>
@@ -32351,9 +31512,6 @@
       <c r="M224" t="n">
         <v>1.6</v>
       </c>
-      <c r="N224" t="n">
-        <v>-34.6</v>
-      </c>
       <c r="P224" t="n">
         <v>-7.1</v>
       </c>
@@ -32506,9 +31664,6 @@
       <c r="M225" t="n">
         <v>-34.2</v>
       </c>
-      <c r="N225" t="n">
-        <v>-20.4</v>
-      </c>
       <c r="P225" t="n">
         <v>-35.9</v>
       </c>
@@ -32651,9 +31806,6 @@
       <c r="M226" t="n">
         <v>-11.8</v>
       </c>
-      <c r="N226" t="n">
-        <v>-36.6</v>
-      </c>
       <c r="P226" t="n">
         <v>-15.2</v>
       </c>
@@ -32806,9 +31958,6 @@
       <c r="M227" t="n">
         <v>-30.4</v>
       </c>
-      <c r="N227" t="n">
-        <v>-27.6</v>
-      </c>
       <c r="P227" t="n">
         <v>-44.5</v>
       </c>
@@ -32952,9 +32101,6 @@
       <c r="M228" t="n">
         <v>2.3</v>
       </c>
-      <c r="N228" t="n">
-        <v>-53.8</v>
-      </c>
       <c r="P228" t="n">
         <v>-4.2</v>
       </c>
@@ -33107,9 +32253,6 @@
       <c r="M229" t="n">
         <v>-24.2</v>
       </c>
-      <c r="N229" t="n">
-        <v>-8.1</v>
-      </c>
       <c r="P229" t="n">
         <v>-37.2</v>
       </c>
@@ -33257,9 +32400,6 @@
       <c r="M230" t="n">
         <v>-1.1</v>
       </c>
-      <c r="N230" t="n">
-        <v>-10.9</v>
-      </c>
       <c r="P230" t="n">
         <v>-16.6</v>
       </c>
@@ -33407,9 +32547,6 @@
       <c r="M231" t="n">
         <v>-18.3</v>
       </c>
-      <c r="N231" t="n">
-        <v>92.90000000000001</v>
-      </c>
       <c r="P231" t="n">
         <v>-36.7</v>
       </c>
@@ -33557,9 +32694,6 @@
       <c r="M232" t="n">
         <v>-28.4</v>
       </c>
-      <c r="N232" t="n">
-        <v>-23.5</v>
-      </c>
       <c r="P232" t="n">
         <v>-36.4</v>
       </c>
@@ -33712,9 +32846,6 @@
       <c r="M233" t="n">
         <v>-26.9</v>
       </c>
-      <c r="N233" t="n">
-        <v>38.1</v>
-      </c>
       <c r="P233" t="n">
         <v>-37.1</v>
       </c>
@@ -33857,9 +32988,6 @@
       <c r="M234" t="n">
         <v>-11.5</v>
       </c>
-      <c r="N234" t="n">
-        <v>29.4</v>
-      </c>
       <c r="P234" t="n">
         <v>-33.1</v>
       </c>
@@ -33921,7 +33049,7 @@
         <v>-11.15</v>
       </c>
       <c r="AM234" t="n">
-        <v>30.74</v>
+        <v>30.78</v>
       </c>
       <c r="AN234" t="n">
         <v>68</v>
@@ -33992,9 +33120,6 @@
       <c r="M235" t="n">
         <v>-22.5</v>
       </c>
-      <c r="N235" t="n">
-        <v>-39.6</v>
-      </c>
       <c r="P235" t="n">
         <v>-25.8</v>
       </c>
@@ -34068,7 +33193,7 @@
         <v>-26.62</v>
       </c>
       <c r="AL235" t="n">
-        <v>-27.61</v>
+        <v>-29.39</v>
       </c>
       <c r="AM235" t="n">
         <v>55.07</v>
@@ -34147,9 +33272,6 @@
       <c r="M236" t="n">
         <v>1.1</v>
       </c>
-      <c r="N236" t="n">
-        <v>10.6</v>
-      </c>
       <c r="P236" t="n">
         <v>-22.3</v>
       </c>
@@ -34442,9 +33564,6 @@
       <c r="M238" t="n">
         <v>-34.3</v>
       </c>
-      <c r="N238" t="n">
-        <v>-33.4</v>
-      </c>
       <c r="P238" t="n">
         <v>-41.1</v>
       </c>
@@ -34592,9 +33711,6 @@
       <c r="M239" t="n">
         <v>11.2</v>
       </c>
-      <c r="N239" t="n">
-        <v>-12.7</v>
-      </c>
       <c r="P239" t="n">
         <v>10.3</v>
       </c>
@@ -34891,9 +34007,6 @@
       <c r="M241" t="n">
         <v>-25.2</v>
       </c>
-      <c r="N241" t="n">
-        <v>-31.1</v>
-      </c>
       <c r="P241" t="n">
         <v>-25.6</v>
       </c>
@@ -35046,9 +34159,6 @@
       <c r="M242" t="n">
         <v>-29.2</v>
       </c>
-      <c r="N242" t="n">
-        <v>1.6</v>
-      </c>
       <c r="P242" t="n">
         <v>-50.8</v>
       </c>
@@ -35198,9 +34308,6 @@
       <c r="M243" t="n">
         <v>22.2</v>
       </c>
-      <c r="N243" t="n">
-        <v>-27.3</v>
-      </c>
       <c r="P243" t="n">
         <v>20.3</v>
       </c>
@@ -35345,9 +34452,6 @@
       <c r="M244" t="n">
         <v>7.4</v>
       </c>
-      <c r="N244" t="n">
-        <v>-13.4</v>
-      </c>
       <c r="P244" t="n">
         <v>5</v>
       </c>
@@ -35492,9 +34596,6 @@
       <c r="M245" t="n">
         <v>64.90000000000001</v>
       </c>
-      <c r="N245" t="n">
-        <v>37.6</v>
-      </c>
       <c r="P245" t="n">
         <v>51.1</v>
       </c>
@@ -35637,9 +34738,6 @@
       <c r="M246" t="n">
         <v>22.5</v>
       </c>
-      <c r="N246" t="n">
-        <v>8.699999999999999</v>
-      </c>
       <c r="P246" t="n">
         <v>17.1</v>
       </c>
@@ -35770,9 +34868,6 @@
       <c r="M247" t="n">
         <v>-28.7</v>
       </c>
-      <c r="N247" t="n">
-        <v>-6.5</v>
-      </c>
       <c r="P247" t="n">
         <v>-39.4</v>
       </c>
@@ -35915,9 +35010,6 @@
       <c r="M248" t="n">
         <v>3.4</v>
       </c>
-      <c r="N248" t="n">
-        <v>35.3</v>
-      </c>
       <c r="P248" t="n">
         <v>-17.1</v>
       </c>
@@ -36060,9 +35152,6 @@
       <c r="M249" t="n">
         <v>-30.2</v>
       </c>
-      <c r="N249" t="n">
-        <v>-51</v>
-      </c>
       <c r="P249" t="n">
         <v>-33.9</v>
       </c>
@@ -36215,9 +35304,6 @@
       <c r="M250" t="n">
         <v>-24.2</v>
       </c>
-      <c r="N250" t="n">
-        <v>-29.8</v>
-      </c>
       <c r="P250" t="n">
         <v>-32.4</v>
       </c>
@@ -36356,9 +35442,6 @@
       <c r="M251" t="n">
         <v>13.7</v>
       </c>
-      <c r="N251" t="n">
-        <v>-13.5</v>
-      </c>
       <c r="P251" t="n">
         <v>-28.1</v>
       </c>
@@ -36502,9 +35585,6 @@
       <c r="M252" t="n">
         <v>55.8</v>
       </c>
-      <c r="N252" t="n">
-        <v>6.5</v>
-      </c>
       <c r="P252" t="n">
         <v>35.7</v>
       </c>
@@ -36643,9 +35723,6 @@
       <c r="M253" t="n">
         <v>-20.1</v>
       </c>
-      <c r="N253" t="n">
-        <v>-32.1</v>
-      </c>
       <c r="P253" t="n">
         <v>-21.7</v>
       </c>
@@ -36795,9 +35872,6 @@
       <c r="M254" t="n">
         <v>-0.4</v>
       </c>
-      <c r="N254" t="n">
-        <v>9.699999999999999</v>
-      </c>
       <c r="O254" t="inlineStr">
         <is>
           <t>WR20</t>
@@ -36955,9 +36029,6 @@
       <c r="M255" t="n">
         <v>58.8</v>
       </c>
-      <c r="N255" t="n">
-        <v>32.8</v>
-      </c>
       <c r="P255" t="n">
         <v>44.2</v>
       </c>
@@ -37105,9 +36176,6 @@
       <c r="M256" t="n">
         <v>28.6</v>
       </c>
-      <c r="N256" t="n">
-        <v>17.3</v>
-      </c>
       <c r="P256" t="n">
         <v>21.9</v>
       </c>
@@ -37250,9 +36318,6 @@
       <c r="M257" t="n">
         <v>69.59999999999999</v>
       </c>
-      <c r="N257" t="n">
-        <v>34.5</v>
-      </c>
       <c r="P257" t="n">
         <v>31.9</v>
       </c>
@@ -37400,9 +36465,6 @@
       <c r="M258" t="n">
         <v>25.2</v>
       </c>
-      <c r="N258" t="n">
-        <v>-19.9</v>
-      </c>
       <c r="P258" t="n">
         <v>23.7</v>
       </c>
@@ -37471,7 +36533,7 @@
         <v>-24.7</v>
       </c>
       <c r="AL258" t="n">
-        <v>-25.79</v>
+        <v>-25.8</v>
       </c>
       <c r="AM258" t="n">
         <v>10.86</v>
@@ -37550,9 +36612,6 @@
       <c r="M259" t="n">
         <v>-5.5</v>
       </c>
-      <c r="N259" t="n">
-        <v>-23.4</v>
-      </c>
       <c r="O259" t="inlineStr">
         <is>
           <t>WR30</t>
@@ -37710,9 +36769,6 @@
       <c r="M260" t="n">
         <v>15.6</v>
       </c>
-      <c r="N260" t="n">
-        <v>-43.5</v>
-      </c>
       <c r="P260" t="n">
         <v>13.1</v>
       </c>
@@ -37783,7 +36839,7 @@
         <v>-49.16</v>
       </c>
       <c r="AL260" t="n">
-        <v>-49.74</v>
+        <v>-49.75</v>
       </c>
       <c r="AM260" t="n">
         <v>8.56</v>
@@ -37862,9 +36918,6 @@
       <c r="M261" t="n">
         <v>-29.9</v>
       </c>
-      <c r="N261" t="n">
-        <v>-10.5</v>
-      </c>
       <c r="P261" t="n">
         <v>-41.6</v>
       </c>
@@ -38012,9 +37065,6 @@
       <c r="M262" t="n">
         <v>39.4</v>
       </c>
-      <c r="N262" t="n">
-        <v>45.5</v>
-      </c>
       <c r="P262" t="n">
         <v>13.8</v>
       </c>
@@ -38157,9 +37207,6 @@
       <c r="M263" t="n">
         <v>-4.2</v>
       </c>
-      <c r="N263" t="n">
-        <v>-14.5</v>
-      </c>
       <c r="O263" t="inlineStr">
         <is>
           <t>WR30</t>
@@ -38309,9 +37356,6 @@
       <c r="M264" t="n">
         <v>4.1</v>
       </c>
-      <c r="N264" t="n">
-        <v>4.9</v>
-      </c>
       <c r="P264" t="n">
         <v>-6.3</v>
       </c>
@@ -38454,9 +37498,6 @@
       <c r="M265" t="n">
         <v>-21.7</v>
       </c>
-      <c r="N265" t="n">
-        <v>36.4</v>
-      </c>
       <c r="P265" t="n">
         <v>-33.7</v>
       </c>
@@ -38599,9 +37640,6 @@
       <c r="M266" t="n">
         <v>-38.3</v>
       </c>
-      <c r="N266" t="n">
-        <v>6.9</v>
-      </c>
       <c r="P266" t="n">
         <v>-48.2</v>
       </c>
@@ -38749,9 +37787,6 @@
       <c r="M267" t="n">
         <v>-0.4</v>
       </c>
-      <c r="N267" t="n">
-        <v>-20.4</v>
-      </c>
       <c r="P267" t="n">
         <v>-14.2</v>
       </c>
@@ -38904,9 +37939,6 @@
       <c r="M268" t="n">
         <v>-12</v>
       </c>
-      <c r="N268" t="n">
-        <v>-15.1</v>
-      </c>
       <c r="P268" t="n">
         <v>-24.6</v>
       </c>
@@ -39053,9 +38085,6 @@
       <c r="M269" t="n">
         <v>-19.7</v>
       </c>
-      <c r="N269" t="n">
-        <v>-38.9</v>
-      </c>
       <c r="P269" t="n">
         <v>-21.6</v>
       </c>
@@ -39200,9 +38229,6 @@
       <c r="M270" t="n">
         <v>-6.4</v>
       </c>
-      <c r="N270" t="n">
-        <v>23.9</v>
-      </c>
       <c r="P270" t="n">
         <v>-12.3</v>
       </c>
@@ -39345,9 +38371,6 @@
       <c r="M271" t="n">
         <v>4.6</v>
       </c>
-      <c r="N271" t="n">
-        <v>2.8</v>
-      </c>
       <c r="P271" t="n">
         <v>1.5</v>
       </c>
@@ -39495,9 +38518,6 @@
       <c r="M272" t="n">
         <v>-0.2</v>
       </c>
-      <c r="N272" t="n">
-        <v>70.2</v>
-      </c>
       <c r="O272" t="inlineStr">
         <is>
           <t>WR20</t>
@@ -39579,7 +38599,7 @@
         <v>-6.51</v>
       </c>
       <c r="AM272" t="n">
-        <v>87.08</v>
+        <v>87.12</v>
       </c>
       <c r="AN272" t="n">
         <v>68</v>
@@ -39650,9 +38670,6 @@
       <c r="M273" t="n">
         <v>0.9</v>
       </c>
-      <c r="N273" t="n">
-        <v>3.4</v>
-      </c>
       <c r="P273" t="n">
         <v>-29.6</v>
       </c>
@@ -39797,9 +38814,6 @@
       <c r="M274" t="n">
         <v>16.5</v>
       </c>
-      <c r="N274" t="n">
-        <v>-18.9</v>
-      </c>
       <c r="P274" t="n">
         <v>11.6</v>
       </c>
@@ -39944,9 +38958,6 @@
       <c r="M275" t="n">
         <v>-9.6</v>
       </c>
-      <c r="N275" t="n">
-        <v>24.7</v>
-      </c>
       <c r="O275" t="inlineStr">
         <is>
           <t>WR30</t>
@@ -40099,9 +39110,6 @@
       <c r="M276" t="n">
         <v>-11.3</v>
       </c>
-      <c r="N276" t="n">
-        <v>-27.4</v>
-      </c>
       <c r="P276" t="n">
         <v>-25.4</v>
       </c>
@@ -40246,9 +39254,6 @@
       <c r="M277" t="n">
         <v>14.9</v>
       </c>
-      <c r="N277" t="n">
-        <v>-11.1</v>
-      </c>
       <c r="P277" t="n">
         <v>14.1</v>
       </c>
@@ -40396,9 +39401,6 @@
       <c r="M278" t="n">
         <v>-32.8</v>
       </c>
-      <c r="N278" t="n">
-        <v>-26.1</v>
-      </c>
       <c r="P278" t="n">
         <v>-50.4</v>
       </c>
@@ -40548,9 +39550,6 @@
       <c r="M279" t="n">
         <v>-40.3</v>
       </c>
-      <c r="N279" t="n">
-        <v>-42.3</v>
-      </c>
       <c r="P279" t="n">
         <v>-41.9</v>
       </c>
@@ -40703,9 +39702,6 @@
       <c r="M280" t="n">
         <v>-48.5</v>
       </c>
-      <c r="N280" t="n">
-        <v>-51.8</v>
-      </c>
       <c r="P280" t="n">
         <v>-48.8</v>
       </c>
@@ -40858,9 +39854,6 @@
       <c r="M281" t="n">
         <v>-26.7</v>
       </c>
-      <c r="N281" t="n">
-        <v>-38.8</v>
-      </c>
       <c r="P281" t="n">
         <v>-36.4</v>
       </c>
@@ -41004,9 +39997,6 @@
       <c r="M282" t="n">
         <v>-0.5</v>
       </c>
-      <c r="N282" t="n">
-        <v>63.1</v>
-      </c>
       <c r="O282" t="inlineStr">
         <is>
           <t>WR20</t>
@@ -41159,9 +40149,6 @@
       <c r="M283" t="n">
         <v>7.1</v>
       </c>
-      <c r="N283" t="n">
-        <v>56.4</v>
-      </c>
       <c r="P283" t="n">
         <v>-17.9</v>
       </c>
@@ -41309,9 +40296,6 @@
       <c r="M284" t="n">
         <v>7.6</v>
       </c>
-      <c r="N284" t="n">
-        <v>15.5</v>
-      </c>
       <c r="P284" t="n">
         <v>-26.5</v>
       </c>
@@ -41454,9 +40438,6 @@
       <c r="M285" t="n">
         <v>-2.1</v>
       </c>
-      <c r="N285" t="n">
-        <v>13.5</v>
-      </c>
       <c r="O285" t="inlineStr">
         <is>
           <t>WR30</t>
@@ -41609,9 +40590,6 @@
       <c r="M286" t="n">
         <v>-9</v>
       </c>
-      <c r="N286" t="n">
-        <v>-2.4</v>
-      </c>
       <c r="P286" t="n">
         <v>-18</v>
       </c>
@@ -41761,9 +40739,6 @@
       <c r="M287" t="n">
         <v>-42.2</v>
       </c>
-      <c r="N287" t="n">
-        <v>-38.8</v>
-      </c>
       <c r="P287" t="n">
         <v>-46.7</v>
       </c>
@@ -41837,7 +40812,7 @@
         <v>-17.46</v>
       </c>
       <c r="AL287" t="n">
-        <v>-19.88</v>
+        <v>-19.87</v>
       </c>
       <c r="AM287" t="n">
         <v>45.74</v>
@@ -41916,9 +40891,6 @@
       <c r="M288" t="n">
         <v>-3.4</v>
       </c>
-      <c r="N288" t="n">
-        <v>-24</v>
-      </c>
       <c r="P288" t="n">
         <v>-10.1</v>
       </c>
@@ -42071,9 +41043,6 @@
       <c r="M289" t="n">
         <v>2.9</v>
       </c>
-      <c r="N289" t="n">
-        <v>-8.699999999999999</v>
-      </c>
       <c r="P289" t="n">
         <v>-0.1</v>
       </c>
@@ -42226,9 +41195,6 @@
       <c r="M290" t="n">
         <v>-8.800000000000001</v>
       </c>
-      <c r="N290" t="n">
-        <v>-8.199999999999999</v>
-      </c>
       <c r="P290" t="n">
         <v>-10.8</v>
       </c>
@@ -42370,9 +41336,6 @@
       <c r="M291" t="n">
         <v>0.2</v>
       </c>
-      <c r="N291" t="n">
-        <v>-0.2</v>
-      </c>
       <c r="P291" t="n">
         <v>-7.8</v>
       </c>
@@ -42395,9 +41358,6 @@
       </c>
       <c r="W291" t="b">
         <v>0</v>
-      </c>
-      <c r="X291" s="13" t="n">
-        <v>46317</v>
       </c>
       <c r="Y291" s="13" t="n">
         <v>46224</v>
@@ -42515,9 +41475,6 @@
       <c r="M292" t="n">
         <v>21.4</v>
       </c>
-      <c r="N292" t="n">
-        <v>-0.5</v>
-      </c>
       <c r="P292" t="n">
         <v>19.8</v>
       </c>
@@ -42643,28 +41600,25 @@
         <v>2.1</v>
       </c>
       <c r="I293" t="n">
-        <v>21.4</v>
+        <v>22</v>
       </c>
       <c r="J293" t="n">
-        <v>6.91</v>
+        <v>6.37</v>
       </c>
       <c r="K293" t="n">
-        <v>20.57</v>
+        <v>19.96</v>
       </c>
       <c r="L293" t="n">
-        <v>-1.07</v>
+        <v>-1.56</v>
       </c>
       <c r="M293" t="n">
-        <v>13.6</v>
-      </c>
-      <c r="N293" t="n">
-        <v>34.8</v>
+        <v>14.2</v>
       </c>
       <c r="P293" t="n">
         <v>6.5</v>
       </c>
       <c r="Q293" t="n">
-        <v>30.35</v>
+        <v>30.2</v>
       </c>
       <c r="R293" t="inlineStr">
         <is>
@@ -42698,16 +41652,16 @@
         </is>
       </c>
       <c r="AB293" t="n">
-        <v>9.32</v>
+        <v>8.76</v>
       </c>
       <c r="AC293" t="n">
-        <v>20.62</v>
+        <v>20.02</v>
       </c>
       <c r="AD293" t="n">
-        <v>-0.92</v>
+        <v>-1.42</v>
       </c>
       <c r="AE293" t="n">
-        <v>-1.07</v>
+        <v>-1.56</v>
       </c>
       <c r="AF293" t="n">
         <v>34.49</v>
@@ -42728,10 +41682,10 @@
         <v>43.36</v>
       </c>
       <c r="AL293" t="n">
-        <v>-1.07</v>
+        <v>-1.56</v>
       </c>
       <c r="AM293" t="n">
-        <v>46.43</v>
+        <v>45.69</v>
       </c>
       <c r="AN293" t="n">
         <v>68</v>
@@ -42740,7 +41694,7 @@
         <v>66</v>
       </c>
       <c r="AP293" t="n">
-        <v>39.21</v>
+        <v>38.51</v>
       </c>
       <c r="AR293" t="n">
         <v>2.52</v>
@@ -42802,9 +41756,6 @@
       <c r="M294" t="n">
         <v>-8.6</v>
       </c>
-      <c r="N294" t="n">
-        <v>-21.4</v>
-      </c>
       <c r="P294" t="n">
         <v>-12.7</v>
       </c>
@@ -42952,9 +41903,6 @@
       <c r="M295" t="n">
         <v>23.7</v>
       </c>
-      <c r="N295" t="n">
-        <v>-12.7</v>
-      </c>
       <c r="P295" t="n">
         <v>20.2</v>
       </c>
@@ -43099,9 +42047,6 @@
       <c r="M296" t="n">
         <v>-43.3</v>
       </c>
-      <c r="N296" t="n">
-        <v>7.7</v>
-      </c>
       <c r="P296" t="n">
         <v>-55.7</v>
       </c>
@@ -43249,9 +42194,6 @@
       <c r="M297" t="n">
         <v>29.3</v>
       </c>
-      <c r="N297" t="n">
-        <v>-7.9</v>
-      </c>
       <c r="P297" t="n">
         <v>5.2</v>
       </c>
@@ -43395,9 +42337,6 @@
       <c r="M298" t="n">
         <v>-0.9</v>
       </c>
-      <c r="N298" t="n">
-        <v>-8.699999999999999</v>
-      </c>
       <c r="O298" t="inlineStr">
         <is>
           <t>WR20</t>
@@ -43550,9 +42489,6 @@
       <c r="M299" t="n">
         <v>23</v>
       </c>
-      <c r="N299" t="n">
-        <v>-24.8</v>
-      </c>
       <c r="P299" t="n">
         <v>5.7</v>
       </c>
@@ -43691,9 +42627,6 @@
       <c r="M300" t="n">
         <v>12.2</v>
       </c>
-      <c r="N300" t="n">
-        <v>-10.6</v>
-      </c>
       <c r="P300" t="n">
         <v>8.800000000000001</v>
       </c>
@@ -43841,9 +42774,6 @@
       <c r="M301" t="n">
         <v>45.6</v>
       </c>
-      <c r="N301" t="n">
-        <v>11.4</v>
-      </c>
       <c r="P301" t="n">
         <v>25</v>
       </c>
@@ -43987,9 +42917,6 @@
       <c r="M302" t="n">
         <v>-20</v>
       </c>
-      <c r="N302" t="n">
-        <v>-18.5</v>
-      </c>
       <c r="P302" t="n">
         <v>-33</v>
       </c>
@@ -44142,9 +43069,6 @@
       <c r="M303" t="n">
         <v>56.3</v>
       </c>
-      <c r="N303" t="n">
-        <v>46</v>
-      </c>
       <c r="P303" t="n">
         <v>34.3</v>
       </c>
@@ -44297,9 +43221,6 @@
       <c r="M304" t="n">
         <v>-9</v>
       </c>
-      <c r="N304" t="n">
-        <v>26.6</v>
-      </c>
       <c r="O304" t="inlineStr">
         <is>
           <t>WR20</t>
@@ -44452,9 +43373,6 @@
       <c r="M305" t="n">
         <v>-25.3</v>
       </c>
-      <c r="N305" t="n">
-        <v>43.4</v>
-      </c>
       <c r="P305" t="n">
         <v>-43.3</v>
       </c>
@@ -44531,7 +43449,7 @@
         <v>-5.49</v>
       </c>
       <c r="AM305" t="n">
-        <v>63.66</v>
+        <v>63.71</v>
       </c>
       <c r="AN305" t="n">
         <v>68</v>
@@ -44601,9 +43519,6 @@
       </c>
       <c r="M306" t="n">
         <v>-4.1</v>
-      </c>
-      <c r="N306" t="n">
-        <v>-17.9</v>
       </c>
       <c r="O306" t="inlineStr">
         <is>
@@ -44752,7 +43667,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>298 (+7 pending)</t>
+          <t>298 (+0 pending)</t>
         </is>
       </c>
     </row>
@@ -44776,7 +43691,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>$48,992.72  (-2.74% price-weighted)</t>
+          <t>$48,992.73  (-2.74% price-weighted)</t>
         </is>
       </c>
     </row>
@@ -44894,13 +43809,13 @@
         <v>0.98</v>
       </c>
       <c r="E12" t="n">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="F12" t="n">
         <v>52.36</v>
       </c>
       <c r="G12" t="n">
-        <v>-14.03</v>
+        <v>-14.04</v>
       </c>
     </row>
     <row r="13">
@@ -44925,7 +43840,7 @@
         <v>31.58</v>
       </c>
       <c r="G13" t="n">
-        <v>-21.37</v>
+        <v>-21.39</v>
       </c>
     </row>
     <row r="14">
@@ -45035,10 +43950,10 @@
         <v>-1.9</v>
       </c>
       <c r="F18" t="n">
-        <v>3.4</v>
+        <v>3.36</v>
       </c>
       <c r="G18" t="n">
-        <v>-13.61</v>
+        <v>-13.63</v>
       </c>
     </row>
     <row r="19">
@@ -45088,7 +44003,7 @@
         <v>3.83</v>
       </c>
       <c r="G20" t="n">
-        <v>-16.37</v>
+        <v>-16.39</v>
       </c>
     </row>
     <row r="21">
@@ -45193,19 +44108,19 @@
         <v>34</v>
       </c>
       <c r="C26" t="n">
-        <v>1.58</v>
+        <v>1.56</v>
       </c>
       <c r="D26" t="n">
         <v>59</v>
       </c>
       <c r="E26" t="n">
-        <v>4.03</v>
+        <v>4.01</v>
       </c>
       <c r="F26" t="n">
         <v>59</v>
       </c>
       <c r="G26" t="n">
-        <v>-8.66</v>
+        <v>-8.67</v>
       </c>
     </row>
     <row r="27">
@@ -45952,22 +44867,22 @@
         <v>0.86</v>
       </c>
       <c r="H5" t="n">
-        <v>-14.96</v>
+        <v>-14.99</v>
       </c>
       <c r="I5" t="n">
-        <v>-49.74</v>
+        <v>-49.75</v>
       </c>
       <c r="J5" t="n">
         <v>34.5</v>
       </c>
       <c r="K5" t="n">
-        <v>21.02</v>
+        <v>21.01</v>
       </c>
       <c r="L5" t="n">
         <v>26</v>
       </c>
       <c r="M5" t="n">
-        <v>8.24</v>
+        <v>8.210000000000001</v>
       </c>
     </row>
     <row r="6">
@@ -45995,7 +44910,7 @@
         <v>-10.21</v>
       </c>
       <c r="H6" t="n">
-        <v>-20.34</v>
+        <v>-20.36</v>
       </c>
       <c r="I6" t="n">
         <v>-63.91</v>
@@ -46004,7 +44919,7 @@
         <v>47</v>
       </c>
       <c r="K6" t="n">
-        <v>19.63</v>
+        <v>19.64</v>
       </c>
       <c r="L6" t="n">
         <v>59</v>
@@ -46038,7 +44953,7 @@
         <v>-2.47</v>
       </c>
       <c r="H7" t="n">
-        <v>-16.73</v>
+        <v>-16.74</v>
       </c>
       <c r="I7" t="n">
         <v>-63.91</v>
@@ -46053,7 +44968,7 @@
         <v>132</v>
       </c>
       <c r="M7" t="n">
-        <v>3.62</v>
+        <v>3.61</v>
       </c>
     </row>
     <row r="8"/>
@@ -46067,7 +44982,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Avg drawdown (MAE%, less-negative is better): PASS -13.3 vs FAIL -20.34  -&gt;  PASS better</t>
+          <t>Avg drawdown (MAE%, less-negative is better): PASS -13.3 vs FAIL -20.36  -&gt;  PASS better</t>
         </is>
       </c>
     </row>
@@ -48370,29 +47285,45 @@
           <t>DECLINING</t>
         </is>
       </c>
-      <c r="E31" t="n">
-        <v>78.7</v>
-      </c>
-      <c r="F31" t="n">
-        <v>0.309</v>
-      </c>
-      <c r="G31" t="n">
-        <v>7</v>
-      </c>
-      <c r="H31" t="n">
-        <v>15.96</v>
-      </c>
-      <c r="I31" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="J31" t="n">
-        <v>26</v>
-      </c>
-      <c r="K31" t="n">
-        <v>0.14</v>
-      </c>
-      <c r="L31" t="n">
-        <v>22.4</v>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>78.7</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>0.309</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>15.96</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>2.3</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>26.0</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>0.14</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>22.4</t>
+        </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
@@ -63953,8 +62884,10 @@
           <t>DECLINING</t>
         </is>
       </c>
-      <c r="L8" t="n">
-        <v>78.7</v>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>78.7</t>
+        </is>
       </c>
     </row>
     <row r="9">

--- a/STS_holy_grail.xlsx
+++ b/STS_holy_grail.xlsx
@@ -1280,7 +1280,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Active</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -1294,15 +1294,27 @@
       <c r="H4" t="n">
         <v>-9.800000000000001</v>
       </c>
+      <c r="I4" t="n">
+        <v>-13.6</v>
+      </c>
+      <c r="L4" t="n">
+        <v>-2.32</v>
+      </c>
       <c r="M4" t="n">
-        <v>2.3</v>
+        <v>2.8</v>
+      </c>
+      <c r="N4" t="n">
+        <v>1.8</v>
       </c>
       <c r="P4" t="n">
-        <v>2.3</v>
+        <v>1.8</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>252.5</v>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -1310,8 +1322,65 @@
           <t>RE-QUAL D200G 2026-10-22</t>
         </is>
       </c>
+      <c r="T4" s="13" t="n">
+        <v>46239</v>
+      </c>
+      <c r="U4" t="n">
+        <v>-11.96</v>
+      </c>
+      <c r="V4" t="n">
+        <v>56</v>
+      </c>
+      <c r="W4" t="b">
+        <v>0</v>
+      </c>
+      <c r="X4" s="13" t="n">
+        <v>46329</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>259.53</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>259.53</v>
+      </c>
       <c r="AI4" t="n">
-        <v>257.8200073242188</v>
+        <v>257.16</v>
+      </c>
+      <c r="AJ4" t="n">
+        <v>257.16</v>
+      </c>
+      <c r="AK4" t="n">
+        <v>-0.91</v>
+      </c>
+      <c r="AL4" t="n">
+        <v>-2.32</v>
+      </c>
+      <c r="AM4" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR4" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="AT4" t="n">
+        <v>-0.92</v>
       </c>
     </row>
     <row r="5">
@@ -2241,7 +2310,7 @@
         <v>-5.8</v>
       </c>
       <c r="I12" t="n">
-        <v>-14.5</v>
+        <v>-15.7</v>
       </c>
       <c r="L12" t="n">
         <v>-7.43</v>
@@ -2250,7 +2319,7 @@
         <v>0</v>
       </c>
       <c r="N12" t="n">
-        <v>-6.9</v>
+        <v>-7</v>
       </c>
       <c r="P12" t="n">
         <v>-1.6</v>
@@ -2302,13 +2371,13 @@
         <v>225.01</v>
       </c>
       <c r="AI12" t="n">
-        <v>210.1</v>
+        <v>210.33</v>
       </c>
       <c r="AJ12" t="n">
-        <v>210.1</v>
+        <v>210.33</v>
       </c>
       <c r="AK12" t="n">
-        <v>-6.63</v>
+        <v>-6.53</v>
       </c>
       <c r="AL12" t="n">
         <v>-7.43</v>
@@ -2317,16 +2386,16 @@
         <v>1.75</v>
       </c>
       <c r="AN12" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AO12" t="n">
         <v>0</v>
       </c>
       <c r="AR12" t="n">
-        <v>-0.93</v>
+        <v>-1.45</v>
       </c>
       <c r="AT12" t="n">
-        <v>-5.69</v>
+        <v>-5.07</v>
       </c>
     </row>
     <row r="13">
@@ -3412,7 +3481,7 @@
         <v>-8.800000000000001</v>
       </c>
       <c r="I21" t="n">
-        <v>-5.1</v>
+        <v>-5.4</v>
       </c>
       <c r="L21" t="n">
         <v>-1.66</v>
@@ -3421,7 +3490,7 @@
         <v>-8.4</v>
       </c>
       <c r="N21" t="n">
-        <v>0.1</v>
+        <v>-1.3</v>
       </c>
       <c r="P21" t="n">
         <v>-13.4</v>
@@ -3458,7 +3527,7 @@
         <v>46310</v>
       </c>
       <c r="Z21" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AB21" t="n">
         <v>9.470000000000001</v>
@@ -3479,13 +3548,13 @@
         <v>13.84</v>
       </c>
       <c r="AI21" t="n">
-        <v>15.07</v>
+        <v>14.86</v>
       </c>
       <c r="AJ21" t="n">
-        <v>15.07</v>
+        <v>14.86</v>
       </c>
       <c r="AK21" t="n">
-        <v>8.890000000000001</v>
+        <v>7.37</v>
       </c>
       <c r="AL21" t="n">
         <v>-1.66</v>
@@ -3494,16 +3563,16 @@
         <v>9.470000000000001</v>
       </c>
       <c r="AN21" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AO21" t="n">
         <v>6</v>
       </c>
       <c r="AR21" t="n">
-        <v>-1.41</v>
+        <v>-1.93</v>
       </c>
       <c r="AT21" t="n">
-        <v>10.3</v>
+        <v>9.300000000000001</v>
       </c>
     </row>
     <row r="22">
@@ -4760,7 +4829,7 @@
         <v>14.7</v>
       </c>
       <c r="I31" t="n">
-        <v>45.6</v>
+        <v>36</v>
       </c>
       <c r="J31" t="n">
         <v>22.36</v>
@@ -4772,7 +4841,7 @@
         <v>2.2</v>
       </c>
       <c r="N31" t="n">
-        <v>37</v>
+        <v>32.1</v>
       </c>
       <c r="P31" t="n">
         <v>-16.6</v>
@@ -4809,7 +4878,7 @@
         <v>46303</v>
       </c>
       <c r="Z31" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AB31" t="n">
         <v>24.68</v>
@@ -4833,13 +4902,13 @@
         <v>195.43</v>
       </c>
       <c r="AI31" t="n">
-        <v>258.74</v>
+        <v>249.37</v>
       </c>
       <c r="AJ31" t="n">
-        <v>258.74</v>
+        <v>249.37</v>
       </c>
       <c r="AK31" t="n">
-        <v>32.4</v>
+        <v>27.6</v>
       </c>
       <c r="AL31" t="n">
         <v>-2.24</v>
@@ -4848,16 +4917,16 @@
         <v>32.73</v>
       </c>
       <c r="AN31" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AO31" t="n">
         <v>12</v>
       </c>
       <c r="AR31" t="n">
-        <v>-1.82</v>
+        <v>-2.34</v>
       </c>
       <c r="AT31" t="n">
-        <v>34.22</v>
+        <v>29.94</v>
       </c>
     </row>
     <row r="32">
@@ -5564,7 +5633,7 @@
         <v>2.8</v>
       </c>
       <c r="I37" t="n">
-        <v>4.3</v>
+        <v>9.9</v>
       </c>
       <c r="J37" t="n">
         <v>2.42</v>
@@ -5576,7 +5645,7 @@
         <v>-8.800000000000001</v>
       </c>
       <c r="N37" t="n">
-        <v>-2.4</v>
+        <v>-2.1</v>
       </c>
       <c r="O37" t="inlineStr">
         <is>
@@ -5618,7 +5687,7 @@
         <v>46295</v>
       </c>
       <c r="Z37" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AB37" t="n">
         <v>6.86</v>
@@ -5639,13 +5708,13 @@
         <v>17.36</v>
       </c>
       <c r="AI37" t="n">
-        <v>17.89</v>
+        <v>17.91</v>
       </c>
       <c r="AJ37" t="n">
-        <v>17.89</v>
+        <v>17.91</v>
       </c>
       <c r="AK37" t="n">
-        <v>3.05</v>
+        <v>3.17</v>
       </c>
       <c r="AL37" t="n">
         <v>-1.61</v>
@@ -5654,16 +5723,16 @@
         <v>6.86</v>
       </c>
       <c r="AN37" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AO37" t="n">
         <v>1</v>
       </c>
       <c r="AR37" t="n">
-        <v>-0.37</v>
+        <v>-0.89</v>
       </c>
       <c r="AT37" t="n">
-        <v>3.43</v>
+        <v>4.06</v>
       </c>
     </row>
     <row r="38">
@@ -6830,7 +6899,7 @@
         <v>-0.9</v>
       </c>
       <c r="I46" t="n">
-        <v>-13.2</v>
+        <v>-12.5</v>
       </c>
       <c r="J46" t="n">
         <v>-3.75</v>
@@ -6845,7 +6914,7 @@
         <v>-12.9</v>
       </c>
       <c r="N46" t="n">
-        <v>-20</v>
+        <v>-21.6</v>
       </c>
       <c r="P46" t="n">
         <v>-19.3</v>
@@ -6897,31 +6966,36 @@
         <v>115.12</v>
       </c>
       <c r="AI46" t="n">
-        <v>101.82</v>
+        <v>99.64</v>
       </c>
       <c r="AJ46" t="n">
-        <v>101.82</v>
+        <v>99.64</v>
       </c>
       <c r="AK46" t="n">
-        <v>-11.55</v>
+        <v>-13.45</v>
       </c>
       <c r="AL46" t="n">
-        <v>-12.52</v>
+        <v>-13.6</v>
       </c>
       <c r="AM46" t="n">
         <v>4.59</v>
       </c>
       <c r="AN46" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AO46" t="n">
         <v>1</v>
       </c>
       <c r="AR46" t="n">
-        <v>-0.3</v>
+        <v>-0.82</v>
       </c>
       <c r="AT46" t="n">
-        <v>-11.25</v>
+        <v>-12.63</v>
+      </c>
+      <c r="AU46" t="inlineStr">
+        <is>
+          <t>dipping</t>
+        </is>
       </c>
     </row>
     <row r="47">
@@ -6960,7 +7034,7 @@
         <v>20.7</v>
       </c>
       <c r="I47" t="n">
-        <v>-4.7</v>
+        <v>-4.9</v>
       </c>
       <c r="J47" t="n">
         <v>-1.49</v>
@@ -6975,7 +7049,7 @@
         <v>17.3</v>
       </c>
       <c r="N47" t="n">
-        <v>20.5</v>
+        <v>17.8</v>
       </c>
       <c r="P47" t="n">
         <v>11.4</v>
@@ -7012,7 +7086,7 @@
         <v>46311</v>
       </c>
       <c r="Z47" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AA47" t="inlineStr">
         <is>
@@ -7038,13 +7112,13 @@
         <v>166.56</v>
       </c>
       <c r="AI47" t="n">
-        <v>175.76</v>
+        <v>172.01</v>
       </c>
       <c r="AJ47" t="n">
-        <v>175.76</v>
+        <v>172.01</v>
       </c>
       <c r="AK47" t="n">
-        <v>5.52</v>
+        <v>3.27</v>
       </c>
       <c r="AL47" t="n">
         <v>-10.54</v>
@@ -7053,16 +7127,16 @@
         <v>7.55</v>
       </c>
       <c r="AN47" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AO47" t="n">
         <v>21</v>
       </c>
       <c r="AR47" t="n">
-        <v>-0.3</v>
+        <v>-0.82</v>
       </c>
       <c r="AT47" t="n">
-        <v>5.82</v>
+        <v>4.09</v>
       </c>
     </row>
     <row r="48">
@@ -7657,7 +7731,7 @@
         <v>31.3</v>
       </c>
       <c r="I52" t="n">
-        <v>25.9</v>
+        <v>22.5</v>
       </c>
       <c r="J52" t="n">
         <v>1.47</v>
@@ -7672,7 +7746,7 @@
         <v>3.5</v>
       </c>
       <c r="N52" t="n">
-        <v>19.3</v>
+        <v>23.6</v>
       </c>
       <c r="P52" t="n">
         <v>-30.3</v>
@@ -7709,7 +7783,7 @@
         <v>46301</v>
       </c>
       <c r="Z52" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AA52" t="inlineStr">
         <is>
@@ -7738,13 +7812,13 @@
         <v>10.85</v>
       </c>
       <c r="AI52" t="n">
-        <v>12.03</v>
+        <v>12.46</v>
       </c>
       <c r="AJ52" t="n">
-        <v>12.03</v>
+        <v>12.46</v>
       </c>
       <c r="AK52" t="n">
-        <v>10.88</v>
+        <v>14.84</v>
       </c>
       <c r="AL52" t="n">
         <v>-5.99</v>
@@ -7753,16 +7827,16 @@
         <v>18.71</v>
       </c>
       <c r="AN52" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AO52" t="n">
         <v>16</v>
       </c>
       <c r="AR52" t="n">
-        <v>0.35</v>
+        <v>-0.18</v>
       </c>
       <c r="AT52" t="n">
-        <v>10.53</v>
+        <v>15.01</v>
       </c>
     </row>
     <row r="53">
@@ -8498,7 +8572,7 @@
         <v>4.6</v>
       </c>
       <c r="I58" t="n">
-        <v>1.9</v>
+        <v>-4.9</v>
       </c>
       <c r="J58" t="n">
         <v>-3.41</v>
@@ -8513,7 +8587,7 @@
         <v>-10.3</v>
       </c>
       <c r="N58" t="n">
-        <v>8.6</v>
+        <v>7.5</v>
       </c>
       <c r="P58" t="n">
         <v>-19.9</v>
@@ -8550,7 +8624,7 @@
         <v>46301</v>
       </c>
       <c r="Z58" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AA58" t="inlineStr">
         <is>
@@ -8579,13 +8653,13 @@
         <v>218.76</v>
       </c>
       <c r="AI58" t="n">
-        <v>254.95</v>
+        <v>252.2</v>
       </c>
       <c r="AJ58" t="n">
-        <v>254.95</v>
+        <v>252.2</v>
       </c>
       <c r="AK58" t="n">
-        <v>16.54</v>
+        <v>15.29</v>
       </c>
       <c r="AL58" t="n">
         <v>-8.949999999999999</v>
@@ -8594,16 +8668,16 @@
         <v>17.1</v>
       </c>
       <c r="AN58" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AO58" t="n">
         <v>25</v>
       </c>
       <c r="AR58" t="n">
-        <v>0.35</v>
+        <v>-0.17</v>
       </c>
       <c r="AT58" t="n">
-        <v>16.19</v>
+        <v>15.46</v>
       </c>
     </row>
     <row r="59">
@@ -8777,7 +8851,7 @@
         <v>10.5</v>
       </c>
       <c r="I60" t="n">
-        <v>0.8</v>
+        <v>-6.9</v>
       </c>
       <c r="J60" t="n">
         <v>-3.62</v>
@@ -8792,7 +8866,7 @@
         <v>-5.7</v>
       </c>
       <c r="N60" t="n">
-        <v>7.1</v>
+        <v>4.6</v>
       </c>
       <c r="O60" t="inlineStr">
         <is>
@@ -8834,7 +8908,7 @@
         <v>46317</v>
       </c>
       <c r="Z60" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA60" t="inlineStr">
         <is>
@@ -8860,13 +8934,13 @@
         <v>250.35</v>
       </c>
       <c r="AI60" t="n">
-        <v>270.55</v>
+        <v>263.82</v>
       </c>
       <c r="AJ60" t="n">
-        <v>270.55</v>
+        <v>263.82</v>
       </c>
       <c r="AK60" t="n">
-        <v>8.07</v>
+        <v>5.38</v>
       </c>
       <c r="AL60" t="n">
         <v>-10.26</v>
@@ -8875,16 +8949,16 @@
         <v>8.69</v>
       </c>
       <c r="AN60" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AO60" t="n">
         <v>25</v>
       </c>
       <c r="AR60" t="n">
-        <v>0.35</v>
+        <v>-0.17</v>
       </c>
       <c r="AT60" t="n">
-        <v>7.71</v>
+        <v>5.55</v>
       </c>
     </row>
     <row r="61">
@@ -10089,7 +10163,7 @@
         <v>35.1</v>
       </c>
       <c r="I69" t="n">
-        <v>45.6</v>
+        <v>36</v>
       </c>
       <c r="J69" t="n">
         <v>-7.78</v>
@@ -10104,7 +10178,7 @@
         <v>-3.1</v>
       </c>
       <c r="N69" t="n">
-        <v>37</v>
+        <v>32.1</v>
       </c>
       <c r="O69" t="inlineStr">
         <is>
@@ -10146,7 +10220,7 @@
         <v>46296</v>
       </c>
       <c r="Z69" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AA69" t="inlineStr">
         <is>
@@ -10175,13 +10249,13 @@
         <v>190.53</v>
       </c>
       <c r="AI69" t="n">
-        <v>258.74</v>
+        <v>249.37</v>
       </c>
       <c r="AJ69" t="n">
-        <v>258.74</v>
+        <v>249.37</v>
       </c>
       <c r="AK69" t="n">
-        <v>35.8</v>
+        <v>30.88</v>
       </c>
       <c r="AL69" t="n">
         <v>-10.39</v>
@@ -10190,16 +10264,16 @@
         <v>36.14</v>
       </c>
       <c r="AN69" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AO69" t="n">
         <v>27</v>
       </c>
       <c r="AR69" t="n">
-        <v>0.75</v>
+        <v>0.23</v>
       </c>
       <c r="AT69" t="n">
-        <v>35.05</v>
+        <v>30.65</v>
       </c>
     </row>
     <row r="70">
@@ -10810,7 +10884,7 @@
         <v>16.3</v>
       </c>
       <c r="N74" t="n">
-        <v>-18.8</v>
+        <v>-19.3</v>
       </c>
       <c r="P74" t="n">
         <v>13.8</v>
@@ -10862,13 +10936,13 @@
         <v>83.75</v>
       </c>
       <c r="AI74" t="n">
-        <v>58.36</v>
+        <v>58.02</v>
       </c>
       <c r="AJ74" t="n">
-        <v>58.36</v>
+        <v>58.02</v>
       </c>
       <c r="AK74" t="n">
-        <v>-30.32</v>
+        <v>-30.72</v>
       </c>
       <c r="AL74" t="n">
         <v>-33.34</v>
@@ -10877,16 +10951,16 @@
         <v>2.66</v>
       </c>
       <c r="AN74" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="AO74" t="n">
         <v>0</v>
       </c>
       <c r="AR74" t="n">
-        <v>0.15</v>
+        <v>-0.37</v>
       </c>
       <c r="AT74" t="n">
-        <v>-30.47</v>
+        <v>-30.35</v>
       </c>
       <c r="AU74" t="inlineStr">
         <is>
@@ -10930,7 +11004,7 @@
         <v>11.1</v>
       </c>
       <c r="I75" t="n">
-        <v>-10.1</v>
+        <v>-11.5</v>
       </c>
       <c r="J75" t="n">
         <v>-8.85</v>
@@ -10945,7 +11019,7 @@
         <v>1.4</v>
       </c>
       <c r="N75" t="n">
-        <v>-0.2</v>
+        <v>-1.3</v>
       </c>
       <c r="P75" t="n">
         <v>-9.800000000000001</v>
@@ -10997,13 +11071,13 @@
         <v>131.78</v>
       </c>
       <c r="AI75" t="n">
-        <v>123.7</v>
+        <v>122.08</v>
       </c>
       <c r="AJ75" t="n">
-        <v>123.7</v>
+        <v>122.08</v>
       </c>
       <c r="AK75" t="n">
-        <v>-6.13</v>
+        <v>-7.36</v>
       </c>
       <c r="AL75" t="n">
         <v>-16.3</v>
@@ -11012,16 +11086,16 @@
         <v>0.74</v>
       </c>
       <c r="AN75" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="AO75" t="n">
         <v>1</v>
       </c>
       <c r="AR75" t="n">
-        <v>1.03</v>
+        <v>0.5</v>
       </c>
       <c r="AT75" t="n">
-        <v>-7.16</v>
+        <v>-7.86</v>
       </c>
       <c r="AU75" t="inlineStr">
         <is>
@@ -11065,7 +11139,7 @@
         <v>-19.9</v>
       </c>
       <c r="I76" t="n">
-        <v>-3.5</v>
+        <v>-7.7</v>
       </c>
       <c r="J76" t="n">
         <v>7.04</v>
@@ -11080,7 +11154,7 @@
         <v>0.4</v>
       </c>
       <c r="N76" t="n">
-        <v>8.5</v>
+        <v>5.2</v>
       </c>
       <c r="P76" t="n">
         <v>2.1</v>
@@ -11117,7 +11191,7 @@
         <v>46276</v>
       </c>
       <c r="Z76" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AA76" t="inlineStr">
         <is>
@@ -11146,13 +11220,13 @@
         <v>66.86</v>
       </c>
       <c r="AI76" t="n">
-        <v>72.40000000000001</v>
+        <v>70.08</v>
       </c>
       <c r="AJ76" t="n">
-        <v>72.40000000000001</v>
+        <v>70.08</v>
       </c>
       <c r="AK76" t="n">
-        <v>8.289999999999999</v>
+        <v>4.82</v>
       </c>
       <c r="AL76" t="n">
         <v>-1.24</v>
@@ -11161,16 +11235,16 @@
         <v>21.85</v>
       </c>
       <c r="AN76" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="AO76" t="n">
         <v>22</v>
       </c>
       <c r="AR76" t="n">
-        <v>1.03</v>
+        <v>0.5</v>
       </c>
       <c r="AT76" t="n">
-        <v>7.25</v>
+        <v>4.31</v>
       </c>
     </row>
     <row r="77">
@@ -11209,7 +11283,7 @@
         <v>-9.1</v>
       </c>
       <c r="I77" t="n">
-        <v>-14.7</v>
+        <v>-17.7</v>
       </c>
       <c r="J77" t="n">
         <v>-5.75</v>
@@ -11224,7 +11298,7 @@
         <v>-30.4</v>
       </c>
       <c r="N77" t="n">
-        <v>-36.6</v>
+        <v>-36.3</v>
       </c>
       <c r="P77" t="n">
         <v>-33.7</v>
@@ -11276,13 +11350,13 @@
         <v>15.93</v>
       </c>
       <c r="AI77" t="n">
-        <v>13.47</v>
+        <v>13.48</v>
       </c>
       <c r="AJ77" t="n">
-        <v>13.47</v>
+        <v>13.48</v>
       </c>
       <c r="AK77" t="n">
-        <v>-15.42</v>
+        <v>-15.35</v>
       </c>
       <c r="AL77" t="n">
         <v>-17.24</v>
@@ -11291,16 +11365,16 @@
         <v>0.85</v>
       </c>
       <c r="AN77" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="AO77" t="n">
         <v>0</v>
       </c>
       <c r="AR77" t="n">
-        <v>0.23</v>
+        <v>-0.29</v>
       </c>
       <c r="AT77" t="n">
-        <v>-15.65</v>
+        <v>-15.06</v>
       </c>
       <c r="AU77" t="inlineStr">
         <is>
@@ -11629,7 +11703,7 @@
         <v>9.699999999999999</v>
       </c>
       <c r="I80" t="n">
-        <v>-15.2</v>
+        <v>-16</v>
       </c>
       <c r="J80" t="n">
         <v>-10.83</v>
@@ -11644,7 +11718,7 @@
         <v>4.1</v>
       </c>
       <c r="N80" t="n">
-        <v>-4</v>
+        <v>-4.5</v>
       </c>
       <c r="P80" t="n">
         <v>-6.5</v>
@@ -11696,13 +11770,13 @@
         <v>133.75</v>
       </c>
       <c r="AI80" t="n">
-        <v>118.75</v>
+        <v>117.97</v>
       </c>
       <c r="AJ80" t="n">
-        <v>118.75</v>
+        <v>117.97</v>
       </c>
       <c r="AK80" t="n">
-        <v>-11.21</v>
+        <v>-11.8</v>
       </c>
       <c r="AL80" t="n">
         <v>-21.17</v>
@@ -11711,16 +11785,16 @@
         <v>0.08</v>
       </c>
       <c r="AN80" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="AO80" t="n">
         <v>0</v>
       </c>
       <c r="AR80" t="n">
-        <v>0.23</v>
+        <v>-0.29</v>
       </c>
       <c r="AT80" t="n">
-        <v>-11.45</v>
+        <v>-11.51</v>
       </c>
       <c r="AU80" t="inlineStr">
         <is>
@@ -12359,7 +12433,7 @@
         <v>1.3</v>
       </c>
       <c r="I85" t="n">
-        <v>-2.6</v>
+        <v>-0.3</v>
       </c>
       <c r="J85" t="n">
         <v>-6.82</v>
@@ -12374,7 +12448,7 @@
         <v>-29.7</v>
       </c>
       <c r="N85" t="n">
-        <v>-20.8</v>
+        <v>-21</v>
       </c>
       <c r="P85" t="n">
         <v>-44.3</v>
@@ -12426,13 +12500,13 @@
         <v>46.92</v>
       </c>
       <c r="AI85" t="n">
-        <v>46.01</v>
+        <v>45.69</v>
       </c>
       <c r="AJ85" t="n">
-        <v>46.01</v>
+        <v>45.69</v>
       </c>
       <c r="AK85" t="n">
-        <v>-1.94</v>
+        <v>-2.62</v>
       </c>
       <c r="AL85" t="n">
         <v>-11.79</v>
@@ -12441,16 +12515,16 @@
         <v>2.43</v>
       </c>
       <c r="AN85" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="AO85" t="n">
         <v>0</v>
       </c>
       <c r="AR85" t="n">
-        <v>-0.8</v>
+        <v>-1.32</v>
       </c>
       <c r="AT85" t="n">
-        <v>-1.14</v>
+        <v>-1.31</v>
       </c>
     </row>
     <row r="86">
@@ -12788,7 +12862,7 @@
         <v>9.800000000000001</v>
       </c>
       <c r="N88" t="n">
-        <v>-14.8</v>
+        <v>-14.5</v>
       </c>
       <c r="P88" t="n">
         <v>8.5</v>
@@ -12825,7 +12899,7 @@
         <v>46273</v>
       </c>
       <c r="Z88" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="AA88" t="inlineStr">
         <is>
@@ -12854,31 +12928,31 @@
         <v>443.5</v>
       </c>
       <c r="AI88" t="n">
-        <v>375.58</v>
+        <v>377.24</v>
       </c>
       <c r="AJ88" t="n">
-        <v>375.58</v>
+        <v>377.24</v>
       </c>
       <c r="AK88" t="n">
-        <v>-15.31</v>
+        <v>-14.94</v>
       </c>
       <c r="AL88" t="n">
-        <v>-15.41</v>
+        <v>-15.94</v>
       </c>
       <c r="AM88" t="n">
         <v>23.39</v>
       </c>
       <c r="AN88" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="AO88" t="n">
         <v>21</v>
       </c>
       <c r="AR88" t="n">
-        <v>0.45</v>
+        <v>-0.08</v>
       </c>
       <c r="AT88" t="n">
-        <v>-15.76</v>
+        <v>-14.86</v>
       </c>
       <c r="AU88" t="inlineStr">
         <is>
@@ -13345,7 +13419,7 @@
         <v>-17.1</v>
       </c>
       <c r="I92" t="n">
-        <v>-14.5</v>
+        <v>-18.5</v>
       </c>
       <c r="J92" t="n">
         <v>-7.68</v>
@@ -13360,7 +13434,7 @@
         <v>-20.5</v>
       </c>
       <c r="N92" t="n">
-        <v>-33.1</v>
+        <v>-33.6</v>
       </c>
       <c r="P92" t="n">
         <v>-27.1</v>
@@ -13412,13 +13486,13 @@
         <v>97.91</v>
       </c>
       <c r="AI92" t="n">
-        <v>77.98</v>
+        <v>77.2</v>
       </c>
       <c r="AJ92" t="n">
-        <v>77.98</v>
+        <v>77.2</v>
       </c>
       <c r="AK92" t="n">
-        <v>-20.36</v>
+        <v>-21.15</v>
       </c>
       <c r="AL92" t="n">
         <v>-21.63</v>
@@ -13427,16 +13501,16 @@
         <v>1.77</v>
       </c>
       <c r="AN92" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="AO92" t="n">
         <v>4</v>
       </c>
       <c r="AR92" t="n">
-        <v>-0.19</v>
+        <v>-0.71</v>
       </c>
       <c r="AT92" t="n">
-        <v>-20.16</v>
+        <v>-20.44</v>
       </c>
       <c r="AU92" t="inlineStr">
         <is>
@@ -13778,7 +13852,7 @@
         <v>5.8</v>
       </c>
       <c r="I95" t="n">
-        <v>25.9</v>
+        <v>22.5</v>
       </c>
       <c r="J95" t="n">
         <v>8.66</v>
@@ -13793,7 +13867,7 @@
         <v>-4.1</v>
       </c>
       <c r="N95" t="n">
-        <v>19.3</v>
+        <v>23.6</v>
       </c>
       <c r="O95" t="inlineStr">
         <is>
@@ -13835,7 +13909,7 @@
         <v>46262</v>
       </c>
       <c r="Z95" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="AA95" t="inlineStr">
         <is>
@@ -13864,13 +13938,13 @@
         <v>10.28</v>
       </c>
       <c r="AI95" t="n">
-        <v>12.03</v>
+        <v>12.46</v>
       </c>
       <c r="AJ95" t="n">
-        <v>12.03</v>
+        <v>12.46</v>
       </c>
       <c r="AK95" t="n">
-        <v>17.02</v>
+        <v>21.21</v>
       </c>
       <c r="AL95" t="n">
         <v>-2.14</v>
@@ -13879,16 +13953,16 @@
         <v>25.29</v>
       </c>
       <c r="AN95" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="AO95" t="n">
         <v>30</v>
       </c>
       <c r="AR95" t="n">
-        <v>-0.76</v>
+        <v>-1.28</v>
       </c>
       <c r="AT95" t="n">
-        <v>17.79</v>
+        <v>22.49</v>
       </c>
     </row>
     <row r="96">
@@ -13927,7 +14001,7 @@
         <v>-4.2</v>
       </c>
       <c r="I96" t="n">
-        <v>-7.1</v>
+        <v>-11.4</v>
       </c>
       <c r="J96" t="n">
         <v>-7.73</v>
@@ -13942,7 +14016,7 @@
         <v>1.4</v>
       </c>
       <c r="N96" t="n">
-        <v>-11.9</v>
+        <v>-12.3</v>
       </c>
       <c r="P96" t="n">
         <v>-3.5</v>
@@ -13994,31 +14068,31 @@
         <v>372.92</v>
       </c>
       <c r="AI96" t="n">
-        <v>323.24</v>
+        <v>321.68</v>
       </c>
       <c r="AJ96" t="n">
-        <v>323.24</v>
+        <v>321.68</v>
       </c>
       <c r="AK96" t="n">
-        <v>-13.32</v>
+        <v>-13.74</v>
       </c>
       <c r="AL96" t="n">
-        <v>-13.92</v>
+        <v>-14.13</v>
       </c>
       <c r="AM96" t="n">
         <v>2.12</v>
       </c>
       <c r="AN96" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="AO96" t="n">
         <v>26</v>
       </c>
       <c r="AR96" t="n">
-        <v>-0.76</v>
+        <v>-1.28</v>
       </c>
       <c r="AT96" t="n">
-        <v>-12.56</v>
+        <v>-12.46</v>
       </c>
       <c r="AU96" t="inlineStr">
         <is>
@@ -15782,7 +15856,7 @@
         <v>44.3</v>
       </c>
       <c r="I109" t="n">
-        <v>45.6</v>
+        <v>36</v>
       </c>
       <c r="J109" t="n">
         <v>-3.81</v>
@@ -15797,7 +15871,7 @@
         <v>-8</v>
       </c>
       <c r="N109" t="n">
-        <v>37</v>
+        <v>32.1</v>
       </c>
       <c r="O109" t="inlineStr">
         <is>
@@ -15839,7 +15913,7 @@
         <v>46279</v>
       </c>
       <c r="Z109" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AA109" t="inlineStr">
         <is>
@@ -15868,13 +15942,13 @@
         <v>184.64</v>
       </c>
       <c r="AI109" t="n">
-        <v>258.74</v>
+        <v>249.37</v>
       </c>
       <c r="AJ109" t="n">
-        <v>258.74</v>
+        <v>249.37</v>
       </c>
       <c r="AK109" t="n">
-        <v>40.13</v>
+        <v>35.06</v>
       </c>
       <c r="AL109" t="n">
         <v>-7.53</v>
@@ -15883,16 +15957,16 @@
         <v>40.48</v>
       </c>
       <c r="AN109" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="AO109" t="n">
         <v>42</v>
       </c>
       <c r="AR109" t="n">
-        <v>0.14</v>
+        <v>-0.38</v>
       </c>
       <c r="AT109" t="n">
-        <v>39.99</v>
+        <v>35.44</v>
       </c>
     </row>
     <row r="110">
@@ -16210,7 +16284,7 @@
         <v>37.7</v>
       </c>
       <c r="I112" t="n">
-        <v>0.8</v>
+        <v>-6.9</v>
       </c>
       <c r="J112" t="n">
         <v>-6.45</v>
@@ -16225,7 +16299,7 @@
         <v>1.8</v>
       </c>
       <c r="N112" t="n">
-        <v>7.1</v>
+        <v>4.6</v>
       </c>
       <c r="P112" t="n">
         <v>-29.3</v>
@@ -16262,7 +16336,7 @@
         <v>46261</v>
       </c>
       <c r="Z112" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="AA112" t="inlineStr">
         <is>
@@ -16288,13 +16362,13 @@
         <v>275</v>
       </c>
       <c r="AI112" t="n">
-        <v>270.55</v>
+        <v>263.82</v>
       </c>
       <c r="AJ112" t="n">
-        <v>270.55</v>
+        <v>263.82</v>
       </c>
       <c r="AK112" t="n">
-        <v>-1.62</v>
+        <v>-4.07</v>
       </c>
       <c r="AL112" t="n">
         <v>-18.3</v>
@@ -16303,16 +16377,16 @@
         <v>7.1</v>
       </c>
       <c r="AN112" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="AO112" t="n">
         <v>6</v>
       </c>
       <c r="AR112" t="n">
-        <v>0.14</v>
+        <v>-0.38</v>
       </c>
       <c r="AT112" t="n">
-        <v>-1.76</v>
+        <v>-3.68</v>
       </c>
       <c r="AU112" t="inlineStr">
         <is>
@@ -17090,7 +17164,7 @@
         <v>-7.1</v>
       </c>
       <c r="I118" t="n">
-        <v>-15.1</v>
+        <v>-14.6</v>
       </c>
       <c r="J118" t="n">
         <v>2.22</v>
@@ -17105,7 +17179,7 @@
         <v>4.9</v>
       </c>
       <c r="N118" t="n">
-        <v>-10.9</v>
+        <v>-11.5</v>
       </c>
       <c r="P118" t="n">
         <v>-9</v>
@@ -17142,7 +17216,7 @@
         <v>46258</v>
       </c>
       <c r="Z118" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="AA118" t="inlineStr">
         <is>
@@ -17171,13 +17245,13 @@
         <v>50.78</v>
       </c>
       <c r="AI118" t="n">
-        <v>43.33</v>
+        <v>43.02</v>
       </c>
       <c r="AJ118" t="n">
-        <v>43.33</v>
+        <v>43.02</v>
       </c>
       <c r="AK118" t="n">
-        <v>-14.67</v>
+        <v>-15.28</v>
       </c>
       <c r="AL118" t="n">
         <v>-21.33</v>
@@ -17186,16 +17260,16 @@
         <v>11.12</v>
       </c>
       <c r="AN118" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="AO118" t="n">
         <v>20</v>
       </c>
       <c r="AR118" t="n">
-        <v>-0.01</v>
+        <v>-0.54</v>
       </c>
       <c r="AT118" t="n">
-        <v>-14.66</v>
+        <v>-14.75</v>
       </c>
       <c r="AU118" t="inlineStr">
         <is>
@@ -17807,7 +17881,7 @@
         <v>-9.1</v>
       </c>
       <c r="I123" t="n">
-        <v>-13.8</v>
+        <v>-14.1</v>
       </c>
       <c r="J123" t="n">
         <v>-5.07</v>
@@ -17822,7 +17896,7 @@
         <v>3.7</v>
       </c>
       <c r="N123" t="n">
-        <v>-18.9</v>
+        <v>-16.7</v>
       </c>
       <c r="P123" t="n">
         <v>1.7</v>
@@ -17859,7 +17933,7 @@
         <v>46287</v>
       </c>
       <c r="Z123" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AA123" t="inlineStr">
         <is>
@@ -17888,13 +17962,13 @@
         <v>112.19</v>
       </c>
       <c r="AI123" t="n">
-        <v>91.13</v>
+        <v>93.53</v>
       </c>
       <c r="AJ123" t="n">
-        <v>91.13</v>
+        <v>93.53</v>
       </c>
       <c r="AK123" t="n">
-        <v>-18.77</v>
+        <v>-16.63</v>
       </c>
       <c r="AL123" t="n">
         <v>-23.29</v>
@@ -17903,16 +17977,16 @@
         <v>14.5</v>
       </c>
       <c r="AN123" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="AO123" t="n">
         <v>25</v>
       </c>
       <c r="AR123" t="n">
-        <v>-0.01</v>
+        <v>-0.54</v>
       </c>
       <c r="AT123" t="n">
-        <v>-18.76</v>
+        <v>-16.1</v>
       </c>
       <c r="AU123" t="inlineStr">
         <is>
@@ -17956,7 +18030,7 @@
         <v>-31.8</v>
       </c>
       <c r="I124" t="n">
-        <v>-16.7</v>
+        <v>-16.3</v>
       </c>
       <c r="J124" t="n">
         <v>-7.89</v>
@@ -17971,7 +18045,7 @@
         <v>-12.7</v>
       </c>
       <c r="N124" t="n">
-        <v>-22.6</v>
+        <v>-23</v>
       </c>
       <c r="P124" t="n">
         <v>-15.8</v>
@@ -18023,13 +18097,13 @@
         <v>50.2</v>
       </c>
       <c r="AI124" t="n">
-        <v>41.75</v>
+        <v>41.49</v>
       </c>
       <c r="AJ124" t="n">
-        <v>41.75</v>
+        <v>41.49</v>
       </c>
       <c r="AK124" t="n">
-        <v>-16.83</v>
+        <v>-17.35</v>
       </c>
       <c r="AL124" t="n">
         <v>-27.27</v>
@@ -18038,16 +18112,16 @@
         <v>4.72</v>
       </c>
       <c r="AN124" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="AO124" t="n">
         <v>3</v>
       </c>
       <c r="AR124" t="n">
-        <v>-0.01</v>
+        <v>-0.54</v>
       </c>
       <c r="AT124" t="n">
-        <v>-16.82</v>
+        <v>-16.81</v>
       </c>
       <c r="AU124" t="inlineStr">
         <is>
@@ -18505,7 +18579,7 @@
         <v>-11.7</v>
       </c>
       <c r="I128" t="n">
-        <v>-4.2</v>
+        <v>-6.4</v>
       </c>
       <c r="J128" t="n">
         <v>2.64</v>
@@ -18520,7 +18594,7 @@
         <v>-25.1</v>
       </c>
       <c r="N128" t="n">
-        <v>-20.5</v>
+        <v>-20.8</v>
       </c>
       <c r="P128" t="n">
         <v>-31.4</v>
@@ -18557,7 +18631,7 @@
         <v>46262</v>
       </c>
       <c r="Z128" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="AA128" t="inlineStr">
         <is>
@@ -18583,13 +18657,13 @@
         <v>64.77</v>
       </c>
       <c r="AI128" t="n">
-        <v>60.83</v>
+        <v>60.49</v>
       </c>
       <c r="AJ128" t="n">
-        <v>60.83</v>
+        <v>60.49</v>
       </c>
       <c r="AK128" t="n">
-        <v>-6.08</v>
+        <v>-6.61</v>
       </c>
       <c r="AL128" t="n">
         <v>-13.39</v>
@@ -18598,13 +18672,13 @@
         <v>8.279999999999999</v>
       </c>
       <c r="AN128" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="AO128" t="n">
         <v>6</v>
       </c>
       <c r="AR128" t="n">
-        <v>-0.01</v>
+        <v>-0.54</v>
       </c>
       <c r="AT128" t="n">
         <v>-6.07</v>
@@ -22817,7 +22891,7 @@
         <v>-10</v>
       </c>
       <c r="I158" t="n">
-        <v>25.9</v>
+        <v>22.5</v>
       </c>
       <c r="J158" t="n">
         <v>3.54</v>
@@ -22832,7 +22906,7 @@
         <v>-11.4</v>
       </c>
       <c r="N158" t="n">
-        <v>19.3</v>
+        <v>23.6</v>
       </c>
       <c r="P158" t="n">
         <v>-30.7</v>
@@ -22869,7 +22943,7 @@
         <v>46245</v>
       </c>
       <c r="Z158" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="AA158" t="inlineStr">
         <is>
@@ -22898,13 +22972,13 @@
         <v>10.03</v>
       </c>
       <c r="AI158" t="n">
-        <v>12.03</v>
+        <v>12.46</v>
       </c>
       <c r="AJ158" t="n">
-        <v>12.03</v>
+        <v>12.46</v>
       </c>
       <c r="AK158" t="n">
-        <v>20</v>
+        <v>24.29</v>
       </c>
       <c r="AL158" t="n">
         <v>-5.44</v>
@@ -22913,16 +22987,16 @@
         <v>28.48</v>
       </c>
       <c r="AN158" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="AO158" t="n">
         <v>47</v>
       </c>
       <c r="AR158" t="n">
-        <v>-1.29</v>
+        <v>-1.8</v>
       </c>
       <c r="AT158" t="n">
-        <v>21.29</v>
+        <v>26.09</v>
       </c>
     </row>
     <row r="159">
@@ -23536,7 +23610,7 @@
         <v>9.4</v>
       </c>
       <c r="I163" t="n">
-        <v>-7.1</v>
+        <v>-9.9</v>
       </c>
       <c r="J163" t="n">
         <v>-8.5</v>
@@ -23551,7 +23625,7 @@
         <v>14.7</v>
       </c>
       <c r="N163" t="n">
-        <v>-7.5</v>
+        <v>-11</v>
       </c>
       <c r="P163" t="n">
         <v>-0.5</v>
@@ -23588,7 +23662,7 @@
         <v>46238</v>
       </c>
       <c r="Z163" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="AA163" t="inlineStr">
         <is>
@@ -23614,13 +23688,13 @@
         <v>15.77</v>
       </c>
       <c r="AI163" t="n">
-        <v>12.6</v>
+        <v>12.11</v>
       </c>
       <c r="AJ163" t="n">
-        <v>12.6</v>
+        <v>12.11</v>
       </c>
       <c r="AK163" t="n">
-        <v>-20.1</v>
+        <v>-23.21</v>
       </c>
       <c r="AL163" t="n">
         <v>-26.25</v>
@@ -23629,16 +23703,16 @@
         <v>8.5</v>
       </c>
       <c r="AN163" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="AO163" t="n">
         <v>2</v>
       </c>
       <c r="AR163" t="n">
-        <v>2.19</v>
+        <v>1.66</v>
       </c>
       <c r="AT163" t="n">
-        <v>-22.29</v>
+        <v>-24.87</v>
       </c>
       <c r="AU163" t="inlineStr">
         <is>
@@ -24851,7 +24925,7 @@
         <v>-7.4</v>
       </c>
       <c r="I172" t="n">
-        <v>-3.5</v>
+        <v>-7.7</v>
       </c>
       <c r="J172" t="n">
         <v>10.43</v>
@@ -24866,7 +24940,7 @@
         <v>7.3</v>
       </c>
       <c r="N172" t="n">
-        <v>8.5</v>
+        <v>5.2</v>
       </c>
       <c r="P172" t="n">
         <v>-6.2</v>
@@ -24903,7 +24977,7 @@
         <v>46237</v>
       </c>
       <c r="Z172" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="AA172" t="inlineStr">
         <is>
@@ -24932,13 +25006,13 @@
         <v>70.92</v>
       </c>
       <c r="AI172" t="n">
-        <v>72.40000000000001</v>
+        <v>70.08</v>
       </c>
       <c r="AJ172" t="n">
-        <v>72.40000000000001</v>
+        <v>70.08</v>
       </c>
       <c r="AK172" t="n">
-        <v>2.09</v>
+        <v>-1.18</v>
       </c>
       <c r="AL172" t="n">
         <v>-6.9</v>
@@ -24947,19 +25021,22 @@
         <v>27.52</v>
       </c>
       <c r="AN172" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="AO172" t="n">
         <v>21</v>
       </c>
+      <c r="AP172" t="n">
+        <v>-1.18</v>
+      </c>
       <c r="AR172" t="n">
-        <v>4.05</v>
+        <v>3.51</v>
       </c>
       <c r="AS172" t="n">
         <v>3.51</v>
       </c>
       <c r="AT172" t="n">
-        <v>-1.96</v>
+        <v>-4.69</v>
       </c>
     </row>
     <row r="173">
@@ -25564,7 +25641,7 @@
         <v>25.1</v>
       </c>
       <c r="I177" t="n">
-        <v>-1.3</v>
+        <v>-0.5</v>
       </c>
       <c r="J177" t="n">
         <v>10.45</v>
@@ -25579,7 +25656,7 @@
         <v>25</v>
       </c>
       <c r="N177" t="n">
-        <v>21</v>
+        <v>19.2</v>
       </c>
       <c r="P177" t="n">
         <v>-6.8</v>
@@ -25616,7 +25693,7 @@
         <v>46233</v>
       </c>
       <c r="Z177" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="AA177" t="inlineStr">
         <is>
@@ -25645,13 +25722,13 @@
         <v>24.39</v>
       </c>
       <c r="AI177" t="n">
-        <v>25.65</v>
+        <v>25.3</v>
       </c>
       <c r="AJ177" t="n">
-        <v>25.65</v>
+        <v>25.3</v>
       </c>
       <c r="AK177" t="n">
-        <v>5.16</v>
+        <v>3.73</v>
       </c>
       <c r="AL177" t="n">
         <v>-7.51</v>
@@ -25660,7 +25737,7 @@
         <v>22.95</v>
       </c>
       <c r="AN177" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="AO177" t="n">
         <v>1</v>
@@ -25669,13 +25746,13 @@
         <v>5.16</v>
       </c>
       <c r="AR177" t="n">
-        <v>3.5</v>
+        <v>2.96</v>
       </c>
       <c r="AS177" t="n">
         <v>3.5</v>
       </c>
       <c r="AT177" t="n">
-        <v>1.67</v>
+        <v>0.77</v>
       </c>
     </row>
     <row r="178">
@@ -26324,7 +26401,7 @@
         <v>-11.5</v>
       </c>
       <c r="I182" t="n">
-        <v>-3.1</v>
+        <v>-3.4</v>
       </c>
       <c r="J182" t="n">
         <v>-18.43</v>
@@ -26339,7 +26416,7 @@
         <v>-24.2</v>
       </c>
       <c r="N182" t="n">
-        <v>-21.9</v>
+        <v>-22.7</v>
       </c>
       <c r="P182" t="n">
         <v>-25.7</v>
@@ -26376,7 +26453,7 @@
         <v>46230</v>
       </c>
       <c r="Z182" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="AA182" t="inlineStr">
         <is>
@@ -26402,13 +26479,13 @@
         <v>268.74</v>
       </c>
       <c r="AI182" t="n">
-        <v>227.28</v>
+        <v>224.03</v>
       </c>
       <c r="AJ182" t="n">
-        <v>227.28</v>
+        <v>224.03</v>
       </c>
       <c r="AK182" t="n">
-        <v>-15.43</v>
+        <v>-16.64</v>
       </c>
       <c r="AL182" t="n">
         <v>-26.39</v>
@@ -26417,7 +26494,7 @@
         <v>8.130000000000001</v>
       </c>
       <c r="AN182" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="AO182" t="n">
         <v>3</v>
@@ -26426,13 +26503,13 @@
         <v>-13.19</v>
       </c>
       <c r="AR182" t="n">
-        <v>3.7</v>
+        <v>3.16</v>
       </c>
       <c r="AS182" t="n">
         <v>4.05</v>
       </c>
       <c r="AT182" t="n">
-        <v>-19.13</v>
+        <v>-19.8</v>
       </c>
       <c r="AU182" t="inlineStr">
         <is>
@@ -27372,7 +27449,7 @@
         <v>13.9</v>
       </c>
       <c r="I189" t="n">
-        <v>-14.5</v>
+        <v>-15.7</v>
       </c>
       <c r="J189" t="n">
         <v>-12.11</v>
@@ -27387,7 +27464,7 @@
         <v>46.7</v>
       </c>
       <c r="N189" t="n">
-        <v>-6.9</v>
+        <v>-7</v>
       </c>
       <c r="P189" t="n">
         <v>42.3</v>
@@ -27424,7 +27501,7 @@
         <v>46224</v>
       </c>
       <c r="Z189" t="n">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="AA189" t="inlineStr">
         <is>
@@ -27453,13 +27530,13 @@
         <v>272</v>
       </c>
       <c r="AI189" t="n">
-        <v>210.1</v>
+        <v>210.33</v>
       </c>
       <c r="AJ189" t="n">
-        <v>210.1</v>
+        <v>210.33</v>
       </c>
       <c r="AK189" t="n">
-        <v>-22.76</v>
+        <v>-22.67</v>
       </c>
       <c r="AL189" t="n">
         <v>-23.42</v>
@@ -27468,7 +27545,7 @@
         <v>23.89</v>
       </c>
       <c r="AN189" t="n">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="AO189" t="n">
         <v>46</v>
@@ -27477,13 +27554,13 @@
         <v>-6.11</v>
       </c>
       <c r="AR189" t="n">
-        <v>2.52</v>
+        <v>1.98</v>
       </c>
       <c r="AS189" t="n">
         <v>4.4</v>
       </c>
       <c r="AT189" t="n">
-        <v>-25.27</v>
+        <v>-24.65</v>
       </c>
       <c r="AU189" t="inlineStr">
         <is>
@@ -27982,7 +28059,7 @@
         <v>18.5</v>
       </c>
       <c r="I193" t="n">
-        <v>-9.300000000000001</v>
+        <v>-13.6</v>
       </c>
       <c r="J193" t="n">
         <v>3.77</v>
@@ -27997,7 +28074,7 @@
         <v>51.9</v>
       </c>
       <c r="N193" t="n">
-        <v>2.3</v>
+        <v>1.8</v>
       </c>
       <c r="P193" t="n">
         <v>49.5</v>
@@ -28034,7 +28111,7 @@
         <v>46224</v>
       </c>
       <c r="Z193" t="n">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="AA193" t="inlineStr">
         <is>
@@ -28063,13 +28140,13 @@
         <v>309.39</v>
       </c>
       <c r="AI193" t="n">
-        <v>257.82</v>
+        <v>257.16</v>
       </c>
       <c r="AJ193" t="n">
-        <v>257.82</v>
+        <v>257.16</v>
       </c>
       <c r="AK193" t="n">
-        <v>-16.67</v>
+        <v>-16.88</v>
       </c>
       <c r="AL193" t="n">
         <v>-20.94</v>
@@ -28078,7 +28155,7 @@
         <v>29.85</v>
       </c>
       <c r="AN193" t="n">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="AO193" t="n">
         <v>55</v>
@@ -28087,13 +28164,13 @@
         <v>5.18</v>
       </c>
       <c r="AR193" t="n">
-        <v>2.52</v>
+        <v>1.98</v>
       </c>
       <c r="AS193" t="n">
         <v>4.4</v>
       </c>
       <c r="AT193" t="n">
-        <v>-19.18</v>
+        <v>-18.86</v>
       </c>
       <c r="AU193" t="inlineStr">
         <is>
@@ -28902,7 +28979,7 @@
         <v>51.8</v>
       </c>
       <c r="N199" t="n">
-        <v>-14.8</v>
+        <v>-14.5</v>
       </c>
       <c r="P199" t="n">
         <v>46.3</v>
@@ -28934,7 +29011,7 @@
         <v>46226</v>
       </c>
       <c r="Z199" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="AA199" t="inlineStr">
         <is>
@@ -28960,22 +29037,22 @@
         <v>545.05</v>
       </c>
       <c r="AI199" t="n">
-        <v>375.58</v>
+        <v>377.24</v>
       </c>
       <c r="AJ199" t="n">
-        <v>375.58</v>
+        <v>377.24</v>
       </c>
       <c r="AK199" t="n">
-        <v>-31.09</v>
+        <v>-30.79</v>
       </c>
       <c r="AL199" t="n">
-        <v>-31.17</v>
+        <v>-31.6</v>
       </c>
       <c r="AM199" t="n">
         <v>5.66</v>
       </c>
       <c r="AN199" t="n">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="AO199" t="n">
         <v>3</v>
@@ -28984,13 +29061,13 @@
         <v>-14.83</v>
       </c>
       <c r="AR199" t="n">
-        <v>2.52</v>
+        <v>1.98</v>
       </c>
       <c r="AS199" t="n">
         <v>4.4</v>
       </c>
       <c r="AT199" t="n">
-        <v>-33.61</v>
+        <v>-32.77</v>
       </c>
       <c r="AU199" t="inlineStr">
         <is>
@@ -31271,7 +31348,7 @@
         <v>13.9</v>
       </c>
       <c r="I215" t="n">
-        <v>7.5</v>
+        <v>10.3</v>
       </c>
       <c r="J215" t="n">
         <v>-6.26</v>
@@ -31286,7 +31363,7 @@
         <v>73.3</v>
       </c>
       <c r="N215" t="n">
-        <v>26.8</v>
+        <v>28.5</v>
       </c>
       <c r="P215" t="n">
         <v>67.09999999999999</v>
@@ -31318,7 +31395,7 @@
         <v>46224</v>
       </c>
       <c r="Z215" t="n">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="AA215" t="inlineStr">
         <is>
@@ -31347,13 +31424,13 @@
         <v>517</v>
       </c>
       <c r="AI215" t="n">
-        <v>507.93</v>
+        <v>516.79</v>
       </c>
       <c r="AJ215" t="n">
-        <v>507.93</v>
+        <v>516.79</v>
       </c>
       <c r="AK215" t="n">
-        <v>-1.75</v>
+        <v>-0.04</v>
       </c>
       <c r="AL215" t="n">
         <v>-17.98</v>
@@ -31362,7 +31439,7 @@
         <v>27.37</v>
       </c>
       <c r="AN215" t="n">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="AO215" t="n">
         <v>55</v>
@@ -31371,13 +31448,13 @@
         <v>17.12</v>
       </c>
       <c r="AR215" t="n">
-        <v>2.52</v>
+        <v>1.98</v>
       </c>
       <c r="AS215" t="n">
         <v>4.4</v>
       </c>
       <c r="AT215" t="n">
-        <v>-4.27</v>
+        <v>-2.02</v>
       </c>
       <c r="AU215" t="inlineStr">
         <is>
@@ -33819,7 +33896,7 @@
         <v>3.7</v>
       </c>
       <c r="I232" t="n">
-        <v>-15.1</v>
+        <v>-14.6</v>
       </c>
       <c r="J232" t="n">
         <v>4.03</v>
@@ -33834,7 +33911,7 @@
         <v>-1.1</v>
       </c>
       <c r="N232" t="n">
-        <v>-10.9</v>
+        <v>-11.5</v>
       </c>
       <c r="P232" t="n">
         <v>-16.6</v>
@@ -33866,7 +33943,7 @@
         <v>46231</v>
       </c>
       <c r="Z232" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="AA232" t="inlineStr">
         <is>
@@ -33895,13 +33972,13 @@
         <v>50.22</v>
       </c>
       <c r="AI232" t="n">
-        <v>43.33</v>
+        <v>43.02</v>
       </c>
       <c r="AJ232" t="n">
-        <v>43.33</v>
+        <v>43.02</v>
       </c>
       <c r="AK232" t="n">
-        <v>-13.72</v>
+        <v>-14.34</v>
       </c>
       <c r="AL232" t="n">
         <v>-20.45</v>
@@ -33910,7 +33987,7 @@
         <v>12.36</v>
       </c>
       <c r="AN232" t="n">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="AO232" t="n">
         <v>43</v>
@@ -33919,13 +33996,13 @@
         <v>-12.74</v>
       </c>
       <c r="AR232" t="n">
-        <v>2.52</v>
+        <v>1.98</v>
       </c>
       <c r="AS232" t="n">
         <v>4.4</v>
       </c>
       <c r="AT232" t="n">
-        <v>-16.24</v>
+        <v>-16.32</v>
       </c>
       <c r="AU232" t="inlineStr">
         <is>
@@ -34709,7 +34786,7 @@
         <v>24.8</v>
       </c>
       <c r="I238" t="n">
-        <v>16.1</v>
+        <v>14.2</v>
       </c>
       <c r="J238" t="n">
         <v>0.72</v>
@@ -34724,7 +34801,7 @@
         <v>1.1</v>
       </c>
       <c r="N238" t="n">
-        <v>10.6</v>
+        <v>7.3</v>
       </c>
       <c r="P238" t="n">
         <v>-22.3</v>
@@ -34781,13 +34858,13 @@
         <v>20.61</v>
       </c>
       <c r="AI238" t="n">
-        <v>21.6</v>
+        <v>20.95</v>
       </c>
       <c r="AJ238" t="n">
-        <v>21.6</v>
+        <v>20.95</v>
       </c>
       <c r="AK238" t="n">
-        <v>4.81</v>
+        <v>1.66</v>
       </c>
       <c r="AL238" t="n">
         <v>-23.57</v>
@@ -34796,7 +34873,7 @@
         <v>4.96</v>
       </c>
       <c r="AN238" t="n">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="AO238" t="n">
         <v>67</v>
@@ -34805,13 +34882,13 @@
         <v>-12.66</v>
       </c>
       <c r="AR238" t="n">
-        <v>2.52</v>
+        <v>1.98</v>
       </c>
       <c r="AS238" t="n">
         <v>4.4</v>
       </c>
       <c r="AT238" t="n">
-        <v>2.3</v>
+        <v>-0.32</v>
       </c>
       <c r="AU238" t="inlineStr">
         <is>
@@ -36637,7 +36714,7 @@
         <v>-30.2</v>
       </c>
       <c r="N251" t="n">
-        <v>-51</v>
+        <v>-49.5</v>
       </c>
       <c r="P251" t="n">
         <v>-33.9</v>
@@ -36674,7 +36751,7 @@
         <v>46224</v>
       </c>
       <c r="Z251" t="n">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="AA251" t="inlineStr">
         <is>
@@ -36703,22 +36780,22 @@
         <v>58.11</v>
       </c>
       <c r="AI251" t="n">
-        <v>38.77</v>
+        <v>39.79</v>
       </c>
       <c r="AJ251" t="n">
-        <v>38.77</v>
+        <v>39.79</v>
       </c>
       <c r="AK251" t="n">
-        <v>-33.28</v>
+        <v>-31.53</v>
       </c>
       <c r="AL251" t="n">
-        <v>-34.95</v>
+        <v>-36.81</v>
       </c>
       <c r="AM251" t="n">
         <v>29.2</v>
       </c>
       <c r="AN251" t="n">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="AO251" t="n">
         <v>17</v>
@@ -36727,13 +36804,13 @@
         <v>-19.01</v>
       </c>
       <c r="AR251" t="n">
-        <v>2.52</v>
+        <v>1.98</v>
       </c>
       <c r="AS251" t="n">
         <v>4.4</v>
       </c>
       <c r="AT251" t="n">
-        <v>-35.8</v>
+        <v>-33.51</v>
       </c>
       <c r="AU251" t="inlineStr">
         <is>
@@ -36777,7 +36854,7 @@
         <v>6</v>
       </c>
       <c r="I252" t="n">
-        <v>-14.4</v>
+        <v>-13.6</v>
       </c>
       <c r="J252" t="n">
         <v>-2.71</v>
@@ -36792,7 +36869,7 @@
         <v>-24.2</v>
       </c>
       <c r="N252" t="n">
-        <v>-29.8</v>
+        <v>-30.5</v>
       </c>
       <c r="P252" t="n">
         <v>-32.4</v>
@@ -36844,13 +36921,13 @@
         <v>74.5</v>
       </c>
       <c r="AI252" t="n">
-        <v>57.54</v>
+        <v>56.85</v>
       </c>
       <c r="AJ252" t="n">
-        <v>57.54</v>
+        <v>56.85</v>
       </c>
       <c r="AK252" t="n">
-        <v>-22.77</v>
+        <v>-23.69</v>
       </c>
       <c r="AL252" t="n">
         <v>-33.33</v>
@@ -36859,7 +36936,7 @@
         <v>3.09</v>
       </c>
       <c r="AN252" t="n">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="AO252" t="n">
         <v>14</v>
@@ -36868,13 +36945,13 @@
         <v>-30.59</v>
       </c>
       <c r="AR252" t="n">
-        <v>2.52</v>
+        <v>1.98</v>
       </c>
       <c r="AS252" t="n">
         <v>4.4</v>
       </c>
       <c r="AT252" t="n">
-        <v>-25.28</v>
+        <v>-25.67</v>
       </c>
       <c r="AU252" t="inlineStr">
         <is>
@@ -37205,7 +37282,7 @@
         <v>-37.4</v>
       </c>
       <c r="I255" t="n">
-        <v>-20.3</v>
+        <v>-24.1</v>
       </c>
       <c r="J255" t="n">
         <v>1.06</v>
@@ -37220,7 +37297,7 @@
         <v>-20.1</v>
       </c>
       <c r="N255" t="n">
-        <v>-32.1</v>
+        <v>-33.3</v>
       </c>
       <c r="P255" t="n">
         <v>-21.7</v>
@@ -37254,7 +37331,7 @@
         <v>46225</v>
       </c>
       <c r="Z255" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="AA255" t="inlineStr">
         <is>
@@ -37283,22 +37360,22 @@
         <v>44.28</v>
       </c>
       <c r="AI255" t="n">
-        <v>38.7</v>
+        <v>37.91</v>
       </c>
       <c r="AJ255" t="n">
-        <v>38.7</v>
+        <v>37.91</v>
       </c>
       <c r="AK255" t="n">
-        <v>-12.61</v>
+        <v>-14.39</v>
       </c>
       <c r="AL255" t="n">
-        <v>-13.4</v>
+        <v>-14.42</v>
       </c>
       <c r="AM255" t="n">
         <v>24.31</v>
       </c>
       <c r="AN255" t="n">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="AO255" t="n">
         <v>17</v>
@@ -37307,13 +37384,13 @@
         <v>-6.31</v>
       </c>
       <c r="AR255" t="n">
-        <v>2.52</v>
+        <v>1.98</v>
       </c>
       <c r="AS255" t="n">
         <v>4.4</v>
       </c>
       <c r="AT255" t="n">
-        <v>-15.13</v>
+        <v>-16.37</v>
       </c>
       <c r="AU255" t="inlineStr">
         <is>
@@ -38719,7 +38796,7 @@
         <v>24.2</v>
       </c>
       <c r="I265" t="n">
-        <v>-29.9</v>
+        <v>-29.4</v>
       </c>
       <c r="J265" t="n">
         <v>14.8</v>
@@ -38734,7 +38811,7 @@
         <v>-4.2</v>
       </c>
       <c r="N265" t="n">
-        <v>-14.5</v>
+        <v>-13.1</v>
       </c>
       <c r="O265" t="inlineStr">
         <is>
@@ -38771,7 +38848,7 @@
         <v>46223</v>
       </c>
       <c r="Z265" t="n">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="AA265" t="inlineStr">
         <is>
@@ -38800,13 +38877,13 @@
         <v>501.64</v>
       </c>
       <c r="AI265" t="n">
-        <v>414.6</v>
+        <v>420.37</v>
       </c>
       <c r="AJ265" t="n">
-        <v>414.6</v>
+        <v>420.37</v>
       </c>
       <c r="AK265" t="n">
-        <v>-17.35</v>
+        <v>-16.2</v>
       </c>
       <c r="AL265" t="n">
         <v>-24.85</v>
@@ -38815,7 +38892,7 @@
         <v>29.9</v>
       </c>
       <c r="AN265" t="n">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="AO265" t="n">
         <v>22</v>
@@ -38824,13 +38901,13 @@
         <v>-17.6</v>
       </c>
       <c r="AR265" t="n">
-        <v>2.52</v>
+        <v>1.98</v>
       </c>
       <c r="AS265" t="n">
         <v>4.4</v>
       </c>
       <c r="AT265" t="n">
-        <v>-19.87</v>
+        <v>-18.18</v>
       </c>
       <c r="AU265" t="inlineStr">
         <is>
@@ -39311,7 +39388,7 @@
         <v>19.4</v>
       </c>
       <c r="I269" t="n">
-        <v>-15.9</v>
+        <v>-16.6</v>
       </c>
       <c r="J269" t="n">
         <v>9.869999999999999</v>
@@ -39326,7 +39403,7 @@
         <v>-0.4</v>
       </c>
       <c r="N269" t="n">
-        <v>-20.4</v>
+        <v>-22.4</v>
       </c>
       <c r="P269" t="n">
         <v>-14.2</v>
@@ -39363,7 +39440,7 @@
         <v>46230</v>
       </c>
       <c r="Z269" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="AA269" t="inlineStr">
         <is>
@@ -39392,13 +39469,13 @@
         <v>45.7</v>
       </c>
       <c r="AI269" t="n">
-        <v>35.38</v>
+        <v>34.4</v>
       </c>
       <c r="AJ269" t="n">
-        <v>35.38</v>
+        <v>34.4</v>
       </c>
       <c r="AK269" t="n">
-        <v>-22.58</v>
+        <v>-24.73</v>
       </c>
       <c r="AL269" t="n">
         <v>-29.26</v>
@@ -39407,7 +39484,7 @@
         <v>17.33</v>
       </c>
       <c r="AN269" t="n">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="AO269" t="n">
         <v>12</v>
@@ -39416,13 +39493,13 @@
         <v>-17.26</v>
       </c>
       <c r="AR269" t="n">
-        <v>2.52</v>
+        <v>1.98</v>
       </c>
       <c r="AS269" t="n">
         <v>4.4</v>
       </c>
       <c r="AT269" t="n">
-        <v>-25.1</v>
+        <v>-26.71</v>
       </c>
       <c r="AU269" t="inlineStr">
         <is>
@@ -39615,7 +39692,7 @@
         <v>2.4</v>
       </c>
       <c r="I271" t="n">
-        <v>-29.1</v>
+        <v>-28.9</v>
       </c>
       <c r="J271" t="n">
         <v>-1.89</v>
@@ -39630,7 +39707,7 @@
         <v>-19.7</v>
       </c>
       <c r="N271" t="n">
-        <v>-38.9</v>
+        <v>-38</v>
       </c>
       <c r="P271" t="n">
         <v>-21.6</v>
@@ -39662,7 +39739,7 @@
         <v>46240</v>
       </c>
       <c r="Z271" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="AA271" t="inlineStr">
         <is>
@@ -39691,13 +39768,13 @@
         <v>120.59</v>
       </c>
       <c r="AI271" t="n">
-        <v>92.54000000000001</v>
+        <v>93.67</v>
       </c>
       <c r="AJ271" t="n">
-        <v>92.54000000000001</v>
+        <v>93.67</v>
       </c>
       <c r="AK271" t="n">
-        <v>-23.26</v>
+        <v>-22.33</v>
       </c>
       <c r="AL271" t="n">
         <v>-24.54</v>
@@ -39706,7 +39783,7 @@
         <v>19.06</v>
       </c>
       <c r="AN271" t="n">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="AO271" t="n">
         <v>25</v>
@@ -39715,13 +39792,13 @@
         <v>-19.03</v>
       </c>
       <c r="AR271" t="n">
-        <v>2.52</v>
+        <v>1.98</v>
       </c>
       <c r="AS271" t="n">
         <v>4.4</v>
       </c>
       <c r="AT271" t="n">
-        <v>-25.78</v>
+        <v>-24.31</v>
       </c>
       <c r="AU271" t="inlineStr">
         <is>
@@ -40359,7 +40436,7 @@
         <v>2.3</v>
       </c>
       <c r="I276" t="n">
-        <v>-13.8</v>
+        <v>-14.1</v>
       </c>
       <c r="J276" t="n">
         <v>-2.12</v>
@@ -40374,7 +40451,7 @@
         <v>16.5</v>
       </c>
       <c r="N276" t="n">
-        <v>-18.9</v>
+        <v>-16.7</v>
       </c>
       <c r="P276" t="n">
         <v>11.6</v>
@@ -40406,7 +40483,7 @@
         <v>46224</v>
       </c>
       <c r="Z276" t="n">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="AA276" t="inlineStr">
         <is>
@@ -40432,13 +40509,13 @@
         <v>120.43</v>
       </c>
       <c r="AI276" t="n">
-        <v>91.13</v>
+        <v>93.53</v>
       </c>
       <c r="AJ276" t="n">
-        <v>91.13</v>
+        <v>93.53</v>
       </c>
       <c r="AK276" t="n">
-        <v>-24.33</v>
+        <v>-22.34</v>
       </c>
       <c r="AL276" t="n">
         <v>-28.54</v>
@@ -40447,7 +40524,7 @@
         <v>6.67</v>
       </c>
       <c r="AN276" t="n">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="AO276" t="n">
         <v>48</v>
@@ -40456,13 +40533,13 @@
         <v>-17.02</v>
       </c>
       <c r="AR276" t="n">
-        <v>2.52</v>
+        <v>1.98</v>
       </c>
       <c r="AS276" t="n">
         <v>4.4</v>
       </c>
       <c r="AT276" t="n">
-        <v>-26.85</v>
+        <v>-24.32</v>
       </c>
       <c r="AU276" t="inlineStr">
         <is>
@@ -41721,7 +41798,7 @@
         <v>25.8</v>
       </c>
       <c r="I285" t="n">
-        <v>11.1</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="J285" t="n">
         <v>12.95</v>
@@ -41736,7 +41813,7 @@
         <v>7.1</v>
       </c>
       <c r="N285" t="n">
-        <v>56.4</v>
+        <v>50.7</v>
       </c>
       <c r="P285" t="n">
         <v>-17.9</v>
@@ -41773,7 +41850,7 @@
         <v>46231</v>
       </c>
       <c r="Z285" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="AA285" t="inlineStr">
         <is>
@@ -41802,13 +41879,13 @@
         <v>96.34</v>
       </c>
       <c r="AI285" t="n">
-        <v>161.49</v>
+        <v>155.82</v>
       </c>
       <c r="AJ285" t="n">
-        <v>161.49</v>
+        <v>155.82</v>
       </c>
       <c r="AK285" t="n">
-        <v>67.63</v>
+        <v>61.74</v>
       </c>
       <c r="AL285" t="n">
         <v>-6.51</v>
@@ -41817,7 +41894,7 @@
         <v>70.04000000000001</v>
       </c>
       <c r="AN285" t="n">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="AO285" t="n">
         <v>65</v>
@@ -41826,13 +41903,13 @@
         <v>56.61</v>
       </c>
       <c r="AR285" t="n">
-        <v>2.52</v>
+        <v>1.98</v>
       </c>
       <c r="AS285" t="n">
         <v>4.4</v>
       </c>
       <c r="AT285" t="n">
-        <v>65.11</v>
+        <v>59.76</v>
       </c>
     </row>
     <row r="286">
@@ -42171,7 +42248,7 @@
         <v>5.5</v>
       </c>
       <c r="I288" t="n">
-        <v>4.3</v>
+        <v>9.9</v>
       </c>
       <c r="J288" t="n">
         <v>1.46</v>
@@ -42186,7 +42263,7 @@
         <v>-9</v>
       </c>
       <c r="N288" t="n">
-        <v>-2.4</v>
+        <v>-2.1</v>
       </c>
       <c r="P288" t="n">
         <v>-18</v>
@@ -42223,7 +42300,7 @@
         <v>46295</v>
       </c>
       <c r="Z288" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AA288" t="inlineStr">
         <is>
@@ -42249,13 +42326,13 @@
         <v>17.49</v>
       </c>
       <c r="AI288" t="n">
-        <v>17.89</v>
+        <v>17.91</v>
       </c>
       <c r="AJ288" t="n">
-        <v>17.89</v>
+        <v>17.91</v>
       </c>
       <c r="AK288" t="n">
-        <v>2.29</v>
+        <v>2.4</v>
       </c>
       <c r="AL288" t="n">
         <v>-19.94</v>
@@ -42264,7 +42341,7 @@
         <v>6.06</v>
       </c>
       <c r="AN288" t="n">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="AO288" t="n">
         <v>51</v>
@@ -42273,13 +42350,13 @@
         <v>1.66</v>
       </c>
       <c r="AR288" t="n">
-        <v>2.52</v>
+        <v>1.98</v>
       </c>
       <c r="AS288" t="n">
         <v>4.4</v>
       </c>
       <c r="AT288" t="n">
-        <v>-0.23</v>
+        <v>0.42</v>
       </c>
       <c r="AU288" t="inlineStr">
         <is>
@@ -42323,7 +42400,7 @@
         <v>-17.5</v>
       </c>
       <c r="I289" t="n">
-        <v>-18</v>
+        <v>-17.2</v>
       </c>
       <c r="J289" t="n">
         <v>11.63</v>
@@ -42338,7 +42415,7 @@
         <v>-42.2</v>
       </c>
       <c r="N289" t="n">
-        <v>-38.8</v>
+        <v>-35.6</v>
       </c>
       <c r="P289" t="n">
         <v>-46.7</v>
@@ -42375,7 +42452,7 @@
         <v>46224</v>
       </c>
       <c r="Z289" t="n">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="AA289" t="inlineStr">
         <is>
@@ -42404,22 +42481,22 @@
         <v>142.6</v>
       </c>
       <c r="AI289" t="n">
-        <v>117.7</v>
+        <v>123.25</v>
       </c>
       <c r="AJ289" t="n">
-        <v>117.7</v>
+        <v>123.25</v>
       </c>
       <c r="AK289" t="n">
-        <v>-17.46</v>
+        <v>-13.57</v>
       </c>
       <c r="AL289" t="n">
-        <v>-19.87</v>
+        <v>-20.59</v>
       </c>
       <c r="AM289" t="n">
         <v>45.74</v>
       </c>
       <c r="AN289" t="n">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="AO289" t="n">
         <v>19</v>
@@ -42428,13 +42505,13 @@
         <v>-10.85</v>
       </c>
       <c r="AR289" t="n">
-        <v>2.52</v>
+        <v>1.98</v>
       </c>
       <c r="AS289" t="n">
         <v>4.4</v>
       </c>
       <c r="AT289" t="n">
-        <v>-19.98</v>
+        <v>-15.55</v>
       </c>
       <c r="AU289" t="inlineStr">
         <is>
@@ -42633,7 +42710,7 @@
         <v>1.6</v>
       </c>
       <c r="I291" t="n">
-        <v>8.5</v>
+        <v>9.9</v>
       </c>
       <c r="J291" t="n">
         <v>4.01</v>
@@ -42648,7 +42725,7 @@
         <v>2.9</v>
       </c>
       <c r="N291" t="n">
-        <v>-8.699999999999999</v>
+        <v>-8.300000000000001</v>
       </c>
       <c r="P291" t="n">
         <v>-0.1</v>
@@ -42685,7 +42762,7 @@
         <v>46225</v>
       </c>
       <c r="Z291" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="AA291" t="inlineStr">
         <is>
@@ -42714,13 +42791,13 @@
         <v>53.22</v>
       </c>
       <c r="AI291" t="n">
-        <v>46.69</v>
+        <v>46.92</v>
       </c>
       <c r="AJ291" t="n">
-        <v>46.69</v>
+        <v>46.92</v>
       </c>
       <c r="AK291" t="n">
-        <v>-12.27</v>
+        <v>-11.84</v>
       </c>
       <c r="AL291" t="n">
         <v>-28.93</v>
@@ -42729,7 +42806,7 @@
         <v>12.6</v>
       </c>
       <c r="AN291" t="n">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="AO291" t="n">
         <v>12</v>
@@ -42738,13 +42815,13 @@
         <v>-21.31</v>
       </c>
       <c r="AR291" t="n">
-        <v>2.52</v>
+        <v>1.98</v>
       </c>
       <c r="AS291" t="n">
         <v>4.4</v>
       </c>
       <c r="AT291" t="n">
-        <v>-14.79</v>
+        <v>-13.82</v>
       </c>
       <c r="AU291" t="inlineStr">
         <is>
@@ -43216,7 +43293,7 @@
         <v>2.1</v>
       </c>
       <c r="I295" t="n">
-        <v>22.5</v>
+        <v>24.3</v>
       </c>
       <c r="J295" t="n">
         <v>6.37</v>
@@ -43231,7 +43308,7 @@
         <v>13.9</v>
       </c>
       <c r="N295" t="n">
-        <v>35.1</v>
+        <v>41.3</v>
       </c>
       <c r="P295" t="n">
         <v>6.8</v>
@@ -43263,7 +43340,7 @@
         <v>46225</v>
       </c>
       <c r="Z295" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="AA295" t="inlineStr">
         <is>
@@ -43292,37 +43369,37 @@
         <v>34.49</v>
       </c>
       <c r="AI295" t="n">
-        <v>49.44</v>
+        <v>51.9</v>
       </c>
       <c r="AJ295" t="n">
-        <v>49.44</v>
+        <v>51.9</v>
       </c>
       <c r="AK295" t="n">
-        <v>43.36</v>
+        <v>50.49</v>
       </c>
       <c r="AL295" t="n">
         <v>-1.56</v>
       </c>
       <c r="AM295" t="n">
-        <v>46.43</v>
+        <v>51.91</v>
       </c>
       <c r="AN295" t="n">
+        <v>69</v>
+      </c>
+      <c r="AO295" t="n">
         <v>68</v>
-      </c>
-      <c r="AO295" t="n">
-        <v>66</v>
       </c>
       <c r="AP295" t="n">
         <v>39.21</v>
       </c>
       <c r="AR295" t="n">
-        <v>2.52</v>
+        <v>1.98</v>
       </c>
       <c r="AS295" t="n">
         <v>4.4</v>
       </c>
       <c r="AT295" t="n">
-        <v>40.84</v>
+        <v>48.51</v>
       </c>
     </row>
     <row r="296">
@@ -45325,7 +45402,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>304 (+3 pending)</t>
+          <t>305 (+2 pending)</t>
         </is>
       </c>
     </row>
@@ -45337,7 +45414,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>$52,060.17</t>
+          <t>$52,319.70</t>
         </is>
       </c>
     </row>
@@ -45349,7 +45426,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>$50,423.43  (-3.14% price-weighted)</t>
+          <t>$50,640.28  (-3.21% price-weighted)</t>
         </is>
       </c>
     </row>
@@ -45361,7 +45438,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>-1.65%  &lt;- judge the system by this line</t>
+          <t>-1.73%  &lt;- judge the system by this line</t>
         </is>
       </c>
     </row>
@@ -45373,7 +45450,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-2.30%</t>
+          <t>-2.29%</t>
         </is>
       </c>
     </row>
@@ -45385,7 +45462,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>136 reached, 64 wins (47%)</t>
+          <t>137 reached, 64 wins (47%)</t>
         </is>
       </c>
     </row>
@@ -45461,19 +45538,19 @@
         <v>195</v>
       </c>
       <c r="C12" t="n">
-        <v>1.66</v>
+        <v>1.48</v>
       </c>
       <c r="D12" t="n">
-        <v>1.03</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="E12" t="n">
-        <v>1.91</v>
+        <v>1.87</v>
       </c>
       <c r="F12" t="n">
-        <v>51.79</v>
+        <v>51.28</v>
       </c>
       <c r="G12" t="n">
-        <v>-13.97</v>
+        <v>-14</v>
       </c>
     </row>
     <row r="13">
@@ -45486,10 +45563,10 @@
         <v>77</v>
       </c>
       <c r="C13" t="n">
-        <v>-5.03</v>
+        <v>-4.94</v>
       </c>
       <c r="D13" t="n">
-        <v>-5.79</v>
+        <v>-5.65</v>
       </c>
       <c r="E13" t="n">
         <v>5.06</v>
@@ -45498,7 +45575,7 @@
         <v>29.87</v>
       </c>
       <c r="G13" t="n">
-        <v>-21.41</v>
+        <v>-21.42</v>
       </c>
     </row>
     <row r="14">
@@ -45508,22 +45585,22 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C14" t="n">
-        <v>-13.69</v>
+        <v>-13.17</v>
       </c>
       <c r="D14" t="n">
-        <v>-14.19</v>
+        <v>-13.58</v>
       </c>
       <c r="E14" t="n">
         <v>7.05</v>
       </c>
       <c r="F14" t="n">
-        <v>21.88</v>
+        <v>21.21</v>
       </c>
       <c r="G14" t="n">
-        <v>-21.67</v>
+        <v>-21.09</v>
       </c>
     </row>
     <row r="15"/>
@@ -45571,22 +45648,22 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="C17" t="n">
-        <v>-6.72</v>
+        <v>-6.83</v>
       </c>
       <c r="D17" t="n">
-        <v>31.63</v>
+        <v>30.3</v>
       </c>
       <c r="E17" t="n">
-        <v>-7.17</v>
+        <v>-7.19</v>
       </c>
       <c r="F17" t="n">
-        <v>3.95</v>
+        <v>3.83</v>
       </c>
       <c r="G17" t="n">
-        <v>-19.42</v>
+        <v>-19.26</v>
       </c>
     </row>
     <row r="18">
@@ -45599,19 +45676,19 @@
         <v>42</v>
       </c>
       <c r="C18" t="n">
-        <v>-1.04</v>
+        <v>-1</v>
       </c>
       <c r="D18" t="n">
         <v>52.38</v>
       </c>
       <c r="E18" t="n">
-        <v>-1.81</v>
+        <v>-1.67</v>
       </c>
       <c r="F18" t="n">
         <v>3.4</v>
       </c>
       <c r="G18" t="n">
-        <v>-14.3</v>
+        <v>-14.31</v>
       </c>
     </row>
     <row r="19">
@@ -45649,19 +45726,19 @@
         <v>144</v>
       </c>
       <c r="C20" t="n">
-        <v>0.61</v>
+        <v>0.54</v>
       </c>
       <c r="D20" t="n">
         <v>44.44</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.15</v>
+        <v>-0.13</v>
       </c>
       <c r="F20" t="n">
         <v>3.45</v>
       </c>
       <c r="G20" t="n">
-        <v>-16.11</v>
+        <v>-16.14</v>
       </c>
     </row>
     <row r="21">
@@ -45899,13 +45976,13 @@
         <v>5</v>
       </c>
       <c r="C32" t="n">
-        <v>13.41</v>
+        <v>12.4</v>
       </c>
       <c r="D32" t="n">
         <v>80</v>
       </c>
       <c r="E32" t="n">
-        <v>14.12</v>
+        <v>13.21</v>
       </c>
       <c r="F32" t="n">
         <v>-13.85</v>
@@ -45921,13 +45998,13 @@
         <v>12</v>
       </c>
       <c r="C33" t="n">
-        <v>-4.7</v>
+        <v>-4.66</v>
       </c>
       <c r="D33" t="n">
         <v>41.67</v>
       </c>
       <c r="E33" t="n">
-        <v>-5</v>
+        <v>-4.84</v>
       </c>
       <c r="F33" t="n">
         <v>-16.62</v>
@@ -45943,13 +46020,13 @@
         <v>29</v>
       </c>
       <c r="C34" t="n">
-        <v>4.4</v>
+        <v>4.31</v>
       </c>
       <c r="D34" t="n">
         <v>48.28</v>
       </c>
       <c r="E34" t="n">
-        <v>4.25</v>
+        <v>4.19</v>
       </c>
       <c r="F34" t="n">
         <v>-14.24</v>
@@ -46467,31 +46544,31 @@
         <v>115</v>
       </c>
       <c r="C4" t="n">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="D4" t="n">
-        <v>5.73</v>
+        <v>5.39</v>
       </c>
       <c r="E4" t="n">
-        <v>3.21</v>
+        <v>2.57</v>
       </c>
       <c r="F4" t="n">
-        <v>55.3</v>
+        <v>54.8</v>
       </c>
       <c r="G4" t="n">
-        <v>5.06</v>
+        <v>4.82</v>
       </c>
       <c r="H4" t="n">
-        <v>-13.17</v>
+        <v>-13.09</v>
       </c>
       <c r="I4" t="n">
         <v>-43.08</v>
       </c>
       <c r="J4" t="n">
-        <v>24.6</v>
+        <v>24.3</v>
       </c>
       <c r="K4" t="n">
-        <v>21.44</v>
+        <v>21.28</v>
       </c>
       <c r="L4" t="n">
         <v>48</v>
@@ -46513,16 +46590,16 @@
         <v>56</v>
       </c>
       <c r="D5" t="n">
-        <v>2.38</v>
+        <v>2.43</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.52</v>
+        <v>-0.98</v>
       </c>
       <c r="F5" t="n">
-        <v>48.2</v>
+        <v>46.4</v>
       </c>
       <c r="G5" t="n">
-        <v>1.6</v>
+        <v>1.75</v>
       </c>
       <c r="H5" t="n">
         <v>-14.97</v>
@@ -46534,13 +46611,13 @@
         <v>33.9</v>
       </c>
       <c r="K5" t="n">
-        <v>21.2</v>
+        <v>21.3</v>
       </c>
       <c r="L5" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="M5" t="n">
-        <v>8.029999999999999</v>
+        <v>7.72</v>
       </c>
     </row>
     <row r="6">
@@ -46556,25 +46633,25 @@
         <v>134</v>
       </c>
       <c r="D6" t="n">
-        <v>-9.609999999999999</v>
+        <v>-9.58</v>
       </c>
       <c r="E6" t="n">
-        <v>-11.54</v>
+        <v>-11.68</v>
       </c>
       <c r="F6" t="n">
         <v>30.6</v>
       </c>
       <c r="G6" t="n">
-        <v>-10.19</v>
+        <v>-10.09</v>
       </c>
       <c r="H6" t="n">
-        <v>-20.35</v>
+        <v>-20.39</v>
       </c>
       <c r="I6" t="n">
         <v>-63.91</v>
       </c>
       <c r="J6" t="n">
-        <v>47</v>
+        <v>47.8</v>
       </c>
       <c r="K6" t="n">
         <v>19.37</v>
@@ -46596,37 +46673,37 @@
         <v>307</v>
       </c>
       <c r="C7" t="n">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="D7" t="n">
-        <v>-1.65</v>
+        <v>-1.73</v>
       </c>
       <c r="E7" t="n">
-        <v>-3.52</v>
+        <v>-3.71</v>
       </c>
       <c r="F7" t="n">
-        <v>43.1</v>
+        <v>42.6</v>
       </c>
       <c r="G7" t="n">
-        <v>-2.3</v>
+        <v>-2.29</v>
       </c>
       <c r="H7" t="n">
-        <v>-16.67</v>
+        <v>-16.64</v>
       </c>
       <c r="I7" t="n">
         <v>-63.91</v>
       </c>
       <c r="J7" t="n">
-        <v>36.2</v>
+        <v>36.4</v>
       </c>
       <c r="K7" t="n">
-        <v>20.49</v>
+        <v>20.45</v>
       </c>
       <c r="L7" t="n">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="M7" t="n">
-        <v>3.49</v>
+        <v>3.45</v>
       </c>
     </row>
     <row r="8"/>
@@ -46640,28 +46717,28 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Avg drawdown (MAE%, less-negative is better): PASS -13.17 vs FAIL -20.35  -&gt;  PASS better</t>
+          <t>Avg drawdown (MAE%, less-negative is better): PASS -13.09 vs FAIL -20.39  -&gt;  PASS better</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Deep-drawdown rate (MAE&lt;=-20%): PASS 24.6 vs FAIL 47.0  -&gt;  PASS better</t>
+          <t>Deep-drawdown rate (MAE&lt;=-20%): PASS 24.3 vs FAIL 47.8  -&gt;  PASS better</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Avg return %: PASS 5.73 vs FAIL -9.61  -&gt;  PASS better</t>
+          <t>Avg return %: PASS 5.39 vs FAIL -9.58  -&gt;  PASS better</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Win rate %: PASS 55.3 vs FAIL 30.6  -&gt;  PASS better</t>
+          <t>Win rate %: PASS 54.8 vs FAIL 30.6  -&gt;  PASS better</t>
         </is>
       </c>
     </row>
@@ -56194,29 +56271,45 @@
           <t>LEVERAGED</t>
         </is>
       </c>
-      <c r="E130" t="n">
-        <v>54.3</v>
-      </c>
-      <c r="F130" t="n">
-        <v>0.222</v>
-      </c>
-      <c r="G130" t="n">
-        <v>7</v>
-      </c>
-      <c r="H130" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="I130" t="n">
-        <v>8</v>
-      </c>
-      <c r="J130" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="K130" t="n">
-        <v>2.03</v>
-      </c>
-      <c r="L130" t="n">
-        <v>8.4</v>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>54.3</t>
+        </is>
+      </c>
+      <c r="F130" t="inlineStr">
+        <is>
+          <t>0.222</t>
+        </is>
+      </c>
+      <c r="G130" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="H130" t="inlineStr">
+        <is>
+          <t>1.36</t>
+        </is>
+      </c>
+      <c r="I130" t="inlineStr">
+        <is>
+          <t>8.0</t>
+        </is>
+      </c>
+      <c r="J130" t="inlineStr">
+        <is>
+          <t>4.7</t>
+        </is>
+      </c>
+      <c r="K130" t="inlineStr">
+        <is>
+          <t>2.03</t>
+        </is>
+      </c>
+      <c r="L130" t="inlineStr">
+        <is>
+          <t>8.4</t>
+        </is>
       </c>
       <c r="M130" t="inlineStr">
         <is>
@@ -64333,8 +64426,10 @@
           <t>LEVERAGED</t>
         </is>
       </c>
-      <c r="L3" t="n">
-        <v>54.3</v>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>54.3</t>
+        </is>
       </c>
     </row>
     <row r="4">
@@ -64643,7 +64738,11 @@
           <t>1</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr"/>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>259.53</t>
+        </is>
+      </c>
       <c r="E9" t="inlineStr">
         <is>
           <t>6.1</t>
